--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -7,12 +7,13 @@
   </bookViews>
   <sheets>
     <sheet name="User Rights" r:id="rId3" sheetId="1"/>
+    <sheet name="About" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="83">
   <si>
     <t>User Right</t>
   </si>
@@ -255,6 +256,12 @@
   </si>
   <si>
     <t>DASHBOARD_CONTACT_ACCESS</t>
+  </si>
+  <si>
+    <t>SORMAS Version</t>
+  </si>
+  <si>
+    <t>1.8.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -3460,4 +3467,24 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -261,7 +261,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.8.0-SNAPSHOT</t>
+    <t>1.9.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="87">
   <si>
     <t>User Right</t>
   </si>
@@ -33,10 +33,13 @@
     <t>Surveillance Officer</t>
   </si>
   <si>
-    <t>Informant</t>
-  </si>
-  <si>
-    <t>Case Supervisor</t>
+    <t>Hospital Informant</t>
+  </si>
+  <si>
+    <t>Community Informant</t>
+  </si>
+  <si>
+    <t>Clinician</t>
   </si>
   <si>
     <t>Case Officer</t>
@@ -51,7 +54,10 @@
     <t>Event Officer</t>
   </si>
   <si>
-    <t>Lab Manager</t>
+    <t>Lab Officer</t>
+  </si>
+  <si>
+    <t>External Lab Officer</t>
   </si>
   <si>
     <t>National Observer</t>
@@ -60,6 +66,9 @@
     <t>State Observer</t>
   </si>
   <si>
+    <t>District Observer</t>
+  </si>
+  <si>
     <t>CASE_CREATE</t>
   </si>
   <si>
@@ -228,6 +237,9 @@
     <t>OUTBREAK_CONFIGURE_RESTRICTED</t>
   </si>
   <si>
+    <t>STATISTICS_ACCESS</t>
+  </si>
+  <si>
     <t>STATISTICS_EXPORT</t>
   </si>
   <si>
@@ -261,7 +273,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.9.0-SNAPSHOT</t>
+    <t>1.10.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -389,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P65"/>
+  <dimension ref="A1:S66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -407,6 +419,9 @@
     <col min="13" max="13" width="14.0" customWidth="true"/>
     <col min="14" max="14" width="14.0" customWidth="true"/>
     <col min="15" max="15" width="14.0" customWidth="true"/>
+    <col min="16" max="16" width="14.0" customWidth="true"/>
+    <col min="17" max="17" width="14.0" customWidth="true"/>
+    <col min="18" max="18" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,3013 +470,3654 @@
       <c r="O1" t="s" s="3">
         <v>14</v>
       </c>
+      <c r="P1" t="s" s="3">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s" s="3">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="L27" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R28" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L29" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L30" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="L30" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="3">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R33" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="3">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N35" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R35" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="3">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B37" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B39" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="3">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="3">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K43" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B47" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O49" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B54" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B57" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B58" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B59" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R60" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B62" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="O65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="3">
+        <v>84</v>
+      </c>
+      <c r="B66" t="s">
+        <v>84</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3476,12 +4132,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -273,7 +273,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.10.0-SNAPSHOT</t>
+    <t>1.11.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -2344,8 +2344,8 @@
       <c r="E35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>20</v>
+      <c r="F35" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2512,8 +2512,8 @@
       <c r="E38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>20</v>
+      <c r="F38" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="94">
   <si>
     <t>User Right</t>
   </si>
@@ -270,10 +270,31 @@
     <t>DASHBOARD_CONTACT_ACCESS</t>
   </si>
   <si>
+    <t>THERAPY_VIEW</t>
+  </si>
+  <si>
+    <t>PRESCRIPTION_CREATE</t>
+  </si>
+  <si>
+    <t>PRESCRIPTION_EDIT</t>
+  </si>
+  <si>
+    <t>PRESCRIPTION_DELETE</t>
+  </si>
+  <si>
+    <t>TREATMENT_CREATE</t>
+  </si>
+  <si>
+    <t>TREATMENT_EDIT</t>
+  </si>
+  <si>
+    <t>TREATMENT_DELETE</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.11.0-SNAPSHOT</t>
+    <t>1.12.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -401,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S66"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -4120,6 +4141,398 @@
         <v>19</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="s" s="3">
+        <v>85</v>
+      </c>
+      <c r="B67" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="3">
+        <v>86</v>
+      </c>
+      <c r="B68" t="s">
+        <v>86</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="B69" t="s">
+        <v>87</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="3">
+        <v>88</v>
+      </c>
+      <c r="B70" t="s">
+        <v>88</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="3">
+        <v>89</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="3">
+        <v>90</v>
+      </c>
+      <c r="B72" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="3">
+        <v>91</v>
+      </c>
+      <c r="B73" t="s">
+        <v>91</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q73" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -4132,12 +4545,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="98">
   <si>
     <t>User Right</t>
   </si>
@@ -291,10 +291,22 @@
     <t>TREATMENT_DELETE</t>
   </si>
   <si>
+    <t>CLINICAL_COURSE_VIEW</t>
+  </si>
+  <si>
+    <t>CLINICAL_VISIT_CREATE</t>
+  </si>
+  <si>
+    <t>CLINICAL_VISIT_EDIT</t>
+  </si>
+  <si>
+    <t>CLINICAL_VISIT_DELETE</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.12.0-SNAPSHOT</t>
+    <t>1.13.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -422,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S73"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -4533,6 +4545,230 @@
         <v>20</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="s" s="3">
+        <v>92</v>
+      </c>
+      <c r="B74" t="s">
+        <v>92</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="3">
+        <v>93</v>
+      </c>
+      <c r="B75" t="s">
+        <v>93</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="3">
+        <v>94</v>
+      </c>
+      <c r="B76" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R76" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="3">
+        <v>95</v>
+      </c>
+      <c r="B77" t="s">
+        <v>95</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -4545,12 +4781,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="99">
   <si>
     <t>User Right</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>CLINICAL_COURSE_VIEW</t>
+  </si>
+  <si>
+    <t>CLINICAL_COURSE_EDIT</t>
   </si>
   <si>
     <t>CLINICAL_VISIT_CREATE</t>
@@ -434,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -4163,8 +4166,8 @@
       <c r="C67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>19</v>
+      <c r="D67" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>20</v>
@@ -4181,8 +4184,8 @@
       <c r="I67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J67" s="2" t="s">
-        <v>20</v>
+      <c r="J67" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>20</v>
@@ -4199,14 +4202,14 @@
       <c r="O67" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>19</v>
+      <c r="P67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="68">
@@ -4219,8 +4222,8 @@
       <c r="C68" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>19</v>
+      <c r="D68" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>20</v>
@@ -4237,8 +4240,8 @@
       <c r="I68" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J68" s="2" t="s">
-        <v>20</v>
+      <c r="J68" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>20</v>
@@ -4275,8 +4278,8 @@
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>19</v>
+      <c r="D69" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>20</v>
@@ -4293,8 +4296,8 @@
       <c r="I69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J69" s="2" t="s">
-        <v>20</v>
+      <c r="J69" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>20</v>
@@ -4387,8 +4390,8 @@
       <c r="C71" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>19</v>
+      <c r="D71" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>20</v>
@@ -4405,8 +4408,8 @@
       <c r="I71" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J71" s="2" t="s">
-        <v>20</v>
+      <c r="J71" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>20</v>
@@ -4443,8 +4446,8 @@
       <c r="C72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>19</v>
+      <c r="D72" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>20</v>
@@ -4461,8 +4464,8 @@
       <c r="I72" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J72" s="2" t="s">
-        <v>20</v>
+      <c r="J72" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K72" s="2" t="s">
         <v>20</v>
@@ -4555,8 +4558,8 @@
       <c r="C74" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>19</v>
+      <c r="D74" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>20</v>
@@ -4573,8 +4576,8 @@
       <c r="I74" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J74" s="2" t="s">
-        <v>20</v>
+      <c r="J74" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>20</v>
@@ -4591,14 +4594,14 @@
       <c r="O74" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>19</v>
+      <c r="P74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="75">
@@ -4611,8 +4614,8 @@
       <c r="C75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>19</v>
+      <c r="D75" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>20</v>
@@ -4629,8 +4632,8 @@
       <c r="I75" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J75" s="2" t="s">
-        <v>20</v>
+      <c r="J75" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>20</v>
@@ -4667,8 +4670,8 @@
       <c r="C76" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>19</v>
+      <c r="D76" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>20</v>
@@ -4685,8 +4688,8 @@
       <c r="I76" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>20</v>
+      <c r="J76" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>20</v>
@@ -4738,11 +4741,11 @@
       <c r="H77" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>20</v>
+      <c r="I77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>20</v>
@@ -4766,6 +4769,62 @@
         <v>20</v>
       </c>
       <c r="R77" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="3">
+        <v>96</v>
+      </c>
+      <c r="B78" t="s">
+        <v>96</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R78" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4781,12 +4840,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="104">
   <si>
     <t>User Right</t>
   </si>
@@ -123,6 +123,9 @@
     <t>SAMPLE_EDIT</t>
   </si>
   <si>
+    <t>SAMPLE_EDIT_NOT_OWNED</t>
+  </si>
+  <si>
     <t>SAMPLE_DELETE</t>
   </si>
   <si>
@@ -135,10 +138,22 @@
     <t>SAMPLE_VIEW_ARCHIVED</t>
   </si>
   <si>
-    <t>SAMPLETEST_CREATE</t>
-  </si>
-  <si>
-    <t>SAMPLETEST_EDIT</t>
+    <t>PATHOGEN_TEST_CREATE</t>
+  </si>
+  <si>
+    <t>PATHOGEN_TEST_EDIT</t>
+  </si>
+  <si>
+    <t>ADDITIONAL_TEST_VIEW</t>
+  </si>
+  <si>
+    <t>ADDITIONAL_TEST_CREATE</t>
+  </si>
+  <si>
+    <t>ADDITIONAL_TEST_EDIT</t>
+  </si>
+  <si>
+    <t>ADDITIONAL_TEST_DELETE</t>
   </si>
   <si>
     <t>CONTACT_CREATE</t>
@@ -309,7 +324,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.13.0-SNAPSHOT</t>
+    <t>1.14.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -437,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S78"/>
+  <dimension ref="A1:S83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -1425,8 +1440,8 @@
       <c r="D18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>20</v>
+      <c r="E18" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>20</v>
@@ -1478,11 +1493,11 @@
       <c r="C19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>19</v>
+      <c r="D19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>20</v>
@@ -1493,8 +1508,8 @@
       <c r="H19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>19</v>
+      <c r="I19" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>20</v>
@@ -1508,11 +1523,11 @@
       <c r="M19" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N19" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>19</v>
+      <c r="N19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>20</v>
@@ -1555,8 +1570,8 @@
       <c r="J20" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>19</v>
+      <c r="K20" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>20</v>
@@ -1567,17 +1582,17 @@
       <c r="N20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>19</v>
+      <c r="O20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1593,8 +1608,8 @@
       <c r="D21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>20</v>
+      <c r="E21" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>20</v>
@@ -1620,8 +1635,8 @@
       <c r="M21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N21" s="2" t="s">
-        <v>20</v>
+      <c r="N21" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>20</v>
@@ -1649,8 +1664,8 @@
       <c r="D22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>19</v>
+      <c r="E22" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>20</v>
@@ -1667,8 +1682,8 @@
       <c r="J22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K22" s="2" t="s">
-        <v>20</v>
+      <c r="K22" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>20</v>
@@ -1676,20 +1691,20 @@
       <c r="M22" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>20</v>
+      <c r="N22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="23">
@@ -1764,8 +1779,8 @@
       <c r="E24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>19</v>
+      <c r="F24" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1773,26 +1788,26 @@
       <c r="H24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I24" s="2" t="s">
-        <v>20</v>
+      <c r="I24" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>19</v>
+      <c r="K24" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>20</v>
+      <c r="N24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="P24" s="2" t="s">
         <v>20</v>
@@ -1814,14 +1829,14 @@
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>19</v>
+      <c r="D25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -1832,32 +1847,32 @@
       <c r="I25" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>19</v>
+      <c r="J25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1870,8 +1885,8 @@
       <c r="C26" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>19</v>
+      <c r="D26" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>20</v>
@@ -1885,14 +1900,14 @@
       <c r="H26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>19</v>
+      <c r="I26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>20</v>
@@ -1900,11 +1915,11 @@
       <c r="M26" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>20</v>
+      <c r="N26" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O26" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>20</v>
@@ -1926,14 +1941,14 @@
       <c r="C27" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>19</v>
+      <c r="D27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -1941,26 +1956,26 @@
       <c r="H27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>19</v>
+      <c r="I27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>20</v>
+      <c r="N27" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>20</v>
@@ -2041,11 +2056,11 @@
       <c r="D29" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>20</v>
+      <c r="E29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2109,8 +2124,8 @@
       <c r="H30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>20</v>
+      <c r="I30" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>20</v>
@@ -2121,8 +2136,8 @@
       <c r="L30" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>20</v>
+      <c r="M30" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>20</v>
@@ -2130,14 +2145,14 @@
       <c r="O30" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>20</v>
+      <c r="P30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="31">
@@ -2153,8 +2168,8 @@
       <c r="D31" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>19</v>
+      <c r="E31" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>20</v>
@@ -2165,8 +2180,8 @@
       <c r="H31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>19</v>
+      <c r="I31" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>20</v>
@@ -2180,20 +2195,20 @@
       <c r="M31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N31" s="1" t="s">
-        <v>19</v>
+      <c r="N31" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>19</v>
+      <c r="P31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -2209,11 +2224,11 @@
       <c r="D32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>20</v>
+      <c r="E32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -2221,8 +2236,8 @@
       <c r="H32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>19</v>
+      <c r="I32" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>20</v>
@@ -2230,8 +2245,8 @@
       <c r="K32" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>20</v>
+      <c r="L32" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>20</v>
@@ -2242,14 +2257,14 @@
       <c r="O32" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>19</v>
+      <c r="P32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -2262,8 +2277,8 @@
       <c r="C33" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>19</v>
+      <c r="D33" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>20</v>
@@ -2283,11 +2298,11 @@
       <c r="J33" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>19</v>
+      <c r="K33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>20</v>
@@ -2389,8 +2404,8 @@
       <c r="H35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>19</v>
+      <c r="I35" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>20</v>
@@ -2398,14 +2413,14 @@
       <c r="K35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>20</v>
+      <c r="L35" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N35" s="1" t="s">
-        <v>19</v>
+      <c r="N35" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O35" s="2" t="s">
         <v>20</v>
@@ -2436,35 +2451,35 @@
       <c r="E36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>19</v>
+      <c r="F36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>19</v>
+      <c r="J36" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>19</v>
+      <c r="L36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="N36" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>19</v>
+      <c r="O36" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="P36" s="1" t="s">
         <v>19</v>
@@ -2489,47 +2504,47 @@
       <c r="D37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>19</v>
+      <c r="E37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>19</v>
+      <c r="J37" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R37" s="2" t="s">
-        <v>20</v>
+      <c r="L37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="38">
@@ -2545,11 +2560,11 @@
       <c r="D38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>19</v>
+      <c r="E38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2557,8 +2572,8 @@
       <c r="H38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>19</v>
+      <c r="I38" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>20</v>
@@ -2566,14 +2581,14 @@
       <c r="K38" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>20</v>
+      <c r="L38" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>19</v>
+      <c r="N38" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>20</v>
@@ -2613,8 +2628,8 @@
       <c r="H39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>19</v>
+      <c r="I39" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>20</v>
@@ -2622,8 +2637,8 @@
       <c r="K39" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L39" s="2" t="s">
-        <v>20</v>
+      <c r="L39" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>20</v>
@@ -2634,14 +2649,14 @@
       <c r="O39" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>19</v>
+      <c r="P39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R39" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -2669,23 +2684,23 @@
       <c r="H40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>20</v>
+      <c r="I40" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>20</v>
+      <c r="K40" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M40" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>20</v>
+      <c r="M40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>20</v>
@@ -2740,11 +2755,11 @@
       <c r="M41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>20</v>
+      <c r="N41" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="P41" s="1" t="s">
         <v>19</v>
@@ -2775,32 +2790,32 @@
       <c r="F42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>20</v>
+      <c r="G42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="O42" s="2" t="s">
-        <v>20</v>
+      <c r="N42" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="P42" s="2" t="s">
         <v>20</v>
@@ -2828,8 +2843,8 @@
       <c r="E43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>20</v>
+      <c r="F43" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>20</v>
@@ -2858,14 +2873,14 @@
       <c r="O43" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>19</v>
+      <c r="P43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -2878,8 +2893,8 @@
       <c r="C44" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>20</v>
+      <c r="D44" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>20</v>
@@ -2893,14 +2908,14 @@
       <c r="H44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>20</v>
+      <c r="I44" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>20</v>
+      <c r="K44" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>20</v>
@@ -2914,14 +2929,14 @@
       <c r="O44" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R44" s="2" t="s">
-        <v>20</v>
+      <c r="P44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q44" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="45">
@@ -2937,11 +2952,11 @@
       <c r="D45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>20</v>
+      <c r="E45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
@@ -2949,20 +2964,20 @@
       <c r="H45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>19</v>
+      <c r="I45" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>19</v>
+      <c r="K45" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>20</v>
+      <c r="M45" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>20</v>
@@ -2970,14 +2985,14 @@
       <c r="O45" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>19</v>
+      <c r="P45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -2999,23 +3014,23 @@
       <c r="F46" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L46" s="2" t="s">
-        <v>20</v>
+      <c r="G46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L46" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>19</v>
@@ -3026,14 +3041,14 @@
       <c r="O46" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R46" s="2" t="s">
-        <v>20</v>
+      <c r="P46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47">
@@ -3099,32 +3114,32 @@
       <c r="B48" t="s">
         <v>66</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>20</v>
+      <c r="C48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K48" s="2" t="s">
-        <v>20</v>
+      <c r="K48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>20</v>
@@ -3132,20 +3147,20 @@
       <c r="M48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N48" s="2" t="s">
-        <v>20</v>
+      <c r="N48" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>20</v>
+      <c r="P48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="49">
@@ -3158,29 +3173,29 @@
       <c r="C49" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>19</v>
+      <c r="D49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>19</v>
+      <c r="K49" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>20</v>
@@ -3194,14 +3209,14 @@
       <c r="O49" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>19</v>
+      <c r="P49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -3214,8 +3229,8 @@
       <c r="C50" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>20</v>
+      <c r="D50" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>20</v>
@@ -3229,14 +3244,14 @@
       <c r="H50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>20</v>
+      <c r="I50" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>20</v>
+      <c r="K50" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>20</v>
@@ -3250,14 +3265,14 @@
       <c r="O50" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>20</v>
+      <c r="P50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="51">
@@ -3270,14 +3285,14 @@
       <c r="C51" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>20</v>
+      <c r="D51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3297,8 +3312,8 @@
       <c r="L51" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M51" s="2" t="s">
-        <v>20</v>
+      <c r="M51" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>20</v>
@@ -3326,14 +3341,14 @@
       <c r="C52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>20</v>
+      <c r="D52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3353,8 +3368,8 @@
       <c r="L52" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>20</v>
+      <c r="M52" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>20</v>
@@ -3379,23 +3394,23 @@
       <c r="B53" t="s">
         <v>71</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>20</v>
+      <c r="C53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>20</v>
@@ -3418,14 +3433,14 @@
       <c r="O53" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>19</v>
+      <c r="P53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="54">
@@ -3441,26 +3456,26 @@
       <c r="D54" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>20</v>
+      <c r="E54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K54" s="2" t="s">
-        <v>20</v>
+      <c r="K54" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>20</v>
@@ -3474,14 +3489,14 @@
       <c r="O54" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R54" s="2" t="s">
-        <v>20</v>
+      <c r="P54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="55">
@@ -3491,14 +3506,14 @@
       <c r="B55" t="s">
         <v>73</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>20</v>
+      <c r="C55" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>19</v>
+      <c r="E55" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>20</v>
@@ -3550,11 +3565,11 @@
       <c r="C56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>19</v>
+      <c r="D56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>20</v>
@@ -3565,14 +3580,14 @@
       <c r="H56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>19</v>
+      <c r="I56" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K56" s="1" t="s">
-        <v>19</v>
+      <c r="K56" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>20</v>
@@ -3580,20 +3595,20 @@
       <c r="M56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N56" s="1" t="s">
-        <v>19</v>
+      <c r="N56" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>19</v>
+      <c r="P56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="57">
@@ -3606,11 +3621,11 @@
       <c r="C57" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>19</v>
+      <c r="D57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>20</v>
@@ -3621,14 +3636,14 @@
       <c r="H57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>19</v>
+      <c r="I57" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>19</v>
+      <c r="K57" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>20</v>
@@ -3636,20 +3651,20 @@
       <c r="M57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N57" s="1" t="s">
-        <v>19</v>
+      <c r="N57" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>19</v>
+      <c r="P57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="58">
@@ -3665,8 +3680,8 @@
       <c r="D58" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>20</v>
+      <c r="E58" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>20</v>
@@ -3698,14 +3713,14 @@
       <c r="O58" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R58" s="2" t="s">
-        <v>20</v>
+      <c r="P58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="59">
@@ -3718,8 +3733,8 @@
       <c r="C59" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>20</v>
+      <c r="D59" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>20</v>
@@ -3771,14 +3786,14 @@
       <c r="B60" t="s">
         <v>78</v>
       </c>
-      <c r="C60" s="1" t="s">
-        <v>19</v>
+      <c r="C60" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>20</v>
+      <c r="E60" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>20</v>
@@ -3830,11 +3845,11 @@
       <c r="C61" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>20</v>
+      <c r="D61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>20</v>
@@ -3845,14 +3860,14 @@
       <c r="H61" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>20</v>
+      <c r="I61" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>20</v>
+      <c r="K61" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>20</v>
@@ -3860,20 +3875,20 @@
       <c r="M61" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N61" s="2" t="s">
-        <v>20</v>
+      <c r="N61" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R61" s="2" t="s">
-        <v>20</v>
+      <c r="P61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="62">
@@ -3901,14 +3916,14 @@
       <c r="H62" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I62" s="2" t="s">
-        <v>20</v>
+      <c r="I62" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K62" s="2" t="s">
-        <v>20</v>
+      <c r="K62" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>20</v>
@@ -3916,8 +3931,8 @@
       <c r="M62" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N62" s="2" t="s">
-        <v>20</v>
+      <c r="N62" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>20</v>
@@ -3942,8 +3957,8 @@
       <c r="C63" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>20</v>
+      <c r="D63" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>20</v>
@@ -3998,11 +4013,11 @@
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>19</v>
+      <c r="D64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>20</v>
@@ -4013,35 +4028,35 @@
       <c r="H64" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>19</v>
+      <c r="I64" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>19</v>
+      <c r="K64" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>19</v>
+      <c r="M64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>19</v>
+      <c r="P64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -4054,11 +4069,11 @@
       <c r="C65" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>19</v>
+      <c r="D65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>20</v>
@@ -4069,8 +4084,8 @@
       <c r="H65" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>19</v>
+      <c r="I65" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>20</v>
@@ -4081,23 +4096,23 @@
       <c r="L65" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>19</v>
+      <c r="M65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="O65" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>19</v>
+      <c r="P65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="66">
@@ -4110,8 +4125,8 @@
       <c r="C66" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>19</v>
+      <c r="D66" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>20</v>
@@ -4131,8 +4146,8 @@
       <c r="J66" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>19</v>
+      <c r="K66" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>20</v>
@@ -4146,14 +4161,14 @@
       <c r="O66" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>19</v>
+      <c r="P66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R66" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="67">
@@ -4166,11 +4181,11 @@
       <c r="C67" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>20</v>
+      <c r="D67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>20</v>
@@ -4181,11 +4196,11 @@
       <c r="H67" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>19</v>
+      <c r="I67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>20</v>
@@ -4202,14 +4217,14 @@
       <c r="O67" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R67" s="2" t="s">
-        <v>20</v>
+      <c r="P67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="68">
@@ -4237,11 +4252,11 @@
       <c r="H68" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J68" s="1" t="s">
-        <v>19</v>
+      <c r="I68" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>20</v>
@@ -4278,11 +4293,11 @@
       <c r="C69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>20</v>
+      <c r="D69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>20</v>
@@ -4296,32 +4311,32 @@
       <c r="I69" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>20</v>
+      <c r="J69" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N69" s="2" t="s">
-        <v>20</v>
+      <c r="M69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q69" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R69" s="2" t="s">
-        <v>20</v>
+      <c r="P69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="70">
@@ -4334,11 +4349,11 @@
       <c r="C70" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>20</v>
+      <c r="D70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>20</v>
@@ -4349,8 +4364,8 @@
       <c r="H70" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>20</v>
+      <c r="I70" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>20</v>
@@ -4361,23 +4376,23 @@
       <c r="L70" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N70" s="2" t="s">
-        <v>20</v>
+      <c r="M70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R70" s="2" t="s">
-        <v>20</v>
+      <c r="P70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="71">
@@ -4390,8 +4405,8 @@
       <c r="C71" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>20</v>
+      <c r="D71" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>20</v>
@@ -4405,14 +4420,14 @@
       <c r="H71" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J71" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>20</v>
+      <c r="I71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>20</v>
@@ -4426,14 +4441,14 @@
       <c r="O71" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="P71" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q71" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="R71" s="2" t="s">
-        <v>20</v>
+      <c r="P71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="72">
@@ -4517,11 +4532,11 @@
       <c r="H73" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>20</v>
+      <c r="I73" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K73" s="2" t="s">
         <v>20</v>
@@ -4629,11 +4644,11 @@
       <c r="H75" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>19</v>
+      <c r="I75" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>20</v>
@@ -4825,6 +4840,286 @@
         <v>20</v>
       </c>
       <c r="R78" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="3">
+        <v>97</v>
+      </c>
+      <c r="B79" t="s">
+        <v>97</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R79" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="3">
+        <v>98</v>
+      </c>
+      <c r="B80" t="s">
+        <v>98</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="3">
+        <v>99</v>
+      </c>
+      <c r="B81" t="s">
+        <v>99</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R81" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="3">
+        <v>100</v>
+      </c>
+      <c r="B82" t="s">
+        <v>100</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R82" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="3">
+        <v>101</v>
+      </c>
+      <c r="B83" t="s">
+        <v>101</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R83" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4840,12 +5135,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1496" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="105">
   <si>
     <t>User Right</t>
   </si>
@@ -285,6 +285,9 @@
     <t>DASHBOARD_CONTACT_ACCESS</t>
   </si>
   <si>
+    <t>CASE_MANAGEMENT_ACCESS</t>
+  </si>
+  <si>
     <t>THERAPY_VIEW</t>
   </si>
   <si>
@@ -324,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.14.0-SNAPSHOT</t>
+    <t>1.15.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S83"/>
+  <dimension ref="A1:S84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -4644,11 +4647,11 @@
       <c r="H75" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>20</v>
+      <c r="I75" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>20</v>
@@ -4700,11 +4703,11 @@
       <c r="H76" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>19</v>
+      <c r="I76" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>20</v>
@@ -4812,11 +4815,11 @@
       <c r="H78" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>20</v>
+      <c r="I78" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>20</v>
@@ -4868,11 +4871,11 @@
       <c r="H79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>19</v>
+      <c r="I79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>20</v>
@@ -5092,11 +5095,11 @@
       <c r="H83" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>20</v>
+      <c r="I83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>20</v>
@@ -5120,6 +5123,62 @@
         <v>20</v>
       </c>
       <c r="R83" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="3">
+        <v>102</v>
+      </c>
+      <c r="B84" t="s">
+        <v>102</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="O84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="P84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="R84" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5135,12 +5194,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -327,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.15.0-SNAPSHOT</t>
+    <t>1.16.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -327,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.16.0-SNAPSHOT</t>
+    <t>1.17.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -327,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.17.0-SNAPSHOT</t>
+    <t>1.18.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -327,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.18.0-SNAPSHOT</t>
+    <t>1.19.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -327,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.19.0-SNAPSHOT</t>
+    <t>1.20.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -4494,8 +4494,8 @@
       <c r="M72" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="N72" s="2" t="s">
-        <v>20</v>
+      <c r="N72" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>20</v>
@@ -4703,8 +4703,8 @@
       <c r="H76" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>20</v>
+      <c r="I76" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>20</v>
@@ -4871,8 +4871,8 @@
       <c r="H79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>20</v>
+      <c r="I79" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>20</v>
@@ -5151,8 +5151,8 @@
       <c r="H84" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>20</v>
+      <c r="I84" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>20</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -327,7 +327,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.20.0-SNAPSHOT</t>
+    <t>1.21.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="106">
   <si>
     <t>User Right</t>
   </si>
@@ -69,6 +69,9 @@
     <t>District Observer</t>
   </si>
   <si>
+    <t>National Clinician</t>
+  </si>
+  <si>
     <t>CASE_CREATE</t>
   </si>
   <si>
@@ -327,7 +330,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.21.0-SNAPSHOT</t>
+    <t>1.22.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -455,7 +458,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:S84"/>
+  <dimension ref="A1:T84"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -476,6 +479,7 @@
     <col min="16" max="16" width="14.0" customWidth="true"/>
     <col min="17" max="17" width="14.0" customWidth="true"/>
     <col min="18" max="18" width="14.0" customWidth="true"/>
+    <col min="19" max="19" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,4652 +537,4904 @@
       <c r="R1" t="s" s="3">
         <v>17</v>
       </c>
+      <c r="S1" t="s" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S7" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S8" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S9" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S15" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="3">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S20" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="3">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S23" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S24" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S25" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S26" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S27" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S28" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B31" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S33" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="3">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S35" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="3">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S40" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="3">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R42" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S42" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R43" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S43" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="3">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="3">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S50" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R54" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R58" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S60" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R61" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S62" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R67" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R71" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R72" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S72" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R73" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S73" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R74" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S74" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R75" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S75" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R76" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S76" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R77" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S77" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R78" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S78" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R79" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S79" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R80" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S80" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R81" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S81" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R82" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S82" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R83" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S83" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B84" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R84" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="S84" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5194,12 +5450,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="114">
   <si>
     <t>User Right</t>
   </si>
@@ -72,6 +72,15 @@
     <t>National Clinician</t>
   </si>
   <si>
+    <t>POE Informant</t>
+  </si>
+  <si>
+    <t>POE Supervisor</t>
+  </si>
+  <si>
+    <t>POE National User</t>
+  </si>
+  <si>
     <t>CASE_CREATE</t>
   </si>
   <si>
@@ -90,6 +99,9 @@
     <t>CASE_TRANSFER</t>
   </si>
   <si>
+    <t>CASE_REFER_FROM_POE</t>
+  </si>
+  <si>
     <t>CASE_INVESTIGATE</t>
   </si>
   <si>
@@ -276,6 +288,12 @@
     <t>INFRASTRUCTURE_VIEW</t>
   </si>
   <si>
+    <t>INFRASTRUCTURE_EXPORT</t>
+  </si>
+  <si>
+    <t>INFRASTRUCTURE_IMPORT</t>
+  </si>
+  <si>
     <t>USER_RIGHTS_MANAGE</t>
   </si>
   <si>
@@ -327,10 +345,16 @@
     <t>CLINICAL_VISIT_DELETE</t>
   </si>
   <si>
+    <t>PORT_HEALTH_INFO_VIEW</t>
+  </si>
+  <si>
+    <t>PORT_HEALTH_INFO_EDIT</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.22.0-SNAPSHOT</t>
+    <t>1.23.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -458,7 +482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:T84"/>
+  <dimension ref="A1:W89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -480,6 +504,9 @@
     <col min="17" max="17" width="14.0" customWidth="true"/>
     <col min="18" max="18" width="14.0" customWidth="true"/>
     <col min="19" max="19" width="14.0" customWidth="true"/>
+    <col min="20" max="20" width="14.0" customWidth="true"/>
+    <col min="21" max="21" width="14.0" customWidth="true"/>
+    <col min="22" max="22" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -540,4902 +567,5998 @@
       <c r="S1" t="s" s="3">
         <v>18</v>
       </c>
+      <c r="T1" t="s" s="3">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s" s="3">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s" s="3">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="3">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="3">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="3">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="3">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V15" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="3">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="3">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="3">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="3">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="3">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="3">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="3">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V27" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="3">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O28" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S28" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U28" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="3">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B29" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S29" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="3">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M31" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S31" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="3">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B32" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S32" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="3">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S33" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="3">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S34" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="3">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S35" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="3">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="3">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V37" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="3">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="3">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V39" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="3">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V40" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="3">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="3">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O43" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="3">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N44" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V44" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="3">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="3">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R47" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V47" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S48" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V48" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R49" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V49" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="3">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>21</v>
+        <v>75</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H53" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S53" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>20</v>
+        <v>76</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S57" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U57" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R59" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>82</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>20</v>
+        <v>83</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S62" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B63" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R63" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S63" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S64" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="3">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S65" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="3">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="3">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="3">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P68" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="3">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="Q69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="R69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="S69" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="3">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="3">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="3">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B72" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q72" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R72" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V72" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="3">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J73" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="M73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N73" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q73" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R73" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="3">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="P74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R74" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S75" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="3">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S77" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="3">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B78" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S78" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="3">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S79" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="3">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B80" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S80" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="3">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B81" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S81" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s" s="3">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B82" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S82" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="3">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B83" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S83" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="3">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B84" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="S84" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="T84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="3">
+        <v>107</v>
+      </c>
+      <c r="B85" t="s">
+        <v>107</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S85" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U85" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="3">
+        <v>108</v>
+      </c>
+      <c r="B86" t="s">
+        <v>108</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S86" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="B87" t="s">
+        <v>109</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U87" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="3">
+        <v>110</v>
+      </c>
+      <c r="B88" t="s">
+        <v>110</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V88" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="3">
+        <v>111</v>
+      </c>
+      <c r="B89" t="s">
+        <v>111</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V89" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -5450,12 +6573,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1960" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="115">
   <si>
     <t>User Right</t>
   </si>
@@ -129,6 +129,9 @@
     <t>CASE_VIEW_ARCHIVED</t>
   </si>
   <si>
+    <t>CASE_MERGE</t>
+  </si>
+  <si>
     <t>SAMPLE_CREATE</t>
   </si>
   <si>
@@ -354,7 +357,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.23.0-SNAPSHOT</t>
+    <t>1.24.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -482,7 +485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W89"/>
+  <dimension ref="A1:W90"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -1539,26 +1542,26 @@
       <c r="C16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>23</v>
+      <c r="D16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>24</v>
@@ -1569,8 +1572,8 @@
       <c r="M16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N16" s="1" t="s">
-        <v>23</v>
+      <c r="N16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>24</v>
@@ -1584,8 +1587,8 @@
       <c r="R16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S16" s="1" t="s">
-        <v>23</v>
+      <c r="S16" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>24</v>
@@ -1628,29 +1631,29 @@
       <c r="J17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>23</v>
+      <c r="K17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>23</v>
+      <c r="O17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S17" s="1" t="s">
         <v>23</v>
@@ -1696,14 +1699,14 @@
       <c r="J18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>24</v>
+      <c r="K18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>23</v>
@@ -1711,14 +1714,14 @@
       <c r="O18" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R18" s="2" t="s">
-        <v>24</v>
+      <c r="P18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>23</v>
@@ -1743,26 +1746,26 @@
       <c r="C19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>24</v>
+      <c r="D19" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
+      <c r="F19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>24</v>
@@ -1773,11 +1776,11 @@
       <c r="M19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>24</v>
+      <c r="N19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P19" s="2" t="s">
         <v>24</v>
@@ -1788,8 +1791,8 @@
       <c r="R19" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>24</v>
+      <c r="S19" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T19" s="2" t="s">
         <v>24</v>
@@ -1814,8 +1817,8 @@
       <c r="D20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>24</v>
+      <c r="E20" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>24</v>
@@ -1879,11 +1882,11 @@
       <c r="C21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>23</v>
+      <c r="D21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>24</v>
@@ -1894,8 +1897,8 @@
       <c r="H21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>23</v>
+      <c r="I21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -1909,11 +1912,11 @@
       <c r="M21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N21" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>23</v>
+      <c r="N21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="P21" s="2" t="s">
         <v>24</v>
@@ -1924,8 +1927,8 @@
       <c r="R21" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S21" s="1" t="s">
-        <v>23</v>
+      <c r="S21" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T21" s="2" t="s">
         <v>24</v>
@@ -1968,8 +1971,8 @@
       <c r="J22" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>23</v>
+      <c r="K22" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>24</v>
@@ -1980,17 +1983,17 @@
       <c r="N22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>23</v>
+      <c r="O22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S22" s="1" t="s">
         <v>23</v>
@@ -2018,8 +2021,8 @@
       <c r="D23" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>24</v>
+      <c r="E23" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>24</v>
@@ -2045,8 +2048,8 @@
       <c r="M23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N23" s="2" t="s">
-        <v>24</v>
+      <c r="N23" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O23" s="2" t="s">
         <v>24</v>
@@ -2086,8 +2089,8 @@
       <c r="D24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>23</v>
+      <c r="E24" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>24</v>
@@ -2104,8 +2107,8 @@
       <c r="J24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>24</v>
+      <c r="K24" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>24</v>
@@ -2113,20 +2116,20 @@
       <c r="M24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>24</v>
+      <c r="N24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S24" s="1" t="s">
         <v>23</v>
@@ -2219,11 +2222,11 @@
       <c r="C26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>24</v>
+      <c r="D26" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>24</v>
@@ -2237,8 +2240,8 @@
       <c r="I26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>23</v>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
@@ -2438,11 +2441,11 @@
       <c r="H29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
+      <c r="I29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>24</v>
@@ -2453,11 +2456,11 @@
       <c r="M29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>24</v>
+      <c r="N29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P29" s="2" t="s">
         <v>24</v>
@@ -2468,8 +2471,8 @@
       <c r="R29" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S29" s="2" t="s">
-        <v>24</v>
+      <c r="S29" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T29" s="2" t="s">
         <v>24</v>
@@ -2491,14 +2494,14 @@
       <c r="C30" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>23</v>
+      <c r="D30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>24</v>
@@ -2512,11 +2515,11 @@
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>23</v>
+      <c r="K30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>24</v>
@@ -2574,8 +2577,8 @@
       <c r="H31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>23</v>
+      <c r="I31" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -2586,8 +2589,8 @@
       <c r="L31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>23</v>
+      <c r="M31" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>24</v>
@@ -2595,17 +2598,17 @@
       <c r="O31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>23</v>
+      <c r="P31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S31" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>24</v>
@@ -2630,11 +2633,11 @@
       <c r="D32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>24</v>
+      <c r="E32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>24</v>
@@ -2642,8 +2645,8 @@
       <c r="H32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>24</v>
+      <c r="I32" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>24</v>
@@ -2651,11 +2654,11 @@
       <c r="K32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M32" s="2" t="s">
-        <v>24</v>
+      <c r="L32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>24</v>
@@ -2663,17 +2666,17 @@
       <c r="O32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R32" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S32" s="2" t="s">
-        <v>24</v>
+      <c r="P32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>24</v>
@@ -2698,11 +2701,11 @@
       <c r="D33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>23</v>
+      <c r="E33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>24</v>
@@ -2719,8 +2722,8 @@
       <c r="K33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>23</v>
+      <c r="L33" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>24</v>
@@ -2763,14 +2766,14 @@
       <c r="C34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>24</v>
+      <c r="D34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>24</v>
@@ -2784,11 +2787,11 @@
       <c r="J34" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>24</v>
+      <c r="K34" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>24</v>
@@ -2831,8 +2834,8 @@
       <c r="C35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>23</v>
+      <c r="D35" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>24</v>
@@ -2852,11 +2855,11 @@
       <c r="J35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>23</v>
+      <c r="K35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>24</v>
@@ -2902,11 +2905,11 @@
       <c r="D36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>23</v>
+      <c r="E36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>24</v>
@@ -2973,8 +2976,8 @@
       <c r="E37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>24</v>
+      <c r="F37" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>24</v>
@@ -2982,8 +2985,8 @@
       <c r="H37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>23</v>
+      <c r="I37" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>24</v>
@@ -2991,29 +2994,29 @@
       <c r="K37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>24</v>
+      <c r="L37" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N37" s="1" t="s">
-        <v>23</v>
+      <c r="N37" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>23</v>
+      <c r="P37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S37" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T37" s="2" t="s">
         <v>24</v>
@@ -3038,8 +3041,8 @@
       <c r="D38" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>24</v>
+      <c r="E38" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>24</v>
@@ -3065,8 +3068,8 @@
       <c r="M38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>24</v>
+      <c r="N38" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>24</v>
@@ -3118,8 +3121,8 @@
       <c r="H39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>24</v>
+      <c r="I39" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>24</v>
@@ -3127,8 +3130,8 @@
       <c r="K39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>23</v>
+      <c r="L39" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M39" s="2" t="s">
         <v>24</v>
@@ -3139,17 +3142,17 @@
       <c r="O39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R39" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S39" s="2" t="s">
-        <v>24</v>
+      <c r="P39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T39" s="2" t="s">
         <v>24</v>
@@ -3242,11 +3245,11 @@
       <c r="D41" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>23</v>
+      <c r="E41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>24</v>
@@ -3254,8 +3257,8 @@
       <c r="H41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>23</v>
+      <c r="I41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>24</v>
@@ -3263,14 +3266,14 @@
       <c r="K41" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>24</v>
+      <c r="L41" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>23</v>
+      <c r="N41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>24</v>
@@ -3284,17 +3287,17 @@
       <c r="R41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S41" s="1" t="s">
-        <v>23</v>
+      <c r="S41" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U41" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>23</v>
+      <c r="U41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="42">
@@ -3316,47 +3319,47 @@
       <c r="F42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>23</v>
+      <c r="G42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>23</v>
+      <c r="J42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>23</v>
+      <c r="L42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>23</v>
+      <c r="O42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T42" s="1" t="s">
-        <v>23</v>
+      <c r="T42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="U42" s="1" t="s">
         <v>23</v>
@@ -3411,14 +3414,14 @@
       <c r="O43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q43" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R43" s="2" t="s">
-        <v>24</v>
+      <c r="P43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>23</v>
@@ -3452,32 +3455,32 @@
       <c r="F44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>24</v>
+      <c r="G44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>24</v>
+      <c r="J44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L44" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>24</v>
+      <c r="L44" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O44" s="2" t="s">
-        <v>24</v>
+      <c r="O44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>24</v>
@@ -3491,8 +3494,8 @@
       <c r="S44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T44" s="2" t="s">
-        <v>24</v>
+      <c r="T44" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="U44" s="1" t="s">
         <v>23</v>
@@ -3514,11 +3517,11 @@
       <c r="D45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>24</v>
+      <c r="E45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>24</v>
@@ -3541,20 +3544,20 @@
       <c r="M45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>24</v>
+      <c r="N45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>23</v>
+      <c r="P45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q45" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R45" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>23</v>
@@ -3582,11 +3585,11 @@
       <c r="D46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>23</v>
+      <c r="E46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>24</v>
@@ -3594,20 +3597,20 @@
       <c r="H46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>24</v>
+      <c r="I46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K46" s="2" t="s">
-        <v>24</v>
+      <c r="K46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M46" s="1" t="s">
-        <v>23</v>
+      <c r="M46" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>24</v>
@@ -3615,26 +3618,26 @@
       <c r="O46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S46" s="2" t="s">
-        <v>24</v>
+      <c r="P46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T46" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V46" s="2" t="s">
-        <v>24</v>
+      <c r="U46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="47">
@@ -3656,23 +3659,23 @@
       <c r="F47" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>23</v>
+      <c r="G47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>23</v>
@@ -3683,23 +3686,23 @@
       <c r="O47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>23</v>
+      <c r="P47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>24</v>
@@ -3724,23 +3727,23 @@
       <c r="F48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>24</v>
+      <c r="G48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>23</v>
@@ -3751,23 +3754,23 @@
       <c r="O48" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U48" s="2" t="s">
-        <v>24</v>
+      <c r="P48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U48" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="V48" s="2" t="s">
         <v>24</v>
@@ -3789,8 +3792,8 @@
       <c r="E49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>24</v>
+      <c r="F49" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>24</v>
@@ -3798,47 +3801,47 @@
       <c r="H49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>23</v>
+      <c r="I49" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>23</v>
+      <c r="K49" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M49" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>23</v>
+      <c r="M49" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S49" s="1" t="s">
-        <v>23</v>
+      <c r="P49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V49" s="1" t="s">
-        <v>23</v>
+      <c r="U49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V49" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="50">
@@ -3851,11 +3854,11 @@
       <c r="C50" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>24</v>
+      <c r="D50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>24</v>
@@ -3866,14 +3869,14 @@
       <c r="H50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>24</v>
+      <c r="I50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>24</v>
+      <c r="K50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
@@ -3881,32 +3884,32 @@
       <c r="M50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N50" s="2" t="s">
-        <v>24</v>
+      <c r="N50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>24</v>
+      <c r="P50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>24</v>
+      <c r="U50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="51">
@@ -3919,8 +3922,8 @@
       <c r="C51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>23</v>
+      <c r="D51" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>24</v>
@@ -3934,14 +3937,14 @@
       <c r="H51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>23</v>
+      <c r="I51" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>23</v>
+      <c r="K51" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>24</v>
@@ -3955,26 +3958,26 @@
       <c r="O51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>23</v>
+      <c r="P51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U51" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V51" s="1" t="s">
-        <v>23</v>
+      <c r="U51" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="52">
@@ -3990,11 +3993,11 @@
       <c r="D52" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>23</v>
+      <c r="E52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>24</v>
@@ -4002,20 +4005,20 @@
       <c r="H52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>24</v>
+      <c r="I52" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>24</v>
+      <c r="K52" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>23</v>
+      <c r="M52" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>24</v>
@@ -4023,26 +4026,26 @@
       <c r="O52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S52" s="2" t="s">
-        <v>24</v>
+      <c r="P52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S52" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>24</v>
+      <c r="U52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V52" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="53">
@@ -4120,23 +4123,23 @@
       <c r="B54" t="s">
         <v>76</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>24</v>
+      <c r="C54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>23</v>
+      <c r="G54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>24</v>
@@ -4150,8 +4153,8 @@
       <c r="L54" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M54" s="2" t="s">
-        <v>24</v>
+      <c r="M54" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>24</v>
@@ -4188,14 +4191,14 @@
       <c r="B55" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>23</v>
+      <c r="C55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>23</v>
@@ -4206,14 +4209,14 @@
       <c r="H55" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>23</v>
+      <c r="I55" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>23</v>
+      <c r="K55" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>24</v>
@@ -4227,17 +4230,17 @@
       <c r="O55" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>23</v>
+      <c r="P55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T55" s="2" t="s">
         <v>24</v>
@@ -4259,29 +4262,29 @@
       <c r="C56" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>24</v>
+      <c r="D56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>24</v>
+      <c r="K56" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>24</v>
@@ -4295,17 +4298,17 @@
       <c r="O56" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>24</v>
+      <c r="P56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>24</v>
@@ -4463,11 +4466,11 @@
       <c r="C59" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>23</v>
+      <c r="D59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>24</v>
@@ -4499,26 +4502,26 @@
       <c r="O59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>23</v>
+      <c r="P59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V59" s="1" t="s">
-        <v>23</v>
+      <c r="U59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="60">
@@ -4534,8 +4537,8 @@
       <c r="D60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>24</v>
+      <c r="E60" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>24</v>
@@ -4567,26 +4570,26 @@
       <c r="O60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>24</v>
+      <c r="P60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>24</v>
+      <c r="U60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="61">
@@ -4596,14 +4599,14 @@
       <c r="B61" t="s">
         <v>83</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>23</v>
+      <c r="C61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>24</v>
@@ -4664,11 +4667,11 @@
       <c r="B62" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>23</v>
+      <c r="C62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>23</v>
@@ -4682,14 +4685,14 @@
       <c r="H62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>23</v>
+      <c r="I62" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K62" s="1" t="s">
-        <v>23</v>
+      <c r="K62" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>24</v>
@@ -4697,32 +4700,32 @@
       <c r="M62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N62" s="1" t="s">
-        <v>23</v>
+      <c r="N62" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S62" s="1" t="s">
-        <v>23</v>
+      <c r="P62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V62" s="1" t="s">
-        <v>23</v>
+      <c r="U62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -4806,8 +4809,8 @@
       <c r="D64" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>24</v>
+      <c r="E64" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>24</v>
@@ -4818,14 +4821,14 @@
       <c r="H64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>24</v>
+      <c r="I64" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K64" s="2" t="s">
-        <v>24</v>
+      <c r="K64" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>24</v>
@@ -4833,32 +4836,32 @@
       <c r="M64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N64" s="2" t="s">
-        <v>24</v>
+      <c r="N64" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S64" s="2" t="s">
-        <v>24</v>
+      <c r="P64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>24</v>
+      <c r="U64" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="65">
@@ -4871,8 +4874,8 @@
       <c r="C65" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>24</v>
+      <c r="D65" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>24</v>
@@ -5075,11 +5078,11 @@
       <c r="C68" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>23</v>
+      <c r="D68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>24</v>
@@ -5111,26 +5114,26 @@
       <c r="O68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>23</v>
+      <c r="P68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U68" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>23</v>
+      <c r="U68" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="69">
@@ -5211,11 +5214,11 @@
       <c r="C70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>24</v>
+      <c r="D70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>24</v>
@@ -5247,26 +5250,26 @@
       <c r="O70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>24</v>
+      <c r="P70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V70" s="2" t="s">
-        <v>24</v>
+      <c r="U70" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="71">
@@ -5347,11 +5350,11 @@
       <c r="C72" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>23</v>
+      <c r="D72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>24</v>
@@ -5362,47 +5365,47 @@
       <c r="H72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>23</v>
+      <c r="I72" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>23</v>
+      <c r="K72" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>23</v>
+      <c r="M72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>23</v>
+      <c r="P72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T72" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U72" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V72" s="1" t="s">
-        <v>23</v>
+      <c r="U72" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="73">
@@ -5436,8 +5439,8 @@
       <c r="J73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K73" s="2" t="s">
-        <v>24</v>
+      <c r="K73" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>24</v>
@@ -5486,8 +5489,8 @@
       <c r="D74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>24</v>
+      <c r="E74" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>24</v>
@@ -5498,23 +5501,23 @@
       <c r="H74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>24</v>
+      <c r="I74" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>23</v>
+      <c r="K74" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M74" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N74" s="2" t="s">
-        <v>24</v>
+      <c r="M74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>24</v>
@@ -5528,17 +5531,17 @@
       <c r="R74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S74" s="2" t="s">
-        <v>24</v>
+      <c r="S74" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U74" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>24</v>
+      <c r="U74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V74" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="75">
@@ -5551,8 +5554,8 @@
       <c r="C75" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>24</v>
+      <c r="D75" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>24</v>
@@ -5566,14 +5569,14 @@
       <c r="H75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K75" s="2" t="s">
-        <v>24</v>
+      <c r="I75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>24</v>
@@ -5581,23 +5584,23 @@
       <c r="M75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N75" s="1" t="s">
-        <v>23</v>
+      <c r="N75" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S75" s="1" t="s">
-        <v>23</v>
+      <c r="P75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>24</v>
@@ -5649,8 +5652,8 @@
       <c r="M76" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N76" s="2" t="s">
-        <v>24</v>
+      <c r="N76" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>24</v>
@@ -5841,8 +5844,8 @@
       <c r="I79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J79" s="2" t="s">
-        <v>24</v>
+      <c r="J79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>24</v>
@@ -5909,8 +5912,8 @@
       <c r="I80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>23</v>
+      <c r="J80" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>24</v>
@@ -6045,8 +6048,8 @@
       <c r="I82" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J82" s="2" t="s">
-        <v>24</v>
+      <c r="J82" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>24</v>
@@ -6113,8 +6116,8 @@
       <c r="I83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>23</v>
+      <c r="J83" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>24</v>
@@ -6385,8 +6388,8 @@
       <c r="I87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J87" s="2" t="s">
-        <v>24</v>
+      <c r="J87" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>24</v>
@@ -6435,62 +6438,62 @@
       <c r="C88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H88" s="1" t="s">
-        <v>23</v>
+      <c r="D88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>23</v>
+      <c r="J88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O88" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R88" s="1" t="s">
-        <v>23</v>
+      <c r="P88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U88" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V88" s="1" t="s">
-        <v>23</v>
+      <c r="T88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U88" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="89">
@@ -6512,41 +6515,41 @@
       <c r="F89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>24</v>
+      <c r="G89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q89" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R89" s="2" t="s">
-        <v>24</v>
+      <c r="P89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S89" s="1" t="s">
         <v>23</v>
@@ -6558,6 +6561,74 @@
         <v>23</v>
       </c>
       <c r="V89" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="3">
+        <v>112</v>
+      </c>
+      <c r="B90" t="s">
+        <v>112</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V90" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -6573,12 +6644,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -357,7 +357,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.24.0-SNAPSHOT</t>
+    <t>1.25.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -357,7 +357,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.25.0-SNAPSHOT</t>
+    <t>1.26.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="120">
   <si>
     <t>User Right</t>
   </si>
@@ -162,6 +162,9 @@
     <t>PATHOGEN_TEST_EDIT</t>
   </si>
   <si>
+    <t>PATHOGEN_TEST_DELETE</t>
+  </si>
+  <si>
     <t>ADDITIONAL_TEST_VIEW</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
     <t>VISIT_EDIT</t>
   </si>
   <si>
+    <t>VISIT_DELETE</t>
+  </si>
+  <si>
     <t>TASK_CREATE</t>
   </si>
   <si>
@@ -222,6 +228,9 @@
     <t>TASK_VIEW_ARCHIVED</t>
   </si>
   <si>
+    <t>TASK_DELETE</t>
+  </si>
+  <si>
     <t>EVENT_CREATE</t>
   </si>
   <si>
@@ -237,6 +246,9 @@
     <t>EVENT_ARCHIVE</t>
   </si>
   <si>
+    <t>EVENT_DELETE</t>
+  </si>
+  <si>
     <t>EVENT_VIEW_ARCHIVED</t>
   </si>
   <si>
@@ -354,10 +366,13 @@
     <t>PORT_HEALTH_INFO_EDIT</t>
   </si>
   <si>
+    <t>POPULATION_MANAGE</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.26.0-SNAPSHOT</t>
+    <t>1.27.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -485,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W90"/>
+  <dimension ref="A1:W95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -2305,11 +2320,11 @@
       <c r="H27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>23</v>
+      <c r="I27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>24</v>
@@ -2320,11 +2335,11 @@
       <c r="M27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N27" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>23</v>
+      <c r="N27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>24</v>
@@ -2335,8 +2350,8 @@
       <c r="R27" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S27" s="1" t="s">
-        <v>23</v>
+      <c r="S27" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>24</v>
@@ -2509,11 +2524,11 @@
       <c r="H30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
+      <c r="I30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
@@ -2524,11 +2539,11 @@
       <c r="M30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>24</v>
+      <c r="N30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O30" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="P30" s="2" t="s">
         <v>24</v>
@@ -2539,8 +2554,8 @@
       <c r="R30" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S30" s="2" t="s">
-        <v>24</v>
+      <c r="S30" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>24</v>
@@ -2562,14 +2577,14 @@
       <c r="C31" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>23</v>
+      <c r="D31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>24</v>
@@ -2583,11 +2598,11 @@
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>23</v>
+      <c r="K31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>24</v>
@@ -2645,8 +2660,8 @@
       <c r="H32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>23</v>
+      <c r="I32" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>24</v>
@@ -2657,8 +2672,8 @@
       <c r="L32" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M32" s="1" t="s">
-        <v>23</v>
+      <c r="M32" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>24</v>
@@ -2666,17 +2681,17 @@
       <c r="O32" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>23</v>
+      <c r="P32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S32" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T32" s="2" t="s">
         <v>24</v>
@@ -2701,11 +2716,11 @@
       <c r="D33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>24</v>
+      <c r="E33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>24</v>
@@ -2713,8 +2728,8 @@
       <c r="H33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I33" s="2" t="s">
-        <v>24</v>
+      <c r="I33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>24</v>
@@ -2722,11 +2737,11 @@
       <c r="K33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M33" s="2" t="s">
-        <v>24</v>
+      <c r="L33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>24</v>
@@ -2734,17 +2749,17 @@
       <c r="O33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R33" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S33" s="2" t="s">
-        <v>24</v>
+      <c r="P33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T33" s="2" t="s">
         <v>24</v>
@@ -2769,11 +2784,11 @@
       <c r="D34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>23</v>
+      <c r="E34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>24</v>
@@ -2790,8 +2805,8 @@
       <c r="K34" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>23</v>
+      <c r="L34" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>24</v>
@@ -2834,14 +2849,14 @@
       <c r="C35" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>24</v>
+      <c r="D35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>24</v>
@@ -2855,11 +2870,11 @@
       <c r="J35" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>24</v>
+      <c r="K35" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>24</v>
@@ -2902,8 +2917,8 @@
       <c r="C36" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>23</v>
+      <c r="D36" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>24</v>
@@ -2923,11 +2938,11 @@
       <c r="J36" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>23</v>
+      <c r="K36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>24</v>
@@ -2973,11 +2988,11 @@
       <c r="D37" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>23</v>
+      <c r="E37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>24</v>
@@ -3044,8 +3059,8 @@
       <c r="E38" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>24</v>
+      <c r="F38" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>24</v>
@@ -3053,8 +3068,8 @@
       <c r="H38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>23</v>
+      <c r="I38" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>24</v>
@@ -3062,29 +3077,29 @@
       <c r="K38" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>24</v>
+      <c r="L38" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>23</v>
+      <c r="N38" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>23</v>
+      <c r="P38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>24</v>
@@ -3109,8 +3124,8 @@
       <c r="D39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>24</v>
+      <c r="E39" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>24</v>
@@ -3136,8 +3151,8 @@
       <c r="M39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N39" s="2" t="s">
-        <v>24</v>
+      <c r="N39" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>24</v>
@@ -3189,8 +3204,8 @@
       <c r="H40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>24</v>
+      <c r="I40" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>24</v>
@@ -3198,8 +3213,8 @@
       <c r="K40" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>23</v>
+      <c r="L40" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>24</v>
@@ -3210,17 +3225,17 @@
       <c r="O40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>24</v>
+      <c r="P40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>24</v>
@@ -3313,11 +3328,11 @@
       <c r="D42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>23</v>
+      <c r="E42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>24</v>
@@ -3325,8 +3340,8 @@
       <c r="H42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>23</v>
+      <c r="I42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>24</v>
@@ -3334,14 +3349,14 @@
       <c r="K42" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>24</v>
+      <c r="L42" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N42" s="1" t="s">
-        <v>23</v>
+      <c r="N42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>24</v>
@@ -3355,17 +3370,17 @@
       <c r="R42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S42" s="1" t="s">
-        <v>23</v>
+      <c r="S42" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U42" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>23</v>
+      <c r="U42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="43">
@@ -3378,62 +3393,62 @@
       <c r="C43" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>23</v>
+      <c r="D43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U43" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="44">
@@ -3455,32 +3470,32 @@
       <c r="F44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>23</v>
+      <c r="G44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>23</v>
+      <c r="J44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>23</v>
+      <c r="L44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>23</v>
+      <c r="O44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="P44" s="2" t="s">
         <v>24</v>
@@ -3494,8 +3509,8 @@
       <c r="S44" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T44" s="1" t="s">
-        <v>23</v>
+      <c r="T44" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="U44" s="1" t="s">
         <v>23</v>
@@ -3523,47 +3538,47 @@
       <c r="F45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>24</v>
+      <c r="G45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J45" s="2" t="s">
-        <v>24</v>
+      <c r="J45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M45" s="2" t="s">
-        <v>24</v>
+      <c r="L45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q45" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R45" s="2" t="s">
-        <v>24</v>
+      <c r="O45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S45" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T45" s="2" t="s">
-        <v>24</v>
+      <c r="T45" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="U45" s="1" t="s">
         <v>23</v>
@@ -3585,53 +3600,53 @@
       <c r="D46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>24</v>
+      <c r="E46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J46" s="2" t="s">
-        <v>24</v>
+      <c r="J46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O46" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>23</v>
+      <c r="L46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O46" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T46" s="2" t="s">
-        <v>24</v>
+      <c r="T46" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="U46" s="1" t="s">
         <v>23</v>
@@ -3665,23 +3680,23 @@
       <c r="H47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>24</v>
+      <c r="I47" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>24</v>
+      <c r="K47" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>24</v>
+      <c r="M47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>24</v>
@@ -3695,17 +3710,17 @@
       <c r="R47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S47" s="2" t="s">
-        <v>24</v>
+      <c r="S47" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U47" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V47" s="2" t="s">
-        <v>24</v>
+      <c r="U47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="48">
@@ -3721,32 +3736,32 @@
       <c r="D48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>23</v>
+      <c r="E48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>23</v>
+      <c r="J48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" s="1" t="s">
-        <v>23</v>
+      <c r="L48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>24</v>
@@ -3766,14 +3781,14 @@
       <c r="S48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T48" s="1" t="s">
-        <v>23</v>
+      <c r="T48" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="U48" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="V48" s="2" t="s">
-        <v>24</v>
+      <c r="V48" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="49">
@@ -3786,14 +3801,14 @@
       <c r="C49" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>23</v>
+      <c r="D49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>24</v>
@@ -3813,8 +3828,8 @@
       <c r="L49" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>23</v>
+      <c r="M49" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>24</v>
@@ -3860,8 +3875,8 @@
       <c r="E50" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>24</v>
+      <c r="F50" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>24</v>
@@ -3869,47 +3884,47 @@
       <c r="H50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>23</v>
+      <c r="I50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>23</v>
+      <c r="K50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>23</v>
+      <c r="M50" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S50" s="1" t="s">
-        <v>23</v>
+      <c r="P50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U50" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V50" s="1" t="s">
-        <v>23</v>
+      <c r="U50" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V50" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="51">
@@ -3922,35 +3937,35 @@
       <c r="C51" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M51" s="2" t="s">
-        <v>24</v>
+      <c r="D51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>24</v>
@@ -3958,23 +3973,23 @@
       <c r="O51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U51" s="2" t="s">
-        <v>24</v>
+      <c r="P51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>24</v>
@@ -3993,11 +4008,11 @@
       <c r="D52" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>24</v>
+      <c r="E52" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>24</v>
@@ -4005,20 +4020,20 @@
       <c r="H52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>23</v>
+      <c r="I52" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>23</v>
+      <c r="K52" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>24</v>
+      <c r="M52" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>24</v>
@@ -4026,26 +4041,26 @@
       <c r="O52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>23</v>
+      <c r="P52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T52" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U52" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V52" s="1" t="s">
-        <v>23</v>
+      <c r="U52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="53">
@@ -4064,8 +4079,8 @@
       <c r="E53" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>23</v>
+      <c r="F53" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>24</v>
@@ -4073,47 +4088,47 @@
       <c r="H53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I53" s="2" t="s">
-        <v>24</v>
+      <c r="I53" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K53" s="2" t="s">
-        <v>24</v>
+      <c r="K53" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>24</v>
+      <c r="M53" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>24</v>
+      <c r="P53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T53" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U53" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>24</v>
+      <c r="U53" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="54">
@@ -4126,14 +4141,14 @@
       <c r="C54" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>23</v>
+      <c r="D54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>24</v>
@@ -4153,8 +4168,8 @@
       <c r="L54" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M54" s="1" t="s">
-        <v>23</v>
+      <c r="M54" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>24</v>
@@ -4191,8 +4206,8 @@
       <c r="B55" t="s">
         <v>77</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>24</v>
+      <c r="C55" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>24</v>
@@ -4200,14 +4215,14 @@
       <c r="E55" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>23</v>
+      <c r="F55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>24</v>
@@ -4265,17 +4280,17 @@
       <c r="D56" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>23</v>
+      <c r="E56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>23</v>
@@ -4313,11 +4328,11 @@
       <c r="T56" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U56" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>24</v>
+      <c r="U56" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="57">
@@ -4330,14 +4345,14 @@
       <c r="C57" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>24</v>
+      <c r="D57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>24</v>
@@ -4357,8 +4372,8 @@
       <c r="L57" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M57" s="2" t="s">
-        <v>24</v>
+      <c r="M57" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>24</v>
@@ -4398,14 +4413,14 @@
       <c r="C58" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>24</v>
+      <c r="D58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>24</v>
@@ -4425,8 +4440,8 @@
       <c r="L58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>24</v>
+      <c r="M58" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>24</v>
@@ -4463,8 +4478,8 @@
       <c r="B59" t="s">
         <v>81</v>
       </c>
-      <c r="C59" s="1" t="s">
-        <v>23</v>
+      <c r="C59" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>24</v>
@@ -4472,14 +4487,14 @@
       <c r="E59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>24</v>
+      <c r="F59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>24</v>
@@ -4540,23 +4555,23 @@
       <c r="E60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>24</v>
+      <c r="F60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K60" s="2" t="s">
-        <v>24</v>
+      <c r="K60" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>24</v>
@@ -4585,11 +4600,11 @@
       <c r="T60" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U60" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V60" s="1" t="s">
-        <v>23</v>
+      <c r="U60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="61">
@@ -4602,8 +4617,8 @@
       <c r="C61" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>23</v>
+      <c r="D61" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>24</v>
@@ -4667,14 +4682,14 @@
       <c r="B62" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>24</v>
+      <c r="C62" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>23</v>
+      <c r="E62" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>24</v>
@@ -4738,11 +4753,11 @@
       <c r="C63" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>23</v>
+      <c r="D63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>24</v>
@@ -4753,14 +4768,14 @@
       <c r="H63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>23</v>
+      <c r="I63" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>23</v>
+      <c r="K63" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>24</v>
@@ -4768,32 +4783,32 @@
       <c r="M63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N63" s="1" t="s">
-        <v>23</v>
+      <c r="N63" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>23</v>
+      <c r="P63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S63" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T63" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V63" s="1" t="s">
-        <v>23</v>
+      <c r="U63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="64">
@@ -4821,14 +4836,14 @@
       <c r="H64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>23</v>
+      <c r="I64" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>23</v>
+      <c r="K64" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>24</v>
@@ -4836,8 +4851,8 @@
       <c r="M64" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N64" s="1" t="s">
-        <v>23</v>
+      <c r="N64" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>24</v>
@@ -4939,14 +4954,14 @@
       <c r="B66" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>23</v>
+      <c r="C66" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>24</v>
+      <c r="E66" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>24</v>
@@ -5010,11 +5025,11 @@
       <c r="C67" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>24</v>
+      <c r="D67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>24</v>
@@ -5025,14 +5040,14 @@
       <c r="H67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>24</v>
+      <c r="I67" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>24</v>
+      <c r="K67" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>24</v>
@@ -5040,32 +5055,32 @@
       <c r="M67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N67" s="2" t="s">
-        <v>24</v>
+      <c r="N67" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S67" s="2" t="s">
-        <v>24</v>
+      <c r="P67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>24</v>
+      <c r="U67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="68">
@@ -5078,11 +5093,11 @@
       <c r="C68" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>24</v>
+      <c r="D68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>24</v>
@@ -5093,14 +5108,14 @@
       <c r="H68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I68" s="2" t="s">
-        <v>24</v>
+      <c r="I68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>24</v>
+      <c r="K68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>24</v>
@@ -5108,32 +5123,32 @@
       <c r="M68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N68" s="2" t="s">
-        <v>24</v>
+      <c r="N68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>24</v>
+      <c r="P68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U68" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>24</v>
+      <c r="U68" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="69">
@@ -5149,8 +5164,8 @@
       <c r="D69" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E69" s="1" t="s">
-        <v>23</v>
+      <c r="E69" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>24</v>
@@ -5182,26 +5197,26 @@
       <c r="O69" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>23</v>
+      <c r="P69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U69" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>23</v>
+      <c r="U69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="70">
@@ -5214,11 +5229,11 @@
       <c r="C70" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>23</v>
+      <c r="D70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>24</v>
@@ -5250,26 +5265,26 @@
       <c r="O70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>23</v>
+      <c r="P70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U70" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V70" s="1" t="s">
-        <v>23</v>
+      <c r="U70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V70" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="71">
@@ -5433,23 +5448,23 @@
       <c r="H73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>23</v>
+      <c r="I73" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>23</v>
+      <c r="K73" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M73" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>23</v>
+      <c r="M73" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>24</v>
@@ -5501,8 +5516,8 @@
       <c r="H74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>23</v>
+      <c r="I74" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>24</v>
@@ -5513,11 +5528,11 @@
       <c r="L74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>23</v>
+      <c r="M74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>24</v>
@@ -5554,8 +5569,8 @@
       <c r="C75" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>23</v>
+      <c r="D75" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>24</v>
@@ -5575,8 +5590,8 @@
       <c r="J75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>23</v>
+      <c r="K75" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>24</v>
@@ -5590,14 +5605,14 @@
       <c r="O75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>23</v>
+      <c r="P75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S75" s="2" t="s">
         <v>24</v>
@@ -5637,11 +5652,11 @@
       <c r="H76" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>23</v>
+      <c r="I76" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>24</v>
@@ -5652,8 +5667,8 @@
       <c r="M76" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N76" s="1" t="s">
-        <v>23</v>
+      <c r="N76" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>24</v>
@@ -5667,8 +5682,8 @@
       <c r="R76" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S76" s="1" t="s">
-        <v>23</v>
+      <c r="S76" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T76" s="2" t="s">
         <v>24</v>
@@ -5690,11 +5705,11 @@
       <c r="C77" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>24</v>
+      <c r="D77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>24</v>
@@ -5708,32 +5723,32 @@
       <c r="I77" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>24</v>
+      <c r="J77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N77" s="2" t="s">
-        <v>24</v>
+      <c r="M77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>24</v>
+      <c r="P77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>23</v>
@@ -5741,11 +5756,11 @@
       <c r="T77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U77" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>24</v>
+      <c r="U77" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V77" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="78">
@@ -5758,11 +5773,11 @@
       <c r="C78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>24</v>
+      <c r="D78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>24</v>
@@ -5776,8 +5791,8 @@
       <c r="I78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>23</v>
+      <c r="J78" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>24</v>
@@ -5785,23 +5800,23 @@
       <c r="L78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N78" s="2" t="s">
-        <v>24</v>
+      <c r="M78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R78" s="2" t="s">
-        <v>24</v>
+      <c r="P78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S78" s="1" t="s">
         <v>23</v>
@@ -5809,11 +5824,11 @@
       <c r="T78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U78" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>24</v>
+      <c r="U78" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="79">
@@ -5826,8 +5841,8 @@
       <c r="C79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>24</v>
+      <c r="D79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>24</v>
@@ -5841,14 +5856,14 @@
       <c r="H79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>24</v>
+      <c r="I79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>24</v>
@@ -5862,17 +5877,17 @@
       <c r="O79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S79" s="1" t="s">
-        <v>23</v>
+      <c r="P79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T79" s="2" t="s">
         <v>24</v>
@@ -5912,8 +5927,8 @@
       <c r="I80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>24</v>
+      <c r="J80" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>24</v>
@@ -5924,8 +5939,8 @@
       <c r="M80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>24</v>
+      <c r="N80" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>24</v>
@@ -6116,8 +6131,8 @@
       <c r="I83" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J83" s="2" t="s">
-        <v>24</v>
+      <c r="J83" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>24</v>
@@ -6184,8 +6199,8 @@
       <c r="I84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>23</v>
+      <c r="J84" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>24</v>
@@ -6388,8 +6403,8 @@
       <c r="I87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J87" s="1" t="s">
-        <v>23</v>
+      <c r="J87" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>24</v>
@@ -6456,8 +6471,8 @@
       <c r="I88" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J88" s="2" t="s">
-        <v>24</v>
+      <c r="J88" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>24</v>
@@ -6506,20 +6521,20 @@
       <c r="C89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H89" s="1" t="s">
-        <v>23</v>
+      <c r="D89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>23</v>
@@ -6527,41 +6542,41 @@
       <c r="J89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>23</v>
+      <c r="K89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R89" s="1" t="s">
-        <v>23</v>
+      <c r="P89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R89" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U89" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V89" s="1" t="s">
-        <v>23</v>
+      <c r="T89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U89" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="90">
@@ -6574,14 +6589,14 @@
       <c r="C90" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>23</v>
+      <c r="D90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>24</v>
@@ -6589,11 +6604,11 @@
       <c r="H90" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I90" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>24</v>
+      <c r="I90" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>24</v>
@@ -6622,14 +6637,354 @@
       <c r="S90" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U90" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V90" s="1" t="s">
-        <v>23</v>
+      <c r="T90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U90" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="3">
+        <v>113</v>
+      </c>
+      <c r="B91" t="s">
+        <v>113</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S91" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U91" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="3">
+        <v>114</v>
+      </c>
+      <c r="B92" t="s">
+        <v>114</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S92" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U92" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="3">
+        <v>115</v>
+      </c>
+      <c r="B93" t="s">
+        <v>115</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U93" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V93" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="3">
+        <v>116</v>
+      </c>
+      <c r="B94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V94" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="3">
+        <v>117</v>
+      </c>
+      <c r="B95" t="s">
+        <v>117</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U95" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V95" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6644,12 +6999,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -372,7 +372,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.27.0-SNAPSHOT</t>
+    <t>1.28.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -372,7 +372,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.28.0-SNAPSHOT</t>
+    <t>1.29.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -2175,8 +2175,8 @@
       <c r="E25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>24</v>
+      <c r="F25" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>24</v>
@@ -2243,8 +2243,8 @@
       <c r="E26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>24</v>
+      <c r="F26" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>24</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -372,7 +372,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.29.0-SNAPSHOT</t>
+    <t>1.30.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2092" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="123">
   <si>
     <t>User Right</t>
   </si>
@@ -369,10 +369,19 @@
     <t>POPULATION_MANAGE</t>
   </si>
   <si>
+    <t>LINE_LISTING_CONFIGURE</t>
+  </si>
+  <si>
+    <t>LINE_LISTING_CONFIGURE_NATION</t>
+  </si>
+  <si>
+    <t>AGGREGATE_REPORT_VIEW</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.30.0-SNAPSHOT</t>
+    <t>1.31.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -500,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W95"/>
+  <dimension ref="A1:W98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -6987,6 +6996,210 @@
         <v>24</v>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" t="s" s="3">
+        <v>118</v>
+      </c>
+      <c r="B96" t="s">
+        <v>118</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U96" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="3">
+        <v>119</v>
+      </c>
+      <c r="B97" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U97" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="3">
+        <v>120</v>
+      </c>
+      <c r="B98" t="s">
+        <v>120</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U98" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V98" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -6999,12 +7212,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2158" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="124">
   <si>
     <t>User Right</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>AGGREGATE_REPORT_VIEW</t>
+  </si>
+  <si>
+    <t>AGGREGATE_REPORT_EXPORT</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -509,7 +512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W98"/>
+  <dimension ref="A1:W99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -7200,6 +7203,74 @@
         <v>23</v>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="s" s="3">
+        <v>121</v>
+      </c>
+      <c r="B99" t="s">
+        <v>121</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U99" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V99" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -7212,12 +7283,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -384,7 +384,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.31.0-SNAPSHOT</t>
+    <t>1.32.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2224" uniqueCount="126">
   <si>
     <t>User Right</t>
   </si>
@@ -303,10 +303,16 @@
     <t>INFRASTRUCTURE_VIEW</t>
   </si>
   <si>
+    <t>INFRASTRUCTURE_VIEW_ARCHIVED</t>
+  </si>
+  <si>
     <t>INFRASTRUCTURE_EXPORT</t>
   </si>
   <si>
     <t>INFRASTRUCTURE_IMPORT</t>
+  </si>
+  <si>
+    <t>INFRASTRUCTURE_ARCHIVE</t>
   </si>
   <si>
     <t>USER_RIGHTS_MANAGE</t>
@@ -512,7 +518,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:W99"/>
+  <dimension ref="A1:W101"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -5516,8 +5522,8 @@
       <c r="D74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>23</v>
+      <c r="E74" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>24</v>
@@ -5552,23 +5558,23 @@
       <c r="P74" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Q74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>23</v>
+      <c r="Q74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T74" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V74" s="1" t="s">
-        <v>23</v>
+      <c r="U74" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="75">
@@ -5581,11 +5587,11 @@
       <c r="C75" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>24</v>
+      <c r="D75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>24</v>
@@ -5617,26 +5623,26 @@
       <c r="O75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S75" s="2" t="s">
-        <v>24</v>
+      <c r="P75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U75" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V75" s="2" t="s">
-        <v>24</v>
+      <c r="U75" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="76">
@@ -5720,8 +5726,8 @@
       <c r="D77" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>23</v>
+      <c r="E77" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>24</v>
@@ -5732,47 +5738,47 @@
       <c r="H77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>23</v>
+      <c r="I77" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>23</v>
+      <c r="K77" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>23</v>
+      <c r="M77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S77" s="1" t="s">
-        <v>23</v>
+      <c r="P77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U77" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V77" s="1" t="s">
-        <v>23</v>
+      <c r="U77" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="78">
@@ -5785,11 +5791,11 @@
       <c r="C78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>23</v>
+      <c r="D78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>24</v>
@@ -5800,8 +5806,8 @@
       <c r="H78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I78" s="1" t="s">
-        <v>23</v>
+      <c r="I78" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>24</v>
@@ -5812,35 +5818,35 @@
       <c r="L78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N78" s="1" t="s">
-        <v>23</v>
+      <c r="M78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S78" s="1" t="s">
-        <v>23</v>
+      <c r="P78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T78" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U78" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V78" s="1" t="s">
-        <v>23</v>
+      <c r="U78" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="79">
@@ -5856,8 +5862,8 @@
       <c r="D79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>24</v>
+      <c r="E79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>24</v>
@@ -5868,8 +5874,8 @@
       <c r="H79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>24</v>
+      <c r="I79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>24</v>
@@ -5880,11 +5886,11 @@
       <c r="L79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N79" s="2" t="s">
-        <v>24</v>
+      <c r="M79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O79" s="2" t="s">
         <v>24</v>
@@ -5898,17 +5904,17 @@
       <c r="R79" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S79" s="2" t="s">
-        <v>24</v>
+      <c r="S79" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="T79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V79" s="2" t="s">
-        <v>24</v>
+      <c r="U79" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V79" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="80">
@@ -5921,11 +5927,11 @@
       <c r="C80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>24</v>
+      <c r="D80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>24</v>
@@ -5939,8 +5945,8 @@
       <c r="I80" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>23</v>
+      <c r="J80" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>24</v>
@@ -5948,8 +5954,8 @@
       <c r="L80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>24</v>
+      <c r="M80" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="N80" s="1" t="s">
         <v>23</v>
@@ -5957,14 +5963,14 @@
       <c r="O80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>24</v>
+      <c r="P80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="S80" s="1" t="s">
         <v>23</v>
@@ -5972,11 +5978,11 @@
       <c r="T80" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>24</v>
+      <c r="U80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V80" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="81">
@@ -5989,8 +5995,8 @@
       <c r="C81" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>24</v>
+      <c r="D81" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>24</v>
@@ -6004,14 +6010,14 @@
       <c r="H81" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>24</v>
+      <c r="I81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="L81" s="2" t="s">
         <v>24</v>
@@ -6025,17 +6031,17 @@
       <c r="O81" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P81" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q81" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R81" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S81" s="1" t="s">
-        <v>23</v>
+      <c r="P81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T81" s="2" t="s">
         <v>24</v>
@@ -6087,8 +6093,8 @@
       <c r="M82" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N82" s="2" t="s">
-        <v>24</v>
+      <c r="N82" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>24</v>
@@ -6211,8 +6217,8 @@
       <c r="I84" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J84" s="2" t="s">
-        <v>24</v>
+      <c r="J84" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>24</v>
@@ -6347,8 +6353,8 @@
       <c r="I86" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J86" s="1" t="s">
-        <v>23</v>
+      <c r="J86" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>24</v>
@@ -6415,8 +6421,8 @@
       <c r="I87" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J87" s="2" t="s">
-        <v>24</v>
+      <c r="J87" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>24</v>
@@ -6551,8 +6557,8 @@
       <c r="I89" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>23</v>
+      <c r="J89" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>24</v>
@@ -6755,8 +6761,8 @@
       <c r="I92" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J92" s="2" t="s">
-        <v>24</v>
+      <c r="J92" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>24</v>
@@ -6805,20 +6811,20 @@
       <c r="C93" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>23</v>
+      <c r="D93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>23</v>
@@ -6826,41 +6832,41 @@
       <c r="J93" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>23</v>
+      <c r="K93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R93" s="1" t="s">
-        <v>23</v>
+      <c r="P93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="S93" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U93" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V93" s="1" t="s">
-        <v>23</v>
+      <c r="T93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U93" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="94">
@@ -6873,14 +6879,14 @@
       <c r="C94" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>23</v>
+      <c r="D94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>24</v>
@@ -6888,8 +6894,8 @@
       <c r="H94" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I94" s="2" t="s">
-        <v>24</v>
+      <c r="I94" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>24</v>
@@ -6921,14 +6927,14 @@
       <c r="S94" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V94" s="1" t="s">
-        <v>23</v>
+      <c r="T94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U94" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="95">
@@ -6941,62 +6947,62 @@
       <c r="C95" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N95" s="2" t="s">
-        <v>24</v>
+      <c r="D95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="O95" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="R95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="S95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U95" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V95" s="2" t="s">
-        <v>24</v>
+      <c r="P95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U95" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V95" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="96">
@@ -7015,8 +7021,8 @@
       <c r="E96" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>24</v>
+      <c r="F96" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>24</v>
@@ -7054,17 +7060,17 @@
       <c r="R96" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="S96" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T96" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="U96" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="V96" s="2" t="s">
-        <v>24</v>
+      <c r="S96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U96" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V96" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="97">
@@ -7077,8 +7083,8 @@
       <c r="C97" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>23</v>
+      <c r="D97" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>24</v>
@@ -7151,23 +7157,23 @@
       <c r="E98" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>23</v>
+      <c r="F98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>23</v>
+      <c r="I98" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K98" s="1" t="s">
-        <v>23</v>
+      <c r="K98" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L98" s="2" t="s">
         <v>24</v>
@@ -7181,26 +7187,26 @@
       <c r="O98" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="T98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="U98" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V98" s="1" t="s">
-        <v>23</v>
+      <c r="P98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="99">
@@ -7216,8 +7222,8 @@
       <c r="D99" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E99" s="1" t="s">
-        <v>23</v>
+      <c r="E99" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>24</v>
@@ -7228,14 +7234,14 @@
       <c r="H99" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="I99" s="1" t="s">
-        <v>23</v>
+      <c r="I99" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K99" s="1" t="s">
-        <v>23</v>
+      <c r="K99" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="L99" s="2" t="s">
         <v>24</v>
@@ -7249,25 +7255,161 @@
       <c r="O99" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="R99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S99" s="1" t="s">
-        <v>23</v>
+      <c r="P99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="T99" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="U99" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V99" s="1" t="s">
+      <c r="U99" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="3">
+        <v>122</v>
+      </c>
+      <c r="B100" t="s">
+        <v>122</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="U100" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V100" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="3">
+        <v>123</v>
+      </c>
+      <c r="B101" t="s">
+        <v>123</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="V101" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -7283,12 +7425,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -390,7 +390,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.32.0-SNAPSHOT</t>
+    <t>1.33.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -390,7 +390,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.33.0-SNAPSHOT</t>
+    <t>1.34.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -21,7 +21,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Admin</t>
+    <t>Administrator</t>
   </si>
   <si>
     <t>National User</t>
@@ -39,7 +39,7 @@
     <t>Community Informant</t>
   </si>
   <si>
-    <t>Clinician</t>
+    <t>Arzt/Ärztin</t>
   </si>
   <si>
     <t>Case Officer</t>
@@ -48,7 +48,7 @@
     <t>Contact Supervisor</t>
   </si>
   <si>
-    <t>Contact Officer</t>
+    <t>Ansprechpartner</t>
   </si>
   <si>
     <t>Event Officer</t>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -21,7 +21,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Administrator</t>
+    <t>Admin</t>
   </si>
   <si>
     <t>National User</t>
@@ -39,7 +39,7 @@
     <t>Community Informant</t>
   </si>
   <si>
-    <t>Arzt/Ärztin</t>
+    <t>Clinician</t>
   </si>
   <si>
     <t>Case Officer</t>
@@ -48,7 +48,7 @@
     <t>Contact Supervisor</t>
   </si>
   <si>
-    <t>Ansprechpartner</t>
+    <t>Contact Officer</t>
   </si>
   <si>
     <t>Event Officer</t>
@@ -390,7 +390,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.34.0-SNAPSHOT</t>
+    <t>1.35.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -396,7 +396,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.36.0-SNAPSHOT</t>
+    <t>1.37.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2417" uniqueCount="131">
   <si>
     <t>User Right</t>
   </si>
@@ -126,6 +126,9 @@
     <t>CASE_EXPORT</t>
   </si>
   <si>
+    <t>CASE_SHARE</t>
+  </si>
+  <si>
     <t>CASE_ARCHIVE</t>
   </si>
   <si>
@@ -210,6 +213,9 @@
     <t>CONTACT_VIEW_ARCHIVED</t>
   </si>
   <si>
+    <t>CONTACT_REASSIGN_CASE</t>
+  </si>
+  <si>
     <t>VISIT_CREATE</t>
   </si>
   <si>
@@ -391,6 +397,9 @@
   </si>
   <si>
     <t>AGGREGATE_REPORT_EXPORT</t>
+  </si>
+  <si>
+    <t>AGGREGATE_REPORT_EDIT</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -524,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:X102"/>
+  <dimension ref="A1:X105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -1272,8 +1281,8 @@
       <c r="C11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>25</v>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>25</v>
@@ -1485,11 +1494,11 @@
       <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>25</v>
+      <c r="D14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>25</v>
@@ -1500,14 +1509,14 @@
       <c r="H14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>25</v>
+      <c r="I14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>25</v>
+      <c r="K14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1521,26 +1530,26 @@
       <c r="O14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>25</v>
+      <c r="P14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>25</v>
+      <c r="U14" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W14" s="2" t="s">
         <v>25</v>
@@ -1556,8 +1565,8 @@
       <c r="C15" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>24</v>
+      <c r="D15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>25</v>
@@ -1571,14 +1580,14 @@
       <c r="H15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>24</v>
+      <c r="I15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>24</v>
+      <c r="K15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1592,26 +1601,26 @@
       <c r="O15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>24</v>
+      <c r="P15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>24</v>
+      <c r="U15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W15" s="2" t="s">
         <v>25</v>
@@ -1627,8 +1636,8 @@
       <c r="C16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>25</v>
+      <c r="D16" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>25</v>
@@ -1642,14 +1651,14 @@
       <c r="H16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="2" t="s">
-        <v>25</v>
+      <c r="I16" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>25</v>
+      <c r="K16" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1663,26 +1672,26 @@
       <c r="O16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>25</v>
+      <c r="P16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>25</v>
+      <c r="U16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V16" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W16" s="2" t="s">
         <v>25</v>
@@ -1698,26 +1707,26 @@
       <c r="C17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>24</v>
+      <c r="D17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>25</v>
@@ -1728,8 +1737,8 @@
       <c r="M17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N17" s="1" t="s">
-        <v>24</v>
+      <c r="N17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>25</v>
@@ -1743,8 +1752,8 @@
       <c r="R17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S17" s="1" t="s">
-        <v>24</v>
+      <c r="S17" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>25</v>
@@ -1790,29 +1799,29 @@
       <c r="J18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>24</v>
+      <c r="K18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N18" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>24</v>
+      <c r="O18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="S18" s="1" t="s">
         <v>24</v>
@@ -1861,14 +1870,14 @@
       <c r="J19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>25</v>
+      <c r="K19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>24</v>
@@ -1876,14 +1885,14 @@
       <c r="O19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>25</v>
+      <c r="P19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="S19" s="1" t="s">
         <v>24</v>
@@ -1911,26 +1920,26 @@
       <c r="C20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>25</v>
+      <c r="D20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>25</v>
+      <c r="F20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>25</v>
@@ -1941,11 +1950,11 @@
       <c r="M20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>25</v>
+      <c r="N20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>25</v>
@@ -1956,8 +1965,8 @@
       <c r="R20" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S20" s="2" t="s">
-        <v>25</v>
+      <c r="S20" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T20" s="2" t="s">
         <v>25</v>
@@ -1985,8 +1994,8 @@
       <c r="D21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>25</v>
+      <c r="E21" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>25</v>
@@ -2056,8 +2065,8 @@
       <c r="D22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>24</v>
+      <c r="E22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>25</v>
@@ -2068,8 +2077,8 @@
       <c r="H22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>24</v>
+      <c r="I22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>25</v>
@@ -2083,11 +2092,11 @@
       <c r="M22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N22" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>24</v>
+      <c r="N22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>25</v>
@@ -2098,8 +2107,8 @@
       <c r="R22" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S22" s="1" t="s">
-        <v>24</v>
+      <c r="S22" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T22" s="2" t="s">
         <v>25</v>
@@ -2145,8 +2154,8 @@
       <c r="J23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>24</v>
+      <c r="K23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2157,17 +2166,17 @@
       <c r="N23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O23" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>24</v>
+      <c r="O23" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="S23" s="1" t="s">
         <v>24</v>
@@ -2198,8 +2207,8 @@
       <c r="D24" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>25</v>
+      <c r="E24" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>25</v>
@@ -2225,8 +2234,8 @@
       <c r="M24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N24" s="2" t="s">
-        <v>25</v>
+      <c r="N24" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>25</v>
@@ -2269,11 +2278,11 @@
       <c r="D25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>24</v>
+      <c r="E25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>25</v>
@@ -2287,8 +2296,8 @@
       <c r="J25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K25" s="2" t="s">
-        <v>25</v>
+      <c r="K25" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2296,20 +2305,20 @@
       <c r="M25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R25" s="2" t="s">
-        <v>25</v>
+      <c r="N25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>24</v>
@@ -2408,14 +2417,14 @@
       <c r="C27" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>25</v>
+      <c r="D27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>25</v>
@@ -2423,8 +2432,8 @@
       <c r="H27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>25</v>
+      <c r="I27" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>25</v>
@@ -2438,11 +2447,11 @@
       <c r="M27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N27" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>25</v>
+      <c r="N27" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="P27" s="2" t="s">
         <v>25</v>
@@ -2453,8 +2462,8 @@
       <c r="R27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S27" s="2" t="s">
-        <v>25</v>
+      <c r="S27" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T27" s="2" t="s">
         <v>25</v>
@@ -2479,8 +2488,8 @@
       <c r="C28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>25</v>
+      <c r="D28" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>25</v>
@@ -2494,11 +2503,11 @@
       <c r="H28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>24</v>
+      <c r="I28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>25</v>
@@ -2509,11 +2518,11 @@
       <c r="M28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N28" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>24</v>
+      <c r="N28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="P28" s="2" t="s">
         <v>25</v>
@@ -2524,8 +2533,8 @@
       <c r="R28" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S28" s="1" t="s">
-        <v>24</v>
+      <c r="S28" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T28" s="2" t="s">
         <v>25</v>
@@ -2707,11 +2716,11 @@
       <c r="H31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>25</v>
+      <c r="I31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>25</v>
@@ -2722,11 +2731,11 @@
       <c r="M31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>25</v>
+      <c r="N31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O31" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>25</v>
@@ -2737,8 +2746,8 @@
       <c r="R31" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S31" s="2" t="s">
-        <v>25</v>
+      <c r="S31" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T31" s="2" t="s">
         <v>25</v>
@@ -2766,11 +2775,11 @@
       <c r="D32" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>24</v>
+      <c r="E32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>25</v>
@@ -2784,11 +2793,11 @@
       <c r="J32" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>24</v>
+      <c r="K32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>25</v>
@@ -2834,14 +2843,14 @@
       <c r="C33" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>25</v>
+      <c r="D33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>25</v>
@@ -2855,11 +2864,11 @@
       <c r="J33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>25</v>
+      <c r="K33" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>25</v>
@@ -2891,8 +2900,8 @@
       <c r="V33" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W33" s="1" t="s">
-        <v>24</v>
+      <c r="W33" s="2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="34">
@@ -2905,14 +2914,14 @@
       <c r="C34" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>24</v>
+      <c r="D34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>25</v>
@@ -2920,20 +2929,20 @@
       <c r="H34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>24</v>
+      <c r="I34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>24</v>
+      <c r="K34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>25</v>
@@ -2941,17 +2950,17 @@
       <c r="O34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>24</v>
+      <c r="P34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T34" s="2" t="s">
         <v>25</v>
@@ -2962,8 +2971,8 @@
       <c r="V34" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="W34" s="2" t="s">
-        <v>25</v>
+      <c r="W34" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="35">
@@ -2979,11 +2988,11 @@
       <c r="D35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>25</v>
+      <c r="E35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>25</v>
@@ -2991,8 +3000,8 @@
       <c r="H35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>25</v>
+      <c r="I35" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>25</v>
@@ -3000,11 +3009,11 @@
       <c r="K35" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M35" s="2" t="s">
-        <v>25</v>
+      <c r="L35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>25</v>
@@ -3012,17 +3021,17 @@
       <c r="O35" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R35" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S35" s="2" t="s">
-        <v>25</v>
+      <c r="P35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T35" s="2" t="s">
         <v>25</v>
@@ -3050,11 +3059,11 @@
       <c r="D36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>24</v>
+      <c r="E36" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>25</v>
@@ -3071,8 +3080,8 @@
       <c r="K36" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>24</v>
+      <c r="L36" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>25</v>
@@ -3118,14 +3127,14 @@
       <c r="C37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>25</v>
+      <c r="D37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>25</v>
@@ -3139,11 +3148,11 @@
       <c r="J37" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L37" s="2" t="s">
-        <v>25</v>
+      <c r="K37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>25</v>
@@ -3210,11 +3219,11 @@
       <c r="J38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>24</v>
+      <c r="K38" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>25</v>
@@ -3263,11 +3272,11 @@
       <c r="D39" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>24</v>
+      <c r="E39" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>25</v>
@@ -3337,8 +3346,8 @@
       <c r="E40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>25</v>
+      <c r="F40" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>25</v>
@@ -3346,8 +3355,8 @@
       <c r="H40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>24</v>
+      <c r="I40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>25</v>
@@ -3355,29 +3364,29 @@
       <c r="K40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>25</v>
+      <c r="L40" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N40" s="1" t="s">
-        <v>24</v>
+      <c r="N40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>24</v>
+      <c r="P40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T40" s="2" t="s">
         <v>25</v>
@@ -3405,8 +3414,8 @@
       <c r="D41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>25</v>
+      <c r="E41" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F41" s="2" t="s">
         <v>25</v>
@@ -3432,8 +3441,8 @@
       <c r="M41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N41" s="2" t="s">
-        <v>25</v>
+      <c r="N41" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>25</v>
@@ -3488,8 +3497,8 @@
       <c r="H42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>25</v>
+      <c r="I42" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>25</v>
@@ -3497,8 +3506,8 @@
       <c r="K42" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>24</v>
+      <c r="L42" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>25</v>
@@ -3509,17 +3518,17 @@
       <c r="O42" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R42" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>25</v>
+      <c r="P42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T42" s="2" t="s">
         <v>25</v>
@@ -3547,11 +3556,11 @@
       <c r="D43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>25</v>
+      <c r="E43" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>25</v>
@@ -3615,8 +3624,8 @@
       <c r="C44" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D44" s="2" t="s">
-        <v>25</v>
+      <c r="D44" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>25</v>
@@ -3636,11 +3645,11 @@
       <c r="J44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>25</v>
+      <c r="K44" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>25</v>
@@ -3689,11 +3698,11 @@
       <c r="D45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>24</v>
+      <c r="E45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>25</v>
@@ -3701,8 +3710,8 @@
       <c r="H45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>24</v>
+      <c r="I45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>25</v>
@@ -3710,14 +3719,14 @@
       <c r="K45" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L45" s="2" t="s">
-        <v>25</v>
+      <c r="L45" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N45" s="1" t="s">
-        <v>24</v>
+      <c r="N45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>25</v>
@@ -3731,17 +3740,17 @@
       <c r="R45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S45" s="1" t="s">
-        <v>24</v>
+      <c r="S45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V45" s="1" t="s">
-        <v>24</v>
+      <c r="U45" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V45" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W45" s="2" t="s">
         <v>25</v>
@@ -3760,59 +3769,59 @@
       <c r="D46" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V46" s="1" t="s">
-        <v>24</v>
+      <c r="E46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U46" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V46" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W46" s="2" t="s">
         <v>25</v>
@@ -3837,32 +3846,32 @@
       <c r="F47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>24</v>
+      <c r="G47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>24</v>
+      <c r="J47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="K47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>24</v>
+      <c r="L47" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>24</v>
+      <c r="O47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="P47" s="2" t="s">
         <v>25</v>
@@ -3876,8 +3885,8 @@
       <c r="S47" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T47" s="1" t="s">
-        <v>24</v>
+      <c r="T47" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="U47" s="1" t="s">
         <v>24</v>
@@ -3908,47 +3917,47 @@
       <c r="F48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>25</v>
+      <c r="G48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="2" t="s">
-        <v>25</v>
+      <c r="J48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>25</v>
+      <c r="L48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q48" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R48" s="2" t="s">
-        <v>25</v>
+      <c r="O48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="S48" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T48" s="2" t="s">
-        <v>25</v>
+      <c r="T48" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="U48" s="1" t="s">
         <v>24</v>
@@ -3973,53 +3982,53 @@
       <c r="D49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>25</v>
+      <c r="E49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="2" t="s">
-        <v>25</v>
+      <c r="J49" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>24</v>
+      <c r="L49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O49" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T49" s="2" t="s">
-        <v>25</v>
+      <c r="T49" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="U49" s="1" t="s">
         <v>24</v>
@@ -4041,14 +4050,14 @@
       <c r="C50" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>25</v>
+      <c r="D50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>25</v>
@@ -4056,14 +4065,14 @@
       <c r="H50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>25</v>
+      <c r="I50" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>25</v>
+      <c r="K50" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -4071,8 +4080,8 @@
       <c r="M50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N50" s="2" t="s">
-        <v>25</v>
+      <c r="N50" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>25</v>
@@ -4086,17 +4095,17 @@
       <c r="R50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S50" s="2" t="s">
-        <v>25</v>
+      <c r="S50" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T50" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>25</v>
+      <c r="U50" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V50" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W50" s="2" t="s">
         <v>25</v>
@@ -4115,11 +4124,11 @@
       <c r="D51" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>24</v>
+      <c r="E51" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>25</v>
@@ -4127,20 +4136,20 @@
       <c r="H51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>25</v>
+      <c r="I51" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>25</v>
+      <c r="K51" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M51" s="1" t="s">
-        <v>24</v>
+      <c r="M51" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>25</v>
@@ -4148,26 +4157,26 @@
       <c r="O51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>25</v>
+      <c r="P51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T51" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U51" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>25</v>
+      <c r="U51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W51" s="2" t="s">
         <v>25</v>
@@ -4186,32 +4195,32 @@
       <c r="D52" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>24</v>
+      <c r="E52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>25</v>
@@ -4219,23 +4228,23 @@
       <c r="O52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T52" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U52" s="1" t="s">
-        <v>24</v>
+      <c r="P52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>25</v>
@@ -4331,32 +4340,32 @@
       <c r="E54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>25</v>
+      <c r="F54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J54" s="2" t="s">
-        <v>25</v>
+      <c r="J54" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M54" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>24</v>
+      <c r="L54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>25</v>
@@ -4373,14 +4382,14 @@
       <c r="S54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T54" s="2" t="s">
-        <v>25</v>
+      <c r="T54" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="U54" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V54" s="1" t="s">
-        <v>24</v>
+      <c r="V54" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W54" s="2" t="s">
         <v>25</v>
@@ -4396,14 +4405,14 @@
       <c r="C55" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>25</v>
+      <c r="D55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>25</v>
@@ -4423,8 +4432,8 @@
       <c r="L55" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M55" s="2" t="s">
-        <v>25</v>
+      <c r="M55" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>25</v>
@@ -4467,11 +4476,11 @@
       <c r="C56" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>25</v>
+      <c r="D56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>25</v>
@@ -4482,14 +4491,14 @@
       <c r="H56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>25</v>
+      <c r="I56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K56" s="2" t="s">
-        <v>25</v>
+      <c r="K56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -4497,32 +4506,32 @@
       <c r="M56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N56" s="2" t="s">
-        <v>25</v>
+      <c r="N56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>25</v>
+      <c r="P56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T56" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U56" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V56" s="2" t="s">
-        <v>25</v>
+      <c r="U56" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V56" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W56" s="2" t="s">
         <v>25</v>
@@ -4538,8 +4547,8 @@
       <c r="C57" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>24</v>
+      <c r="D57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>25</v>
@@ -4553,14 +4562,14 @@
       <c r="H57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>24</v>
+      <c r="I57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>24</v>
+      <c r="K57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -4574,26 +4583,26 @@
       <c r="O57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>24</v>
+      <c r="P57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T57" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U57" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V57" s="1" t="s">
-        <v>24</v>
+      <c r="U57" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W57" s="2" t="s">
         <v>25</v>
@@ -4612,11 +4621,11 @@
       <c r="D58" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>24</v>
+      <c r="E58" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>25</v>
@@ -4636,8 +4645,8 @@
       <c r="L58" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M58" s="1" t="s">
-        <v>24</v>
+      <c r="M58" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>25</v>
@@ -4683,11 +4692,11 @@
       <c r="D59" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>24</v>
+      <c r="E59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>25</v>
@@ -4695,20 +4704,20 @@
       <c r="H59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I59" s="2" t="s">
-        <v>25</v>
+      <c r="I59" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>25</v>
+      <c r="K59" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M59" s="1" t="s">
-        <v>24</v>
+      <c r="M59" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>25</v>
@@ -4716,26 +4725,26 @@
       <c r="O59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>25</v>
+      <c r="P59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U59" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>25</v>
+      <c r="U59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W59" s="2" t="s">
         <v>25</v>
@@ -4748,23 +4757,23 @@
       <c r="B60" t="s">
         <v>83</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>25</v>
+      <c r="C60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G60" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>24</v>
+      <c r="G60" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>25</v>
@@ -4778,8 +4787,8 @@
       <c r="L60" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M60" s="2" t="s">
-        <v>25</v>
+      <c r="M60" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>25</v>
@@ -4831,26 +4840,26 @@
       <c r="F61" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>24</v>
+      <c r="G61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K61" s="1" t="s">
-        <v>24</v>
+      <c r="K61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M61" s="2" t="s">
-        <v>25</v>
+      <c r="M61" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>25</v>
@@ -4858,17 +4867,17 @@
       <c r="O61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>24</v>
+      <c r="P61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R61" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S61" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T61" s="2" t="s">
         <v>25</v>
@@ -4890,8 +4899,8 @@
       <c r="B62" t="s">
         <v>85</v>
       </c>
-      <c r="C62" s="1" t="s">
-        <v>24</v>
+      <c r="C62" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>25</v>
@@ -4899,14 +4908,14 @@
       <c r="E62" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>25</v>
+      <c r="F62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>25</v>
@@ -4964,29 +4973,29 @@
       <c r="C63" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>25</v>
+      <c r="D63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K63" s="2" t="s">
-        <v>25</v>
+      <c r="K63" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>25</v>
@@ -5000,17 +5009,17 @@
       <c r="O63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R63" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S63" s="2" t="s">
-        <v>25</v>
+      <c r="P63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T63" s="2" t="s">
         <v>25</v>
@@ -5106,11 +5115,11 @@
       <c r="C65" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>24</v>
+      <c r="D65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>25</v>
@@ -5142,26 +5151,26 @@
       <c r="O65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>24</v>
+      <c r="P65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U65" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>24</v>
+      <c r="U65" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>25</v>
@@ -5177,8 +5186,8 @@
       <c r="C66" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>24</v>
+      <c r="D66" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>25</v>
@@ -5245,11 +5254,11 @@
       <c r="B67" t="s">
         <v>90</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>25</v>
+      <c r="C67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>24</v>
@@ -5284,26 +5293,26 @@
       <c r="O67" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P67" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R67" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S67" s="2" t="s">
-        <v>25</v>
+      <c r="P67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U67" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>25</v>
+      <c r="U67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V67" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W67" s="2" t="s">
         <v>25</v>
@@ -5322,8 +5331,8 @@
       <c r="D68" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>24</v>
+      <c r="E68" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>25</v>
@@ -5334,14 +5343,14 @@
       <c r="H68" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I68" s="1" t="s">
-        <v>24</v>
+      <c r="I68" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>24</v>
+      <c r="K68" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
@@ -5349,32 +5358,32 @@
       <c r="M68" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>24</v>
+      <c r="N68" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>24</v>
+      <c r="P68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T68" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U68" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>24</v>
+      <c r="U68" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W68" s="2" t="s">
         <v>25</v>
@@ -5387,11 +5396,11 @@
       <c r="B69" t="s">
         <v>92</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>24</v>
+      <c r="C69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>24</v>
@@ -5405,14 +5414,14 @@
       <c r="H69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I69" s="1" t="s">
-        <v>24</v>
+      <c r="I69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>24</v>
+      <c r="K69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -5420,32 +5429,32 @@
       <c r="M69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N69" s="1" t="s">
-        <v>24</v>
+      <c r="N69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>24</v>
+      <c r="P69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U69" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>24</v>
+      <c r="U69" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W69" s="2" t="s">
         <v>25</v>
@@ -5464,8 +5473,8 @@
       <c r="D70" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>25</v>
+      <c r="E70" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>25</v>
@@ -5476,14 +5485,14 @@
       <c r="H70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>25</v>
+      <c r="I70" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>25</v>
+      <c r="K70" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
@@ -5491,32 +5500,32 @@
       <c r="M70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N70" s="2" t="s">
-        <v>25</v>
+      <c r="N70" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>25</v>
+      <c r="P70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U70" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V70" s="2" t="s">
-        <v>25</v>
+      <c r="U70" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V70" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W70" s="2" t="s">
         <v>25</v>
@@ -5532,11 +5541,11 @@
       <c r="C71" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>25</v>
+      <c r="D71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>25</v>
@@ -5547,14 +5556,14 @@
       <c r="H71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>25</v>
+      <c r="I71" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>25</v>
+      <c r="K71" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -5562,32 +5571,32 @@
       <c r="M71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N71" s="2" t="s">
-        <v>25</v>
+      <c r="N71" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>25</v>
+      <c r="P71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S71" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U71" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V71" s="2" t="s">
-        <v>25</v>
+      <c r="U71" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V71" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W71" s="2" t="s">
         <v>25</v>
@@ -5603,8 +5612,8 @@
       <c r="C72" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>25</v>
+      <c r="D72" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>25</v>
@@ -5745,11 +5754,11 @@
       <c r="C74" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>24</v>
+      <c r="D74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>25</v>
@@ -5781,26 +5790,26 @@
       <c r="O74" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>24</v>
+      <c r="P74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T74" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U74" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V74" s="1" t="s">
-        <v>24</v>
+      <c r="U74" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W74" s="2" t="s">
         <v>25</v>
@@ -5816,8 +5825,8 @@
       <c r="C75" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>24</v>
+      <c r="D75" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>25</v>
@@ -5852,8 +5861,8 @@
       <c r="O75" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>24</v>
+      <c r="P75" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="Q75" s="2" t="s">
         <v>25</v>
@@ -5958,8 +5967,8 @@
       <c r="C77" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>25</v>
+      <c r="D77" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>25</v>
@@ -5994,8 +6003,8 @@
       <c r="O77" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P77" s="2" t="s">
-        <v>25</v>
+      <c r="P77" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="Q77" s="2" t="s">
         <v>25</v>
@@ -6032,8 +6041,8 @@
       <c r="D78" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>25</v>
+      <c r="E78" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>25</v>
@@ -6065,26 +6074,26 @@
       <c r="O78" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>25</v>
+      <c r="P78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S78" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T78" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U78" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>25</v>
+      <c r="U78" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W78" s="2" t="s">
         <v>25</v>
@@ -6174,8 +6183,8 @@
       <c r="D80" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E80" s="1" t="s">
-        <v>24</v>
+      <c r="E80" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>25</v>
@@ -6186,47 +6195,47 @@
       <c r="H80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I80" s="1" t="s">
-        <v>24</v>
+      <c r="I80" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>24</v>
+      <c r="K80" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>24</v>
+      <c r="M80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>24</v>
+      <c r="P80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U80" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V80" s="1" t="s">
-        <v>24</v>
+      <c r="U80" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>25</v>
@@ -6242,11 +6251,11 @@
       <c r="C81" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>24</v>
+      <c r="D81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>25</v>
@@ -6257,8 +6266,8 @@
       <c r="H81" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I81" s="1" t="s">
-        <v>24</v>
+      <c r="I81" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>25</v>
@@ -6269,35 +6278,35 @@
       <c r="L81" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N81" s="1" t="s">
-        <v>24</v>
+      <c r="M81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S81" s="1" t="s">
-        <v>24</v>
+      <c r="P81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S81" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T81" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U81" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V81" s="1" t="s">
-        <v>24</v>
+      <c r="U81" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W81" s="2" t="s">
         <v>25</v>
@@ -6316,8 +6325,8 @@
       <c r="D82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>25</v>
+      <c r="E82" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>25</v>
@@ -6328,8 +6337,8 @@
       <c r="H82" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I82" s="2" t="s">
-        <v>25</v>
+      <c r="I82" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>25</v>
@@ -6340,11 +6349,11 @@
       <c r="L82" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M82" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N82" s="2" t="s">
-        <v>25</v>
+      <c r="M82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O82" s="2" t="s">
         <v>25</v>
@@ -6358,17 +6367,17 @@
       <c r="R82" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="S82" s="2" t="s">
-        <v>25</v>
+      <c r="S82" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="T82" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U82" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V82" s="2" t="s">
-        <v>25</v>
+      <c r="U82" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V82" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W82" s="2" t="s">
         <v>25</v>
@@ -6384,11 +6393,11 @@
       <c r="C83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>25</v>
+      <c r="D83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>25</v>
@@ -6402,8 +6411,8 @@
       <c r="I83" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>24</v>
+      <c r="J83" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>25</v>
@@ -6411,8 +6420,8 @@
       <c r="L83" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M83" s="2" t="s">
-        <v>25</v>
+      <c r="M83" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="N83" s="1" t="s">
         <v>24</v>
@@ -6420,14 +6429,14 @@
       <c r="O83" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R83" s="2" t="s">
-        <v>25</v>
+      <c r="P83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>24</v>
@@ -6435,11 +6444,11 @@
       <c r="T83" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U83" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>25</v>
+      <c r="U83" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V83" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W83" s="2" t="s">
         <v>25</v>
@@ -6455,8 +6464,8 @@
       <c r="C84" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>25</v>
+      <c r="D84" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>25</v>
@@ -6470,14 +6479,14 @@
       <c r="H84" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I84" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>25</v>
+      <c r="I84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>25</v>
@@ -6491,17 +6500,17 @@
       <c r="O84" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R84" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>24</v>
+      <c r="P84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T84" s="2" t="s">
         <v>25</v>
@@ -6556,8 +6565,8 @@
       <c r="M85" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="N85" s="2" t="s">
-        <v>25</v>
+      <c r="N85" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O85" s="2" t="s">
         <v>25</v>
@@ -6686,8 +6695,8 @@
       <c r="I87" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J87" s="2" t="s">
-        <v>25</v>
+      <c r="J87" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>25</v>
@@ -6828,8 +6837,8 @@
       <c r="I89" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J89" s="1" t="s">
-        <v>24</v>
+      <c r="J89" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>25</v>
@@ -6899,8 +6908,8 @@
       <c r="I90" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J90" s="2" t="s">
-        <v>25</v>
+      <c r="J90" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>25</v>
@@ -7041,8 +7050,8 @@
       <c r="I92" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>24</v>
+      <c r="J92" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>25</v>
@@ -7254,8 +7263,8 @@
       <c r="I95" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="J95" s="2" t="s">
-        <v>25</v>
+      <c r="J95" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>25</v>
@@ -7307,20 +7316,20 @@
       <c r="C96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H96" s="1" t="s">
-        <v>24</v>
+      <c r="D96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>24</v>
@@ -7328,41 +7337,41 @@
       <c r="J96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="M96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>24</v>
+      <c r="K96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="O96" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R96" s="1" t="s">
-        <v>24</v>
+      <c r="P96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R96" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="S96" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U96" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V96" s="1" t="s">
-        <v>24</v>
+      <c r="T96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U96" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>25</v>
@@ -7378,14 +7387,14 @@
       <c r="C97" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>24</v>
+      <c r="D97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>25</v>
@@ -7393,8 +7402,8 @@
       <c r="H97" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I97" s="2" t="s">
-        <v>25</v>
+      <c r="I97" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>25</v>
@@ -7426,14 +7435,14 @@
       <c r="S97" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U97" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V97" s="1" t="s">
-        <v>24</v>
+      <c r="T97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U97" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>25</v>
@@ -7449,62 +7458,62 @@
       <c r="C98" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N98" s="2" t="s">
-        <v>25</v>
+      <c r="D98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="O98" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="R98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U98" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V98" s="2" t="s">
-        <v>25</v>
+      <c r="P98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U98" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V98" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>25</v>
@@ -7526,8 +7535,8 @@
       <c r="E99" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>25</v>
+      <c r="F99" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>25</v>
@@ -7565,17 +7574,17 @@
       <c r="R99" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V99" s="2" t="s">
-        <v>25</v>
+      <c r="S99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V99" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="W99" s="2" t="s">
         <v>25</v>
@@ -7591,8 +7600,8 @@
       <c r="C100" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>24</v>
+      <c r="D100" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>25</v>
@@ -7668,23 +7677,23 @@
       <c r="E101" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>24</v>
+      <c r="F101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>24</v>
+      <c r="I101" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K101" s="1" t="s">
-        <v>24</v>
+      <c r="K101" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>25</v>
@@ -7698,26 +7707,26 @@
       <c r="O101" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V101" s="1" t="s">
-        <v>24</v>
+      <c r="P101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U101" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W101" s="2" t="s">
         <v>25</v>
@@ -7736,8 +7745,8 @@
       <c r="D102" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E102" s="1" t="s">
-        <v>24</v>
+      <c r="E102" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>25</v>
@@ -7748,14 +7757,14 @@
       <c r="H102" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>24</v>
+      <c r="I102" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K102" s="1" t="s">
-        <v>24</v>
+      <c r="K102" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>25</v>
@@ -7769,28 +7778,241 @@
       <c r="O102" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="P102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="R102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="S102" s="1" t="s">
-        <v>24</v>
+      <c r="P102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="T102" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="U102" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="V102" s="1" t="s">
-        <v>24</v>
+      <c r="U102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="W102" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="3">
+        <v>126</v>
+      </c>
+      <c r="B103" t="s">
+        <v>126</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O103" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V103" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="3">
+        <v>127</v>
+      </c>
+      <c r="B104" t="s">
+        <v>127</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T104" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="U104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V104" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="3">
+        <v>128</v>
+      </c>
+      <c r="B105" t="s">
+        <v>128</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O105" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="R105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="S105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="V105" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="W105" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -7806,12 +8028,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -405,7 +405,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.37.0-SNAPSHOT</t>
+    <t>1.38.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -417,7 +417,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.39.0-SNAPSHOT</t>
+    <t>1.40.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -417,7 +417,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.40.0-SNAPSHOT</t>
+    <t>1.41.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2677" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="139">
   <si>
     <t>User Right</t>
   </si>
@@ -414,10 +414,22 @@
     <t>AGGREGATE_REPORT_EDIT</t>
   </si>
   <si>
+    <t>SEE_PERSONAL_DATA_IN_JURISDICTION</t>
+  </si>
+  <si>
+    <t>SEE_PERSONAL_DATA_OUTSIDE_JURISDICTION</t>
+  </si>
+  <si>
+    <t>SEE_SENSITIVE_DATA_IN_JURISDICTION</t>
+  </si>
+  <si>
+    <t>SEE_SENSITIVE_DATA_OUTSIDE_JURISDICTION</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.41.0-SNAPSHOT</t>
+    <t>1.42.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -545,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z107"/>
+  <dimension ref="A1:Z111"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -8814,6 +8826,314 @@
         <v>27</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="s" s="3">
+        <v>133</v>
+      </c>
+      <c r="B108" t="s">
+        <v>133</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y108" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="3">
+        <v>134</v>
+      </c>
+      <c r="B109" t="s">
+        <v>134</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y109" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="3">
+        <v>135</v>
+      </c>
+      <c r="B110" t="s">
+        <v>135</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V110" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y110" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="3">
+        <v>136</v>
+      </c>
+      <c r="B111" t="s">
+        <v>136</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y111" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -8826,12 +9146,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2777" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2877" uniqueCount="143">
   <si>
     <t>User Right</t>
   </si>
@@ -424,6 +424,18 @@
   </si>
   <si>
     <t>SEE_SENSITIVE_DATA_OUTSIDE_JURISDICTION</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_VIEW</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_EDIT</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_ARCHIVE</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_DELETE</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -557,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z111"/>
+  <dimension ref="A1:Z115"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -9134,6 +9146,314 @@
         <v>27</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="s" s="3">
+        <v>137</v>
+      </c>
+      <c r="B112" t="s">
+        <v>137</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U112" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="V112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y112" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="3">
+        <v>138</v>
+      </c>
+      <c r="B113" t="s">
+        <v>138</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y113" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="3">
+        <v>139</v>
+      </c>
+      <c r="B114" t="s">
+        <v>139</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D114" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y114" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="3">
+        <v>140</v>
+      </c>
+      <c r="B115" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y115" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -9146,12 +9466,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -63,7 +63,7 @@
     <t>National Observer</t>
   </si>
   <si>
-    <t>State Observer</t>
+    <t>Region Observer</t>
   </si>
   <si>
     <t>District Observer</t>
@@ -108,7 +108,7 @@
     <t>District</t>
   </si>
   <si>
-    <t>Health facility</t>
+    <t>Facility</t>
   </si>
   <si>
     <t>Community</t>
@@ -492,7 +492,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.44.0-SNAPSHOT</t>
+    <t>1.45.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2952" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="160">
   <si>
     <t>User Right</t>
   </si>
@@ -477,10 +477,22 @@
     <t>CAMPAIGN_DELETE</t>
   </si>
   <si>
+    <t>CAMPAIGN_FORM_DATA_VIEW</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_FORM_DATA_EDIT</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_FORM_DATA_ARCHIVE</t>
+  </si>
+  <si>
+    <t>CAMPAIGN_FORM_DATA_DELETE</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.43.0-SNAPSHOT</t>
+    <t>1.44.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -608,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z118"/>
+  <dimension ref="A1:Z122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -1685,14 +1697,14 @@
       <c r="O14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>37</v>
+      <c r="P14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>37</v>
@@ -2532,14 +2544,14 @@
       <c r="O25" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>37</v>
+      <c r="P25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S25" s="1" t="s">
         <v>37</v>
@@ -3841,14 +3853,14 @@
       <c r="O42" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>37</v>
+      <c r="P42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R42" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>37</v>
@@ -4380,14 +4392,14 @@
       <c r="O49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R49" s="1" t="s">
-        <v>37</v>
+      <c r="P49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R49" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>37</v>
@@ -5150,14 +5162,14 @@
       <c r="O59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>37</v>
+      <c r="P59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S59" s="1" t="s">
         <v>37</v>
@@ -6382,14 +6394,14 @@
       <c r="O75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>37</v>
+      <c r="P75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>37</v>
@@ -6921,14 +6933,14 @@
       <c r="O82" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P82" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q82" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R82" s="1" t="s">
-        <v>37</v>
+      <c r="P82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>37</v>
@@ -9000,14 +9012,14 @@
       <c r="O109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P109" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q109" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R109" s="1" t="s">
-        <v>37</v>
+      <c r="P109" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q109" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S109" s="1" t="s">
         <v>37</v>
@@ -9721,6 +9733,314 @@
         <v>38</v>
       </c>
       <c r="Y118" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="3">
+        <v>154</v>
+      </c>
+      <c r="B119" t="s">
+        <v>154</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y119" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="3">
+        <v>155</v>
+      </c>
+      <c r="B120" t="s">
+        <v>155</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U120" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X120" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y120" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="3">
+        <v>156</v>
+      </c>
+      <c r="B121" t="s">
+        <v>156</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y121" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="3">
+        <v>157</v>
+      </c>
+      <c r="B122" t="s">
+        <v>157</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y122" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -9736,12 +10056,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -492,7 +492,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.44.0-SNAPSHOT</t>
+    <t>1.46.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -492,7 +492,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.44.0-SNAPSHOT</t>
+    <t>1.45.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3127" uniqueCount="163">
   <si>
     <t>User Right</t>
   </si>
@@ -255,7 +255,7 @@
     <t>CONTACT_REASSIGN_CASE</t>
   </si>
   <si>
-    <t>CONTACT_CREATE_PIA_ACCOUNT</t>
+    <t>MANAGE_EXTERNAL_SYMPTOM_JOURNAL</t>
   </si>
   <si>
     <t>VISIT_CREATE</t>
@@ -288,6 +288,15 @@
     <t>TASK_DELETE</t>
   </si>
   <si>
+    <t>ACTION_CREATE</t>
+  </si>
+  <si>
+    <t>ACTION_DELETE</t>
+  </si>
+  <si>
+    <t>ACTION_EDIT</t>
+  </si>
+  <si>
     <t>EVENT_CREATE</t>
   </si>
   <si>
@@ -492,7 +501,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.45.0-SNAPSHOT</t>
+    <t>1.46.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -620,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z122"/>
+  <dimension ref="A1:Z125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -2073,8 +2082,8 @@
       <c r="L19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>38</v>
+      <c r="M19" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>37</v>
@@ -2227,8 +2236,8 @@
       <c r="L21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>38</v>
+      <c r="M21" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>37</v>
@@ -2304,8 +2313,8 @@
       <c r="L22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>38</v>
+      <c r="M22" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>38</v>
@@ -2689,8 +2698,8 @@
       <c r="L27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>38</v>
+      <c r="M27" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>37</v>
@@ -2766,8 +2775,8 @@
       <c r="L28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>38</v>
+      <c r="M28" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>37</v>
@@ -4972,35 +4981,35 @@
       <c r="C57" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>37</v>
+      <c r="D57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>38</v>
@@ -5008,23 +5017,23 @@
       <c r="O57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>37</v>
+      <c r="P57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U57" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>38</v>
@@ -5132,8 +5141,8 @@
       <c r="E59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>38</v>
+      <c r="F59" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>38</v>
@@ -5141,23 +5150,23 @@
       <c r="H59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>37</v>
+      <c r="I59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>37</v>
+      <c r="K59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>37</v>
+      <c r="M59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>38</v>
@@ -5171,17 +5180,17 @@
       <c r="R59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S59" s="1" t="s">
-        <v>37</v>
+      <c r="S59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V59" s="1" t="s">
-        <v>37</v>
+      <c r="U59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W59" s="2" t="s">
         <v>38</v>
@@ -5203,35 +5212,35 @@
       <c r="C60" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>38</v>
+      <c r="D60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>38</v>
@@ -5239,23 +5248,23 @@
       <c r="O60" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U60" s="2" t="s">
-        <v>38</v>
+      <c r="P60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V60" s="2" t="s">
         <v>38</v>
@@ -5283,11 +5292,11 @@
       <c r="D61" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>38</v>
+      <c r="E61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>38</v>
@@ -5307,8 +5316,8 @@
       <c r="L61" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M61" s="2" t="s">
-        <v>38</v>
+      <c r="M61" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>38</v>
@@ -5360,8 +5369,8 @@
       <c r="D62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>38</v>
+      <c r="E62" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>38</v>
@@ -5387,20 +5396,20 @@
       <c r="M62" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N62" s="2" t="s">
-        <v>38</v>
+      <c r="N62" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>37</v>
+      <c r="P62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>37</v>
@@ -5434,14 +5443,14 @@
       <c r="C63" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>37</v>
+      <c r="D63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>38</v>
@@ -5461,8 +5470,8 @@
       <c r="L63" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M63" s="1" t="s">
-        <v>37</v>
+      <c r="M63" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>38</v>
@@ -5514,11 +5523,11 @@
       <c r="D64" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>37</v>
+      <c r="E64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>38</v>
@@ -5538,8 +5547,8 @@
       <c r="L64" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>37</v>
+      <c r="M64" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>38</v>
@@ -5603,14 +5612,14 @@
       <c r="H65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>38</v>
+      <c r="I65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K65" s="2" t="s">
-        <v>38</v>
+      <c r="K65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>38</v>
@@ -5624,26 +5633,26 @@
       <c r="O65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>38</v>
+      <c r="P65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>38</v>
+      <c r="U65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>38</v>
@@ -5662,23 +5671,23 @@
       <c r="B66" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>38</v>
+      <c r="C66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>37</v>
+      <c r="G66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>38</v>
@@ -5692,8 +5701,8 @@
       <c r="L66" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M66" s="2" t="s">
-        <v>38</v>
+      <c r="M66" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>38</v>
@@ -5751,26 +5760,26 @@
       <c r="F67" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>37</v>
+      <c r="G67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>37</v>
+      <c r="K67" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M67" s="2" t="s">
-        <v>38</v>
+      <c r="M67" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>38</v>
@@ -5778,17 +5787,17 @@
       <c r="O67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>37</v>
+      <c r="P67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>38</v>
@@ -5819,8 +5828,8 @@
       <c r="C68" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>38</v>
+      <c r="D68" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>38</v>
@@ -5893,8 +5902,8 @@
       <c r="B69" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>37</v>
+      <c r="C69" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>38</v>
@@ -5902,14 +5911,14 @@
       <c r="E69" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>38</v>
+      <c r="F69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>38</v>
@@ -5973,29 +5982,29 @@
       <c r="C70" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>38</v>
+      <c r="D70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>38</v>
+      <c r="K70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>38</v>
@@ -6009,17 +6018,17 @@
       <c r="O70" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>38</v>
+      <c r="P70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>38</v>
@@ -6050,11 +6059,11 @@
       <c r="C71" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>37</v>
+      <c r="D71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>38</v>
@@ -6086,26 +6095,26 @@
       <c r="O71" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>37</v>
+      <c r="P71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V71" s="1" t="s">
-        <v>37</v>
+      <c r="U71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W71" s="2" t="s">
         <v>38</v>
@@ -6127,8 +6136,8 @@
       <c r="C72" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>37</v>
+      <c r="D72" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>38</v>
@@ -6201,14 +6210,14 @@
       <c r="B73" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>38</v>
+      <c r="C73" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>37</v>
+      <c r="E73" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>38</v>
@@ -6296,14 +6305,14 @@
       <c r="H74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>37</v>
+      <c r="I74" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>37</v>
+      <c r="K74" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>38</v>
@@ -6311,8 +6320,8 @@
       <c r="M74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N74" s="1" t="s">
-        <v>37</v>
+      <c r="N74" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>38</v>
@@ -6361,8 +6370,8 @@
       <c r="D75" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>37</v>
+      <c r="E75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>38</v>
@@ -6373,14 +6382,14 @@
       <c r="H75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>37</v>
+      <c r="I75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>37</v>
+      <c r="K75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>38</v>
@@ -6388,8 +6397,8 @@
       <c r="M75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N75" s="1" t="s">
-        <v>37</v>
+      <c r="N75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>38</v>
@@ -6403,17 +6412,17 @@
       <c r="R75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S75" s="1" t="s">
-        <v>37</v>
+      <c r="S75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U75" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V75" s="1" t="s">
-        <v>37</v>
+      <c r="U75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W75" s="2" t="s">
         <v>38</v>
@@ -6432,14 +6441,14 @@
       <c r="B76" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>38</v>
+      <c r="C76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>38</v>
@@ -6512,11 +6521,11 @@
       <c r="C77" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>38</v>
+      <c r="D77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>38</v>
@@ -6527,14 +6536,14 @@
       <c r="H77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>38</v>
+      <c r="I77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>38</v>
+      <c r="K77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>38</v>
@@ -6542,32 +6551,32 @@
       <c r="M77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N77" s="2" t="s">
-        <v>38</v>
+      <c r="N77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>38</v>
+      <c r="P77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>38</v>
+      <c r="U77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W77" s="2" t="s">
         <v>38</v>
@@ -6589,11 +6598,11 @@
       <c r="C78" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>38</v>
+      <c r="D78" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>38</v>
@@ -6604,14 +6613,14 @@
       <c r="H78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>38</v>
+      <c r="I78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K78" s="2" t="s">
-        <v>38</v>
+      <c r="K78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>38</v>
@@ -6619,8 +6628,8 @@
       <c r="M78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N78" s="2" t="s">
-        <v>38</v>
+      <c r="N78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>38</v>
@@ -6634,17 +6643,17 @@
       <c r="R78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S78" s="2" t="s">
-        <v>38</v>
+      <c r="S78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U78" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>38</v>
+      <c r="U78" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W78" s="2" t="s">
         <v>38</v>
@@ -6666,8 +6675,8 @@
       <c r="C79" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>38</v>
+      <c r="D79" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>38</v>
@@ -6743,11 +6752,11 @@
       <c r="C80" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>37</v>
+      <c r="D80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>38</v>
@@ -6779,26 +6788,26 @@
       <c r="O80" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>37</v>
+      <c r="P80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V80" s="1" t="s">
-        <v>37</v>
+      <c r="U80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>38</v>
@@ -6820,8 +6829,8 @@
       <c r="C81" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>37</v>
+      <c r="D81" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>38</v>
@@ -6856,8 +6865,8 @@
       <c r="O81" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P81" s="1" t="s">
-        <v>37</v>
+      <c r="P81" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="Q81" s="2" t="s">
         <v>38</v>
@@ -6897,11 +6906,11 @@
       <c r="C82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>37</v>
+      <c r="D82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>38</v>
@@ -6942,17 +6951,17 @@
       <c r="R82" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S82" s="1" t="s">
-        <v>37</v>
+      <c r="S82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T82" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U82" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V82" s="1" t="s">
-        <v>37</v>
+      <c r="U82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W82" s="2" t="s">
         <v>38</v>
@@ -6974,11 +6983,11 @@
       <c r="C83" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>38</v>
+      <c r="D83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>38</v>
@@ -7010,26 +7019,26 @@
       <c r="O83" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S83" s="2" t="s">
-        <v>38</v>
+      <c r="P83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S83" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T83" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>38</v>
+      <c r="U83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V83" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W83" s="2" t="s">
         <v>38</v>
@@ -7087,8 +7096,8 @@
       <c r="O84" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P84" s="2" t="s">
-        <v>38</v>
+      <c r="P84" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q84" s="2" t="s">
         <v>38</v>
@@ -7128,11 +7137,11 @@
       <c r="C85" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>38</v>
+      <c r="D85" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>38</v>
@@ -7173,17 +7182,17 @@
       <c r="R85" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S85" s="2" t="s">
-        <v>38</v>
+      <c r="S85" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T85" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U85" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V85" s="2" t="s">
-        <v>38</v>
+      <c r="U85" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V85" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W85" s="2" t="s">
         <v>38</v>
@@ -7205,14 +7214,14 @@
       <c r="C86" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>37</v>
+      <c r="D86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>38</v>
@@ -7220,47 +7229,47 @@
       <c r="H86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N86" s="1" t="s">
-        <v>37</v>
+      <c r="I86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>37</v>
+      <c r="P86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V86" s="1" t="s">
-        <v>37</v>
+      <c r="U86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W86" s="2" t="s">
         <v>38</v>
@@ -7285,11 +7294,11 @@
       <c r="D87" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>37</v>
+      <c r="E87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>38</v>
@@ -7297,11 +7306,11 @@
       <c r="H87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>37</v>
+      <c r="I87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>38</v>
@@ -7309,35 +7318,35 @@
       <c r="L87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>37</v>
+      <c r="M87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S87" s="1" t="s">
-        <v>37</v>
+      <c r="P87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V87" s="1" t="s">
-        <v>37</v>
+      <c r="U87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>38</v>
@@ -7359,8 +7368,8 @@
       <c r="C88" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>37</v>
+      <c r="D88" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>38</v>
@@ -7380,11 +7389,11 @@
       <c r="J88" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>37</v>
+      <c r="K88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>38</v>
@@ -7395,14 +7404,14 @@
       <c r="O88" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R88" s="1" t="s">
-        <v>37</v>
+      <c r="P88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S88" s="2" t="s">
         <v>38</v>
@@ -7439,11 +7448,11 @@
       <c r="D89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>38</v>
+      <c r="E89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>38</v>
@@ -7451,23 +7460,23 @@
       <c r="H89" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>38</v>
+      <c r="I89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>38</v>
+      <c r="L89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>38</v>
@@ -7481,17 +7490,17 @@
       <c r="R89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S89" s="2" t="s">
-        <v>38</v>
+      <c r="S89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T89" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V89" s="2" t="s">
-        <v>38</v>
+      <c r="U89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W89" s="2" t="s">
         <v>38</v>
@@ -7513,14 +7522,14 @@
       <c r="C90" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>38</v>
+      <c r="D90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>38</v>
@@ -7540,8 +7549,8 @@
       <c r="L90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M90" s="2" t="s">
-        <v>38</v>
+      <c r="M90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N90" s="1" t="s">
         <v>37</v>
@@ -7549,14 +7558,14 @@
       <c r="O90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>38</v>
+      <c r="P90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>37</v>
@@ -7564,11 +7573,11 @@
       <c r="T90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V90" s="2" t="s">
-        <v>38</v>
+      <c r="U90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>38</v>
@@ -7590,8 +7599,8 @@
       <c r="C91" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>38</v>
+      <c r="D91" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>38</v>
@@ -7605,17 +7614,17 @@
       <c r="H91" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>38</v>
+      <c r="I91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>38</v>
@@ -7626,17 +7635,17 @@
       <c r="O91" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>37</v>
+      <c r="P91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T91" s="2" t="s">
         <v>38</v>
@@ -7667,8 +7676,8 @@
       <c r="C92" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>38</v>
+      <c r="D92" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>38</v>
@@ -7682,14 +7691,14 @@
       <c r="H92" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>38</v>
+      <c r="I92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>38</v>
@@ -7703,17 +7712,17 @@
       <c r="O92" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>37</v>
+      <c r="P92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T92" s="2" t="s">
         <v>38</v>
@@ -7774,8 +7783,8 @@
       <c r="M93" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N93" s="2" t="s">
-        <v>38</v>
+      <c r="N93" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>38</v>
@@ -7839,8 +7848,8 @@
       <c r="I94" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J94" s="2" t="s">
-        <v>38</v>
+      <c r="J94" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>38</v>
@@ -8301,8 +8310,8 @@
       <c r="I100" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J100" s="1" t="s">
-        <v>37</v>
+      <c r="J100" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>38</v>
@@ -8455,8 +8464,8 @@
       <c r="I102" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J102" s="2" t="s">
-        <v>38</v>
+      <c r="J102" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>38</v>
@@ -8514,20 +8523,20 @@
       <c r="C103" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>37</v>
+      <c r="D103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>37</v>
@@ -8535,41 +8544,41 @@
       <c r="J103" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N103" s="1" t="s">
-        <v>37</v>
+      <c r="K103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O103" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R103" s="1" t="s">
-        <v>37</v>
+      <c r="P103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S103" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V103" s="1" t="s">
-        <v>37</v>
+      <c r="T103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>38</v>
@@ -8591,14 +8600,14 @@
       <c r="C104" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>37</v>
+      <c r="D104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>38</v>
@@ -8606,11 +8615,11 @@
       <c r="H104" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>38</v>
+      <c r="I104" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>38</v>
@@ -8639,14 +8648,14 @@
       <c r="S104" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V104" s="1" t="s">
-        <v>37</v>
+      <c r="T104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W104" s="2" t="s">
         <v>38</v>
@@ -8683,8 +8692,8 @@
       <c r="H105" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>38</v>
+      <c r="I105" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>38</v>
@@ -8713,8 +8722,8 @@
       <c r="R105" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S105" s="2" t="s">
-        <v>38</v>
+      <c r="S105" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T105" s="2" t="s">
         <v>38</v>
@@ -8751,56 +8760,56 @@
       <c r="E106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N106" s="2" t="s">
-        <v>38</v>
+      <c r="F106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V106" s="2" t="s">
-        <v>38</v>
+      <c r="P106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V106" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>38</v>
@@ -8825,11 +8834,11 @@
       <c r="D107" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>38</v>
+      <c r="E107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>38</v>
@@ -8867,17 +8876,17 @@
       <c r="R107" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V107" s="2" t="s">
-        <v>38</v>
+      <c r="S107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V107" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W107" s="2" t="s">
         <v>38</v>
@@ -8899,29 +8908,29 @@
       <c r="C108" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>37</v>
+      <c r="D108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>37</v>
+      <c r="I108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K108" s="1" t="s">
-        <v>37</v>
+      <c r="K108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>38</v>
@@ -8935,26 +8944,26 @@
       <c r="O108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V108" s="1" t="s">
-        <v>37</v>
+      <c r="P108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W108" s="2" t="s">
         <v>38</v>
@@ -8991,14 +9000,14 @@
       <c r="H109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I109" s="1" t="s">
-        <v>37</v>
+      <c r="I109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K109" s="1" t="s">
-        <v>37</v>
+      <c r="K109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>38</v>
@@ -9021,17 +9030,17 @@
       <c r="R109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S109" s="1" t="s">
-        <v>37</v>
+      <c r="S109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U109" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V109" s="1" t="s">
-        <v>37</v>
+      <c r="U109" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W109" s="2" t="s">
         <v>38</v>
@@ -9056,26 +9065,26 @@
       <c r="D110" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>37</v>
+      <c r="E110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>37</v>
+      <c r="G110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I110" s="1" t="s">
-        <v>37</v>
+      <c r="I110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K110" s="1" t="s">
-        <v>37</v>
+      <c r="K110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>38</v>
@@ -9089,26 +9098,26 @@
       <c r="O110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V110" s="1" t="s">
-        <v>37</v>
+      <c r="P110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W110" s="2" t="s">
         <v>38</v>
@@ -9127,8 +9136,8 @@
       <c r="B111" t="s">
         <v>146</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>38</v>
+      <c r="C111" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>37</v>
@@ -9142,23 +9151,23 @@
       <c r="G111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>37</v>
+      <c r="H111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J111" s="1" t="s">
-        <v>37</v>
+      <c r="J111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>37</v>
+      <c r="L111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N111" s="2" t="s">
         <v>38</v>
@@ -9166,17 +9175,17 @@
       <c r="O111" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S111" s="2" t="s">
-        <v>38</v>
+      <c r="P111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S111" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T111" s="1" t="s">
         <v>37</v>
@@ -9204,14 +9213,14 @@
       <c r="B112" t="s">
         <v>147</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>38</v>
+      <c r="C112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>38</v>
@@ -9222,14 +9231,14 @@
       <c r="H112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I112" s="2" t="s">
-        <v>38</v>
+      <c r="I112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K112" s="2" t="s">
-        <v>38</v>
+      <c r="K112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>38</v>
@@ -9252,17 +9261,17 @@
       <c r="R112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S112" s="2" t="s">
-        <v>38</v>
+      <c r="S112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V112" s="2" t="s">
-        <v>38</v>
+      <c r="U112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>38</v>
@@ -9281,8 +9290,8 @@
       <c r="B113" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>38</v>
+      <c r="C113" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>37</v>
@@ -9290,29 +9299,29 @@
       <c r="E113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>37</v>
+      <c r="F113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H113" s="1" t="s">
-        <v>37</v>
+      <c r="H113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J113" s="1" t="s">
-        <v>37</v>
+      <c r="J113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>37</v>
+      <c r="L113" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>38</v>
@@ -9320,17 +9329,17 @@
       <c r="O113" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S113" s="2" t="s">
-        <v>38</v>
+      <c r="P113" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R113" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S113" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T113" s="1" t="s">
         <v>37</v>
@@ -9361,35 +9370,35 @@
       <c r="C114" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M114" s="2" t="s">
-        <v>38</v>
+      <c r="D114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>38</v>
@@ -9409,14 +9418,14 @@
       <c r="S114" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V114" s="2" t="s">
-        <v>38</v>
+      <c r="T114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V114" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>38</v>
@@ -9435,17 +9444,17 @@
       <c r="B115" t="s">
         <v>150</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>37</v>
+      <c r="C115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>38</v>
@@ -9453,20 +9462,20 @@
       <c r="H115" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>37</v>
+      <c r="I115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>38</v>
@@ -9489,8 +9498,8 @@
       <c r="T115" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U115" s="1" t="s">
-        <v>37</v>
+      <c r="U115" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V115" s="2" t="s">
         <v>38</v>
@@ -9512,38 +9521,38 @@
       <c r="B116" t="s">
         <v>151</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>37</v>
+      <c r="C116" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>38</v>
+      <c r="E116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>38</v>
@@ -9563,14 +9572,14 @@
       <c r="S116" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V116" s="2" t="s">
-        <v>38</v>
+      <c r="T116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V116" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W116" s="2" t="s">
         <v>38</v>
@@ -9589,11 +9598,11 @@
       <c r="B117" t="s">
         <v>152</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>37</v>
+      <c r="C117" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>38</v>
@@ -9669,14 +9678,14 @@
       <c r="C118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>38</v>
+      <c r="D118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>38</v>
@@ -9684,20 +9693,20 @@
       <c r="H118" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M118" s="2" t="s">
-        <v>38</v>
+      <c r="I118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>38</v>
@@ -9720,8 +9729,8 @@
       <c r="T118" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U118" s="2" t="s">
-        <v>38</v>
+      <c r="U118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V118" s="2" t="s">
         <v>38</v>
@@ -9749,11 +9758,11 @@
       <c r="D119" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>37</v>
+      <c r="E119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>38</v>
@@ -9761,20 +9770,20 @@
       <c r="H119" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>37</v>
+      <c r="I119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>38</v>
@@ -9797,8 +9806,8 @@
       <c r="T119" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U119" s="1" t="s">
-        <v>37</v>
+      <c r="U119" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V119" s="2" t="s">
         <v>38</v>
@@ -9826,8 +9835,8 @@
       <c r="D120" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>37</v>
+      <c r="E120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>38</v>
@@ -9838,14 +9847,14 @@
       <c r="H120" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>37</v>
+      <c r="I120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K120" s="1" t="s">
-        <v>37</v>
+      <c r="K120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>38</v>
@@ -9874,8 +9883,8 @@
       <c r="T120" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U120" s="1" t="s">
-        <v>37</v>
+      <c r="U120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V120" s="2" t="s">
         <v>38</v>
@@ -9900,8 +9909,8 @@
       <c r="C121" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>37</v>
+      <c r="D121" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>38</v>
@@ -9977,14 +9986,14 @@
       <c r="C122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>38</v>
+      <c r="D122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>38</v>
@@ -9992,20 +10001,20 @@
       <c r="H122" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>38</v>
+      <c r="I122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>38</v>
@@ -10028,8 +10037,8 @@
       <c r="T122" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U122" s="2" t="s">
-        <v>38</v>
+      <c r="U122" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V122" s="2" t="s">
         <v>38</v>
@@ -10041,6 +10050,237 @@
         <v>38</v>
       </c>
       <c r="Y122" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="3">
+        <v>158</v>
+      </c>
+      <c r="B123" t="s">
+        <v>158</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y123" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="3">
+        <v>159</v>
+      </c>
+      <c r="B124" t="s">
+        <v>159</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y124" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="3">
+        <v>160</v>
+      </c>
+      <c r="B125" t="s">
+        <v>160</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y125" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -10056,12 +10296,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3052" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3127" uniqueCount="163">
   <si>
     <t>User Right</t>
   </si>
@@ -63,7 +63,7 @@
     <t>National Observer</t>
   </si>
   <si>
-    <t>State Observer</t>
+    <t>Region Observer</t>
   </si>
   <si>
     <t>District Observer</t>
@@ -108,7 +108,7 @@
     <t>District</t>
   </si>
   <si>
-    <t>Health facility</t>
+    <t>Facility</t>
   </si>
   <si>
     <t>Community</t>
@@ -255,7 +255,7 @@
     <t>CONTACT_REASSIGN_CASE</t>
   </si>
   <si>
-    <t>CONTACT_CREATE_PIA_ACCOUNT</t>
+    <t>MANAGE_EXTERNAL_SYMPTOM_JOURNAL</t>
   </si>
   <si>
     <t>VISIT_CREATE</t>
@@ -288,6 +288,15 @@
     <t>TASK_DELETE</t>
   </si>
   <si>
+    <t>ACTION_CREATE</t>
+  </si>
+  <si>
+    <t>ACTION_DELETE</t>
+  </si>
+  <si>
+    <t>ACTION_EDIT</t>
+  </si>
+  <si>
     <t>EVENT_CREATE</t>
   </si>
   <si>
@@ -492,7 +501,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.45.0-SNAPSHOT</t>
+    <t>1.46.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -620,7 +629,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z122"/>
+  <dimension ref="A1:Z125"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -2073,8 +2082,8 @@
       <c r="L19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>38</v>
+      <c r="M19" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N19" s="1" t="s">
         <v>37</v>
@@ -2227,8 +2236,8 @@
       <c r="L21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>38</v>
+      <c r="M21" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N21" s="1" t="s">
         <v>37</v>
@@ -2304,8 +2313,8 @@
       <c r="L22" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>38</v>
+      <c r="M22" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>38</v>
@@ -2689,8 +2698,8 @@
       <c r="L27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>38</v>
+      <c r="M27" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N27" s="1" t="s">
         <v>37</v>
@@ -2766,8 +2775,8 @@
       <c r="L28" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>38</v>
+      <c r="M28" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>37</v>
@@ -4972,35 +4981,35 @@
       <c r="C57" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>37</v>
+      <c r="D57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>38</v>
@@ -5008,23 +5017,23 @@
       <c r="O57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U57" s="1" t="s">
-        <v>37</v>
+      <c r="P57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U57" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>38</v>
@@ -5132,8 +5141,8 @@
       <c r="E59" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>38</v>
+      <c r="F59" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>38</v>
@@ -5141,23 +5150,23 @@
       <c r="H59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>37</v>
+      <c r="I59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>37</v>
+      <c r="K59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M59" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>37</v>
+      <c r="M59" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>38</v>
@@ -5171,17 +5180,17 @@
       <c r="R59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S59" s="1" t="s">
-        <v>37</v>
+      <c r="S59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U59" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V59" s="1" t="s">
-        <v>37</v>
+      <c r="U59" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W59" s="2" t="s">
         <v>38</v>
@@ -5203,35 +5212,35 @@
       <c r="C60" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>38</v>
+      <c r="D60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>38</v>
@@ -5239,23 +5248,23 @@
       <c r="O60" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U60" s="2" t="s">
-        <v>38</v>
+      <c r="P60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U60" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V60" s="2" t="s">
         <v>38</v>
@@ -5283,11 +5292,11 @@
       <c r="D61" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>38</v>
+      <c r="E61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>38</v>
@@ -5307,8 +5316,8 @@
       <c r="L61" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M61" s="2" t="s">
-        <v>38</v>
+      <c r="M61" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>38</v>
@@ -5360,8 +5369,8 @@
       <c r="D62" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>38</v>
+      <c r="E62" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>38</v>
@@ -5387,20 +5396,20 @@
       <c r="M62" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N62" s="2" t="s">
-        <v>38</v>
+      <c r="N62" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>37</v>
+      <c r="P62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S62" s="1" t="s">
         <v>37</v>
@@ -5434,14 +5443,14 @@
       <c r="C63" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>37</v>
+      <c r="D63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>38</v>
@@ -5461,8 +5470,8 @@
       <c r="L63" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M63" s="1" t="s">
-        <v>37</v>
+      <c r="M63" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>38</v>
@@ -5514,11 +5523,11 @@
       <c r="D64" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E64" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>37</v>
+      <c r="E64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>38</v>
@@ -5538,8 +5547,8 @@
       <c r="L64" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>37</v>
+      <c r="M64" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>38</v>
@@ -5603,14 +5612,14 @@
       <c r="H65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>38</v>
+      <c r="I65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K65" s="2" t="s">
-        <v>38</v>
+      <c r="K65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>38</v>
@@ -5624,26 +5633,26 @@
       <c r="O65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>38</v>
+      <c r="P65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T65" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U65" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>38</v>
+      <c r="U65" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W65" s="2" t="s">
         <v>38</v>
@@ -5662,23 +5671,23 @@
       <c r="B66" t="s">
         <v>101</v>
       </c>
-      <c r="C66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>38</v>
+      <c r="C66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G66" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>37</v>
+      <c r="G66" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>38</v>
@@ -5692,8 +5701,8 @@
       <c r="L66" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M66" s="2" t="s">
-        <v>38</v>
+      <c r="M66" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>38</v>
@@ -5751,26 +5760,26 @@
       <c r="F67" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>37</v>
+      <c r="G67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>37</v>
+      <c r="K67" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M67" s="2" t="s">
-        <v>38</v>
+      <c r="M67" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>38</v>
@@ -5778,17 +5787,17 @@
       <c r="O67" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>37</v>
+      <c r="P67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T67" s="2" t="s">
         <v>38</v>
@@ -5819,8 +5828,8 @@
       <c r="C68" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>38</v>
+      <c r="D68" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>38</v>
@@ -5893,8 +5902,8 @@
       <c r="B69" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>37</v>
+      <c r="C69" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>38</v>
@@ -5902,14 +5911,14 @@
       <c r="E69" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>38</v>
+      <c r="F69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>38</v>
@@ -5973,29 +5982,29 @@
       <c r="C70" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>38</v>
+      <c r="D70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>38</v>
+      <c r="K70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>38</v>
@@ -6009,17 +6018,17 @@
       <c r="O70" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R70" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>38</v>
+      <c r="P70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T70" s="2" t="s">
         <v>38</v>
@@ -6050,11 +6059,11 @@
       <c r="C71" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>37</v>
+      <c r="D71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>38</v>
@@ -6086,26 +6095,26 @@
       <c r="O71" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>37</v>
+      <c r="P71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T71" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U71" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V71" s="1" t="s">
-        <v>37</v>
+      <c r="U71" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W71" s="2" t="s">
         <v>38</v>
@@ -6127,8 +6136,8 @@
       <c r="C72" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>37</v>
+      <c r="D72" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>38</v>
@@ -6201,14 +6210,14 @@
       <c r="B73" t="s">
         <v>108</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>38</v>
+      <c r="C73" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>37</v>
+      <c r="E73" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>38</v>
@@ -6296,14 +6305,14 @@
       <c r="H74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>37</v>
+      <c r="I74" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>37</v>
+      <c r="K74" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>38</v>
@@ -6311,8 +6320,8 @@
       <c r="M74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N74" s="1" t="s">
-        <v>37</v>
+      <c r="N74" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>38</v>
@@ -6361,8 +6370,8 @@
       <c r="D75" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>37</v>
+      <c r="E75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>38</v>
@@ -6373,14 +6382,14 @@
       <c r="H75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>37</v>
+      <c r="I75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>37</v>
+      <c r="K75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>38</v>
@@ -6388,8 +6397,8 @@
       <c r="M75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N75" s="1" t="s">
-        <v>37</v>
+      <c r="N75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>38</v>
@@ -6403,17 +6412,17 @@
       <c r="R75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S75" s="1" t="s">
-        <v>37</v>
+      <c r="S75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T75" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U75" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V75" s="1" t="s">
-        <v>37</v>
+      <c r="U75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W75" s="2" t="s">
         <v>38</v>
@@ -6432,14 +6441,14 @@
       <c r="B76" t="s">
         <v>111</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>38</v>
+      <c r="C76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>38</v>
@@ -6512,11 +6521,11 @@
       <c r="C77" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>38</v>
+      <c r="D77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>38</v>
@@ -6527,14 +6536,14 @@
       <c r="H77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I77" s="2" t="s">
-        <v>38</v>
+      <c r="I77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K77" s="2" t="s">
-        <v>38</v>
+      <c r="K77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>38</v>
@@ -6542,32 +6551,32 @@
       <c r="M77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N77" s="2" t="s">
-        <v>38</v>
+      <c r="N77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>38</v>
+      <c r="P77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T77" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U77" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>38</v>
+      <c r="U77" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V77" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W77" s="2" t="s">
         <v>38</v>
@@ -6589,11 +6598,11 @@
       <c r="C78" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D78" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>38</v>
+      <c r="D78" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>38</v>
@@ -6604,14 +6613,14 @@
       <c r="H78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I78" s="2" t="s">
-        <v>38</v>
+      <c r="I78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K78" s="2" t="s">
-        <v>38</v>
+      <c r="K78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>38</v>
@@ -6619,8 +6628,8 @@
       <c r="M78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N78" s="2" t="s">
-        <v>38</v>
+      <c r="N78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>38</v>
@@ -6634,17 +6643,17 @@
       <c r="R78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S78" s="2" t="s">
-        <v>38</v>
+      <c r="S78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U78" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>38</v>
+      <c r="U78" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V78" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W78" s="2" t="s">
         <v>38</v>
@@ -6666,8 +6675,8 @@
       <c r="C79" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>38</v>
+      <c r="D79" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>38</v>
@@ -6743,11 +6752,11 @@
       <c r="C80" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>37</v>
+      <c r="D80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>38</v>
@@ -6779,26 +6788,26 @@
       <c r="O80" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>37</v>
+      <c r="P80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U80" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V80" s="1" t="s">
-        <v>37</v>
+      <c r="U80" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W80" s="2" t="s">
         <v>38</v>
@@ -6820,8 +6829,8 @@
       <c r="C81" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>37</v>
+      <c r="D81" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>38</v>
@@ -6856,8 +6865,8 @@
       <c r="O81" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P81" s="1" t="s">
-        <v>37</v>
+      <c r="P81" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="Q81" s="2" t="s">
         <v>38</v>
@@ -6897,11 +6906,11 @@
       <c r="C82" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>37</v>
+      <c r="D82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>38</v>
@@ -6942,17 +6951,17 @@
       <c r="R82" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S82" s="1" t="s">
-        <v>37</v>
+      <c r="S82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T82" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U82" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V82" s="1" t="s">
-        <v>37</v>
+      <c r="U82" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W82" s="2" t="s">
         <v>38</v>
@@ -6974,11 +6983,11 @@
       <c r="C83" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>38</v>
+      <c r="D83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>38</v>
@@ -7010,26 +7019,26 @@
       <c r="O83" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S83" s="2" t="s">
-        <v>38</v>
+      <c r="P83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S83" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T83" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U83" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>38</v>
+      <c r="U83" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V83" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W83" s="2" t="s">
         <v>38</v>
@@ -7087,8 +7096,8 @@
       <c r="O84" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P84" s="2" t="s">
-        <v>38</v>
+      <c r="P84" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="Q84" s="2" t="s">
         <v>38</v>
@@ -7128,11 +7137,11 @@
       <c r="C85" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>38</v>
+      <c r="D85" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>38</v>
@@ -7173,17 +7182,17 @@
       <c r="R85" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S85" s="2" t="s">
-        <v>38</v>
+      <c r="S85" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T85" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U85" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V85" s="2" t="s">
-        <v>38</v>
+      <c r="U85" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V85" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W85" s="2" t="s">
         <v>38</v>
@@ -7205,14 +7214,14 @@
       <c r="C86" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>37</v>
+      <c r="D86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>38</v>
@@ -7220,47 +7229,47 @@
       <c r="H86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N86" s="1" t="s">
-        <v>37</v>
+      <c r="I86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>37</v>
+      <c r="P86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U86" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V86" s="1" t="s">
-        <v>37</v>
+      <c r="U86" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W86" s="2" t="s">
         <v>38</v>
@@ -7285,11 +7294,11 @@
       <c r="D87" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>37</v>
+      <c r="E87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>38</v>
@@ -7297,11 +7306,11 @@
       <c r="H87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J87" s="1" t="s">
-        <v>37</v>
+      <c r="I87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>38</v>
@@ -7309,35 +7318,35 @@
       <c r="L87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>37</v>
+      <c r="M87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S87" s="1" t="s">
-        <v>37</v>
+      <c r="P87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T87" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U87" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V87" s="1" t="s">
-        <v>37</v>
+      <c r="U87" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W87" s="2" t="s">
         <v>38</v>
@@ -7359,8 +7368,8 @@
       <c r="C88" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>37</v>
+      <c r="D88" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>38</v>
@@ -7380,11 +7389,11 @@
       <c r="J88" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L88" s="1" t="s">
-        <v>37</v>
+      <c r="K88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="M88" s="2" t="s">
         <v>38</v>
@@ -7395,14 +7404,14 @@
       <c r="O88" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q88" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R88" s="1" t="s">
-        <v>37</v>
+      <c r="P88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R88" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S88" s="2" t="s">
         <v>38</v>
@@ -7439,11 +7448,11 @@
       <c r="D89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>38</v>
+      <c r="E89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>38</v>
@@ -7451,23 +7460,23 @@
       <c r="H89" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>38</v>
+      <c r="I89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>38</v>
+      <c r="L89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O89" s="2" t="s">
         <v>38</v>
@@ -7481,17 +7490,17 @@
       <c r="R89" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="S89" s="2" t="s">
-        <v>38</v>
+      <c r="S89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T89" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U89" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V89" s="2" t="s">
-        <v>38</v>
+      <c r="U89" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V89" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W89" s="2" t="s">
         <v>38</v>
@@ -7513,14 +7522,14 @@
       <c r="C90" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>38</v>
+      <c r="D90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>38</v>
@@ -7540,8 +7549,8 @@
       <c r="L90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="M90" s="2" t="s">
-        <v>38</v>
+      <c r="M90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N90" s="1" t="s">
         <v>37</v>
@@ -7549,14 +7558,14 @@
       <c r="O90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R90" s="2" t="s">
-        <v>38</v>
+      <c r="P90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>37</v>
@@ -7564,11 +7573,11 @@
       <c r="T90" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U90" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V90" s="2" t="s">
-        <v>38</v>
+      <c r="U90" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V90" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W90" s="2" t="s">
         <v>38</v>
@@ -7590,8 +7599,8 @@
       <c r="C91" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>38</v>
+      <c r="D91" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>38</v>
@@ -7605,17 +7614,17 @@
       <c r="H91" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J91" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L91" s="2" t="s">
-        <v>38</v>
+      <c r="I91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L91" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>38</v>
@@ -7626,17 +7635,17 @@
       <c r="O91" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R91" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>37</v>
+      <c r="P91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T91" s="2" t="s">
         <v>38</v>
@@ -7667,8 +7676,8 @@
       <c r="C92" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>38</v>
+      <c r="D92" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>38</v>
@@ -7682,14 +7691,14 @@
       <c r="H92" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J92" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K92" s="2" t="s">
-        <v>38</v>
+      <c r="I92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>38</v>
@@ -7703,17 +7712,17 @@
       <c r="O92" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R92" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>37</v>
+      <c r="P92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T92" s="2" t="s">
         <v>38</v>
@@ -7774,8 +7783,8 @@
       <c r="M93" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N93" s="2" t="s">
-        <v>38</v>
+      <c r="N93" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>38</v>
@@ -7839,8 +7848,8 @@
       <c r="I94" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J94" s="2" t="s">
-        <v>38</v>
+      <c r="J94" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>38</v>
@@ -8301,8 +8310,8 @@
       <c r="I100" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J100" s="1" t="s">
-        <v>37</v>
+      <c r="J100" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>38</v>
@@ -8455,8 +8464,8 @@
       <c r="I102" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J102" s="2" t="s">
-        <v>38</v>
+      <c r="J102" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>38</v>
@@ -8514,20 +8523,20 @@
       <c r="C103" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H103" s="1" t="s">
-        <v>37</v>
+      <c r="D103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>37</v>
@@ -8535,41 +8544,41 @@
       <c r="J103" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N103" s="1" t="s">
-        <v>37</v>
+      <c r="K103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O103" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R103" s="1" t="s">
-        <v>37</v>
+      <c r="P103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S103" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U103" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V103" s="1" t="s">
-        <v>37</v>
+      <c r="T103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U103" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V103" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W103" s="2" t="s">
         <v>38</v>
@@ -8591,14 +8600,14 @@
       <c r="C104" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>37</v>
+      <c r="D104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>38</v>
@@ -8606,11 +8615,11 @@
       <c r="H104" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I104" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>38</v>
+      <c r="I104" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>38</v>
@@ -8639,14 +8648,14 @@
       <c r="S104" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U104" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V104" s="1" t="s">
-        <v>37</v>
+      <c r="T104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U104" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W104" s="2" t="s">
         <v>38</v>
@@ -8683,8 +8692,8 @@
       <c r="H105" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>38</v>
+      <c r="I105" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>38</v>
@@ -8713,8 +8722,8 @@
       <c r="R105" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S105" s="2" t="s">
-        <v>38</v>
+      <c r="S105" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T105" s="2" t="s">
         <v>38</v>
@@ -8751,56 +8760,56 @@
       <c r="E106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N106" s="2" t="s">
-        <v>38</v>
+      <c r="F106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U106" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V106" s="2" t="s">
-        <v>38</v>
+      <c r="P106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V106" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>38</v>
@@ -8825,11 +8834,11 @@
       <c r="D107" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>38</v>
+      <c r="E107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G107" s="2" t="s">
         <v>38</v>
@@ -8867,17 +8876,17 @@
       <c r="R107" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V107" s="2" t="s">
-        <v>38</v>
+      <c r="S107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V107" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W107" s="2" t="s">
         <v>38</v>
@@ -8899,29 +8908,29 @@
       <c r="C108" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>37</v>
+      <c r="D108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>37</v>
+      <c r="I108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K108" s="1" t="s">
-        <v>37</v>
+      <c r="K108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>38</v>
@@ -8935,26 +8944,26 @@
       <c r="O108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U108" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V108" s="1" t="s">
-        <v>37</v>
+      <c r="P108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U108" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V108" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W108" s="2" t="s">
         <v>38</v>
@@ -8991,14 +9000,14 @@
       <c r="H109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I109" s="1" t="s">
-        <v>37</v>
+      <c r="I109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K109" s="1" t="s">
-        <v>37</v>
+      <c r="K109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>38</v>
@@ -9021,17 +9030,17 @@
       <c r="R109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S109" s="1" t="s">
-        <v>37</v>
+      <c r="S109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U109" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V109" s="1" t="s">
-        <v>37</v>
+      <c r="U109" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W109" s="2" t="s">
         <v>38</v>
@@ -9056,26 +9065,26 @@
       <c r="D110" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E110" s="1" t="s">
-        <v>37</v>
+      <c r="E110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G110" s="1" t="s">
-        <v>37</v>
+      <c r="G110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I110" s="1" t="s">
-        <v>37</v>
+      <c r="I110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K110" s="1" t="s">
-        <v>37</v>
+      <c r="K110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>38</v>
@@ -9089,26 +9098,26 @@
       <c r="O110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U110" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V110" s="1" t="s">
-        <v>37</v>
+      <c r="P110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U110" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W110" s="2" t="s">
         <v>38</v>
@@ -9127,8 +9136,8 @@
       <c r="B111" t="s">
         <v>146</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>38</v>
+      <c r="C111" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>37</v>
@@ -9142,23 +9151,23 @@
       <c r="G111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>37</v>
+      <c r="H111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J111" s="1" t="s">
-        <v>37</v>
+      <c r="J111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>37</v>
+      <c r="L111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N111" s="2" t="s">
         <v>38</v>
@@ -9166,17 +9175,17 @@
       <c r="O111" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R111" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S111" s="2" t="s">
-        <v>38</v>
+      <c r="P111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S111" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T111" s="1" t="s">
         <v>37</v>
@@ -9204,14 +9213,14 @@
       <c r="B112" t="s">
         <v>147</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>38</v>
+      <c r="C112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>38</v>
@@ -9222,14 +9231,14 @@
       <c r="H112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I112" s="2" t="s">
-        <v>38</v>
+      <c r="I112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K112" s="2" t="s">
-        <v>38</v>
+      <c r="K112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>38</v>
@@ -9252,17 +9261,17 @@
       <c r="R112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S112" s="2" t="s">
-        <v>38</v>
+      <c r="S112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V112" s="2" t="s">
-        <v>38</v>
+      <c r="U112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W112" s="2" t="s">
         <v>38</v>
@@ -9281,8 +9290,8 @@
       <c r="B113" t="s">
         <v>148</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>38</v>
+      <c r="C113" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>37</v>
@@ -9290,29 +9299,29 @@
       <c r="E113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F113" s="1" t="s">
-        <v>37</v>
+      <c r="F113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H113" s="1" t="s">
-        <v>37</v>
+      <c r="H113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J113" s="1" t="s">
-        <v>37</v>
+      <c r="J113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M113" s="1" t="s">
-        <v>37</v>
+      <c r="L113" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>38</v>
@@ -9320,17 +9329,17 @@
       <c r="O113" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R113" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S113" s="2" t="s">
-        <v>38</v>
+      <c r="P113" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R113" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S113" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T113" s="1" t="s">
         <v>37</v>
@@ -9361,35 +9370,35 @@
       <c r="C114" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M114" s="2" t="s">
-        <v>38</v>
+      <c r="D114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M114" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>38</v>
@@ -9409,14 +9418,14 @@
       <c r="S114" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V114" s="2" t="s">
-        <v>38</v>
+      <c r="T114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V114" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W114" s="2" t="s">
         <v>38</v>
@@ -9435,17 +9444,17 @@
       <c r="B115" t="s">
         <v>150</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>37</v>
+      <c r="C115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>38</v>
@@ -9453,20 +9462,20 @@
       <c r="H115" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>37</v>
+      <c r="I115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>38</v>
@@ -9489,8 +9498,8 @@
       <c r="T115" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U115" s="1" t="s">
-        <v>37</v>
+      <c r="U115" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V115" s="2" t="s">
         <v>38</v>
@@ -9512,38 +9521,38 @@
       <c r="B116" t="s">
         <v>151</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>37</v>
+      <c r="C116" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>38</v>
+      <c r="E116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>38</v>
@@ -9563,14 +9572,14 @@
       <c r="S116" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U116" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V116" s="2" t="s">
-        <v>38</v>
+      <c r="T116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U116" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V116" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W116" s="2" t="s">
         <v>38</v>
@@ -9589,11 +9598,11 @@
       <c r="B117" t="s">
         <v>152</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>37</v>
+      <c r="C117" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>38</v>
@@ -9669,14 +9678,14 @@
       <c r="C118" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>38</v>
+      <c r="D118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>38</v>
@@ -9684,20 +9693,20 @@
       <c r="H118" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M118" s="2" t="s">
-        <v>38</v>
+      <c r="I118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>38</v>
@@ -9720,8 +9729,8 @@
       <c r="T118" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U118" s="2" t="s">
-        <v>38</v>
+      <c r="U118" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V118" s="2" t="s">
         <v>38</v>
@@ -9749,11 +9758,11 @@
       <c r="D119" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>37</v>
+      <c r="E119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>38</v>
@@ -9761,20 +9770,20 @@
       <c r="H119" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>37</v>
+      <c r="I119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>38</v>
@@ -9797,8 +9806,8 @@
       <c r="T119" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U119" s="1" t="s">
-        <v>37</v>
+      <c r="U119" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V119" s="2" t="s">
         <v>38</v>
@@ -9826,8 +9835,8 @@
       <c r="D120" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E120" s="1" t="s">
-        <v>37</v>
+      <c r="E120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>38</v>
@@ -9838,14 +9847,14 @@
       <c r="H120" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>37</v>
+      <c r="I120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K120" s="1" t="s">
-        <v>37</v>
+      <c r="K120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L120" s="2" t="s">
         <v>38</v>
@@ -9874,8 +9883,8 @@
       <c r="T120" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U120" s="1" t="s">
-        <v>37</v>
+      <c r="U120" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V120" s="2" t="s">
         <v>38</v>
@@ -9900,8 +9909,8 @@
       <c r="C121" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>37</v>
+      <c r="D121" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>38</v>
@@ -9977,14 +9986,14 @@
       <c r="C122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>38</v>
+      <c r="D122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>38</v>
@@ -9992,20 +10001,20 @@
       <c r="H122" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>38</v>
+      <c r="I122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>38</v>
@@ -10028,8 +10037,8 @@
       <c r="T122" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U122" s="2" t="s">
-        <v>38</v>
+      <c r="U122" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V122" s="2" t="s">
         <v>38</v>
@@ -10041,6 +10050,237 @@
         <v>38</v>
       </c>
       <c r="Y122" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="3">
+        <v>158</v>
+      </c>
+      <c r="B123" t="s">
+        <v>158</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X123" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y123" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="3">
+        <v>159</v>
+      </c>
+      <c r="B124" t="s">
+        <v>159</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y124" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="3">
+        <v>160</v>
+      </c>
+      <c r="B125" t="s">
+        <v>160</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y125" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -10056,12 +10296,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -501,7 +501,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.46.0-SNAPSHOT</t>
+    <t>1.47.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3127" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="164">
   <si>
     <t>User Right</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>DASHBOARD_CONTACT_VIEW_TRANSMISSION_CHAINS</t>
+  </si>
+  <si>
+    <t>DASHBOARD_CAMPAIGNS_ACCESS</t>
   </si>
   <si>
     <t>CASE_MANAGEMENT_ACCESS</t>
@@ -629,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z125"/>
+  <dimension ref="A1:Z126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -7753,14 +7756,14 @@
       <c r="C93" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>38</v>
+      <c r="D93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>38</v>
@@ -7774,17 +7777,17 @@
       <c r="J93" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="K93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M93" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>37</v>
+      <c r="K93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O93" s="2" t="s">
         <v>38</v>
@@ -7798,14 +7801,14 @@
       <c r="R93" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S93" s="1" t="s">
-        <v>37</v>
+      <c r="S93" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="T93" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U93" s="2" t="s">
-        <v>38</v>
+      <c r="U93" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V93" s="2" t="s">
         <v>38</v>
@@ -7860,8 +7863,8 @@
       <c r="M94" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N94" s="2" t="s">
-        <v>38</v>
+      <c r="N94" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O94" s="2" t="s">
         <v>38</v>
@@ -8079,8 +8082,8 @@
       <c r="I97" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J97" s="2" t="s">
-        <v>38</v>
+      <c r="J97" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>38</v>
@@ -8156,8 +8159,8 @@
       <c r="I98" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J98" s="1" t="s">
-        <v>37</v>
+      <c r="J98" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>38</v>
@@ -8310,8 +8313,8 @@
       <c r="I100" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J100" s="2" t="s">
-        <v>38</v>
+      <c r="J100" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>38</v>
@@ -8387,8 +8390,8 @@
       <c r="I101" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J101" s="1" t="s">
-        <v>37</v>
+      <c r="J101" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>38</v>
@@ -8695,8 +8698,8 @@
       <c r="I105" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J105" s="2" t="s">
-        <v>38</v>
+      <c r="J105" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K105" s="2" t="s">
         <v>38</v>
@@ -8754,62 +8757,62 @@
       <c r="C106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>37</v>
+      <c r="D106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="N106" s="1" t="s">
-        <v>37</v>
+      <c r="J106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R106" s="1" t="s">
-        <v>37</v>
+      <c r="P106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R106" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S106" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U106" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V106" s="1" t="s">
-        <v>37</v>
+      <c r="T106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U106" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V106" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W106" s="2" t="s">
         <v>38</v>
@@ -8840,41 +8843,41 @@
       <c r="F107" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N107" s="2" t="s">
-        <v>38</v>
+      <c r="G107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="O107" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q107" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R107" s="2" t="s">
-        <v>38</v>
+      <c r="P107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q107" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R107" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S107" s="1" t="s">
         <v>37</v>
@@ -8908,14 +8911,14 @@
       <c r="C108" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>38</v>
+      <c r="D108" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>38</v>
@@ -8953,17 +8956,17 @@
       <c r="R108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="S108" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T108" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U108" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V108" s="2" t="s">
-        <v>38</v>
+      <c r="S108" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U108" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V108" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W108" s="2" t="s">
         <v>38</v>
@@ -8985,11 +8988,11 @@
       <c r="C109" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D109" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>37</v>
+      <c r="D109" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>38</v>
@@ -9065,8 +9068,8 @@
       <c r="D110" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>38</v>
+      <c r="E110" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>38</v>
@@ -9142,26 +9145,26 @@
       <c r="D111" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>37</v>
+      <c r="E111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I111" s="1" t="s">
-        <v>37</v>
+      <c r="I111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K111" s="1" t="s">
-        <v>37</v>
+      <c r="K111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>38</v>
@@ -9175,26 +9178,26 @@
       <c r="O111" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="S111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="T111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U111" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V111" s="1" t="s">
-        <v>37</v>
+      <c r="P111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U111" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W111" s="2" t="s">
         <v>38</v>
@@ -9222,11 +9225,11 @@
       <c r="E112" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>38</v>
+      <c r="F112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>38</v>
@@ -9252,20 +9255,20 @@
       <c r="O112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q112" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R112" s="2" t="s">
-        <v>38</v>
+      <c r="P112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="S112" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T112" s="2" t="s">
-        <v>38</v>
+      <c r="T112" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="U112" s="1" t="s">
         <v>37</v>
@@ -9302,8 +9305,8 @@
       <c r="F113" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G113" s="1" t="s">
-        <v>37</v>
+      <c r="G113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>38</v>
@@ -9329,20 +9332,20 @@
       <c r="O113" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P113" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q113" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R113" s="1" t="s">
-        <v>37</v>
+      <c r="P113" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q113" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="S113" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T113" s="1" t="s">
-        <v>37</v>
+      <c r="T113" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="U113" s="1" t="s">
         <v>37</v>
@@ -9367,8 +9370,8 @@
       <c r="B114" t="s">
         <v>149</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>38</v>
+      <c r="C114" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>37</v>
@@ -9376,29 +9379,29 @@
       <c r="E114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F114" s="1" t="s">
-        <v>37</v>
+      <c r="F114" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H114" s="1" t="s">
-        <v>37</v>
+      <c r="H114" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J114" s="1" t="s">
-        <v>37</v>
+      <c r="J114" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="K114" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L114" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>37</v>
+      <c r="L114" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>38</v>
@@ -9406,17 +9409,17 @@
       <c r="O114" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="P114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="R114" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S114" s="2" t="s">
-        <v>38</v>
+      <c r="P114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R114" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S114" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="T114" s="1" t="s">
         <v>37</v>
@@ -9447,35 +9450,35 @@
       <c r="C115" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>38</v>
+      <c r="D115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>38</v>
@@ -9495,14 +9498,14 @@
       <c r="S115" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U115" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V115" s="2" t="s">
-        <v>38</v>
+      <c r="T115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U115" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V115" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W115" s="2" t="s">
         <v>38</v>
@@ -9524,35 +9527,35 @@
       <c r="C116" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>37</v>
+      <c r="D116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>38</v>
@@ -9572,14 +9575,14 @@
       <c r="S116" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U116" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="V116" s="1" t="s">
-        <v>37</v>
+      <c r="T116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U116" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V116" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="W116" s="2" t="s">
         <v>38</v>
@@ -9601,35 +9604,35 @@
       <c r="C117" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M117" s="2" t="s">
-        <v>38</v>
+      <c r="D117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M117" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>38</v>
@@ -9649,14 +9652,14 @@
       <c r="S117" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="T117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="U117" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V117" s="2" t="s">
-        <v>38</v>
+      <c r="T117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U117" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V117" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="W117" s="2" t="s">
         <v>38</v>
@@ -9675,17 +9678,17 @@
       <c r="B118" t="s">
         <v>153</v>
       </c>
-      <c r="C118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>37</v>
+      <c r="C118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>38</v>
@@ -9693,20 +9696,20 @@
       <c r="H118" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L118" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M118" s="1" t="s">
-        <v>37</v>
+      <c r="I118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>38</v>
@@ -9729,8 +9732,8 @@
       <c r="T118" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U118" s="1" t="s">
-        <v>37</v>
+      <c r="U118" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V118" s="2" t="s">
         <v>38</v>
@@ -9758,11 +9761,11 @@
       <c r="D119" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>38</v>
+      <c r="E119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>38</v>
@@ -9770,20 +9773,20 @@
       <c r="H119" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L119" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M119" s="2" t="s">
-        <v>38</v>
+      <c r="I119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>38</v>
@@ -9806,8 +9809,8 @@
       <c r="T119" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U119" s="2" t="s">
-        <v>38</v>
+      <c r="U119" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V119" s="2" t="s">
         <v>38</v>
@@ -9909,8 +9912,8 @@
       <c r="C121" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>38</v>
+      <c r="D121" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>38</v>
@@ -9986,14 +9989,14 @@
       <c r="C122" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>37</v>
+      <c r="D122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>38</v>
@@ -10001,20 +10004,20 @@
       <c r="H122" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>37</v>
+      <c r="I122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>38</v>
@@ -10037,8 +10040,8 @@
       <c r="T122" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U122" s="1" t="s">
-        <v>37</v>
+      <c r="U122" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="V122" s="2" t="s">
         <v>38</v>
@@ -10069,8 +10072,8 @@
       <c r="E123" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F123" s="2" t="s">
-        <v>38</v>
+      <c r="F123" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="G123" s="2" t="s">
         <v>38</v>
@@ -10081,17 +10084,17 @@
       <c r="I123" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J123" s="2" t="s">
-        <v>38</v>
+      <c r="J123" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="K123" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L123" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M123" s="2" t="s">
-        <v>38</v>
+      <c r="L123" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>38</v>
@@ -10143,8 +10146,8 @@
       <c r="D124" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>38</v>
+      <c r="E124" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>38</v>
@@ -10155,14 +10158,14 @@
       <c r="H124" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="I124" s="2" t="s">
-        <v>38</v>
+      <c r="I124" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="K124" s="2" t="s">
-        <v>38</v>
+      <c r="K124" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>38</v>
@@ -10191,8 +10194,8 @@
       <c r="T124" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="U124" s="2" t="s">
-        <v>38</v>
+      <c r="U124" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="V124" s="2" t="s">
         <v>38</v>
@@ -10217,8 +10220,8 @@
       <c r="C125" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>38</v>
+      <c r="D125" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>38</v>
@@ -10281,6 +10284,83 @@
         <v>38</v>
       </c>
       <c r="Y125" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="3">
+        <v>161</v>
+      </c>
+      <c r="B126" t="s">
+        <v>161</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y126" s="2" t="s">
         <v>38</v>
       </c>
     </row>
@@ -10296,12 +10376,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3152" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3177" uniqueCount="165">
   <si>
     <t>User Right</t>
   </si>
@@ -501,10 +501,13 @@
     <t>CAMPAIGN_FORM_DATA_DELETE</t>
   </si>
   <si>
+    <t>CAMPAIGN_FORM_DATA_EXPORT</t>
+  </si>
+  <si>
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.47.0-SNAPSHOT</t>
+    <t>1.48.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -632,7 +635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Z126"/>
+  <dimension ref="A1:Z127"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -10364,6 +10367,83 @@
         <v>38</v>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" t="s" s="3">
+        <v>162</v>
+      </c>
+      <c r="B127" t="s">
+        <v>162</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="R127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="T127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U127" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="V127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="X127" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y127" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -10376,12 +10456,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -507,7 +507,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.48.0-SNAPSHOT</t>
+    <t>1.49.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -513,7 +513,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.50.0-SNAPSHOT</t>
+    <t>${project.version}</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3512" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3539" uniqueCount="171">
   <si>
     <t>User Right</t>
   </si>
@@ -517,6 +517,9 @@
   </si>
   <si>
     <t>BAG_EXPORT</t>
+  </si>
+  <si>
+    <t>SORMAS_TO_SORMAS_SHARE</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -650,7 +653,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AB130"/>
+  <dimension ref="A1:AB131"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -1611,8 +1614,8 @@
       <c r="E12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>40</v>
+      <c r="F12" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>40</v>
@@ -10519,8 +10522,8 @@
       <c r="N119" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O119" s="2" t="s">
-        <v>40</v>
+      <c r="O119" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="P119" s="2" t="s">
         <v>40</v>
@@ -11469,6 +11472,89 @@
         <v>40</v>
       </c>
       <c r="AA130" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="3">
+        <v>168</v>
+      </c>
+      <c r="B131" t="s">
+        <v>168</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="M131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="T131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="U131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="W131" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="X131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z131" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA131" s="2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -11484,12 +11570,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -525,7 +525,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.51.0-SNAPSHOT</t>
+    <t>${project.version}</t>
   </si>
 </sst>
 </file>
@@ -6926,8 +6926,8 @@
       <c r="E76" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F76" s="1" t="s">
-        <v>39</v>
+      <c r="F76" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>40</v>
@@ -9825,14 +9825,14 @@
       <c r="C111" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>39</v>
+      <c r="D111" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F111" s="1" t="s">
-        <v>39</v>
+      <c r="F111" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>40</v>
@@ -9914,8 +9914,8 @@
       <c r="E112" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F112" s="1" t="s">
-        <v>39</v>
+      <c r="F112" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>40</v>
@@ -11491,8 +11491,8 @@
       <c r="E131" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F131" s="1" t="s">
-        <v>39</v>
+      <c r="F131" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>39</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -6926,8 +6926,8 @@
       <c r="E76" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>40</v>
+      <c r="F76" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>40</v>
@@ -9825,14 +9825,14 @@
       <c r="C111" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D111" s="2" t="s">
-        <v>40</v>
+      <c r="D111" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>40</v>
+      <c r="F111" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G111" s="2" t="s">
         <v>40</v>
@@ -9914,8 +9914,8 @@
       <c r="E112" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>40</v>
+      <c r="F112" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>40</v>
@@ -11491,8 +11491,8 @@
       <c r="E131" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F131" s="2" t="s">
-        <v>40</v>
+      <c r="F131" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="G131" s="1" t="s">
         <v>39</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -531,7 +531,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.52.0-SNAPSHOT</t>
+    <t>1.53.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -537,7 +537,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.53.0-SNAPSHOT</t>
+    <t>1.54.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -11005,14 +11005,14 @@
       <c r="X120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y120" s="2" t="s">
-        <v>41</v>
+      <c r="Y120" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="Z120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA120" s="2" t="s">
-        <v>41</v>
+      <c r="AA120" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AB120" s="2" t="s">
         <v>41</v>
@@ -11091,14 +11091,14 @@
       <c r="X121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y121" s="2" t="s">
-        <v>41</v>
+      <c r="Y121" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="Z121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA121" s="2" t="s">
-        <v>41</v>
+      <c r="AA121" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AB121" s="2" t="s">
         <v>41</v>
@@ -11177,14 +11177,14 @@
       <c r="X122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y122" s="2" t="s">
-        <v>41</v>
+      <c r="Y122" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="Z122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA122" s="2" t="s">
-        <v>41</v>
+      <c r="AA122" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AB122" s="2" t="s">
         <v>41</v>
@@ -11263,14 +11263,14 @@
       <c r="X123" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y123" s="2" t="s">
-        <v>41</v>
+      <c r="Y123" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="Z123" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA123" s="2" t="s">
-        <v>41</v>
+      <c r="AA123" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AB123" s="2" t="s">
         <v>41</v>
@@ -11372,8 +11372,8 @@
       <c r="C125" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>40</v>
+      <c r="D125" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>41</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3754" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3810" uniqueCount="177">
   <si>
     <t>User Right</t>
   </si>
@@ -381,6 +381,9 @@
     <t>PERFORM_BULK_OPERATIONS</t>
   </si>
   <si>
+    <t>PERFORM_BULK_OPERATIONS_CASE_SAMPLES</t>
+  </si>
+  <si>
     <t>INFRASTRUCTURE_CREATE</t>
   </si>
   <si>
@@ -532,6 +535,9 @@
   </si>
   <si>
     <t>SORMAS_TO_SORMAS_SHARE</t>
+  </si>
+  <si>
+    <t>LAB_MESSAGES</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -665,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC134"/>
+  <dimension ref="A1:AC136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -7852,8 +7858,8 @@
       <c r="E84" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>41</v>
+      <c r="F84" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>41</v>
@@ -8018,14 +8024,14 @@
       <c r="C86" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>40</v>
+      <c r="D86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>41</v>
@@ -8057,26 +8063,26 @@
       <c r="P86" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>40</v>
+      <c r="Q86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U86" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V86" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W86" s="1" t="s">
-        <v>40</v>
+      <c r="V86" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W86" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X86" s="2" t="s">
         <v>41</v>
@@ -8107,11 +8113,11 @@
       <c r="D87" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>41</v>
+      <c r="E87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>41</v>
@@ -8146,23 +8152,23 @@
       <c r="Q87" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R87" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S87" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T87" s="2" t="s">
-        <v>41</v>
+      <c r="R87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T87" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V87" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W87" s="2" t="s">
-        <v>41</v>
+      <c r="V87" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W87" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X87" s="2" t="s">
         <v>41</v>
@@ -8193,11 +8199,11 @@
       <c r="D88" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E88" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>40</v>
+      <c r="E88" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>41</v>
@@ -8229,8 +8235,8 @@
       <c r="P88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q88" s="2" t="s">
-        <v>41</v>
+      <c r="Q88" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="R88" s="2" t="s">
         <v>41</v>
@@ -8238,17 +8244,17 @@
       <c r="S88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T88" s="1" t="s">
-        <v>40</v>
+      <c r="T88" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V88" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W88" s="1" t="s">
-        <v>40</v>
+      <c r="V88" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X88" s="2" t="s">
         <v>41</v>
@@ -8276,14 +8282,14 @@
       <c r="C89" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>41</v>
+      <c r="D89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>41</v>
@@ -8324,17 +8330,17 @@
       <c r="S89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T89" s="2" t="s">
-        <v>41</v>
+      <c r="T89" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V89" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W89" s="2" t="s">
-        <v>41</v>
+      <c r="V89" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W89" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X89" s="2" t="s">
         <v>41</v>
@@ -8362,8 +8368,8 @@
       <c r="C90" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>40</v>
+      <c r="D90" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>41</v>
@@ -8448,8 +8454,8 @@
       <c r="C91" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>41</v>
+      <c r="D91" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
@@ -8534,17 +8540,17 @@
       <c r="C92" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G92" s="1" t="s">
-        <v>40</v>
+      <c r="D92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>41</v>
@@ -8552,47 +8558,47 @@
       <c r="I92" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>40</v>
+      <c r="J92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O92" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>40</v>
+      <c r="Q92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U92" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V92" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W92" s="1" t="s">
-        <v>40</v>
+      <c r="V92" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W92" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X92" s="2" t="s">
         <v>41</v>
@@ -8644,11 +8650,11 @@
       <c r="K93" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L93" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M93" s="2" t="s">
-        <v>41</v>
+      <c r="L93" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="N93" s="1" t="s">
         <v>40</v>
@@ -8709,14 +8715,14 @@
       <c r="D94" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>41</v>
+      <c r="E94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>41</v>
@@ -8724,23 +8730,23 @@
       <c r="I94" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L94" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M94" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>41</v>
+      <c r="J94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P94" s="2" t="s">
         <v>41</v>
@@ -8754,17 +8760,17 @@
       <c r="S94" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T94" s="2" t="s">
-        <v>41</v>
+      <c r="T94" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U94" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W94" s="2" t="s">
-        <v>41</v>
+      <c r="V94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W94" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X94" s="2" t="s">
         <v>41</v>
@@ -8819,8 +8825,8 @@
       <c r="L95" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M95" s="2" t="s">
-        <v>41</v>
+      <c r="M95" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>41</v>
@@ -8881,14 +8887,14 @@
       <c r="D96" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G96" s="1" t="s">
-        <v>40</v>
+      <c r="E96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>41</v>
@@ -8896,20 +8902,20 @@
       <c r="I96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J96" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>40</v>
+      <c r="J96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K96" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M96" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>40</v>
+      <c r="M96" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O96" s="2" t="s">
         <v>41</v>
@@ -8917,14 +8923,14 @@
       <c r="P96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q96" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R96" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>41</v>
+      <c r="Q96" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S96" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="T96" s="2" t="s">
         <v>41</v>
@@ -8932,8 +8938,8 @@
       <c r="U96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V96" s="1" t="s">
-        <v>40</v>
+      <c r="V96" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W96" s="2" t="s">
         <v>41</v>
@@ -8964,17 +8970,17 @@
       <c r="C97" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>41</v>
+      <c r="D97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>41</v>
@@ -8988,17 +8994,17 @@
       <c r="K97" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>40</v>
+      <c r="L97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P97" s="2" t="s">
         <v>41</v>
@@ -9012,14 +9018,14 @@
       <c r="S97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T97" s="1" t="s">
-        <v>40</v>
+      <c r="T97" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V97" s="2" t="s">
-        <v>41</v>
+      <c r="V97" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>41</v>
@@ -9083,8 +9089,8 @@
       <c r="N98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="O98" s="2" t="s">
-        <v>41</v>
+      <c r="O98" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>41</v>
@@ -9329,8 +9335,8 @@
       <c r="J101" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K101" s="2" t="s">
-        <v>41</v>
+      <c r="K101" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>41</v>
@@ -9415,8 +9421,8 @@
       <c r="J102" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K102" s="1" t="s">
-        <v>40</v>
+      <c r="K102" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>41</v>
@@ -9587,8 +9593,8 @@
       <c r="J104" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K104" s="2" t="s">
-        <v>41</v>
+      <c r="K104" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>41</v>
@@ -9673,8 +9679,8 @@
       <c r="J105" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>40</v>
+      <c r="K105" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>41</v>
@@ -10017,8 +10023,8 @@
       <c r="J109" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K109" s="2" t="s">
-        <v>41</v>
+      <c r="K109" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>41</v>
@@ -10082,65 +10088,65 @@
       <c r="C110" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I110" s="1" t="s">
-        <v>40</v>
+      <c r="D110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J110" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>40</v>
+      <c r="K110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O110" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P110" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S110" s="1" t="s">
-        <v>40</v>
+      <c r="Q110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S110" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="T110" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V110" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W110" s="1" t="s">
-        <v>40</v>
+      <c r="U110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V110" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X110" s="2" t="s">
         <v>41</v>
@@ -10180,41 +10186,41 @@
       <c r="G111" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O111" s="2" t="s">
-        <v>41</v>
+      <c r="H111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P111" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R111" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S111" s="2" t="s">
-        <v>41</v>
+      <c r="Q111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S111" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="T111" s="1" t="s">
         <v>40</v>
@@ -10254,17 +10260,17 @@
       <c r="C112" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>41</v>
+      <c r="D112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>41</v>
@@ -10302,17 +10308,17 @@
       <c r="S112" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="U112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W112" s="2" t="s">
-        <v>41</v>
+      <c r="T112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W112" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X112" s="2" t="s">
         <v>41</v>
@@ -10423,17 +10429,17 @@
       <c r="B114" t="s">
         <v>152</v>
       </c>
-      <c r="C114" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>40</v>
+      <c r="C114" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>41</v>
@@ -10444,17 +10450,17 @@
       <c r="I114" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J114" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>40</v>
+      <c r="J114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L114" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>41</v>
@@ -10509,8 +10515,8 @@
       <c r="B115" t="s">
         <v>153</v>
       </c>
-      <c r="C115" s="1" t="s">
-        <v>40</v>
+      <c r="C115" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>40</v>
@@ -10530,17 +10536,17 @@
       <c r="I115" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>41</v>
+      <c r="J115" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>41</v>
@@ -10601,11 +10607,11 @@
       <c r="D116" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>41</v>
+      <c r="E116" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>41</v>
@@ -10687,29 +10693,29 @@
       <c r="D117" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>40</v>
+      <c r="E117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J117" s="1" t="s">
-        <v>40</v>
+      <c r="J117" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L117" s="1" t="s">
-        <v>40</v>
+      <c r="L117" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>41</v>
@@ -10723,26 +10729,26 @@
       <c r="P117" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V117" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W117" s="1" t="s">
-        <v>40</v>
+      <c r="Q117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V117" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X117" s="2" t="s">
         <v>41</v>
@@ -10779,11 +10785,11 @@
       <c r="F118" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G118" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>41</v>
+      <c r="G118" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>41</v>
@@ -10809,20 +10815,20 @@
       <c r="P118" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q118" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R118" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S118" s="2" t="s">
-        <v>41</v>
+      <c r="Q118" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R118" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S118" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="T118" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U118" s="2" t="s">
-        <v>41</v>
+      <c r="U118" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="V118" s="1" t="s">
         <v>40</v>
@@ -10868,8 +10874,8 @@
       <c r="G119" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H119" s="1" t="s">
-        <v>40</v>
+      <c r="H119" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>41</v>
@@ -10895,20 +10901,20 @@
       <c r="P119" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q119" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S119" s="1" t="s">
-        <v>40</v>
+      <c r="Q119" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R119" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S119" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="T119" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U119" s="1" t="s">
-        <v>40</v>
+      <c r="U119" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="V119" s="1" t="s">
         <v>40</v>
@@ -10939,8 +10945,8 @@
       <c r="B120" t="s">
         <v>158</v>
       </c>
-      <c r="C120" s="2" t="s">
-        <v>41</v>
+      <c r="C120" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>40</v>
@@ -10951,29 +10957,29 @@
       <c r="F120" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G120" s="1" t="s">
-        <v>40</v>
+      <c r="G120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H120" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>40</v>
+      <c r="I120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K120" s="1" t="s">
-        <v>40</v>
+      <c r="K120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M120" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N120" s="1" t="s">
-        <v>40</v>
+      <c r="M120" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>41</v>
@@ -10981,17 +10987,17 @@
       <c r="P120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q120" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R120" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S120" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T120" s="2" t="s">
-        <v>41</v>
+      <c r="Q120" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R120" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S120" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T120" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U120" s="1" t="s">
         <v>40</v>
@@ -11005,14 +11011,14 @@
       <c r="X120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y120" s="1" t="s">
-        <v>40</v>
+      <c r="Y120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="Z120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA120" s="1" t="s">
-        <v>40</v>
+      <c r="AA120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="AB120" s="2" t="s">
         <v>41</v>
@@ -11028,38 +11034,38 @@
       <c r="C121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N121" s="2" t="s">
-        <v>41</v>
+      <c r="D121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O121" s="2" t="s">
         <v>41</v>
@@ -11079,14 +11085,14 @@
       <c r="T121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W121" s="2" t="s">
-        <v>41</v>
+      <c r="U121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W121" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X121" s="2" t="s">
         <v>41</v>
@@ -11114,41 +11120,41 @@
       <c r="C122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>40</v>
+      <c r="D122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P122" s="2" t="s">
         <v>41</v>
@@ -11165,14 +11171,14 @@
       <c r="T122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V122" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W122" s="1" t="s">
-        <v>40</v>
+      <c r="U122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X122" s="2" t="s">
         <v>41</v>
@@ -11200,41 +11206,41 @@
       <c r="C123" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O123" s="2" t="s">
-        <v>41</v>
+      <c r="D123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P123" s="2" t="s">
         <v>41</v>
@@ -11251,14 +11257,14 @@
       <c r="T123" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V123" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W123" s="2" t="s">
-        <v>41</v>
+      <c r="U123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V123" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W123" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X123" s="2" t="s">
         <v>41</v>
@@ -11283,20 +11289,20 @@
       <c r="B124" t="s">
         <v>162</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G124" s="1" t="s">
-        <v>40</v>
+      <c r="C124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>41</v>
@@ -11304,20 +11310,20 @@
       <c r="I124" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M124" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N124" s="1" t="s">
-        <v>40</v>
+      <c r="J124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N124" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O124" s="2" t="s">
         <v>41</v>
@@ -11340,8 +11346,8 @@
       <c r="U124" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V124" s="1" t="s">
-        <v>40</v>
+      <c r="V124" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W124" s="2" t="s">
         <v>41</v>
@@ -11349,14 +11355,14 @@
       <c r="X124" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y124" s="2" t="s">
-        <v>41</v>
+      <c r="Y124" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="Z124" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA124" s="2" t="s">
-        <v>41</v>
+      <c r="AA124" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AB124" s="2" t="s">
         <v>41</v>
@@ -11372,17 +11378,17 @@
       <c r="C125" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>41</v>
+      <c r="D125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>41</v>
@@ -11390,20 +11396,20 @@
       <c r="I125" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N125" s="2" t="s">
-        <v>41</v>
+      <c r="J125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M125" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N125" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>41</v>
@@ -11426,8 +11432,8 @@
       <c r="U125" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V125" s="2" t="s">
-        <v>41</v>
+      <c r="V125" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>41</v>
@@ -11458,8 +11464,8 @@
       <c r="C126" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>40</v>
+      <c r="D126" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>41</v>
@@ -11544,8 +11550,8 @@
       <c r="C127" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>41</v>
+      <c r="D127" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>41</v>
@@ -11630,17 +11636,17 @@
       <c r="C128" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>40</v>
+      <c r="D128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>41</v>
@@ -11648,20 +11654,20 @@
       <c r="I128" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M128" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>40</v>
+      <c r="J128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O128" s="2" t="s">
         <v>41</v>
@@ -11684,8 +11690,8 @@
       <c r="U128" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V128" s="1" t="s">
-        <v>40</v>
+      <c r="V128" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W128" s="2" t="s">
         <v>41</v>
@@ -11725,8 +11731,8 @@
       <c r="F129" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G129" s="2" t="s">
-        <v>41</v>
+      <c r="G129" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>41</v>
@@ -11737,17 +11743,17 @@
       <c r="J129" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K129" s="2" t="s">
-        <v>41</v>
+      <c r="K129" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L129" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M129" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N129" s="2" t="s">
-        <v>41</v>
+      <c r="M129" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O129" s="2" t="s">
         <v>41</v>
@@ -11805,11 +11811,11 @@
       <c r="D130" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E130" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>41</v>
+      <c r="E130" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G130" s="2" t="s">
         <v>41</v>
@@ -11820,14 +11826,14 @@
       <c r="I130" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J130" s="2" t="s">
-        <v>41</v>
+      <c r="J130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L130" s="2" t="s">
-        <v>41</v>
+      <c r="L130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="M130" s="2" t="s">
         <v>41</v>
@@ -11856,8 +11862,8 @@
       <c r="U130" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V130" s="2" t="s">
-        <v>41</v>
+      <c r="V130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W130" s="2" t="s">
         <v>41</v>
@@ -11888,8 +11894,8 @@
       <c r="C131" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>41</v>
+      <c r="D131" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>41</v>
@@ -11974,14 +11980,14 @@
       <c r="C132" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>40</v>
+      <c r="D132" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>41</v>
@@ -11992,14 +11998,14 @@
       <c r="I132" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J132" s="1" t="s">
-        <v>40</v>
+      <c r="J132" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L132" s="1" t="s">
-        <v>40</v>
+      <c r="L132" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="M132" s="2" t="s">
         <v>41</v>
@@ -12028,8 +12034,8 @@
       <c r="U132" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V132" s="1" t="s">
-        <v>40</v>
+      <c r="V132" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W132" s="2" t="s">
         <v>41</v>
@@ -12057,17 +12063,17 @@
       <c r="B133" t="s">
         <v>171</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>41</v>
+      <c r="C133" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>41</v>
@@ -12078,14 +12084,14 @@
       <c r="I133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J133" s="2" t="s">
-        <v>41</v>
+      <c r="J133" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L133" s="2" t="s">
-        <v>41</v>
+      <c r="L133" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="M133" s="2" t="s">
         <v>41</v>
@@ -12114,8 +12120,8 @@
       <c r="U133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V133" s="2" t="s">
-        <v>41</v>
+      <c r="V133" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W133" s="2" t="s">
         <v>41</v>
@@ -12132,8 +12138,8 @@
       <c r="AA133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AB133" s="1" t="s">
-        <v>40</v>
+      <c r="AB133" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="134">
@@ -12143,20 +12149,20 @@
       <c r="B134" t="s">
         <v>172</v>
       </c>
-      <c r="C134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>40</v>
+      <c r="C134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>41</v>
@@ -12164,20 +12170,20 @@
       <c r="I134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N134" s="1" t="s">
-        <v>40</v>
+      <c r="J134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O134" s="2" t="s">
         <v>41</v>
@@ -12185,26 +12191,26 @@
       <c r="P134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T134" s="1" t="s">
-        <v>40</v>
+      <c r="Q134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T134" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V134" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W134" s="1" t="s">
-        <v>40</v>
+      <c r="V134" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W134" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X134" s="2" t="s">
         <v>41</v>
@@ -12218,7 +12224,179 @@
       <c r="AA134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AB134" s="2" t="s">
+      <c r="AB134" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="3">
+        <v>173</v>
+      </c>
+      <c r="B135" t="s">
+        <v>173</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W135" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="X135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB135" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="3">
+        <v>174</v>
+      </c>
+      <c r="B136" t="s">
+        <v>174</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA136" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB136" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -12234,12 +12412,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3810" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="178">
   <si>
     <t>User Right</t>
   </si>
@@ -381,6 +381,9 @@
     <t>PERFORM_BULK_OPERATIONS</t>
   </si>
   <si>
+    <t>MANAGE_PUBLIC_EXPORT_CONFIGURATION</t>
+  </si>
+  <si>
     <t>PERFORM_BULK_OPERATIONS_CASE_SAMPLES</t>
   </si>
   <si>
@@ -543,7 +546,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.54.0-SNAPSHOT</t>
+    <t>1.56.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -671,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AC136"/>
+  <dimension ref="A1:AC137"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -7852,8 +7855,8 @@
       <c r="C84" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D84" s="2" t="s">
-        <v>41</v>
+      <c r="D84" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>41</v>
@@ -7944,8 +7947,8 @@
       <c r="E85" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F85" s="2" t="s">
-        <v>41</v>
+      <c r="F85" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>41</v>
@@ -8110,14 +8113,14 @@
       <c r="C87" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>40</v>
+      <c r="D87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>41</v>
@@ -8149,26 +8152,26 @@
       <c r="P87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T87" s="1" t="s">
-        <v>40</v>
+      <c r="Q87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T87" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V87" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W87" s="1" t="s">
-        <v>40</v>
+      <c r="V87" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W87" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X87" s="2" t="s">
         <v>41</v>
@@ -8199,11 +8202,11 @@
       <c r="D88" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>41</v>
+      <c r="E88" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>41</v>
@@ -8238,23 +8241,23 @@
       <c r="Q88" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="R88" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S88" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T88" s="2" t="s">
-        <v>41</v>
+      <c r="R88" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S88" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V88" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W88" s="2" t="s">
-        <v>41</v>
+      <c r="V88" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W88" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X88" s="2" t="s">
         <v>41</v>
@@ -8285,11 +8288,11 @@
       <c r="D89" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>40</v>
+      <c r="E89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>41</v>
@@ -8321,8 +8324,8 @@
       <c r="P89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q89" s="2" t="s">
-        <v>41</v>
+      <c r="Q89" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="R89" s="2" t="s">
         <v>41</v>
@@ -8330,17 +8333,17 @@
       <c r="S89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T89" s="1" t="s">
-        <v>40</v>
+      <c r="T89" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V89" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W89" s="1" t="s">
-        <v>40</v>
+      <c r="V89" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W89" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X89" s="2" t="s">
         <v>41</v>
@@ -8368,14 +8371,14 @@
       <c r="C90" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D90" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" s="2" t="s">
-        <v>41</v>
+      <c r="D90" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>41</v>
@@ -8416,17 +8419,17 @@
       <c r="S90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T90" s="2" t="s">
-        <v>41</v>
+      <c r="T90" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V90" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W90" s="2" t="s">
-        <v>41</v>
+      <c r="V90" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W90" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X90" s="2" t="s">
         <v>41</v>
@@ -8454,8 +8457,8 @@
       <c r="C91" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>40</v>
+      <c r="D91" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
@@ -8540,8 +8543,8 @@
       <c r="C92" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>41</v>
+      <c r="D92" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>41</v>
@@ -8626,17 +8629,17 @@
       <c r="C93" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G93" s="1" t="s">
-        <v>40</v>
+      <c r="D93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>41</v>
@@ -8644,47 +8647,47 @@
       <c r="I93" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>40</v>
+      <c r="J93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O93" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P93" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>40</v>
+      <c r="Q93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T93" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U93" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V93" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W93" s="1" t="s">
-        <v>40</v>
+      <c r="V93" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W93" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X93" s="2" t="s">
         <v>41</v>
@@ -8736,11 +8739,11 @@
       <c r="K94" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L94" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M94" s="2" t="s">
-        <v>41</v>
+      <c r="L94" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>40</v>
@@ -8801,14 +8804,14 @@
       <c r="D95" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>41</v>
+      <c r="E95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>41</v>
@@ -8816,23 +8819,23 @@
       <c r="I95" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L95" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M95" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O95" s="2" t="s">
-        <v>41</v>
+      <c r="J95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>41</v>
@@ -8846,17 +8849,17 @@
       <c r="S95" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="T95" s="2" t="s">
-        <v>41</v>
+      <c r="T95" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U95" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V95" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W95" s="2" t="s">
-        <v>41</v>
+      <c r="V95" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W95" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X95" s="2" t="s">
         <v>41</v>
@@ -8911,8 +8914,8 @@
       <c r="L96" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M96" s="2" t="s">
-        <v>41</v>
+      <c r="M96" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>41</v>
@@ -8973,14 +8976,14 @@
       <c r="D97" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E97" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>40</v>
+      <c r="E97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>41</v>
@@ -8988,20 +8991,20 @@
       <c r="I97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J97" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>40</v>
+      <c r="J97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M97" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>40</v>
+      <c r="M97" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O97" s="2" t="s">
         <v>41</v>
@@ -9009,14 +9012,14 @@
       <c r="P97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R97" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S97" s="2" t="s">
-        <v>41</v>
+      <c r="Q97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S97" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="T97" s="2" t="s">
         <v>41</v>
@@ -9024,8 +9027,8 @@
       <c r="U97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V97" s="1" t="s">
-        <v>40</v>
+      <c r="V97" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W97" s="2" t="s">
         <v>41</v>
@@ -9056,17 +9059,17 @@
       <c r="C98" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>41</v>
+      <c r="D98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>41</v>
@@ -9080,17 +9083,17 @@
       <c r="K98" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N98" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>40</v>
+      <c r="L98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O98" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>41</v>
@@ -9104,14 +9107,14 @@
       <c r="S98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T98" s="1" t="s">
-        <v>40</v>
+      <c r="T98" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V98" s="2" t="s">
-        <v>41</v>
+      <c r="V98" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W98" s="2" t="s">
         <v>41</v>
@@ -9175,8 +9178,8 @@
       <c r="N99" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="O99" s="2" t="s">
-        <v>41</v>
+      <c r="O99" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P99" s="2" t="s">
         <v>41</v>
@@ -9421,8 +9424,8 @@
       <c r="J102" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K102" s="2" t="s">
-        <v>41</v>
+      <c r="K102" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L102" s="2" t="s">
         <v>41</v>
@@ -9507,8 +9510,8 @@
       <c r="J103" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>40</v>
+      <c r="K103" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L103" s="2" t="s">
         <v>41</v>
@@ -9679,8 +9682,8 @@
       <c r="J105" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K105" s="2" t="s">
-        <v>41</v>
+      <c r="K105" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>41</v>
@@ -9765,8 +9768,8 @@
       <c r="J106" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>40</v>
+      <c r="K106" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>41</v>
@@ -10109,8 +10112,8 @@
       <c r="J110" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K110" s="2" t="s">
-        <v>41</v>
+      <c r="K110" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L110" s="2" t="s">
         <v>41</v>
@@ -10174,65 +10177,65 @@
       <c r="C111" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>40</v>
+      <c r="D111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J111" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>40</v>
+      <c r="K111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P111" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S111" s="1" t="s">
-        <v>40</v>
+      <c r="Q111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S111" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="T111" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V111" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W111" s="1" t="s">
-        <v>40</v>
+      <c r="U111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X111" s="2" t="s">
         <v>41</v>
@@ -10272,41 +10275,41 @@
       <c r="G112" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O112" s="2" t="s">
-        <v>41</v>
+      <c r="H112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P112" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R112" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S112" s="2" t="s">
-        <v>41</v>
+      <c r="Q112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S112" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="T112" s="1" t="s">
         <v>40</v>
@@ -10346,17 +10349,17 @@
       <c r="C113" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>41</v>
+      <c r="D113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>41</v>
@@ -10394,17 +10397,17 @@
       <c r="S113" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="T113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="U113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V113" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W113" s="2" t="s">
-        <v>41</v>
+      <c r="T113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="U113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W113" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X113" s="2" t="s">
         <v>41</v>
@@ -10515,17 +10518,17 @@
       <c r="B115" t="s">
         <v>153</v>
       </c>
-      <c r="C115" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>40</v>
+      <c r="C115" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G115" s="2" t="s">
         <v>41</v>
@@ -10536,17 +10539,17 @@
       <c r="I115" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J115" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K115" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>40</v>
+      <c r="J115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L115" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>41</v>
@@ -10601,8 +10604,8 @@
       <c r="B116" t="s">
         <v>154</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>40</v>
+      <c r="C116" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>40</v>
@@ -10622,17 +10625,17 @@
       <c r="I116" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J116" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>41</v>
+      <c r="J116" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>41</v>
@@ -10693,11 +10696,11 @@
       <c r="D117" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>41</v>
+      <c r="E117" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G117" s="2" t="s">
         <v>41</v>
@@ -10779,29 +10782,29 @@
       <c r="D118" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>40</v>
+      <c r="E118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="I118" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J118" s="1" t="s">
-        <v>40</v>
+      <c r="J118" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L118" s="1" t="s">
-        <v>40</v>
+      <c r="L118" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="M118" s="2" t="s">
         <v>41</v>
@@ -10815,26 +10818,26 @@
       <c r="P118" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="U118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V118" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W118" s="1" t="s">
-        <v>40</v>
+      <c r="Q118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V118" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W118" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X118" s="2" t="s">
         <v>41</v>
@@ -10871,11 +10874,11 @@
       <c r="F119" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G119" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>41</v>
+      <c r="G119" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>41</v>
@@ -10901,20 +10904,20 @@
       <c r="P119" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q119" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R119" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S119" s="2" t="s">
-        <v>41</v>
+      <c r="Q119" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S119" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="T119" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U119" s="2" t="s">
-        <v>41</v>
+      <c r="U119" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="V119" s="1" t="s">
         <v>40</v>
@@ -10960,8 +10963,8 @@
       <c r="G120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>40</v>
+      <c r="H120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>41</v>
@@ -10987,20 +10990,20 @@
       <c r="P120" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q120" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R120" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S120" s="1" t="s">
-        <v>40</v>
+      <c r="Q120" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R120" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="T120" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="U120" s="1" t="s">
-        <v>40</v>
+      <c r="U120" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="V120" s="1" t="s">
         <v>40</v>
@@ -11031,8 +11034,8 @@
       <c r="B121" t="s">
         <v>159</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>41</v>
+      <c r="C121" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>40</v>
@@ -11043,29 +11046,29 @@
       <c r="F121" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G121" s="1" t="s">
-        <v>40</v>
+      <c r="G121" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I121" s="1" t="s">
-        <v>40</v>
+      <c r="I121" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="J121" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>40</v>
+      <c r="K121" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M121" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>40</v>
+      <c r="M121" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O121" s="2" t="s">
         <v>41</v>
@@ -11073,17 +11076,17 @@
       <c r="P121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S121" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T121" s="2" t="s">
-        <v>41</v>
+      <c r="Q121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S121" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U121" s="1" t="s">
         <v>40</v>
@@ -11097,14 +11100,14 @@
       <c r="X121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y121" s="1" t="s">
-        <v>40</v>
+      <c r="Y121" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="Z121" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA121" s="1" t="s">
-        <v>40</v>
+      <c r="AA121" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="AB121" s="2" t="s">
         <v>41</v>
@@ -11120,38 +11123,38 @@
       <c r="C122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N122" s="2" t="s">
-        <v>41</v>
+      <c r="D122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O122" s="2" t="s">
         <v>41</v>
@@ -11171,14 +11174,14 @@
       <c r="T122" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V122" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W122" s="2" t="s">
-        <v>41</v>
+      <c r="U122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V122" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W122" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X122" s="2" t="s">
         <v>41</v>
@@ -11206,41 +11209,41 @@
       <c r="C123" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="O123" s="1" t="s">
-        <v>40</v>
+      <c r="D123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O123" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="P123" s="2" t="s">
         <v>41</v>
@@ -11257,14 +11260,14 @@
       <c r="T123" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="V123" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W123" s="1" t="s">
-        <v>40</v>
+      <c r="U123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V123" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X123" s="2" t="s">
         <v>41</v>
@@ -11292,41 +11295,41 @@
       <c r="C124" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O124" s="2" t="s">
-        <v>41</v>
+      <c r="D124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O124" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="P124" s="2" t="s">
         <v>41</v>
@@ -11343,14 +11346,14 @@
       <c r="T124" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="U124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V124" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W124" s="2" t="s">
-        <v>41</v>
+      <c r="U124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="V124" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W124" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X124" s="2" t="s">
         <v>41</v>
@@ -11375,20 +11378,20 @@
       <c r="B125" t="s">
         <v>163</v>
       </c>
-      <c r="C125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>40</v>
+      <c r="C125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>41</v>
@@ -11396,20 +11399,20 @@
       <c r="I125" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M125" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N125" s="1" t="s">
-        <v>40</v>
+      <c r="J125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>41</v>
@@ -11432,8 +11435,8 @@
       <c r="U125" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V125" s="1" t="s">
-        <v>40</v>
+      <c r="V125" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W125" s="2" t="s">
         <v>41</v>
@@ -11441,14 +11444,14 @@
       <c r="X125" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Y125" s="2" t="s">
-        <v>41</v>
+      <c r="Y125" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="Z125" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AA125" s="2" t="s">
-        <v>41</v>
+      <c r="AA125" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="AB125" s="2" t="s">
         <v>41</v>
@@ -11464,17 +11467,17 @@
       <c r="C126" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>41</v>
+      <c r="D126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>41</v>
@@ -11482,20 +11485,20 @@
       <c r="I126" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M126" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N126" s="2" t="s">
-        <v>41</v>
+      <c r="J126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>41</v>
@@ -11518,8 +11521,8 @@
       <c r="U126" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V126" s="2" t="s">
-        <v>41</v>
+      <c r="V126" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W126" s="2" t="s">
         <v>41</v>
@@ -11550,8 +11553,8 @@
       <c r="C127" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>40</v>
+      <c r="D127" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>41</v>
@@ -11636,8 +11639,8 @@
       <c r="C128" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>41</v>
+      <c r="D128" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>41</v>
@@ -11722,17 +11725,17 @@
       <c r="C129" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>40</v>
+      <c r="D129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>41</v>
@@ -11740,20 +11743,20 @@
       <c r="I129" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M129" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N129" s="1" t="s">
-        <v>40</v>
+      <c r="J129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O129" s="2" t="s">
         <v>41</v>
@@ -11776,8 +11779,8 @@
       <c r="U129" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V129" s="1" t="s">
-        <v>40</v>
+      <c r="V129" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W129" s="2" t="s">
         <v>41</v>
@@ -11817,8 +11820,8 @@
       <c r="F130" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G130" s="2" t="s">
-        <v>41</v>
+      <c r="G130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>41</v>
@@ -11829,17 +11832,17 @@
       <c r="J130" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="K130" s="2" t="s">
-        <v>41</v>
+      <c r="K130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="L130" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="M130" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N130" s="2" t="s">
-        <v>41</v>
+      <c r="M130" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N130" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O130" s="2" t="s">
         <v>41</v>
@@ -11897,11 +11900,11 @@
       <c r="D131" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E131" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>41</v>
+      <c r="E131" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>41</v>
@@ -11912,14 +11915,14 @@
       <c r="I131" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J131" s="2" t="s">
-        <v>41</v>
+      <c r="J131" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K131" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L131" s="2" t="s">
-        <v>41</v>
+      <c r="L131" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="M131" s="2" t="s">
         <v>41</v>
@@ -11948,8 +11951,8 @@
       <c r="U131" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V131" s="2" t="s">
-        <v>41</v>
+      <c r="V131" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W131" s="2" t="s">
         <v>41</v>
@@ -11980,8 +11983,8 @@
       <c r="C132" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>41</v>
+      <c r="D132" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>41</v>
@@ -12066,14 +12069,14 @@
       <c r="C133" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>40</v>
+      <c r="D133" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G133" s="2" t="s">
         <v>41</v>
@@ -12084,14 +12087,14 @@
       <c r="I133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J133" s="1" t="s">
-        <v>40</v>
+      <c r="J133" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L133" s="1" t="s">
-        <v>40</v>
+      <c r="L133" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="M133" s="2" t="s">
         <v>41</v>
@@ -12120,8 +12123,8 @@
       <c r="U133" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V133" s="1" t="s">
-        <v>40</v>
+      <c r="V133" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="W133" s="2" t="s">
         <v>41</v>
@@ -12149,17 +12152,17 @@
       <c r="B134" t="s">
         <v>172</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>41</v>
+      <c r="C134" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>41</v>
@@ -12170,14 +12173,14 @@
       <c r="I134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J134" s="2" t="s">
-        <v>41</v>
+      <c r="J134" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="L134" s="2" t="s">
-        <v>41</v>
+      <c r="L134" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="M134" s="2" t="s">
         <v>41</v>
@@ -12206,8 +12209,8 @@
       <c r="U134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V134" s="2" t="s">
-        <v>41</v>
+      <c r="V134" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="W134" s="2" t="s">
         <v>41</v>
@@ -12224,8 +12227,8 @@
       <c r="AA134" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AB134" s="1" t="s">
-        <v>40</v>
+      <c r="AB134" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="135">
@@ -12235,20 +12238,20 @@
       <c r="B135" t="s">
         <v>173</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>40</v>
+      <c r="C135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>41</v>
@@ -12256,20 +12259,20 @@
       <c r="I135" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="M135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="N135" s="1" t="s">
-        <v>40</v>
+      <c r="J135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="O135" s="2" t="s">
         <v>41</v>
@@ -12277,26 +12280,26 @@
       <c r="P135" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="R135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="S135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="T135" s="1" t="s">
-        <v>40</v>
+      <c r="Q135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T135" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="U135" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V135" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="W135" s="1" t="s">
-        <v>40</v>
+      <c r="V135" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W135" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="X135" s="2" t="s">
         <v>41</v>
@@ -12310,8 +12313,8 @@
       <c r="AA135" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AB135" s="2" t="s">
-        <v>41</v>
+      <c r="AB135" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="136">
@@ -12321,8 +12324,8 @@
       <c r="B136" t="s">
         <v>174</v>
       </c>
-      <c r="C136" s="2" t="s">
-        <v>41</v>
+      <c r="C136" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>40</v>
@@ -12330,11 +12333,11 @@
       <c r="E136" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>41</v>
+      <c r="F136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>41</v>
@@ -12342,20 +12345,20 @@
       <c r="I136" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="J136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N136" s="2" t="s">
-        <v>41</v>
+      <c r="J136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="O136" s="2" t="s">
         <v>41</v>
@@ -12363,26 +12366,26 @@
       <c r="P136" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="Q136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="R136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="S136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="T136" s="2" t="s">
-        <v>41</v>
+      <c r="Q136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="S136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="T136" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="U136" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="V136" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="W136" s="2" t="s">
-        <v>41</v>
+      <c r="V136" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="W136" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="X136" s="2" t="s">
         <v>41</v>
@@ -12397,6 +12400,92 @@
         <v>41</v>
       </c>
       <c r="AB136" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s" s="3">
+        <v>175</v>
+      </c>
+      <c r="B137" t="s">
+        <v>175</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="N137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="P137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="R137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="S137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="U137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="V137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="W137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA137" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB137" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -12412,12 +12501,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -546,7 +546,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.56.0-SNAPSHOT</t>
+    <t>1.57.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -555,7 +555,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.57.0-SNAPSHOT</t>
+    <t>1.58.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -555,7 +555,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.58.0-SNAPSHOT</t>
+    <t>1.57.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4033" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4062" uniqueCount="182">
   <si>
     <t>User Right</t>
   </si>
@@ -330,6 +330,9 @@
     <t>EVENT_EDIT</t>
   </si>
   <si>
+    <t>EVENT_IMPORT</t>
+  </si>
+  <si>
     <t>EVENT_EXPORT</t>
   </si>
   <si>
@@ -555,7 +558,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.57.0-SNAPSHOT</t>
+    <t>1.58.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -683,7 +686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD139"/>
+  <dimension ref="A1:AD140"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -6512,14 +6515,14 @@
       <c r="C66" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>41</v>
+      <c r="D66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>42</v>
@@ -6533,14 +6536,14 @@
       <c r="J66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>41</v>
+      <c r="K66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M66" s="1" t="s">
-        <v>41</v>
+      <c r="M66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>42</v>
@@ -6548,8 +6551,8 @@
       <c r="O66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P66" s="1" t="s">
-        <v>41</v>
+      <c r="P66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>42</v>
@@ -6563,20 +6566,20 @@
       <c r="T66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U66" s="1" t="s">
-        <v>41</v>
+      <c r="U66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W66" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X66" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y66" s="2" t="s">
-        <v>42</v>
+      <c r="W66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X66" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y66" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>42</v>
@@ -6601,14 +6604,14 @@
       <c r="C67" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>42</v>
+      <c r="D67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>42</v>
@@ -6622,14 +6625,14 @@
       <c r="J67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K67" s="2" t="s">
-        <v>42</v>
+      <c r="K67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M67" s="2" t="s">
-        <v>42</v>
+      <c r="M67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>42</v>
@@ -6637,8 +6640,8 @@
       <c r="O67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P67" s="2" t="s">
-        <v>42</v>
+      <c r="P67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>42</v>
@@ -6652,17 +6655,17 @@
       <c r="T67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U67" s="2" t="s">
-        <v>42</v>
+      <c r="U67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W67" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X67" s="2" t="s">
-        <v>42</v>
+      <c r="W67" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y67" s="2" t="s">
         <v>42</v>
@@ -6690,8 +6693,8 @@
       <c r="C68" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>41</v>
+      <c r="D68" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>42</v>
@@ -6800,14 +6803,14 @@
       <c r="J69" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>41</v>
+      <c r="K69" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M69" s="1" t="s">
-        <v>41</v>
+      <c r="M69" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>42</v>
@@ -6821,26 +6824,26 @@
       <c r="Q69" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>41</v>
+      <c r="R69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U69" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W69" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>41</v>
+      <c r="W69" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y69" s="2" t="s">
         <v>42</v>
@@ -6871,38 +6874,38 @@
       <c r="D70" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G70" s="1" t="s">
-        <v>41</v>
+      <c r="E70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I70" s="1" t="s">
-        <v>41</v>
+      <c r="I70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>42</v>
+      <c r="K70" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M70" s="2" t="s">
-        <v>42</v>
+      <c r="M70" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>41</v>
+      <c r="O70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>42</v>
@@ -6910,26 +6913,26 @@
       <c r="Q70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R70" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S70" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T70" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U70" s="2" t="s">
-        <v>42</v>
+      <c r="R70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U70" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W70" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X70" s="2" t="s">
-        <v>42</v>
+      <c r="W70" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X70" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>42</v>
@@ -7049,20 +7052,20 @@
       <c r="D72" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>42</v>
+      <c r="E72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>42</v>
+      <c r="I72" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>42</v>
@@ -7079,8 +7082,8 @@
       <c r="N72" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O72" s="2" t="s">
-        <v>42</v>
+      <c r="O72" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>42</v>
@@ -7138,20 +7141,20 @@
       <c r="D73" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>41</v>
+      <c r="E73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>41</v>
+      <c r="I73" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>42</v>
@@ -7168,8 +7171,8 @@
       <c r="N73" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O73" s="1" t="s">
-        <v>41</v>
+      <c r="O73" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>42</v>
@@ -7198,8 +7201,8 @@
       <c r="X73" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y73" s="1" t="s">
-        <v>41</v>
+      <c r="Y73" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Z73" s="2" t="s">
         <v>42</v>
@@ -7221,29 +7224,29 @@
       <c r="B74" t="s">
         <v>113</v>
       </c>
-      <c r="C74" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>42</v>
+      <c r="C74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>41</v>
+      <c r="H74" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>41</v>
+      <c r="J74" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>42</v>
@@ -7257,8 +7260,8 @@
       <c r="N74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O74" s="2" t="s">
-        <v>42</v>
+      <c r="O74" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>42</v>
@@ -7287,8 +7290,8 @@
       <c r="X74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y74" s="2" t="s">
-        <v>42</v>
+      <c r="Y74" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>42</v>
@@ -7310,17 +7313,17 @@
       <c r="B75" t="s">
         <v>114</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>41</v>
+      <c r="C75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>41</v>
@@ -7334,14 +7337,14 @@
       <c r="J75" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>41</v>
+      <c r="K75" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M75" s="1" t="s">
-        <v>41</v>
+      <c r="M75" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>42</v>
@@ -7355,17 +7358,17 @@
       <c r="Q75" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U75" s="1" t="s">
-        <v>41</v>
+      <c r="R75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U75" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V75" s="2" t="s">
         <v>42</v>
@@ -7402,35 +7405,35 @@
       <c r="C76" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>42</v>
+      <c r="D76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M76" s="2" t="s">
-        <v>42</v>
+      <c r="M76" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>42</v>
@@ -7444,17 +7447,17 @@
       <c r="Q76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T76" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U76" s="2" t="s">
-        <v>42</v>
+      <c r="R76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U76" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>42</v>
@@ -7669,14 +7672,14 @@
       <c r="C79" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>41</v>
+      <c r="D79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>42</v>
@@ -7711,26 +7714,26 @@
       <c r="Q79" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U79" s="1" t="s">
-        <v>41</v>
+      <c r="R79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V79" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W79" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X79" s="1" t="s">
-        <v>41</v>
+      <c r="W79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X79" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y79" s="2" t="s">
         <v>42</v>
@@ -7761,11 +7764,11 @@
       <c r="D80" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>42</v>
+      <c r="E80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>42</v>
@@ -7800,26 +7803,26 @@
       <c r="Q80" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U80" s="2" t="s">
-        <v>42</v>
+      <c r="R80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U80" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X80" s="2" t="s">
-        <v>42</v>
+      <c r="W80" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X80" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>42</v>
@@ -7844,17 +7847,17 @@
       <c r="B81" t="s">
         <v>120</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F81" s="1" t="s">
-        <v>41</v>
+      <c r="C81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>42</v>
@@ -7933,17 +7936,17 @@
       <c r="B82" t="s">
         <v>121</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>42</v>
+      <c r="C82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>42</v>
@@ -8028,11 +8031,11 @@
       <c r="D83" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>41</v>
+      <c r="E83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>42</v>
@@ -8046,14 +8049,14 @@
       <c r="J83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K83" s="1" t="s">
-        <v>41</v>
+      <c r="K83" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M83" s="1" t="s">
-        <v>41</v>
+      <c r="M83" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>42</v>
@@ -8061,32 +8064,32 @@
       <c r="O83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P83" s="1" t="s">
-        <v>41</v>
+      <c r="P83" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U83" s="1" t="s">
-        <v>41</v>
+      <c r="R83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X83" s="1" t="s">
-        <v>41</v>
+      <c r="W83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X83" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y83" s="2" t="s">
         <v>42</v>
@@ -8156,14 +8159,14 @@
       <c r="Q84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R84" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S84" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T84" s="2" t="s">
-        <v>42</v>
+      <c r="R84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S84" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U84" s="1" t="s">
         <v>41</v>
@@ -8206,11 +8209,11 @@
       <c r="D85" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>42</v>
+      <c r="E85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>42</v>
@@ -8224,14 +8227,14 @@
       <c r="J85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K85" s="2" t="s">
-        <v>42</v>
+      <c r="K85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M85" s="2" t="s">
-        <v>42</v>
+      <c r="M85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>42</v>
@@ -8239,8 +8242,8 @@
       <c r="O85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P85" s="2" t="s">
-        <v>42</v>
+      <c r="P85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q85" s="2" t="s">
         <v>42</v>
@@ -8254,17 +8257,17 @@
       <c r="T85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U85" s="2" t="s">
-        <v>42</v>
+      <c r="U85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W85" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X85" s="2" t="s">
-        <v>42</v>
+      <c r="W85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y85" s="2" t="s">
         <v>42</v>
@@ -8292,8 +8295,8 @@
       <c r="C86" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>42</v>
+      <c r="D86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>42</v>
@@ -8381,14 +8384,14 @@
       <c r="C87" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>41</v>
+      <c r="D87" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>41</v>
+      <c r="F87" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>42</v>
@@ -8470,8 +8473,8 @@
       <c r="C88" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>42</v>
+      <c r="D88" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>42</v>
@@ -8565,8 +8568,8 @@
       <c r="E89" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F89" s="2" t="s">
-        <v>42</v>
+      <c r="F89" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>42</v>
@@ -8737,14 +8740,14 @@
       <c r="C91" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>41</v>
+      <c r="D91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>42</v>
@@ -8779,26 +8782,26 @@
       <c r="Q91" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U91" s="1" t="s">
-        <v>41</v>
+      <c r="R91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U91" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V91" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W91" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X91" s="1" t="s">
-        <v>41</v>
+      <c r="W91" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X91" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y91" s="2" t="s">
         <v>42</v>
@@ -8829,11 +8832,11 @@
       <c r="D92" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>42</v>
+      <c r="E92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>42</v>
@@ -8871,23 +8874,23 @@
       <c r="R92" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S92" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T92" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U92" s="2" t="s">
-        <v>42</v>
+      <c r="S92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U92" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W92" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X92" s="2" t="s">
-        <v>42</v>
+      <c r="W92" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X92" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>42</v>
@@ -8918,11 +8921,11 @@
       <c r="D93" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E93" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>41</v>
+      <c r="E93" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>42</v>
@@ -8957,8 +8960,8 @@
       <c r="Q93" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R93" s="2" t="s">
-        <v>42</v>
+      <c r="R93" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="S93" s="2" t="s">
         <v>42</v>
@@ -8966,17 +8969,17 @@
       <c r="T93" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U93" s="1" t="s">
-        <v>41</v>
+      <c r="U93" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V93" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W93" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X93" s="1" t="s">
-        <v>41</v>
+      <c r="W93" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X93" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y93" s="2" t="s">
         <v>42</v>
@@ -9004,14 +9007,14 @@
       <c r="C94" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>42</v>
+      <c r="D94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>42</v>
@@ -9055,17 +9058,17 @@
       <c r="T94" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U94" s="2" t="s">
-        <v>42</v>
+      <c r="U94" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W94" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X94" s="2" t="s">
-        <v>42</v>
+      <c r="W94" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X94" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y94" s="2" t="s">
         <v>42</v>
@@ -9093,8 +9096,8 @@
       <c r="C95" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>41</v>
+      <c r="D95" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>42</v>
@@ -9182,8 +9185,8 @@
       <c r="C96" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>42</v>
+      <c r="D96" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>42</v>
@@ -9271,32 +9274,32 @@
       <c r="C97" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G97" s="1" t="s">
-        <v>41</v>
+      <c r="D97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I97" s="1" t="s">
-        <v>41</v>
+      <c r="I97" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L97" s="1" t="s">
-        <v>41</v>
+      <c r="K97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M97" s="2" t="s">
         <v>42</v>
@@ -9304,35 +9307,35 @@
       <c r="N97" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P97" s="1" t="s">
-        <v>41</v>
+      <c r="O97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q97" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U97" s="1" t="s">
-        <v>41</v>
+      <c r="R97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U97" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V97" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W97" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X97" s="1" t="s">
-        <v>41</v>
+      <c r="W97" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X97" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y97" s="2" t="s">
         <v>42</v>
@@ -9363,14 +9366,14 @@
       <c r="D98" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>42</v>
+      <c r="E98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>42</v>
@@ -9381,23 +9384,23 @@
       <c r="J98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K98" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L98" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P98" s="2" t="s">
-        <v>42</v>
+      <c r="K98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P98" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q98" s="2" t="s">
         <v>42</v>
@@ -9411,17 +9414,17 @@
       <c r="T98" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U98" s="2" t="s">
-        <v>42</v>
+      <c r="U98" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W98" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X98" s="2" t="s">
-        <v>42</v>
+      <c r="W98" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X98" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>42</v>
@@ -9464,8 +9467,8 @@
       <c r="H99" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>42</v>
+      <c r="I99" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>42</v>
@@ -9479,8 +9482,8 @@
       <c r="M99" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N99" s="2" t="s">
-        <v>42</v>
+      <c r="N99" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O99" s="2" t="s">
         <v>42</v>
@@ -9541,38 +9544,38 @@
       <c r="D100" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G100" s="1" t="s">
-        <v>41</v>
+      <c r="E100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L100" s="1" t="s">
-        <v>41</v>
+      <c r="I100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N100" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>41</v>
+      <c r="N100" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O100" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P100" s="2" t="s">
         <v>42</v>
@@ -9580,14 +9583,14 @@
       <c r="Q100" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R100" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T100" s="2" t="s">
-        <v>42</v>
+      <c r="R100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S100" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U100" s="2" t="s">
         <v>42</v>
@@ -9595,8 +9598,8 @@
       <c r="V100" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W100" s="1" t="s">
-        <v>41</v>
+      <c r="W100" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X100" s="2" t="s">
         <v>42</v>
@@ -9627,26 +9630,26 @@
       <c r="C101" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G101" s="2" t="s">
-        <v>42</v>
+      <c r="D101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>42</v>
+      <c r="I101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="K101" s="1" t="s">
         <v>41</v>
@@ -9654,17 +9657,17 @@
       <c r="L101" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P101" s="1" t="s">
-        <v>41</v>
+      <c r="M101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q101" s="2" t="s">
         <v>42</v>
@@ -9678,14 +9681,14 @@
       <c r="T101" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U101" s="1" t="s">
-        <v>41</v>
+      <c r="U101" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W101" s="2" t="s">
-        <v>42</v>
+      <c r="W101" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X101" s="2" t="s">
         <v>42</v>
@@ -9752,8 +9755,8 @@
       <c r="O102" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P102" s="2" t="s">
-        <v>42</v>
+      <c r="P102" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q102" s="2" t="s">
         <v>42</v>
@@ -10007,8 +10010,8 @@
       <c r="K105" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L105" s="2" t="s">
-        <v>42</v>
+      <c r="L105" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>42</v>
@@ -10096,8 +10099,8 @@
       <c r="K106" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L106" s="1" t="s">
-        <v>41</v>
+      <c r="L106" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>42</v>
@@ -10274,8 +10277,8 @@
       <c r="K108" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L108" s="2" t="s">
-        <v>42</v>
+      <c r="L108" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M108" s="2" t="s">
         <v>42</v>
@@ -10363,8 +10366,8 @@
       <c r="K109" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L109" s="1" t="s">
-        <v>41</v>
+      <c r="L109" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M109" s="2" t="s">
         <v>42</v>
@@ -10719,8 +10722,8 @@
       <c r="K113" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L113" s="2" t="s">
-        <v>42</v>
+      <c r="L113" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M113" s="2" t="s">
         <v>42</v>
@@ -10784,68 +10787,68 @@
       <c r="C114" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>41</v>
+      <c r="D114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J114" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K114" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P114" s="1" t="s">
-        <v>41</v>
+      <c r="L114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P114" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q114" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T114" s="1" t="s">
-        <v>41</v>
+      <c r="R114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T114" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U114" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W114" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X114" s="1" t="s">
-        <v>41</v>
+      <c r="V114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W114" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X114" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y114" s="2" t="s">
         <v>42</v>
@@ -10885,44 +10888,44 @@
       <c r="G115" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H115" s="2" t="s">
-        <v>42</v>
+      <c r="H115" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P115" s="2" t="s">
-        <v>42</v>
+      <c r="J115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P115" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q115" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S115" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T115" s="2" t="s">
-        <v>42</v>
+      <c r="R115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S115" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T115" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U115" s="1" t="s">
         <v>41</v>
@@ -10962,23 +10965,23 @@
       <c r="C116" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>42</v>
+      <c r="D116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I116" s="2" t="s">
-        <v>42</v>
+      <c r="I116" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>42</v>
@@ -11013,17 +11016,17 @@
       <c r="T116" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X116" s="2" t="s">
-        <v>42</v>
+      <c r="U116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X116" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y116" s="2" t="s">
         <v>42</v>
@@ -11137,17 +11140,17 @@
       <c r="B118" t="s">
         <v>157</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F118" s="1" t="s">
-        <v>41</v>
+      <c r="C118" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>42</v>
@@ -11155,23 +11158,23 @@
       <c r="H118" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I118" s="1" t="s">
-        <v>41</v>
+      <c r="I118" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K118" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L118" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M118" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N118" s="1" t="s">
-        <v>41</v>
+      <c r="K118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N118" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O118" s="2" t="s">
         <v>42</v>
@@ -11226,8 +11229,8 @@
       <c r="B119" t="s">
         <v>158</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>41</v>
+      <c r="C119" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>41</v>
@@ -11244,23 +11247,23 @@
       <c r="H119" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I119" s="2" t="s">
-        <v>42</v>
+      <c r="I119" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K119" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L119" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M119" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N119" s="2" t="s">
-        <v>42</v>
+      <c r="K119" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O119" s="2" t="s">
         <v>42</v>
@@ -11321,11 +11324,11 @@
       <c r="D120" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>42</v>
+      <c r="E120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>42</v>
@@ -11410,32 +11413,32 @@
       <c r="D121" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>41</v>
+      <c r="E121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>41</v>
+      <c r="K121" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M121" s="1" t="s">
-        <v>41</v>
+      <c r="M121" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N121" s="2" t="s">
         <v>42</v>
@@ -11449,26 +11452,26 @@
       <c r="Q121" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W121" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X121" s="1" t="s">
-        <v>41</v>
+      <c r="R121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W121" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y121" s="2" t="s">
         <v>42</v>
@@ -11505,14 +11508,14 @@
       <c r="F122" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G122" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>42</v>
+      <c r="G122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>42</v>
@@ -11538,20 +11541,20 @@
       <c r="Q122" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R122" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S122" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T122" s="2" t="s">
-        <v>42</v>
+      <c r="R122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S122" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U122" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V122" s="2" t="s">
-        <v>42</v>
+      <c r="V122" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="W122" s="1" t="s">
         <v>41</v>
@@ -11597,8 +11600,8 @@
       <c r="G123" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H123" s="1" t="s">
-        <v>41</v>
+      <c r="H123" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I123" s="2" t="s">
         <v>42</v>
@@ -11627,20 +11630,20 @@
       <c r="Q123" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R123" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>41</v>
+      <c r="R123" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U123" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V123" s="1" t="s">
-        <v>41</v>
+      <c r="V123" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>41</v>
@@ -11671,8 +11674,8 @@
       <c r="B124" t="s">
         <v>163</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>42</v>
+      <c r="C124" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>41</v>
@@ -11683,32 +11686,32 @@
       <c r="F124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G124" s="1" t="s">
-        <v>41</v>
+      <c r="G124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I124" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J124" s="1" t="s">
-        <v>41</v>
+      <c r="I124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L124" s="1" t="s">
-        <v>41</v>
+      <c r="L124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N124" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O124" s="1" t="s">
-        <v>41</v>
+      <c r="N124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P124" s="2" t="s">
         <v>42</v>
@@ -11716,17 +11719,17 @@
       <c r="Q124" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R124" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S124" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T124" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U124" s="2" t="s">
-        <v>42</v>
+      <c r="R124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T124" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U124" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V124" s="1" t="s">
         <v>41</v>
@@ -11740,14 +11743,14 @@
       <c r="Y124" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Z124" s="1" t="s">
-        <v>41</v>
+      <c r="Z124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="AA124" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AB124" s="1" t="s">
-        <v>41</v>
+      <c r="AB124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="AC124" s="2" t="s">
         <v>42</v>
@@ -11763,41 +11766,41 @@
       <c r="C125" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O125" s="2" t="s">
-        <v>42</v>
+      <c r="D125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O125" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P125" s="2" t="s">
         <v>42</v>
@@ -11817,14 +11820,14 @@
       <c r="U125" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X125" s="2" t="s">
-        <v>42</v>
+      <c r="V125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X125" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y125" s="2" t="s">
         <v>42</v>
@@ -11852,44 +11855,44 @@
       <c r="C126" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P126" s="1" t="s">
-        <v>41</v>
+      <c r="D126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q126" s="2" t="s">
         <v>42</v>
@@ -11906,14 +11909,14 @@
       <c r="U126" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W126" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X126" s="1" t="s">
-        <v>41</v>
+      <c r="V126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>42</v>
@@ -11941,44 +11944,44 @@
       <c r="C127" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P127" s="2" t="s">
-        <v>42</v>
+      <c r="D127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P127" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q127" s="2" t="s">
         <v>42</v>
@@ -11995,14 +11998,14 @@
       <c r="U127" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W127" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X127" s="2" t="s">
-        <v>42</v>
+      <c r="V127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W127" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X127" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y127" s="2" t="s">
         <v>42</v>
@@ -12027,44 +12030,44 @@
       <c r="B128" t="s">
         <v>167</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>41</v>
+      <c r="C128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I128" s="1" t="s">
-        <v>41</v>
+      <c r="I128" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O128" s="1" t="s">
-        <v>41</v>
+      <c r="K128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P128" s="2" t="s">
         <v>42</v>
@@ -12087,8 +12090,8 @@
       <c r="V128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W128" s="1" t="s">
-        <v>41</v>
+      <c r="W128" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X128" s="2" t="s">
         <v>42</v>
@@ -12096,14 +12099,14 @@
       <c r="Y128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Z128" s="2" t="s">
-        <v>42</v>
+      <c r="Z128" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AA128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AB128" s="2" t="s">
-        <v>42</v>
+      <c r="AB128" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AC128" s="2" t="s">
         <v>42</v>
@@ -12119,41 +12122,41 @@
       <c r="C129" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>42</v>
+      <c r="D129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I129" s="2" t="s">
-        <v>42</v>
+      <c r="I129" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N129" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O129" s="2" t="s">
-        <v>42</v>
+      <c r="K129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N129" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O129" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P129" s="2" t="s">
         <v>42</v>
@@ -12176,8 +12179,8 @@
       <c r="V129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W129" s="2" t="s">
-        <v>42</v>
+      <c r="W129" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X129" s="2" t="s">
         <v>42</v>
@@ -12208,8 +12211,8 @@
       <c r="C130" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>41</v>
+      <c r="D130" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>42</v>
@@ -12297,8 +12300,8 @@
       <c r="C131" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>42</v>
+      <c r="D131" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>42</v>
@@ -12386,41 +12389,41 @@
       <c r="C132" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>41</v>
+      <c r="D132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I132" s="1" t="s">
-        <v>41</v>
+      <c r="I132" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N132" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>41</v>
+      <c r="K132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P132" s="2" t="s">
         <v>42</v>
@@ -12443,8 +12446,8 @@
       <c r="V132" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W132" s="1" t="s">
-        <v>41</v>
+      <c r="W132" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X132" s="2" t="s">
         <v>42</v>
@@ -12484,14 +12487,14 @@
       <c r="F133" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G133" s="2" t="s">
-        <v>42</v>
+      <c r="G133" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I133" s="2" t="s">
-        <v>42</v>
+      <c r="I133" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>42</v>
@@ -12499,17 +12502,17 @@
       <c r="K133" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L133" s="2" t="s">
-        <v>42</v>
+      <c r="L133" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N133" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O133" s="2" t="s">
-        <v>42</v>
+      <c r="N133" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P133" s="2" t="s">
         <v>42</v>
@@ -12567,11 +12570,11 @@
       <c r="D134" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E134" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>42</v>
+      <c r="E134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G134" s="2" t="s">
         <v>42</v>
@@ -12585,14 +12588,14 @@
       <c r="J134" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K134" s="2" t="s">
-        <v>42</v>
+      <c r="K134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L134" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M134" s="2" t="s">
-        <v>42</v>
+      <c r="M134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N134" s="2" t="s">
         <v>42</v>
@@ -12621,8 +12624,8 @@
       <c r="V134" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W134" s="2" t="s">
-        <v>42</v>
+      <c r="W134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X134" s="2" t="s">
         <v>42</v>
@@ -12653,8 +12656,8 @@
       <c r="C135" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>42</v>
+      <c r="D135" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>42</v>
@@ -12742,14 +12745,14 @@
       <c r="C136" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>41</v>
+      <c r="D136" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>42</v>
@@ -12763,14 +12766,14 @@
       <c r="J136" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K136" s="1" t="s">
-        <v>41</v>
+      <c r="K136" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L136" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M136" s="1" t="s">
-        <v>41</v>
+      <c r="M136" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N136" s="2" t="s">
         <v>42</v>
@@ -12799,8 +12802,8 @@
       <c r="V136" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W136" s="1" t="s">
-        <v>41</v>
+      <c r="W136" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X136" s="2" t="s">
         <v>42</v>
@@ -12828,17 +12831,17 @@
       <c r="B137" t="s">
         <v>176</v>
       </c>
-      <c r="C137" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>42</v>
+      <c r="C137" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>42</v>
@@ -12852,14 +12855,14 @@
       <c r="J137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K137" s="2" t="s">
-        <v>42</v>
+      <c r="K137" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M137" s="2" t="s">
-        <v>42</v>
+      <c r="M137" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N137" s="2" t="s">
         <v>42</v>
@@ -12888,8 +12891,8 @@
       <c r="V137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W137" s="2" t="s">
-        <v>42</v>
+      <c r="W137" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X137" s="2" t="s">
         <v>42</v>
@@ -12906,8 +12909,8 @@
       <c r="AB137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AC137" s="1" t="s">
-        <v>41</v>
+      <c r="AC137" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="138">
@@ -12917,44 +12920,44 @@
       <c r="B138" t="s">
         <v>177</v>
       </c>
-      <c r="C138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>41</v>
+      <c r="C138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I138" s="1" t="s">
-        <v>41</v>
+      <c r="I138" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O138" s="1" t="s">
-        <v>41</v>
+      <c r="K138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O138" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P138" s="2" t="s">
         <v>42</v>
@@ -12962,26 +12965,26 @@
       <c r="Q138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U138" s="1" t="s">
-        <v>41</v>
+      <c r="R138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U138" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W138" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X138" s="1" t="s">
-        <v>41</v>
+      <c r="W138" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X138" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y138" s="2" t="s">
         <v>42</v>
@@ -12995,8 +12998,8 @@
       <c r="AB138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AC138" s="2" t="s">
-        <v>42</v>
+      <c r="AC138" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="139">
@@ -13006,8 +13009,8 @@
       <c r="B139" t="s">
         <v>178</v>
       </c>
-      <c r="C139" s="2" t="s">
-        <v>42</v>
+      <c r="C139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>41</v>
@@ -13015,35 +13018,35 @@
       <c r="E139" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>42</v>
+      <c r="F139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I139" s="2" t="s">
-        <v>42</v>
+      <c r="I139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O139" s="2" t="s">
-        <v>42</v>
+      <c r="K139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P139" s="2" t="s">
         <v>42</v>
@@ -13051,26 +13054,26 @@
       <c r="Q139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U139" s="2" t="s">
-        <v>42</v>
+      <c r="R139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W139" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X139" s="2" t="s">
-        <v>42</v>
+      <c r="W139" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X139" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y139" s="2" t="s">
         <v>42</v>
@@ -13085,6 +13088,95 @@
         <v>42</v>
       </c>
       <c r="AC139" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="3">
+        <v>179</v>
+      </c>
+      <c r="B140" t="s">
+        <v>179</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB140" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC140" s="2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13100,12 +13192,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -8132,8 +8132,8 @@
       <c r="H84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>42</v>
+      <c r="I84" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>42</v>
@@ -8221,8 +8221,8 @@
       <c r="H85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>42</v>
+      <c r="I85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>42</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4062" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4091" uniqueCount="183">
   <si>
     <t>User Right</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>PERSON_DELETE</t>
+  </si>
+  <si>
+    <t>PERSON_CONTACT_DETAILS_DELETE</t>
   </si>
   <si>
     <t>SAMPLE_CREATE</t>
@@ -686,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD140"/>
+  <dimension ref="A1:AD141"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -2602,29 +2605,29 @@
       <c r="D22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>41</v>
+      <c r="E22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>41</v>
+      <c r="G22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>42</v>
@@ -2632,11 +2635,11 @@
       <c r="N22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>41</v>
+      <c r="O22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>42</v>
@@ -2650,8 +2653,8 @@
       <c r="T22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>41</v>
+      <c r="U22" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>42</v>
@@ -2715,11 +2718,11 @@
       <c r="L23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>41</v>
+      <c r="M23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>41</v>
@@ -2727,17 +2730,17 @@
       <c r="P23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>41</v>
+      <c r="Q23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U23" s="1" t="s">
         <v>41</v>
@@ -2804,11 +2807,11 @@
       <c r="L24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>42</v>
+      <c r="M24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>41</v>
@@ -2819,14 +2822,14 @@
       <c r="Q24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>42</v>
+      <c r="R24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U24" s="1" t="s">
         <v>41</v>
@@ -2866,8 +2869,8 @@
       <c r="C25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>42</v>
+      <c r="D25" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>41</v>
@@ -2875,23 +2878,23 @@
       <c r="F25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>42</v>
+      <c r="G25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>42</v>
@@ -2902,11 +2905,11 @@
       <c r="O25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>42</v>
+      <c r="P25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>42</v>
@@ -2917,8 +2920,8 @@
       <c r="T25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U25" s="2" t="s">
-        <v>42</v>
+      <c r="U25" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>42</v>
@@ -2955,11 +2958,11 @@
       <c r="C26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>42</v>
+      <c r="D26" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>41</v>
@@ -2988,8 +2991,8 @@
       <c r="N26" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O26" s="2" t="s">
-        <v>42</v>
+      <c r="O26" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>42</v>
@@ -3047,8 +3050,8 @@
       <c r="D27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>41</v>
+      <c r="E27" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>41</v>
@@ -3065,8 +3068,8 @@
       <c r="J27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>41</v>
+      <c r="K27" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>42</v>
@@ -3080,11 +3083,11 @@
       <c r="O27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>41</v>
+      <c r="P27" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>42</v>
@@ -3095,8 +3098,8 @@
       <c r="T27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>41</v>
+      <c r="U27" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>42</v>
@@ -3160,8 +3163,8 @@
       <c r="L28" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>41</v>
+      <c r="M28" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>42</v>
@@ -3172,8 +3175,8 @@
       <c r="P28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q28" s="2" t="s">
-        <v>42</v>
+      <c r="Q28" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>42</v>
@@ -3225,11 +3228,11 @@
       <c r="D29" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>42</v>
+      <c r="E29" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>42</v>
@@ -3258,20 +3261,20 @@
       <c r="O29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>42</v>
+      <c r="P29" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>41</v>
+      <c r="R29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U29" s="1" t="s">
         <v>41</v>
@@ -3314,20 +3317,20 @@
       <c r="D30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>41</v>
+      <c r="E30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>41</v>
+      <c r="I30" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>42</v>
@@ -3338,29 +3341,29 @@
       <c r="L30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>42</v>
+      <c r="M30" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>42</v>
+      <c r="O30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U30" s="1" t="s">
         <v>41</v>
@@ -3492,26 +3495,26 @@
       <c r="D32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>42</v>
+      <c r="E32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>42</v>
+      <c r="I32" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K32" s="2" t="s">
-        <v>42</v>
+      <c r="K32" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>42</v>
@@ -3522,14 +3525,14 @@
       <c r="N32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>42</v>
+      <c r="O32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>42</v>
@@ -3540,8 +3543,8 @@
       <c r="T32" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U32" s="2" t="s">
-        <v>42</v>
+      <c r="U32" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V32" s="2" t="s">
         <v>42</v>
@@ -3578,8 +3581,8 @@
       <c r="C33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>42</v>
+      <c r="D33" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>42</v>
@@ -3599,11 +3602,11 @@
       <c r="J33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>41</v>
+      <c r="K33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>42</v>
@@ -3614,11 +3617,11 @@
       <c r="O33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>41</v>
+      <c r="P33" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>42</v>
@@ -3629,8 +3632,8 @@
       <c r="T33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>41</v>
+      <c r="U33" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>42</v>
@@ -3845,8 +3848,8 @@
       <c r="C36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>41</v>
+      <c r="D36" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>42</v>
@@ -3866,11 +3869,11 @@
       <c r="J36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>42</v>
+      <c r="K36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>42</v>
@@ -3881,11 +3884,11 @@
       <c r="O36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>42</v>
+      <c r="P36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>42</v>
@@ -3896,8 +3899,8 @@
       <c r="T36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U36" s="2" t="s">
-        <v>42</v>
+      <c r="U36" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>42</v>
@@ -3937,20 +3940,20 @@
       <c r="D37" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>41</v>
+      <c r="E37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>41</v>
+      <c r="I37" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>42</v>
@@ -3961,11 +3964,11 @@
       <c r="L37" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M37" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>41</v>
+      <c r="M37" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O37" s="2" t="s">
         <v>42</v>
@@ -4023,23 +4026,23 @@
       <c r="C38" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>42</v>
+      <c r="D38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>42</v>
+      <c r="I38" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>42</v>
@@ -4050,11 +4053,11 @@
       <c r="L38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>42</v>
+      <c r="M38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>42</v>
@@ -4086,8 +4089,8 @@
       <c r="X38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y38" s="1" t="s">
-        <v>41</v>
+      <c r="Y38" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Z38" s="2" t="s">
         <v>42</v>
@@ -4112,41 +4115,41 @@
       <c r="C39" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>41</v>
+      <c r="D39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>41</v>
+      <c r="I39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>41</v>
+      <c r="K39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>41</v>
+      <c r="M39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P39" s="2" t="s">
         <v>42</v>
@@ -4154,17 +4157,17 @@
       <c r="Q39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>41</v>
+      <c r="R39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U39" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>42</v>
@@ -4175,8 +4178,8 @@
       <c r="X39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y39" s="2" t="s">
-        <v>42</v>
+      <c r="Y39" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>42</v>
@@ -4204,26 +4207,26 @@
       <c r="D40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>42</v>
+      <c r="E40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I40" s="2" t="s">
-        <v>42</v>
+      <c r="I40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>42</v>
+      <c r="K40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>42</v>
@@ -4231,11 +4234,11 @@
       <c r="M40" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>42</v>
+      <c r="N40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P40" s="2" t="s">
         <v>42</v>
@@ -4243,17 +4246,17 @@
       <c r="Q40" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U40" s="2" t="s">
-        <v>42</v>
+      <c r="R40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U40" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>42</v>
@@ -4293,20 +4296,20 @@
       <c r="D41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>41</v>
+      <c r="E41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>41</v>
+      <c r="I41" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>42</v>
@@ -4320,8 +4323,8 @@
       <c r="M41" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N41" s="1" t="s">
-        <v>41</v>
+      <c r="N41" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>42</v>
@@ -4382,20 +4385,20 @@
       <c r="D42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>42</v>
+      <c r="E42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I42" s="2" t="s">
-        <v>42</v>
+      <c r="I42" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>42</v>
@@ -4406,11 +4409,11 @@
       <c r="L42" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N42" s="2" t="s">
-        <v>42</v>
+      <c r="M42" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>42</v>
@@ -4483,8 +4486,8 @@
       <c r="H43" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>41</v>
+      <c r="I43" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>42</v>
@@ -4495,11 +4498,11 @@
       <c r="L43" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>41</v>
+      <c r="M43" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>42</v>
@@ -4560,14 +4563,14 @@
       <c r="D44" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>41</v>
+      <c r="E44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>42</v>
@@ -4655,20 +4658,20 @@
       <c r="F45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G45" s="2" t="s">
-        <v>42</v>
+      <c r="G45" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>42</v>
+      <c r="I45" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>41</v>
+      <c r="K45" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>42</v>
@@ -4676,14 +4679,14 @@
       <c r="M45" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>42</v>
+      <c r="N45" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P45" s="1" t="s">
-        <v>41</v>
+      <c r="P45" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q45" s="2" t="s">
         <v>42</v>
@@ -4697,8 +4700,8 @@
       <c r="T45" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U45" s="1" t="s">
-        <v>41</v>
+      <c r="U45" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>42</v>
@@ -4738,11 +4741,11 @@
       <c r="D46" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>42</v>
+      <c r="E46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>42</v>
@@ -4771,20 +4774,20 @@
       <c r="O46" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>42</v>
+      <c r="P46" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R46" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>41</v>
+      <c r="R46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S46" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T46" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U46" s="1" t="s">
         <v>41</v>
@@ -4827,26 +4830,26 @@
       <c r="D47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>41</v>
+      <c r="E47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>41</v>
+      <c r="I47" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K47" s="2" t="s">
-        <v>42</v>
+      <c r="K47" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>42</v>
@@ -4854,8 +4857,8 @@
       <c r="M47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N47" s="1" t="s">
-        <v>41</v>
+      <c r="N47" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>42</v>
@@ -4866,17 +4869,17 @@
       <c r="Q47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R47" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U47" s="2" t="s">
-        <v>42</v>
+      <c r="R47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>42</v>
@@ -4910,20 +4913,20 @@
       <c r="B48" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>42</v>
+      <c r="C48" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>42</v>
+      <c r="E48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>42</v>
@@ -4999,8 +5002,8 @@
       <c r="B49" t="s">
         <v>88</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>41</v>
+      <c r="C49" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>41</v>
@@ -5195,8 +5198,8 @@
       <c r="H51" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>42</v>
+      <c r="I51" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>42</v>
@@ -5207,11 +5210,11 @@
       <c r="L51" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M51" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N51" s="2" t="s">
-        <v>42</v>
+      <c r="M51" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>42</v>
@@ -5272,11 +5275,11 @@
       <c r="D52" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>41</v>
+      <c r="E52" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>42</v>
@@ -5290,14 +5293,14 @@
       <c r="J52" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>41</v>
+      <c r="K52" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>41</v>
+      <c r="M52" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>42</v>
@@ -5305,8 +5308,8 @@
       <c r="O52" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>41</v>
+      <c r="P52" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>42</v>
@@ -5320,8 +5323,8 @@
       <c r="T52" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U52" s="1" t="s">
-        <v>41</v>
+      <c r="U52" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>42</v>
@@ -5367,14 +5370,14 @@
       <c r="F53" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>41</v>
+      <c r="G53" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>41</v>
+      <c r="I53" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>42</v>
@@ -5415,11 +5418,11 @@
       <c r="V53" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W53" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X53" s="1" t="s">
-        <v>41</v>
+      <c r="W53" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>42</v>
@@ -5459,50 +5462,50 @@
       <c r="G54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H54" s="1" t="s">
-        <v>41</v>
+      <c r="H54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>41</v>
+      <c r="J54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L54" s="1" t="s">
-        <v>41</v>
+      <c r="L54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>41</v>
+      <c r="N54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>41</v>
+      <c r="Q54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U54" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V54" s="1" t="s">
-        <v>41</v>
+      <c r="V54" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="W54" s="1" t="s">
         <v>41</v>
@@ -5578,14 +5581,14 @@
       <c r="Q55" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="R55" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S55" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T55" s="2" t="s">
-        <v>42</v>
+      <c r="R55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U55" s="1" t="s">
         <v>41</v>
@@ -5637,35 +5640,35 @@
       <c r="G56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>42</v>
+      <c r="H56" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J56" s="2" t="s">
-        <v>42</v>
+      <c r="J56" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="K56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L56" s="2" t="s">
-        <v>42</v>
+      <c r="L56" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N56" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>42</v>
+      <c r="N56" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Q56" s="2" t="s">
-        <v>42</v>
+      <c r="Q56" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="R56" s="2" t="s">
         <v>42</v>
@@ -5679,8 +5682,8 @@
       <c r="U56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V56" s="2" t="s">
-        <v>42</v>
+      <c r="V56" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="W56" s="1" t="s">
         <v>41</v>
@@ -5717,20 +5720,20 @@
       <c r="D57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>42</v>
+      <c r="E57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I57" s="2" t="s">
-        <v>42</v>
+      <c r="I57" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>42</v>
@@ -5750,20 +5753,20 @@
       <c r="O57" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P57" s="2" t="s">
-        <v>42</v>
+      <c r="P57" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R57" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>41</v>
+      <c r="R57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T57" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U57" s="1" t="s">
         <v>41</v>
@@ -5824,14 +5827,14 @@
       <c r="J58" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>42</v>
+      <c r="K58" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>42</v>
+      <c r="M58" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>42</v>
@@ -5845,26 +5848,26 @@
       <c r="Q58" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R58" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S58" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T58" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U58" s="2" t="s">
-        <v>42</v>
+      <c r="R58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U58" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W58" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X58" s="2" t="s">
-        <v>42</v>
+      <c r="W58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>42</v>
@@ -5895,44 +5898,44 @@
       <c r="D59" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>41</v>
+      <c r="E59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="R59" s="2" t="s">
         <v>42</v>
@@ -5943,17 +5946,17 @@
       <c r="T59" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W59" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X59" s="1" t="s">
-        <v>41</v>
+      <c r="U59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>42</v>
@@ -5993,35 +5996,35 @@
       <c r="G60" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>42</v>
+      <c r="H60" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>42</v>
+      <c r="J60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>42</v>
+      <c r="P60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>42</v>
@@ -6032,17 +6035,17 @@
       <c r="T60" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X60" s="2" t="s">
-        <v>42</v>
+      <c r="U60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>42</v>
@@ -6070,23 +6073,23 @@
       <c r="C61" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>42</v>
+      <c r="D61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I61" s="2" t="s">
-        <v>42</v>
+      <c r="I61" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>42</v>
@@ -6103,8 +6106,8 @@
       <c r="N61" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O61" s="2" t="s">
-        <v>42</v>
+      <c r="O61" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>42</v>
@@ -6159,23 +6162,23 @@
       <c r="C62" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D62" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>41</v>
+      <c r="D62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>41</v>
+      <c r="I62" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>42</v>
@@ -6192,8 +6195,8 @@
       <c r="N62" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O62" s="1" t="s">
-        <v>41</v>
+      <c r="O62" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>42</v>
@@ -6349,26 +6352,26 @@
       <c r="G64" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>41</v>
+      <c r="H64" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>41</v>
+      <c r="J64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>41</v>
@@ -6379,23 +6382,23 @@
       <c r="Q64" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V64" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W64" s="1" t="s">
-        <v>41</v>
+      <c r="R64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V64" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W64" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X64" s="2" t="s">
         <v>42</v>
@@ -6438,26 +6441,26 @@
       <c r="G65" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H65" s="2" t="s">
-        <v>42</v>
+      <c r="H65" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N65" s="2" t="s">
-        <v>42</v>
+      <c r="J65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>41</v>
@@ -6468,23 +6471,23 @@
       <c r="Q65" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V65" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W65" s="2" t="s">
-        <v>42</v>
+      <c r="R65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X65" s="2" t="s">
         <v>42</v>
@@ -6515,23 +6518,23 @@
       <c r="C66" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>42</v>
+      <c r="D66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>42</v>
+      <c r="I66" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>42</v>
@@ -6548,8 +6551,8 @@
       <c r="N66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O66" s="2" t="s">
-        <v>42</v>
+      <c r="O66" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>42</v>
@@ -6578,8 +6581,8 @@
       <c r="X66" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y66" s="1" t="s">
-        <v>41</v>
+      <c r="Y66" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Z66" s="2" t="s">
         <v>42</v>
@@ -6604,14 +6607,14 @@
       <c r="C67" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>41</v>
+      <c r="D67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>42</v>
@@ -6625,14 +6628,14 @@
       <c r="J67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>41</v>
+      <c r="K67" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M67" s="1" t="s">
-        <v>41</v>
+      <c r="M67" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>42</v>
@@ -6640,8 +6643,8 @@
       <c r="O67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P67" s="1" t="s">
-        <v>41</v>
+      <c r="P67" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q67" s="2" t="s">
         <v>42</v>
@@ -6655,20 +6658,20 @@
       <c r="T67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U67" s="1" t="s">
-        <v>41</v>
+      <c r="U67" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V67" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W67" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X67" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y67" s="2" t="s">
-        <v>42</v>
+      <c r="W67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y67" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Z67" s="2" t="s">
         <v>42</v>
@@ -6693,14 +6696,14 @@
       <c r="C68" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>42</v>
+      <c r="D68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>42</v>
@@ -6714,14 +6717,14 @@
       <c r="J68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K68" s="2" t="s">
-        <v>42</v>
+      <c r="K68" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M68" s="2" t="s">
-        <v>42</v>
+      <c r="M68" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>42</v>
@@ -6729,8 +6732,8 @@
       <c r="O68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P68" s="2" t="s">
-        <v>42</v>
+      <c r="P68" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>42</v>
@@ -6744,17 +6747,17 @@
       <c r="T68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U68" s="2" t="s">
-        <v>42</v>
+      <c r="U68" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V68" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W68" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X68" s="2" t="s">
-        <v>42</v>
+      <c r="W68" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X68" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y68" s="2" t="s">
         <v>42</v>
@@ -6782,8 +6785,8 @@
       <c r="C69" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>41</v>
+      <c r="D69" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>42</v>
@@ -6892,14 +6895,14 @@
       <c r="J70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>41</v>
+      <c r="K70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M70" s="1" t="s">
-        <v>41</v>
+      <c r="M70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>42</v>
@@ -6913,26 +6916,26 @@
       <c r="Q70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U70" s="1" t="s">
-        <v>41</v>
+      <c r="R70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V70" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W70" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X70" s="1" t="s">
-        <v>41</v>
+      <c r="W70" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y70" s="2" t="s">
         <v>42</v>
@@ -6963,38 +6966,38 @@
       <c r="D71" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E71" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>41</v>
+      <c r="E71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>41</v>
+      <c r="I71" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>42</v>
+      <c r="K71" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M71" s="2" t="s">
-        <v>42</v>
+      <c r="M71" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O71" s="1" t="s">
-        <v>41</v>
+      <c r="O71" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>42</v>
@@ -7002,26 +7005,26 @@
       <c r="Q71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R71" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S71" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T71" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U71" s="2" t="s">
-        <v>42</v>
+      <c r="R71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U71" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W71" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X71" s="2" t="s">
-        <v>42</v>
+      <c r="W71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X71" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y71" s="2" t="s">
         <v>42</v>
@@ -7141,20 +7144,20 @@
       <c r="D73" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>42</v>
+      <c r="E73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I73" s="2" t="s">
-        <v>42</v>
+      <c r="I73" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>42</v>
@@ -7171,8 +7174,8 @@
       <c r="N73" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O73" s="2" t="s">
-        <v>42</v>
+      <c r="O73" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>42</v>
@@ -7230,20 +7233,20 @@
       <c r="D74" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G74" s="1" t="s">
-        <v>41</v>
+      <c r="E74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>41</v>
+      <c r="I74" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>42</v>
@@ -7260,8 +7263,8 @@
       <c r="N74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O74" s="1" t="s">
-        <v>41</v>
+      <c r="O74" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>42</v>
@@ -7290,8 +7293,8 @@
       <c r="X74" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y74" s="1" t="s">
-        <v>41</v>
+      <c r="Y74" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Z74" s="2" t="s">
         <v>42</v>
@@ -7313,29 +7316,29 @@
       <c r="B75" t="s">
         <v>114</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>42</v>
+      <c r="C75" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>41</v>
+      <c r="H75" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>41</v>
+      <c r="J75" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>42</v>
@@ -7349,8 +7352,8 @@
       <c r="N75" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O75" s="2" t="s">
-        <v>42</v>
+      <c r="O75" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>42</v>
@@ -7379,8 +7382,8 @@
       <c r="X75" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y75" s="2" t="s">
-        <v>42</v>
+      <c r="Y75" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Z75" s="2" t="s">
         <v>42</v>
@@ -7402,17 +7405,17 @@
       <c r="B76" t="s">
         <v>115</v>
       </c>
-      <c r="C76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>41</v>
+      <c r="C76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>41</v>
@@ -7426,14 +7429,14 @@
       <c r="J76" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>41</v>
+      <c r="K76" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M76" s="1" t="s">
-        <v>41</v>
+      <c r="M76" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>42</v>
@@ -7447,17 +7450,17 @@
       <c r="Q76" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T76" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U76" s="1" t="s">
-        <v>41</v>
+      <c r="R76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U76" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V76" s="2" t="s">
         <v>42</v>
@@ -7494,35 +7497,35 @@
       <c r="C77" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>42</v>
+      <c r="D77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M77" s="2" t="s">
-        <v>42</v>
+      <c r="M77" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>42</v>
@@ -7536,17 +7539,17 @@
       <c r="Q77" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T77" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U77" s="2" t="s">
-        <v>42</v>
+      <c r="R77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U77" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V77" s="2" t="s">
         <v>42</v>
@@ -7761,14 +7764,14 @@
       <c r="C80" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>41</v>
+      <c r="D80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>42</v>
@@ -7803,26 +7806,26 @@
       <c r="Q80" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U80" s="1" t="s">
-        <v>41</v>
+      <c r="R80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V80" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W80" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X80" s="1" t="s">
-        <v>41</v>
+      <c r="W80" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y80" s="2" t="s">
         <v>42</v>
@@ -7853,11 +7856,11 @@
       <c r="D81" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>42</v>
+      <c r="E81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>42</v>
@@ -7892,26 +7895,26 @@
       <c r="Q81" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U81" s="2" t="s">
-        <v>42</v>
+      <c r="R81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U81" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V81" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W81" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X81" s="2" t="s">
-        <v>42</v>
+      <c r="W81" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X81" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y81" s="2" t="s">
         <v>42</v>
@@ -7936,17 +7939,17 @@
       <c r="B82" t="s">
         <v>121</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>41</v>
+      <c r="C82" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>42</v>
@@ -8025,17 +8028,17 @@
       <c r="B83" t="s">
         <v>122</v>
       </c>
-      <c r="C83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>42</v>
+      <c r="C83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>42</v>
@@ -8120,11 +8123,11 @@
       <c r="D84" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>41</v>
+      <c r="E84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>42</v>
@@ -8138,14 +8141,14 @@
       <c r="J84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>41</v>
+      <c r="K84" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>41</v>
+      <c r="M84" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>42</v>
@@ -8153,32 +8156,32 @@
       <c r="O84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P84" s="1" t="s">
-        <v>41</v>
+      <c r="P84" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U84" s="1" t="s">
-        <v>41</v>
+      <c r="R84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W84" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X84" s="1" t="s">
-        <v>41</v>
+      <c r="W84" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X84" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y84" s="2" t="s">
         <v>42</v>
@@ -8221,8 +8224,8 @@
       <c r="H85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>42</v>
+      <c r="I85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>42</v>
@@ -8248,14 +8251,14 @@
       <c r="Q85" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R85" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S85" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T85" s="2" t="s">
-        <v>42</v>
+      <c r="R85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S85" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T85" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U85" s="1" t="s">
         <v>41</v>
@@ -8298,11 +8301,11 @@
       <c r="D86" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>42</v>
+      <c r="E86" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>42</v>
@@ -8310,20 +8313,20 @@
       <c r="H86" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>42</v>
+      <c r="I86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>42</v>
+      <c r="K86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M86" s="2" t="s">
-        <v>42</v>
+      <c r="M86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>42</v>
@@ -8331,8 +8334,8 @@
       <c r="O86" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P86" s="2" t="s">
-        <v>42</v>
+      <c r="P86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q86" s="2" t="s">
         <v>42</v>
@@ -8346,17 +8349,17 @@
       <c r="T86" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U86" s="2" t="s">
-        <v>42</v>
+      <c r="U86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V86" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W86" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X86" s="2" t="s">
-        <v>42</v>
+      <c r="W86" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X86" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y86" s="2" t="s">
         <v>42</v>
@@ -8384,8 +8387,8 @@
       <c r="C87" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D87" s="2" t="s">
-        <v>42</v>
+      <c r="D87" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>42</v>
@@ -8473,14 +8476,14 @@
       <c r="C88" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>41</v>
+      <c r="D88" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>41</v>
+      <c r="F88" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>42</v>
@@ -8562,8 +8565,8 @@
       <c r="C89" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>42</v>
+      <c r="D89" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>42</v>
@@ -8657,8 +8660,8 @@
       <c r="E90" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>42</v>
+      <c r="F90" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>42</v>
@@ -8829,14 +8832,14 @@
       <c r="C92" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>41</v>
+      <c r="D92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>42</v>
@@ -8871,26 +8874,26 @@
       <c r="Q92" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U92" s="1" t="s">
-        <v>41</v>
+      <c r="R92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U92" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W92" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X92" s="1" t="s">
-        <v>41</v>
+      <c r="W92" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>42</v>
@@ -8921,11 +8924,11 @@
       <c r="D93" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>42</v>
+      <c r="E93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>42</v>
@@ -8963,23 +8966,23 @@
       <c r="R93" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="S93" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T93" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U93" s="2" t="s">
-        <v>42</v>
+      <c r="S93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U93" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V93" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W93" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X93" s="2" t="s">
-        <v>42</v>
+      <c r="W93" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X93" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y93" s="2" t="s">
         <v>42</v>
@@ -9010,11 +9013,11 @@
       <c r="D94" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>41</v>
+      <c r="E94" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>42</v>
@@ -9049,8 +9052,8 @@
       <c r="Q94" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R94" s="2" t="s">
-        <v>42</v>
+      <c r="R94" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="S94" s="2" t="s">
         <v>42</v>
@@ -9058,17 +9061,17 @@
       <c r="T94" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U94" s="1" t="s">
-        <v>41</v>
+      <c r="U94" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W94" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X94" s="1" t="s">
-        <v>41</v>
+      <c r="W94" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y94" s="2" t="s">
         <v>42</v>
@@ -9096,14 +9099,14 @@
       <c r="C95" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>42</v>
+      <c r="D95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>42</v>
@@ -9147,17 +9150,17 @@
       <c r="T95" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U95" s="2" t="s">
-        <v>42</v>
+      <c r="U95" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V95" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W95" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X95" s="2" t="s">
-        <v>42</v>
+      <c r="W95" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X95" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>42</v>
@@ -9185,8 +9188,8 @@
       <c r="C96" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>41</v>
+      <c r="D96" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>42</v>
@@ -9274,8 +9277,8 @@
       <c r="C97" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>42</v>
+      <c r="D97" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>42</v>
@@ -9363,32 +9366,32 @@
       <c r="C98" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G98" s="1" t="s">
-        <v>41</v>
+      <c r="D98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I98" s="1" t="s">
-        <v>41</v>
+      <c r="I98" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L98" s="1" t="s">
-        <v>41</v>
+      <c r="K98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>42</v>
@@ -9396,35 +9399,35 @@
       <c r="N98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="O98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P98" s="1" t="s">
-        <v>41</v>
+      <c r="O98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P98" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U98" s="1" t="s">
-        <v>41</v>
+      <c r="R98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V98" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W98" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X98" s="1" t="s">
-        <v>41</v>
+      <c r="W98" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>42</v>
@@ -9455,14 +9458,14 @@
       <c r="D99" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>42</v>
+      <c r="E99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>42</v>
@@ -9473,23 +9476,23 @@
       <c r="J99" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M99" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P99" s="2" t="s">
-        <v>42</v>
+      <c r="K99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q99" s="2" t="s">
         <v>42</v>
@@ -9503,17 +9506,17 @@
       <c r="T99" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="U99" s="2" t="s">
-        <v>42</v>
+      <c r="U99" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W99" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X99" s="2" t="s">
-        <v>42</v>
+      <c r="W99" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X99" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y99" s="2" t="s">
         <v>42</v>
@@ -9556,8 +9559,8 @@
       <c r="H100" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I100" s="2" t="s">
-        <v>42</v>
+      <c r="I100" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>42</v>
@@ -9571,8 +9574,8 @@
       <c r="M100" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N100" s="2" t="s">
-        <v>42</v>
+      <c r="N100" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>42</v>
@@ -9633,38 +9636,38 @@
       <c r="D101" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G101" s="1" t="s">
-        <v>41</v>
+      <c r="E101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I101" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>41</v>
+      <c r="I101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N101" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>41</v>
+      <c r="N101" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O101" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P101" s="2" t="s">
         <v>42</v>
@@ -9672,14 +9675,14 @@
       <c r="Q101" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S101" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T101" s="2" t="s">
-        <v>42</v>
+      <c r="R101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U101" s="2" t="s">
         <v>42</v>
@@ -9687,8 +9690,8 @@
       <c r="V101" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W101" s="1" t="s">
-        <v>41</v>
+      <c r="W101" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X101" s="2" t="s">
         <v>42</v>
@@ -9719,26 +9722,26 @@
       <c r="C102" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>42</v>
+      <c r="D102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>42</v>
+      <c r="I102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>41</v>
@@ -9746,17 +9749,17 @@
       <c r="L102" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O102" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P102" s="1" t="s">
-        <v>41</v>
+      <c r="M102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P102" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q102" s="2" t="s">
         <v>42</v>
@@ -9770,14 +9773,14 @@
       <c r="T102" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U102" s="1" t="s">
-        <v>41</v>
+      <c r="U102" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V102" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W102" s="2" t="s">
-        <v>42</v>
+      <c r="W102" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X102" s="2" t="s">
         <v>42</v>
@@ -9844,8 +9847,8 @@
       <c r="O103" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="P103" s="2" t="s">
-        <v>42</v>
+      <c r="P103" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q103" s="2" t="s">
         <v>42</v>
@@ -10099,8 +10102,8 @@
       <c r="K106" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L106" s="2" t="s">
-        <v>42</v>
+      <c r="L106" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>42</v>
@@ -10188,8 +10191,8 @@
       <c r="K107" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L107" s="1" t="s">
-        <v>41</v>
+      <c r="L107" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M107" s="2" t="s">
         <v>42</v>
@@ -10366,8 +10369,8 @@
       <c r="K109" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L109" s="2" t="s">
-        <v>42</v>
+      <c r="L109" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M109" s="2" t="s">
         <v>42</v>
@@ -10455,8 +10458,8 @@
       <c r="K110" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L110" s="1" t="s">
-        <v>41</v>
+      <c r="L110" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M110" s="2" t="s">
         <v>42</v>
@@ -10811,8 +10814,8 @@
       <c r="K114" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L114" s="2" t="s">
-        <v>42</v>
+      <c r="L114" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M114" s="2" t="s">
         <v>42</v>
@@ -10876,68 +10879,68 @@
       <c r="C115" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J115" s="1" t="s">
-        <v>41</v>
+      <c r="D115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K115" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P115" s="1" t="s">
-        <v>41</v>
+      <c r="L115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P115" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q115" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T115" s="1" t="s">
-        <v>41</v>
+      <c r="R115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T115" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U115" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W115" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X115" s="1" t="s">
-        <v>41</v>
+      <c r="V115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W115" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X115" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y115" s="2" t="s">
         <v>42</v>
@@ -10977,44 +10980,44 @@
       <c r="G116" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H116" s="2" t="s">
-        <v>42</v>
+      <c r="H116" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="J116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P116" s="2" t="s">
-        <v>42</v>
+      <c r="J116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P116" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q116" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S116" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T116" s="2" t="s">
-        <v>42</v>
+      <c r="R116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S116" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T116" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U116" s="1" t="s">
         <v>41</v>
@@ -11054,23 +11057,23 @@
       <c r="C117" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>42</v>
+      <c r="D117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I117" s="2" t="s">
-        <v>42</v>
+      <c r="I117" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>42</v>
@@ -11105,17 +11108,17 @@
       <c r="T117" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="U117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="V117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W117" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X117" s="2" t="s">
-        <v>42</v>
+      <c r="U117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W117" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X117" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y117" s="2" t="s">
         <v>42</v>
@@ -11229,17 +11232,17 @@
       <c r="B119" t="s">
         <v>158</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>41</v>
+      <c r="C119" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>42</v>
@@ -11247,23 +11250,23 @@
       <c r="H119" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I119" s="1" t="s">
-        <v>41</v>
+      <c r="I119" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K119" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N119" s="1" t="s">
-        <v>41</v>
+      <c r="K119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N119" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="O119" s="2" t="s">
         <v>42</v>
@@ -11318,8 +11321,8 @@
       <c r="B120" t="s">
         <v>159</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>41</v>
+      <c r="C120" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>41</v>
@@ -11336,23 +11339,23 @@
       <c r="H120" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I120" s="2" t="s">
-        <v>42</v>
+      <c r="I120" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K120" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L120" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M120" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N120" s="2" t="s">
-        <v>42</v>
+      <c r="K120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>42</v>
@@ -11413,11 +11416,11 @@
       <c r="D121" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>42</v>
+      <c r="E121" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>42</v>
@@ -11502,32 +11505,32 @@
       <c r="D122" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>41</v>
+      <c r="E122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K122" s="1" t="s">
-        <v>41</v>
+      <c r="K122" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M122" s="1" t="s">
-        <v>41</v>
+      <c r="M122" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>42</v>
@@ -11541,26 +11544,26 @@
       <c r="Q122" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W122" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X122" s="1" t="s">
-        <v>41</v>
+      <c r="R122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>42</v>
@@ -11597,14 +11600,14 @@
       <c r="F123" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G123" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>42</v>
+      <c r="G123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>42</v>
@@ -11630,20 +11633,20 @@
       <c r="Q123" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R123" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S123" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T123" s="2" t="s">
-        <v>42</v>
+      <c r="R123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="U123" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V123" s="2" t="s">
-        <v>42</v>
+      <c r="V123" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="W123" s="1" t="s">
         <v>41</v>
@@ -11689,8 +11692,8 @@
       <c r="G124" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>41</v>
+      <c r="H124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="I124" s="2" t="s">
         <v>42</v>
@@ -11719,20 +11722,20 @@
       <c r="Q124" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R124" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S124" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T124" s="1" t="s">
-        <v>41</v>
+      <c r="R124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S124" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="U124" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V124" s="1" t="s">
-        <v>41</v>
+      <c r="V124" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="W124" s="1" t="s">
         <v>41</v>
@@ -11763,8 +11766,8 @@
       <c r="B125" t="s">
         <v>164</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>42</v>
+      <c r="C125" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>41</v>
@@ -11775,32 +11778,32 @@
       <c r="F125" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G125" s="1" t="s">
-        <v>41</v>
+      <c r="G125" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H125" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I125" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>41</v>
+      <c r="I125" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="K125" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L125" s="1" t="s">
-        <v>41</v>
+      <c r="L125" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N125" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O125" s="1" t="s">
-        <v>41</v>
+      <c r="N125" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O125" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P125" s="2" t="s">
         <v>42</v>
@@ -11808,17 +11811,17 @@
       <c r="Q125" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T125" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U125" s="2" t="s">
-        <v>42</v>
+      <c r="R125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T125" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U125" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V125" s="1" t="s">
         <v>41</v>
@@ -11832,14 +11835,14 @@
       <c r="Y125" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Z125" s="1" t="s">
-        <v>41</v>
+      <c r="Z125" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="AA125" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AB125" s="1" t="s">
-        <v>41</v>
+      <c r="AB125" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="AC125" s="2" t="s">
         <v>42</v>
@@ -11855,41 +11858,41 @@
       <c r="C126" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O126" s="2" t="s">
-        <v>42</v>
+      <c r="D126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O126" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P126" s="2" t="s">
         <v>42</v>
@@ -11909,14 +11912,14 @@
       <c r="U126" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W126" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X126" s="2" t="s">
-        <v>42</v>
+      <c r="V126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W126" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X126" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>42</v>
@@ -11944,44 +11947,44 @@
       <c r="C127" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="J127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="K127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="P127" s="1" t="s">
-        <v>41</v>
+      <c r="D127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Q127" s="2" t="s">
         <v>42</v>
@@ -11998,14 +12001,14 @@
       <c r="U127" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W127" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X127" s="1" t="s">
-        <v>41</v>
+      <c r="V127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W127" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X127" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y127" s="2" t="s">
         <v>42</v>
@@ -12033,44 +12036,44 @@
       <c r="C128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="P128" s="2" t="s">
-        <v>42</v>
+      <c r="D128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Q128" s="2" t="s">
         <v>42</v>
@@ -12087,14 +12090,14 @@
       <c r="U128" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="V128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="W128" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X128" s="2" t="s">
-        <v>42</v>
+      <c r="V128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W128" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X128" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>42</v>
@@ -12119,44 +12122,44 @@
       <c r="B129" t="s">
         <v>168</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>41</v>
+      <c r="C129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>41</v>
+      <c r="I129" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N129" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O129" s="1" t="s">
-        <v>41</v>
+      <c r="K129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P129" s="2" t="s">
         <v>42</v>
@@ -12179,8 +12182,8 @@
       <c r="V129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W129" s="1" t="s">
-        <v>41</v>
+      <c r="W129" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X129" s="2" t="s">
         <v>42</v>
@@ -12188,14 +12191,14 @@
       <c r="Y129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Z129" s="2" t="s">
-        <v>42</v>
+      <c r="Z129" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AA129" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AB129" s="2" t="s">
-        <v>42</v>
+      <c r="AB129" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="AC129" s="2" t="s">
         <v>42</v>
@@ -12211,41 +12214,41 @@
       <c r="C130" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>42</v>
+      <c r="D130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I130" s="2" t="s">
-        <v>42</v>
+      <c r="I130" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N130" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O130" s="2" t="s">
-        <v>42</v>
+      <c r="K130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N130" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P130" s="2" t="s">
         <v>42</v>
@@ -12268,8 +12271,8 @@
       <c r="V130" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W130" s="2" t="s">
-        <v>42</v>
+      <c r="W130" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X130" s="2" t="s">
         <v>42</v>
@@ -12300,8 +12303,8 @@
       <c r="C131" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>41</v>
+      <c r="D131" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>42</v>
@@ -12389,8 +12392,8 @@
       <c r="C132" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>42</v>
+      <c r="D132" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>42</v>
@@ -12478,41 +12481,41 @@
       <c r="C133" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>41</v>
+      <c r="D133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I133" s="1" t="s">
-        <v>41</v>
+      <c r="I133" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N133" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O133" s="1" t="s">
-        <v>41</v>
+      <c r="K133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P133" s="2" t="s">
         <v>42</v>
@@ -12535,8 +12538,8 @@
       <c r="V133" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W133" s="1" t="s">
-        <v>41</v>
+      <c r="W133" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X133" s="2" t="s">
         <v>42</v>
@@ -12576,14 +12579,14 @@
       <c r="F134" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="G134" s="2" t="s">
-        <v>42</v>
+      <c r="G134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I134" s="2" t="s">
-        <v>42</v>
+      <c r="I134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>42</v>
@@ -12591,17 +12594,17 @@
       <c r="K134" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L134" s="2" t="s">
-        <v>42</v>
+      <c r="L134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="M134" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="N134" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O134" s="2" t="s">
-        <v>42</v>
+      <c r="N134" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P134" s="2" t="s">
         <v>42</v>
@@ -12659,11 +12662,11 @@
       <c r="D135" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E135" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>42</v>
+      <c r="E135" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>42</v>
@@ -12677,14 +12680,14 @@
       <c r="J135" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K135" s="2" t="s">
-        <v>42</v>
+      <c r="K135" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L135" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M135" s="2" t="s">
-        <v>42</v>
+      <c r="M135" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N135" s="2" t="s">
         <v>42</v>
@@ -12713,8 +12716,8 @@
       <c r="V135" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W135" s="2" t="s">
-        <v>42</v>
+      <c r="W135" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X135" s="2" t="s">
         <v>42</v>
@@ -12745,8 +12748,8 @@
       <c r="C136" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>42</v>
+      <c r="D136" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>42</v>
@@ -12834,14 +12837,14 @@
       <c r="C137" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>41</v>
+      <c r="D137" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>42</v>
@@ -12855,14 +12858,14 @@
       <c r="J137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K137" s="1" t="s">
-        <v>41</v>
+      <c r="K137" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="L137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M137" s="1" t="s">
-        <v>41</v>
+      <c r="M137" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="N137" s="2" t="s">
         <v>42</v>
@@ -12891,8 +12894,8 @@
       <c r="V137" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W137" s="1" t="s">
-        <v>41</v>
+      <c r="W137" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="X137" s="2" t="s">
         <v>42</v>
@@ -12920,17 +12923,17 @@
       <c r="B138" t="s">
         <v>177</v>
       </c>
-      <c r="C138" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>42</v>
+      <c r="C138" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>42</v>
@@ -12944,14 +12947,14 @@
       <c r="J138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K138" s="2" t="s">
-        <v>42</v>
+      <c r="K138" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="L138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="M138" s="2" t="s">
-        <v>42</v>
+      <c r="M138" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>42</v>
@@ -12980,8 +12983,8 @@
       <c r="V138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W138" s="2" t="s">
-        <v>42</v>
+      <c r="W138" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="X138" s="2" t="s">
         <v>42</v>
@@ -12998,8 +13001,8 @@
       <c r="AB138" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AC138" s="1" t="s">
-        <v>41</v>
+      <c r="AC138" s="2" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="139">
@@ -13009,44 +13012,44 @@
       <c r="B139" t="s">
         <v>178</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>41</v>
+      <c r="C139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I139" s="1" t="s">
-        <v>41</v>
+      <c r="I139" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="N139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O139" s="1" t="s">
-        <v>41</v>
+      <c r="K139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O139" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="P139" s="2" t="s">
         <v>42</v>
@@ -13054,26 +13057,26 @@
       <c r="Q139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="S139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="T139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="U139" s="1" t="s">
-        <v>41</v>
+      <c r="R139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U139" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="V139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W139" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="X139" s="1" t="s">
-        <v>41</v>
+      <c r="W139" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X139" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="Y139" s="2" t="s">
         <v>42</v>
@@ -13087,8 +13090,8 @@
       <c r="AB139" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AC139" s="2" t="s">
-        <v>42</v>
+      <c r="AC139" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="140">
@@ -13098,8 +13101,8 @@
       <c r="B140" t="s">
         <v>179</v>
       </c>
-      <c r="C140" s="2" t="s">
-        <v>42</v>
+      <c r="C140" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>41</v>
@@ -13107,35 +13110,35 @@
       <c r="E140" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>42</v>
+      <c r="F140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="I140" s="2" t="s">
-        <v>42</v>
+      <c r="I140" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O140" s="2" t="s">
-        <v>42</v>
+      <c r="K140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="N140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="P140" s="2" t="s">
         <v>42</v>
@@ -13143,26 +13146,26 @@
       <c r="Q140" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="R140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="S140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="T140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="U140" s="2" t="s">
-        <v>42</v>
+      <c r="R140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="T140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="U140" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V140" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="W140" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="X140" s="2" t="s">
-        <v>42</v>
+      <c r="W140" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="X140" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="Y140" s="2" t="s">
         <v>42</v>
@@ -13177,6 +13180,95 @@
         <v>42</v>
       </c>
       <c r="AC140" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="3">
+        <v>180</v>
+      </c>
+      <c r="B141" t="s">
+        <v>180</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="N141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="O141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="P141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="T141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="U141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="V141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="X141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB141" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC141" s="2" t="s">
         <v>42</v>
       </c>
     </row>
@@ -13192,12 +13284,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4265" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="330">
   <si>
     <t>User Right</t>
   </si>
@@ -417,6 +417,9 @@
     <t>Reassign the source case of contacts</t>
   </si>
   <si>
+    <t>CONTACT_MERGE</t>
+  </si>
+  <si>
     <t>MANAGE_EXTERNAL_SYMPTOM_JOURNAL</t>
   </si>
   <si>
@@ -999,7 +1002,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.59.0-SNAPSHOT</t>
+    <t>1.60.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD147"/>
+  <dimension ref="A1:AD148"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -5438,28 +5441,28 @@
         <v>134</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>42</v>
+        <v>134</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>42</v>
+      <c r="G49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>42</v>
+      <c r="I49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>43</v>
@@ -5470,11 +5473,11 @@
       <c r="L49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N49" s="1" t="s">
-        <v>42</v>
+      <c r="M49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>43</v>
@@ -5524,25 +5527,25 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
+        <v>135</v>
+      </c>
+      <c r="B50" t="s">
         <v>136</v>
       </c>
-      <c r="B50" t="s">
-        <v>137</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>42</v>
+      <c r="C50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>43</v>
+      <c r="E50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>43</v>
@@ -5613,10 +5616,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
+        <v>137</v>
+      </c>
+      <c r="B51" t="s">
         <v>138</v>
-      </c>
-      <c r="B51" t="s">
-        <v>139</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>42</v>
@@ -5702,11 +5705,11 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
+        <v>139</v>
+      </c>
+      <c r="B52" t="s">
         <v>140</v>
       </c>
-      <c r="B52" t="s">
-        <v>141</v>
-      </c>
       <c r="C52" s="1" t="s">
         <v>42</v>
       </c>
@@ -5725,8 +5728,8 @@
       <c r="H52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>43</v>
+      <c r="I52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>43</v>
@@ -5737,11 +5740,11 @@
       <c r="L52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>43</v>
+      <c r="M52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>43</v>
@@ -5791,22 +5794,22 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="3">
+        <v>141</v>
+      </c>
+      <c r="B53" t="s">
         <v>142</v>
       </c>
-      <c r="B53" t="s">
-        <v>143</v>
-      </c>
       <c r="C53" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>42</v>
+      <c r="E53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>43</v>
@@ -5820,14 +5823,14 @@
       <c r="J53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K53" s="1" t="s">
-        <v>42</v>
+      <c r="K53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>42</v>
+      <c r="M53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>43</v>
@@ -5835,8 +5838,8 @@
       <c r="O53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P53" s="1" t="s">
-        <v>42</v>
+      <c r="P53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q53" s="2" t="s">
         <v>43</v>
@@ -5850,8 +5853,8 @@
       <c r="T53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U53" s="1" t="s">
-        <v>42</v>
+      <c r="U53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V53" s="2" t="s">
         <v>43</v>
@@ -5880,11 +5883,11 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
+        <v>143</v>
+      </c>
+      <c r="B54" t="s">
         <v>144</v>
       </c>
-      <c r="B54" t="s">
-        <v>145</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>42</v>
       </c>
@@ -5897,14 +5900,14 @@
       <c r="F54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>42</v>
+      <c r="G54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>42</v>
+      <c r="I54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>43</v>
@@ -5945,11 +5948,11 @@
       <c r="V54" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X54" s="1" t="s">
-        <v>42</v>
+      <c r="W54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>43</v>
@@ -5969,11 +5972,11 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
+        <v>145</v>
+      </c>
+      <c r="B55" t="s">
         <v>146</v>
       </c>
-      <c r="B55" t="s">
-        <v>147</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>42</v>
       </c>
@@ -5989,50 +5992,50 @@
       <c r="G55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H55" s="1" t="s">
-        <v>42</v>
+      <c r="H55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>42</v>
+      <c r="J55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L55" s="1" t="s">
-        <v>42</v>
+      <c r="L55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>42</v>
+      <c r="N55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>42</v>
+      <c r="Q55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V55" s="1" t="s">
-        <v>42</v>
+      <c r="V55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="W55" s="1" t="s">
         <v>42</v>
@@ -6058,11 +6061,11 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
+        <v>147</v>
+      </c>
+      <c r="B56" t="s">
         <v>148</v>
       </c>
-      <c r="B56" t="s">
-        <v>149</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>42</v>
       </c>
@@ -6108,14 +6111,14 @@
       <c r="Q56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R56" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S56" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T56" s="2" t="s">
-        <v>43</v>
+      <c r="R56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U56" s="1" t="s">
         <v>42</v>
@@ -6147,11 +6150,11 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
+        <v>149</v>
+      </c>
+      <c r="B57" t="s">
         <v>150</v>
       </c>
-      <c r="B57" t="s">
-        <v>151</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>42</v>
       </c>
@@ -6167,35 +6170,35 @@
       <c r="G57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H57" s="2" t="s">
-        <v>43</v>
+      <c r="H57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J57" s="2" t="s">
-        <v>43</v>
+      <c r="J57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L57" s="2" t="s">
-        <v>43</v>
+      <c r="L57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N57" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>43</v>
+      <c r="N57" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q57" s="2" t="s">
-        <v>43</v>
+      <c r="Q57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>43</v>
@@ -6209,8 +6212,8 @@
       <c r="U57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V57" s="2" t="s">
-        <v>43</v>
+      <c r="V57" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="W57" s="1" t="s">
         <v>42</v>
@@ -6236,31 +6239,31 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
+        <v>151</v>
+      </c>
+      <c r="B58" t="s">
         <v>152</v>
       </c>
-      <c r="B58" t="s">
-        <v>153</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>43</v>
+      <c r="E58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I58" s="2" t="s">
-        <v>43</v>
+      <c r="I58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>43</v>
@@ -6280,20 +6283,20 @@
       <c r="O58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P58" s="2" t="s">
-        <v>43</v>
+      <c r="P58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>42</v>
+      <c r="R58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U58" s="1" t="s">
         <v>42</v>
@@ -6325,11 +6328,11 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
+        <v>153</v>
+      </c>
+      <c r="B59" t="s">
         <v>154</v>
       </c>
-      <c r="B59" t="s">
-        <v>155</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>42</v>
       </c>
@@ -6354,14 +6357,14 @@
       <c r="J59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K59" s="2" t="s">
-        <v>43</v>
+      <c r="K59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M59" s="2" t="s">
-        <v>43</v>
+      <c r="M59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>43</v>
@@ -6375,26 +6378,26 @@
       <c r="Q59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>43</v>
+      <c r="R59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X59" s="2" t="s">
-        <v>43</v>
+      <c r="W59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>43</v>
@@ -6414,55 +6417,55 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
+        <v>155</v>
+      </c>
+      <c r="B60" t="s">
         <v>156</v>
       </c>
-      <c r="B60" t="s">
-        <v>157</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>42</v>
+      <c r="E60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>43</v>
@@ -6473,17 +6476,17 @@
       <c r="T60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W60" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X60" s="1" t="s">
-        <v>42</v>
+      <c r="U60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W60" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X60" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>43</v>
@@ -6503,11 +6506,11 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
+        <v>157</v>
+      </c>
+      <c r="B61" t="s">
         <v>158</v>
       </c>
-      <c r="B61" t="s">
-        <v>159</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>42</v>
       </c>
@@ -6523,35 +6526,35 @@
       <c r="G61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="2" t="s">
-        <v>43</v>
+      <c r="H61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N61" s="2" t="s">
-        <v>43</v>
+      <c r="J61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>43</v>
+      <c r="P61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>43</v>
@@ -6562,17 +6565,17 @@
       <c r="T61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X61" s="2" t="s">
-        <v>43</v>
+      <c r="U61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>43</v>
@@ -6592,31 +6595,31 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
+        <v>159</v>
+      </c>
+      <c r="B62" t="s">
         <v>160</v>
       </c>
-      <c r="B62" t="s">
-        <v>161</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>43</v>
+      <c r="D62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I62" s="2" t="s">
-        <v>43</v>
+      <c r="I62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>43</v>
@@ -6633,8 +6636,8 @@
       <c r="N62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O62" s="2" t="s">
-        <v>43</v>
+      <c r="O62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P62" s="2" t="s">
         <v>43</v>
@@ -6681,31 +6684,31 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
+        <v>161</v>
+      </c>
+      <c r="B63" t="s">
         <v>162</v>
       </c>
-      <c r="B63" t="s">
-        <v>163</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>42</v>
+      <c r="D63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>42</v>
+      <c r="I63" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>43</v>
@@ -6722,8 +6725,8 @@
       <c r="N63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O63" s="1" t="s">
-        <v>42</v>
+      <c r="O63" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>43</v>
@@ -6770,10 +6773,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
+        <v>163</v>
+      </c>
+      <c r="B64" t="s">
         <v>164</v>
-      </c>
-      <c r="B64" t="s">
-        <v>165</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>42</v>
@@ -6859,11 +6862,11 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="3">
+        <v>165</v>
+      </c>
+      <c r="B65" t="s">
         <v>166</v>
       </c>
-      <c r="B65" t="s">
-        <v>167</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
@@ -6879,26 +6882,26 @@
       <c r="G65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H65" s="1" t="s">
-        <v>42</v>
+      <c r="H65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>42</v>
+      <c r="J65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O65" s="1" t="s">
         <v>42</v>
@@ -6909,23 +6912,23 @@
       <c r="Q65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W65" s="1" t="s">
-        <v>42</v>
+      <c r="R65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X65" s="2" t="s">
         <v>43</v>
@@ -6948,11 +6951,11 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="3">
+        <v>167</v>
+      </c>
+      <c r="B66" t="s">
         <v>168</v>
       </c>
-      <c r="B66" t="s">
-        <v>169</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>42</v>
       </c>
@@ -6968,26 +6971,26 @@
       <c r="G66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H66" s="2" t="s">
-        <v>43</v>
+      <c r="H66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N66" s="2" t="s">
-        <v>43</v>
+      <c r="J66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O66" s="1" t="s">
         <v>42</v>
@@ -6998,23 +7001,23 @@
       <c r="Q66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W66" s="2" t="s">
-        <v>43</v>
+      <c r="R66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X66" s="2" t="s">
         <v>43</v>
@@ -7037,31 +7040,31 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="3">
+        <v>169</v>
+      </c>
+      <c r="B67" t="s">
         <v>170</v>
       </c>
-      <c r="B67" t="s">
-        <v>171</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>43</v>
+      <c r="D67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>43</v>
+      <c r="I67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>43</v>
@@ -7078,8 +7081,8 @@
       <c r="N67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O67" s="2" t="s">
-        <v>43</v>
+      <c r="O67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>43</v>
@@ -7108,8 +7111,8 @@
       <c r="X67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y67" s="1" t="s">
-        <v>42</v>
+      <c r="Y67" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z67" s="2" t="s">
         <v>43</v>
@@ -7126,22 +7129,22 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="3">
+        <v>171</v>
+      </c>
+      <c r="B68" t="s">
         <v>172</v>
       </c>
-      <c r="B68" t="s">
-        <v>173</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>42</v>
+      <c r="D68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>43</v>
@@ -7155,14 +7158,14 @@
       <c r="J68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>42</v>
+      <c r="K68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M68" s="1" t="s">
-        <v>42</v>
+      <c r="M68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>43</v>
@@ -7170,8 +7173,8 @@
       <c r="O68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>42</v>
+      <c r="P68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>43</v>
@@ -7185,20 +7188,20 @@
       <c r="T68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U68" s="1" t="s">
-        <v>42</v>
+      <c r="U68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y68" s="2" t="s">
-        <v>43</v>
+      <c r="W68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>43</v>
@@ -7215,22 +7218,22 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="3">
+        <v>173</v>
+      </c>
+      <c r="B69" t="s">
         <v>174</v>
       </c>
-      <c r="B69" t="s">
-        <v>175</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>43</v>
+      <c r="D69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>43</v>
@@ -7244,14 +7247,14 @@
       <c r="J69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>43</v>
+      <c r="K69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M69" s="2" t="s">
-        <v>43</v>
+      <c r="M69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>43</v>
@@ -7259,8 +7262,8 @@
       <c r="O69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P69" s="2" t="s">
-        <v>43</v>
+      <c r="P69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>43</v>
@@ -7274,17 +7277,17 @@
       <c r="T69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U69" s="2" t="s">
-        <v>43</v>
+      <c r="U69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X69" s="2" t="s">
-        <v>43</v>
+      <c r="W69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y69" s="2" t="s">
         <v>43</v>
@@ -7304,16 +7307,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="3">
+        <v>175</v>
+      </c>
+      <c r="B70" t="s">
         <v>176</v>
       </c>
-      <c r="B70" t="s">
-        <v>177</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>42</v>
+      <c r="D70" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>43</v>
@@ -7393,11 +7396,11 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="3">
+        <v>177</v>
+      </c>
+      <c r="B71" t="s">
         <v>178</v>
       </c>
-      <c r="B71" t="s">
-        <v>179</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>42</v>
       </c>
@@ -7422,14 +7425,14 @@
       <c r="J71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>42</v>
+      <c r="K71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M71" s="1" t="s">
-        <v>42</v>
+      <c r="M71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>43</v>
@@ -7443,26 +7446,26 @@
       <c r="Q71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U71" s="1" t="s">
-        <v>42</v>
+      <c r="R71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X71" s="1" t="s">
-        <v>42</v>
+      <c r="W71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y71" s="2" t="s">
         <v>43</v>
@@ -7482,49 +7485,49 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="3">
+        <v>179</v>
+      </c>
+      <c r="B72" t="s">
         <v>180</v>
       </c>
-      <c r="B72" t="s">
-        <v>181</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>42</v>
+      <c r="E72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>42</v>
+      <c r="I72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>43</v>
+      <c r="K72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M72" s="2" t="s">
-        <v>43</v>
+      <c r="M72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>42</v>
+      <c r="O72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>43</v>
@@ -7532,26 +7535,26 @@
       <c r="Q72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U72" s="2" t="s">
-        <v>43</v>
+      <c r="R72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X72" s="2" t="s">
-        <v>43</v>
+      <c r="W72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>43</v>
@@ -7571,10 +7574,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="3">
+        <v>181</v>
+      </c>
+      <c r="B73" t="s">
         <v>182</v>
-      </c>
-      <c r="B73" t="s">
-        <v>183</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>42</v>
@@ -7660,31 +7663,31 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="3">
+        <v>183</v>
+      </c>
+      <c r="B74" t="s">
         <v>184</v>
       </c>
-      <c r="B74" t="s">
-        <v>185</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>43</v>
+      <c r="E74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I74" s="2" t="s">
-        <v>43</v>
+      <c r="I74" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>43</v>
@@ -7701,8 +7704,8 @@
       <c r="N74" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O74" s="2" t="s">
-        <v>43</v>
+      <c r="O74" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>43</v>
@@ -7749,31 +7752,31 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
+        <v>185</v>
+      </c>
+      <c r="B75" t="s">
         <v>186</v>
       </c>
-      <c r="B75" t="s">
-        <v>187</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>42</v>
+      <c r="E75" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I75" s="1" t="s">
-        <v>42</v>
+      <c r="I75" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>43</v>
@@ -7790,8 +7793,8 @@
       <c r="N75" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O75" s="1" t="s">
-        <v>42</v>
+      <c r="O75" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P75" s="2" t="s">
         <v>43</v>
@@ -7820,8 +7823,8 @@
       <c r="X75" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y75" s="1" t="s">
-        <v>42</v>
+      <c r="Y75" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z75" s="2" t="s">
         <v>43</v>
@@ -7838,7 +7841,7 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B76" t="s">
         <v>188</v>
@@ -7909,8 +7912,8 @@
       <c r="X76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y76" s="2" t="s">
-        <v>43</v>
+      <c r="Y76" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z76" s="2" t="s">
         <v>43</v>
@@ -8113,23 +8116,23 @@
       <c r="C79" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>43</v>
+      <c r="D79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>43</v>
+      <c r="I79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>43</v>
@@ -8146,8 +8149,8 @@
       <c r="N79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O79" s="2" t="s">
-        <v>43</v>
+      <c r="O79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>43</v>
@@ -8202,8 +8205,8 @@
       <c r="C80" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>42</v>
+      <c r="D80" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>43</v>
@@ -8286,13 +8289,13 @@
         <v>193</v>
       </c>
       <c r="B81" t="s">
-        <v>194</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>43</v>
+        <v>193</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>43</v>
@@ -8300,17 +8303,17 @@
       <c r="F81" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G81" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I81" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J81" s="1" t="s">
-        <v>42</v>
+      <c r="G81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>43</v>
@@ -8372,22 +8375,22 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="3">
+        <v>194</v>
+      </c>
+      <c r="B82" t="s">
         <v>195</v>
       </c>
-      <c r="B82" t="s">
-        <v>196</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>42</v>
+      <c r="C82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>42</v>
@@ -8401,14 +8404,14 @@
       <c r="J82" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K82" s="1" t="s">
-        <v>42</v>
+      <c r="K82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M82" s="1" t="s">
-        <v>42</v>
+      <c r="M82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>43</v>
@@ -8422,17 +8425,17 @@
       <c r="Q82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U82" s="1" t="s">
-        <v>42</v>
+      <c r="R82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>43</v>
@@ -8461,43 +8464,43 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="3">
+        <v>196</v>
+      </c>
+      <c r="B83" t="s">
         <v>197</v>
       </c>
-      <c r="B83" t="s">
-        <v>198</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>43</v>
+      <c r="D83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M83" s="2" t="s">
-        <v>43</v>
+      <c r="M83" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>43</v>
@@ -8511,17 +8514,17 @@
       <c r="Q83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U83" s="2" t="s">
-        <v>43</v>
+      <c r="R83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U83" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>43</v>
@@ -8550,10 +8553,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="3">
+        <v>198</v>
+      </c>
+      <c r="B84" t="s">
         <v>199</v>
-      </c>
-      <c r="B84" t="s">
-        <v>200</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>42</v>
@@ -8639,10 +8642,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="3">
+        <v>200</v>
+      </c>
+      <c r="B85" t="s">
         <v>201</v>
-      </c>
-      <c r="B85" t="s">
-        <v>202</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>42</v>
@@ -8728,22 +8731,22 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="3">
+        <v>202</v>
+      </c>
+      <c r="B86" t="s">
         <v>203</v>
       </c>
-      <c r="B86" t="s">
-        <v>204</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>42</v>
+      <c r="D86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>43</v>
@@ -8778,26 +8781,26 @@
       <c r="Q86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U86" s="1" t="s">
-        <v>42</v>
+      <c r="R86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X86" s="1" t="s">
-        <v>42</v>
+      <c r="W86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y86" s="2" t="s">
         <v>43</v>
@@ -8817,22 +8820,22 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="3">
+        <v>204</v>
+      </c>
+      <c r="B87" t="s">
         <v>205</v>
       </c>
-      <c r="B87" t="s">
-        <v>206</v>
-      </c>
       <c r="C87" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>43</v>
+      <c r="E87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>43</v>
@@ -8867,26 +8870,26 @@
       <c r="Q87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U87" s="2" t="s">
-        <v>43</v>
+      <c r="R87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X87" s="2" t="s">
-        <v>43</v>
+      <c r="W87" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y87" s="2" t="s">
         <v>43</v>
@@ -8906,22 +8909,22 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="3">
+        <v>206</v>
+      </c>
+      <c r="B88" t="s">
         <v>207</v>
       </c>
-      <c r="B88" t="s">
-        <v>208</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>42</v>
+      <c r="C88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>43</v>
@@ -8995,22 +8998,22 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="3">
+        <v>208</v>
+      </c>
+      <c r="B89" t="s">
         <v>209</v>
       </c>
-      <c r="B89" t="s">
-        <v>210</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>43</v>
+      <c r="C89" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>43</v>
@@ -9084,22 +9087,22 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="3">
+        <v>210</v>
+      </c>
+      <c r="B90" t="s">
         <v>211</v>
       </c>
-      <c r="B90" t="s">
-        <v>212</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>42</v>
+      <c r="E90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>43</v>
@@ -9107,20 +9110,20 @@
       <c r="H90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>42</v>
+      <c r="I90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>42</v>
+      <c r="K90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M90" s="1" t="s">
-        <v>42</v>
+      <c r="M90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>43</v>
@@ -9128,32 +9131,32 @@
       <c r="O90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P90" s="1" t="s">
-        <v>42</v>
+      <c r="P90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U90" s="1" t="s">
-        <v>42</v>
+      <c r="R90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X90" s="1" t="s">
-        <v>42</v>
+      <c r="W90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y90" s="2" t="s">
         <v>43</v>
@@ -9173,11 +9176,11 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="3">
+        <v>212</v>
+      </c>
+      <c r="B91" t="s">
         <v>213</v>
       </c>
-      <c r="B91" t="s">
-        <v>214</v>
-      </c>
       <c r="C91" s="1" t="s">
         <v>42</v>
       </c>
@@ -9223,14 +9226,14 @@
       <c r="Q91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T91" s="2" t="s">
-        <v>43</v>
+      <c r="R91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T91" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U91" s="1" t="s">
         <v>42</v>
@@ -9262,22 +9265,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="3">
+        <v>214</v>
+      </c>
+      <c r="B92" t="s">
         <v>215</v>
       </c>
-      <c r="B92" t="s">
-        <v>216</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>43</v>
+      <c r="E92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>43</v>
@@ -9285,20 +9288,20 @@
       <c r="H92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>43</v>
+      <c r="I92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K92" s="2" t="s">
-        <v>43</v>
+      <c r="K92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M92" s="2" t="s">
-        <v>43</v>
+      <c r="M92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>43</v>
@@ -9306,8 +9309,8 @@
       <c r="O92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P92" s="2" t="s">
-        <v>43</v>
+      <c r="P92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q92" s="2" t="s">
         <v>43</v>
@@ -9321,17 +9324,17 @@
       <c r="T92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U92" s="2" t="s">
-        <v>43</v>
+      <c r="U92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X92" s="2" t="s">
-        <v>43</v>
+      <c r="W92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>43</v>
@@ -9351,16 +9354,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="3">
+        <v>216</v>
+      </c>
+      <c r="B93" t="s">
         <v>217</v>
       </c>
-      <c r="B93" t="s">
-        <v>218</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>43</v>
+      <c r="D93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>43</v>
@@ -9440,22 +9443,22 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="3">
+        <v>218</v>
+      </c>
+      <c r="B94" t="s">
         <v>219</v>
       </c>
-      <c r="B94" t="s">
-        <v>220</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>42</v>
+      <c r="D94" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>42</v>
+      <c r="F94" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>43</v>
@@ -9529,16 +9532,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="3">
+        <v>220</v>
+      </c>
+      <c r="B95" t="s">
         <v>221</v>
       </c>
-      <c r="B95" t="s">
-        <v>222</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>43</v>
+      <c r="D95" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>43</v>
@@ -9618,11 +9621,11 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="3">
+        <v>222</v>
+      </c>
+      <c r="B96" t="s">
         <v>223</v>
       </c>
-      <c r="B96" t="s">
-        <v>224</v>
-      </c>
       <c r="C96" s="1" t="s">
         <v>42</v>
       </c>
@@ -9632,8 +9635,8 @@
       <c r="E96" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>43</v>
+      <c r="F96" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>43</v>
@@ -9707,10 +9710,10 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="3">
+        <v>224</v>
+      </c>
+      <c r="B97" t="s">
         <v>225</v>
-      </c>
-      <c r="B97" t="s">
-        <v>226</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>42</v>
@@ -9796,22 +9799,22 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="3">
+        <v>226</v>
+      </c>
+      <c r="B98" t="s">
         <v>227</v>
       </c>
-      <c r="B98" t="s">
-        <v>228</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>42</v>
+      <c r="D98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>43</v>
@@ -9846,26 +9849,26 @@
       <c r="Q98" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U98" s="1" t="s">
-        <v>42</v>
+      <c r="R98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V98" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W98" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X98" s="1" t="s">
-        <v>42</v>
+      <c r="W98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X98" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y98" s="2" t="s">
         <v>43</v>
@@ -9885,22 +9888,22 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="3">
+        <v>228</v>
+      </c>
+      <c r="B99" t="s">
         <v>229</v>
       </c>
-      <c r="B99" t="s">
-        <v>230</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>43</v>
+      <c r="E99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>43</v>
@@ -9938,23 +9941,23 @@
       <c r="R99" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="S99" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U99" s="2" t="s">
-        <v>43</v>
+      <c r="S99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W99" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X99" s="2" t="s">
-        <v>43</v>
+      <c r="W99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y99" s="2" t="s">
         <v>43</v>
@@ -9974,22 +9977,22 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="3">
+        <v>230</v>
+      </c>
+      <c r="B100" t="s">
         <v>231</v>
       </c>
-      <c r="B100" t="s">
-        <v>232</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>42</v>
+      <c r="E100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>43</v>
@@ -10024,8 +10027,8 @@
       <c r="Q100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R100" s="2" t="s">
-        <v>43</v>
+      <c r="R100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="S100" s="2" t="s">
         <v>43</v>
@@ -10033,17 +10036,17 @@
       <c r="T100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U100" s="1" t="s">
-        <v>42</v>
+      <c r="U100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X100" s="1" t="s">
-        <v>42</v>
+      <c r="W100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y100" s="2" t="s">
         <v>43</v>
@@ -10063,22 +10066,22 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="3">
+        <v>232</v>
+      </c>
+      <c r="B101" t="s">
         <v>233</v>
       </c>
-      <c r="B101" t="s">
-        <v>234</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>43</v>
+      <c r="D101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>43</v>
@@ -10122,17 +10125,17 @@
       <c r="T101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U101" s="2" t="s">
-        <v>43</v>
+      <c r="U101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X101" s="2" t="s">
-        <v>43</v>
+      <c r="W101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>43</v>
@@ -10152,16 +10155,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="3">
+        <v>234</v>
+      </c>
+      <c r="B102" t="s">
         <v>235</v>
       </c>
-      <c r="B102" t="s">
-        <v>236</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>42</v>
+      <c r="D102" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>43</v>
@@ -10241,16 +10244,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="3">
+        <v>236</v>
+      </c>
+      <c r="B103" t="s">
         <v>237</v>
       </c>
-      <c r="B103" t="s">
-        <v>238</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>43</v>
+      <c r="D103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>43</v>
@@ -10330,40 +10333,40 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="3">
+        <v>238</v>
+      </c>
+      <c r="B104" t="s">
         <v>239</v>
       </c>
-      <c r="B104" t="s">
-        <v>240</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G104" s="1" t="s">
-        <v>42</v>
+      <c r="D104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I104" s="1" t="s">
-        <v>42</v>
+      <c r="I104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L104" s="1" t="s">
-        <v>42</v>
+      <c r="K104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M104" s="2" t="s">
         <v>43</v>
@@ -10371,35 +10374,35 @@
       <c r="N104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P104" s="1" t="s">
-        <v>42</v>
+      <c r="O104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U104" s="1" t="s">
-        <v>42</v>
+      <c r="R104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X104" s="1" t="s">
-        <v>42</v>
+      <c r="W104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y104" s="2" t="s">
         <v>43</v>
@@ -10419,25 +10422,25 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="3">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
         <v>241</v>
       </c>
-      <c r="B105" t="s">
-        <v>242</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>43</v>
+      <c r="E105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>43</v>
@@ -10448,23 +10451,23 @@
       <c r="J105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P105" s="2" t="s">
-        <v>43</v>
+      <c r="K105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>43</v>
@@ -10478,17 +10481,17 @@
       <c r="T105" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U105" s="2" t="s">
-        <v>43</v>
+      <c r="U105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X105" s="2" t="s">
-        <v>43</v>
+      <c r="W105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y105" s="2" t="s">
         <v>43</v>
@@ -10508,11 +10511,11 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="3">
+        <v>242</v>
+      </c>
+      <c r="B106" t="s">
         <v>243</v>
       </c>
-      <c r="B106" t="s">
-        <v>244</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>42</v>
       </c>
@@ -10531,8 +10534,8 @@
       <c r="H106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I106" s="2" t="s">
-        <v>43</v>
+      <c r="I106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>43</v>
@@ -10546,8 +10549,8 @@
       <c r="M106" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N106" s="2" t="s">
-        <v>43</v>
+      <c r="N106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>43</v>
@@ -10597,49 +10600,49 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="3">
+        <v>244</v>
+      </c>
+      <c r="B107" t="s">
         <v>245</v>
       </c>
-      <c r="B107" t="s">
-        <v>246</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G107" s="1" t="s">
-        <v>42</v>
+      <c r="E107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L107" s="1" t="s">
-        <v>42</v>
+      <c r="I107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O107" s="1" t="s">
-        <v>42</v>
+      <c r="N107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P107" s="2" t="s">
         <v>43</v>
@@ -10647,14 +10650,14 @@
       <c r="Q107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T107" s="2" t="s">
-        <v>43</v>
+      <c r="R107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U107" s="2" t="s">
         <v>43</v>
@@ -10662,8 +10665,8 @@
       <c r="V107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W107" s="1" t="s">
-        <v>42</v>
+      <c r="W107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X107" s="2" t="s">
         <v>43</v>
@@ -10686,34 +10689,34 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="3">
+        <v>246</v>
+      </c>
+      <c r="B108" t="s">
         <v>247</v>
       </c>
-      <c r="B108" t="s">
-        <v>248</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>43</v>
+      <c r="D108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>43</v>
+      <c r="I108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>42</v>
@@ -10721,17 +10724,17 @@
       <c r="L108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P108" s="1" t="s">
-        <v>42</v>
+      <c r="M108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q108" s="2" t="s">
         <v>43</v>
@@ -10745,14 +10748,14 @@
       <c r="T108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U108" s="1" t="s">
-        <v>42</v>
+      <c r="U108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W108" s="2" t="s">
-        <v>43</v>
+      <c r="W108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X108" s="2" t="s">
         <v>43</v>
@@ -10775,11 +10778,11 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="3">
+        <v>248</v>
+      </c>
+      <c r="B109" t="s">
         <v>249</v>
       </c>
-      <c r="B109" t="s">
-        <v>250</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>42</v>
       </c>
@@ -10819,8 +10822,8 @@
       <c r="O109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P109" s="2" t="s">
-        <v>43</v>
+      <c r="P109" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>43</v>
@@ -10864,10 +10867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="3">
+        <v>250</v>
+      </c>
+      <c r="B110" t="s">
         <v>251</v>
-      </c>
-      <c r="B110" t="s">
-        <v>252</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>42</v>
@@ -10953,10 +10956,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="3">
+        <v>252</v>
+      </c>
+      <c r="B111" t="s">
         <v>253</v>
-      </c>
-      <c r="B111" t="s">
-        <v>254</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>42</v>
@@ -11042,11 +11045,11 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="3">
+        <v>254</v>
+      </c>
+      <c r="B112" t="s">
         <v>255</v>
       </c>
-      <c r="B112" t="s">
-        <v>256</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>42</v>
       </c>
@@ -11074,8 +11077,8 @@
       <c r="K112" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L112" s="2" t="s">
-        <v>43</v>
+      <c r="L112" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M112" s="2" t="s">
         <v>43</v>
@@ -11131,11 +11134,11 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="3">
+        <v>256</v>
+      </c>
+      <c r="B113" t="s">
         <v>257</v>
       </c>
-      <c r="B113" t="s">
-        <v>258</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>42</v>
       </c>
@@ -11163,8 +11166,8 @@
       <c r="K113" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>42</v>
+      <c r="L113" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M113" s="2" t="s">
         <v>43</v>
@@ -11220,10 +11223,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="3">
+        <v>258</v>
+      </c>
+      <c r="B114" t="s">
         <v>259</v>
-      </c>
-      <c r="B114" t="s">
-        <v>260</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>42</v>
@@ -11309,11 +11312,11 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="3">
+        <v>260</v>
+      </c>
+      <c r="B115" t="s">
         <v>261</v>
       </c>
-      <c r="B115" t="s">
-        <v>262</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>42</v>
       </c>
@@ -11341,8 +11344,8 @@
       <c r="K115" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L115" s="2" t="s">
-        <v>43</v>
+      <c r="L115" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M115" s="2" t="s">
         <v>43</v>
@@ -11398,11 +11401,11 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="3">
+        <v>262</v>
+      </c>
+      <c r="B116" t="s">
         <v>263</v>
       </c>
-      <c r="B116" t="s">
-        <v>264</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>42</v>
       </c>
@@ -11430,8 +11433,8 @@
       <c r="K116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L116" s="1" t="s">
-        <v>42</v>
+      <c r="L116" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M116" s="2" t="s">
         <v>43</v>
@@ -11487,10 +11490,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="3">
+        <v>264</v>
+      </c>
+      <c r="B117" t="s">
         <v>265</v>
-      </c>
-      <c r="B117" t="s">
-        <v>266</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>42</v>
@@ -11576,10 +11579,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="3">
+        <v>266</v>
+      </c>
+      <c r="B118" t="s">
         <v>267</v>
-      </c>
-      <c r="B118" t="s">
-        <v>268</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>42</v>
@@ -11665,10 +11668,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="3">
+        <v>268</v>
+      </c>
+      <c r="B119" t="s">
         <v>269</v>
-      </c>
-      <c r="B119" t="s">
-        <v>270</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>42</v>
@@ -11754,11 +11757,11 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="3">
+        <v>270</v>
+      </c>
+      <c r="B120" t="s">
         <v>271</v>
       </c>
-      <c r="B120" t="s">
-        <v>272</v>
-      </c>
       <c r="C120" s="1" t="s">
         <v>42</v>
       </c>
@@ -11786,8 +11789,8 @@
       <c r="K120" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L120" s="2" t="s">
-        <v>43</v>
+      <c r="L120" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M120" s="2" t="s">
         <v>43</v>
@@ -11843,76 +11846,76 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="3">
+        <v>272</v>
+      </c>
+      <c r="B121" t="s">
         <v>273</v>
       </c>
-      <c r="B121" t="s">
-        <v>274</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>42</v>
+      <c r="D121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P121" s="1" t="s">
-        <v>42</v>
+      <c r="L121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q121" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T121" s="1" t="s">
-        <v>42</v>
+      <c r="R121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X121" s="1" t="s">
-        <v>42</v>
+      <c r="V121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y121" s="2" t="s">
         <v>43</v>
@@ -11932,11 +11935,11 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="3">
+        <v>274</v>
+      </c>
+      <c r="B122" t="s">
         <v>275</v>
       </c>
-      <c r="B122" t="s">
-        <v>276</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>42</v>
       </c>
@@ -11952,44 +11955,44 @@
       <c r="G122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H122" s="2" t="s">
-        <v>43</v>
+      <c r="H122" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P122" s="2" t="s">
-        <v>43</v>
+      <c r="J122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q122" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T122" s="2" t="s">
-        <v>43</v>
+      <c r="R122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U122" s="1" t="s">
         <v>42</v>
@@ -12021,31 +12024,31 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="3">
+        <v>276</v>
+      </c>
+      <c r="B123" t="s">
         <v>277</v>
       </c>
-      <c r="B123" t="s">
-        <v>278</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>43</v>
+      <c r="D123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I123" s="2" t="s">
-        <v>43</v>
+      <c r="I123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>43</v>
@@ -12080,17 +12083,17 @@
       <c r="T123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X123" s="2" t="s">
-        <v>43</v>
+      <c r="U123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y123" s="2" t="s">
         <v>43</v>
@@ -12110,10 +12113,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="3">
+        <v>278</v>
+      </c>
+      <c r="B124" t="s">
         <v>279</v>
-      </c>
-      <c r="B124" t="s">
-        <v>280</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>42</v>
@@ -12199,22 +12202,22 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="3">
+        <v>280</v>
+      </c>
+      <c r="B125" t="s">
         <v>281</v>
       </c>
-      <c r="B125" t="s">
-        <v>282</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>42</v>
+      <c r="C125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>43</v>
@@ -12222,23 +12225,23 @@
       <c r="H125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I125" s="1" t="s">
-        <v>42</v>
+      <c r="I125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N125" s="1" t="s">
-        <v>42</v>
+      <c r="K125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>43</v>
@@ -12288,13 +12291,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="3">
+        <v>282</v>
+      </c>
+      <c r="B126" t="s">
         <v>283</v>
       </c>
-      <c r="B126" t="s">
-        <v>284</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>42</v>
+      <c r="C126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>42</v>
@@ -12311,23 +12314,23 @@
       <c r="H126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I126" s="2" t="s">
-        <v>43</v>
+      <c r="I126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N126" s="2" t="s">
-        <v>43</v>
+      <c r="K126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>43</v>
@@ -12377,22 +12380,22 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="3">
+        <v>284</v>
+      </c>
+      <c r="B127" t="s">
         <v>285</v>
       </c>
-      <c r="B127" t="s">
-        <v>286</v>
-      </c>
       <c r="C127" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>43</v>
+      <c r="E127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>43</v>
@@ -12466,43 +12469,43 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="3">
+        <v>286</v>
+      </c>
+      <c r="B128" t="s">
         <v>287</v>
       </c>
-      <c r="B128" t="s">
-        <v>288</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>42</v>
+      <c r="E128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K128" s="1" t="s">
-        <v>42</v>
+      <c r="K128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M128" s="1" t="s">
-        <v>42</v>
+      <c r="M128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N128" s="2" t="s">
         <v>43</v>
@@ -12516,26 +12519,26 @@
       <c r="Q128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X128" s="1" t="s">
-        <v>42</v>
+      <c r="R128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>43</v>
@@ -12555,11 +12558,11 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="3">
+        <v>288</v>
+      </c>
+      <c r="B129" t="s">
         <v>289</v>
       </c>
-      <c r="B129" t="s">
-        <v>290</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>42</v>
       </c>
@@ -12572,14 +12575,14 @@
       <c r="F129" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>43</v>
+      <c r="G129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>43</v>
@@ -12605,20 +12608,20 @@
       <c r="Q129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T129" s="2" t="s">
-        <v>43</v>
+      <c r="R129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U129" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V129" s="2" t="s">
-        <v>43</v>
+      <c r="V129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="W129" s="1" t="s">
         <v>42</v>
@@ -12644,11 +12647,11 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="3">
+        <v>290</v>
+      </c>
+      <c r="B130" t="s">
         <v>291</v>
       </c>
-      <c r="B130" t="s">
-        <v>292</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>42</v>
       </c>
@@ -12664,8 +12667,8 @@
       <c r="G130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H130" s="1" t="s">
-        <v>42</v>
+      <c r="H130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>43</v>
@@ -12694,20 +12697,20 @@
       <c r="Q130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R130" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S130" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T130" s="1" t="s">
-        <v>42</v>
+      <c r="R130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V130" s="1" t="s">
-        <v>42</v>
+      <c r="V130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="W130" s="1" t="s">
         <v>42</v>
@@ -12733,13 +12736,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="3">
+        <v>292</v>
+      </c>
+      <c r="B131" t="s">
         <v>293</v>
       </c>
-      <c r="B131" t="s">
-        <v>294</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>43</v>
+      <c r="C131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>42</v>
@@ -12750,32 +12753,32 @@
       <c r="F131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G131" s="1" t="s">
-        <v>42</v>
+      <c r="G131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J131" s="1" t="s">
-        <v>42</v>
+      <c r="I131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L131" s="1" t="s">
-        <v>42</v>
+      <c r="L131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O131" s="1" t="s">
-        <v>42</v>
+      <c r="N131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P131" s="2" t="s">
         <v>43</v>
@@ -12783,17 +12786,17 @@
       <c r="Q131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U131" s="2" t="s">
-        <v>43</v>
+      <c r="R131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V131" s="1" t="s">
         <v>42</v>
@@ -12807,14 +12810,14 @@
       <c r="Y131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z131" s="1" t="s">
-        <v>42</v>
+      <c r="Z131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB131" s="1" t="s">
-        <v>42</v>
+      <c r="AB131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC131" s="2" t="s">
         <v>43</v>
@@ -12822,49 +12825,49 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="3">
+        <v>294</v>
+      </c>
+      <c r="B132" t="s">
         <v>295</v>
       </c>
-      <c r="B132" t="s">
-        <v>296</v>
-      </c>
       <c r="C132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O132" s="2" t="s">
-        <v>43</v>
+      <c r="D132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P132" s="2" t="s">
         <v>43</v>
@@ -12884,14 +12887,14 @@
       <c r="U132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X132" s="2" t="s">
-        <v>43</v>
+      <c r="V132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y132" s="2" t="s">
         <v>43</v>
@@ -12911,52 +12914,52 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="3">
+        <v>296</v>
+      </c>
+      <c r="B133" t="s">
         <v>297</v>
       </c>
-      <c r="B133" t="s">
-        <v>298</v>
-      </c>
       <c r="C133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P133" s="1" t="s">
-        <v>42</v>
+      <c r="D133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P133" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q133" s="2" t="s">
         <v>43</v>
@@ -12973,14 +12976,14 @@
       <c r="U133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W133" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X133" s="1" t="s">
-        <v>42</v>
+      <c r="V133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X133" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y133" s="2" t="s">
         <v>43</v>
@@ -13000,52 +13003,52 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="3">
+        <v>298</v>
+      </c>
+      <c r="B134" t="s">
         <v>299</v>
       </c>
-      <c r="B134" t="s">
-        <v>300</v>
-      </c>
       <c r="C134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P134" s="2" t="s">
-        <v>43</v>
+      <c r="D134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q134" s="2" t="s">
         <v>43</v>
@@ -13062,14 +13065,14 @@
       <c r="U134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X134" s="2" t="s">
-        <v>43</v>
+      <c r="V134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W134" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y134" s="2" t="s">
         <v>43</v>
@@ -13089,49 +13092,49 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="3">
+        <v>300</v>
+      </c>
+      <c r="B135" t="s">
         <v>301</v>
       </c>
-      <c r="B135" t="s">
-        <v>302</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>42</v>
+      <c r="C135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I135" s="1" t="s">
-        <v>42</v>
+      <c r="I135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O135" s="1" t="s">
-        <v>42</v>
+      <c r="K135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P135" s="2" t="s">
         <v>43</v>
@@ -13154,8 +13157,8 @@
       <c r="V135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W135" s="1" t="s">
-        <v>42</v>
+      <c r="W135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X135" s="2" t="s">
         <v>43</v>
@@ -13163,14 +13166,14 @@
       <c r="Y135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z135" s="2" t="s">
-        <v>43</v>
+      <c r="Z135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB135" s="2" t="s">
-        <v>43</v>
+      <c r="AB135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC135" s="2" t="s">
         <v>43</v>
@@ -13178,49 +13181,49 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="3">
+        <v>302</v>
+      </c>
+      <c r="B136" t="s">
         <v>303</v>
       </c>
-      <c r="B136" t="s">
-        <v>304</v>
-      </c>
       <c r="C136" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>43</v>
+      <c r="D136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I136" s="2" t="s">
-        <v>43</v>
+      <c r="I136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O136" s="2" t="s">
-        <v>43</v>
+      <c r="K136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P136" s="2" t="s">
         <v>43</v>
@@ -13243,8 +13246,8 @@
       <c r="V136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W136" s="2" t="s">
-        <v>43</v>
+      <c r="W136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X136" s="2" t="s">
         <v>43</v>
@@ -13267,16 +13270,16 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="3">
+        <v>304</v>
+      </c>
+      <c r="B137" t="s">
         <v>305</v>
       </c>
-      <c r="B137" t="s">
-        <v>306</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>42</v>
+      <c r="D137" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>43</v>
@@ -13356,16 +13359,16 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="3">
+        <v>306</v>
+      </c>
+      <c r="B138" t="s">
         <v>307</v>
       </c>
-      <c r="B138" t="s">
-        <v>308</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D138" s="2" t="s">
-        <v>43</v>
+      <c r="D138" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>43</v>
@@ -13445,49 +13448,49 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="3">
+        <v>308</v>
+      </c>
+      <c r="B139" t="s">
         <v>309</v>
       </c>
-      <c r="B139" t="s">
-        <v>310</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>42</v>
+      <c r="D139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I139" s="1" t="s">
-        <v>42</v>
+      <c r="I139" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N139" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O139" s="1" t="s">
-        <v>42</v>
+      <c r="K139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O139" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P139" s="2" t="s">
         <v>43</v>
@@ -13510,8 +13513,8 @@
       <c r="V139" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W139" s="1" t="s">
-        <v>42</v>
+      <c r="W139" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X139" s="2" t="s">
         <v>43</v>
@@ -13534,11 +13537,11 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="3">
+        <v>310</v>
+      </c>
+      <c r="B140" t="s">
         <v>311</v>
       </c>
-      <c r="B140" t="s">
-        <v>312</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>42</v>
       </c>
@@ -13551,14 +13554,14 @@
       <c r="F140" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G140" s="2" t="s">
-        <v>43</v>
+      <c r="G140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I140" s="2" t="s">
-        <v>43</v>
+      <c r="I140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>43</v>
@@ -13566,17 +13569,17 @@
       <c r="K140" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L140" s="2" t="s">
-        <v>43</v>
+      <c r="L140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O140" s="2" t="s">
-        <v>43</v>
+      <c r="N140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P140" s="2" t="s">
         <v>43</v>
@@ -13623,49 +13626,49 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="3">
+        <v>312</v>
+      </c>
+      <c r="B141" t="s">
         <v>313</v>
       </c>
-      <c r="B141" t="s">
-        <v>314</v>
-      </c>
       <c r="C141" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>43</v>
+      <c r="E141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I141" s="2" t="s">
-        <v>43</v>
+      <c r="I141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O141" s="2" t="s">
-        <v>43</v>
+      <c r="K141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P141" s="2" t="s">
         <v>43</v>
@@ -13688,8 +13691,8 @@
       <c r="V141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W141" s="2" t="s">
-        <v>43</v>
+      <c r="W141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X141" s="2" t="s">
         <v>43</v>
@@ -13712,16 +13715,16 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="3">
+        <v>314</v>
+      </c>
+      <c r="B142" t="s">
         <v>315</v>
       </c>
-      <c r="B142" t="s">
-        <v>316</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D142" s="2" t="s">
-        <v>43</v>
+      <c r="D142" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>43</v>
@@ -13801,22 +13804,22 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="3">
+        <v>316</v>
+      </c>
+      <c r="B143" t="s">
         <v>317</v>
       </c>
-      <c r="B143" t="s">
-        <v>318</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>42</v>
+      <c r="D143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>43</v>
@@ -13830,14 +13833,14 @@
       <c r="J143" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K143" s="1" t="s">
-        <v>42</v>
+      <c r="K143" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L143" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M143" s="1" t="s">
-        <v>42</v>
+      <c r="M143" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N143" s="2" t="s">
         <v>43</v>
@@ -13866,8 +13869,8 @@
       <c r="V143" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W143" s="1" t="s">
-        <v>42</v>
+      <c r="W143" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X143" s="2" t="s">
         <v>43</v>
@@ -13890,22 +13893,22 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="3">
+        <v>318</v>
+      </c>
+      <c r="B144" t="s">
         <v>319</v>
       </c>
-      <c r="B144" t="s">
-        <v>320</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>43</v>
+      <c r="C144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>43</v>
@@ -13919,14 +13922,14 @@
       <c r="J144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K144" s="2" t="s">
-        <v>43</v>
+      <c r="K144" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M144" s="2" t="s">
-        <v>43</v>
+      <c r="M144" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N144" s="2" t="s">
         <v>43</v>
@@ -13955,8 +13958,8 @@
       <c r="V144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W144" s="2" t="s">
-        <v>43</v>
+      <c r="W144" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X144" s="2" t="s">
         <v>43</v>
@@ -13973,55 +13976,55 @@
       <c r="AB144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AC144" s="1" t="s">
-        <v>42</v>
+      <c r="AC144" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s" s="3">
+        <v>320</v>
+      </c>
+      <c r="B145" t="s">
         <v>321</v>
       </c>
-      <c r="B145" t="s">
-        <v>322</v>
-      </c>
-      <c r="C145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G145" s="1" t="s">
-        <v>42</v>
+      <c r="C145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I145" s="1" t="s">
-        <v>42</v>
+      <c r="I145" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O145" s="1" t="s">
-        <v>42</v>
+      <c r="K145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O145" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P145" s="2" t="s">
         <v>43</v>
@@ -14029,26 +14032,26 @@
       <c r="Q145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U145" s="1" t="s">
-        <v>42</v>
+      <c r="R145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U145" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W145" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X145" s="1" t="s">
-        <v>42</v>
+      <c r="W145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X145" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y145" s="2" t="s">
         <v>43</v>
@@ -14062,19 +14065,19 @@
       <c r="AB145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AC145" s="2" t="s">
-        <v>43</v>
+      <c r="AC145" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="3">
+        <v>322</v>
+      </c>
+      <c r="B146" t="s">
         <v>323</v>
       </c>
-      <c r="B146" t="s">
-        <v>324</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>43</v>
+      <c r="C146" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>42</v>
@@ -14082,35 +14085,35 @@
       <c r="E146" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>43</v>
+      <c r="F146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I146" s="2" t="s">
-        <v>43</v>
+      <c r="I146" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O146" s="2" t="s">
-        <v>43</v>
+      <c r="K146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P146" s="2" t="s">
         <v>43</v>
@@ -14118,26 +14121,26 @@
       <c r="Q146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U146" s="2" t="s">
-        <v>43</v>
+      <c r="R146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U146" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X146" s="2" t="s">
-        <v>43</v>
+      <c r="W146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X146" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y146" s="2" t="s">
         <v>43</v>
@@ -14157,90 +14160,179 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="3">
+        <v>324</v>
+      </c>
+      <c r="B147" t="s">
         <v>325</v>
       </c>
-      <c r="B147" t="s">
+      <c r="C147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC147" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="3">
         <v>326</v>
       </c>
-      <c r="C147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC147" s="2" t="s">
+      <c r="B148" t="s">
+        <v>327</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC148" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -14256,12 +14348,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -1002,7 +1002,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.60.0-SNAPSHOT</t>
+    <t>1.0.0</t>
   </si>
 </sst>
 </file>
@@ -4681,8 +4681,8 @@
       <c r="O40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P40" s="2" t="s">
-        <v>43</v>
+      <c r="P40" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q40" s="2" t="s">
         <v>43</v>
@@ -6995,8 +6995,8 @@
       <c r="O66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P66" s="2" t="s">
-        <v>43</v>
+      <c r="P66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>43</v>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4294" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="318">
   <si>
     <t>User Right</t>
   </si>
@@ -225,12 +225,6 @@
     <t>Archive cases</t>
   </si>
   <si>
-    <t>CASE_VIEW_ARCHIVED</t>
-  </si>
-  <si>
-    <t>View archived cases</t>
-  </si>
-  <si>
     <t>CASE_MERGE</t>
   </si>
   <si>
@@ -303,12 +297,6 @@
     <t>Export samples from SORMAS</t>
   </si>
   <si>
-    <t>SAMPLE_VIEW_ARCHIVED</t>
-  </si>
-  <si>
-    <t>View archived samples</t>
-  </si>
-  <si>
     <t>PATHOGEN_TEST_CREATE</t>
   </si>
   <si>
@@ -405,12 +393,6 @@
     <t>Export contacts from SORMAS</t>
   </si>
   <si>
-    <t>CONTACT_VIEW_ARCHIVED</t>
-  </si>
-  <si>
-    <t>View archived contacts</t>
-  </si>
-  <si>
     <t>CONTACT_REASSIGN_CASE</t>
   </si>
   <si>
@@ -474,12 +456,6 @@
     <t>Assign tasks to users</t>
   </si>
   <si>
-    <t>TASK_VIEW_ARCHIVED</t>
-  </si>
-  <si>
-    <t>View archived tasks</t>
-  </si>
-  <si>
     <t>TASK_DELETE</t>
   </si>
   <si>
@@ -552,12 +528,6 @@
     <t>Delete events from the system</t>
   </si>
   <si>
-    <t>EVENT_VIEW_ARCHIVED</t>
-  </si>
-  <si>
-    <t>View archived events</t>
-  </si>
-  <si>
     <t>EVENTPARTICIPANT_CREATE</t>
   </si>
   <si>
@@ -703,12 +673,6 @@
   </si>
   <si>
     <t>View regions/districts/communities/facilities in the system</t>
-  </si>
-  <si>
-    <t>INFRASTRUCTURE_VIEW_ARCHIVED</t>
-  </si>
-  <si>
-    <t>View archived infrastructure data</t>
   </si>
   <si>
     <t>INFRASTRUCTURE_EXPORT</t>
@@ -1130,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD148"/>
+  <dimension ref="A1:AD142"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -2598,14 +2562,14 @@
       <c r="C17" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="1" t="s">
-        <v>42</v>
+      <c r="D17" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>43</v>
+      <c r="F17" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>43</v>
@@ -2619,14 +2583,14 @@
       <c r="J17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>42</v>
+      <c r="K17" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M17" s="1" t="s">
-        <v>42</v>
+      <c r="M17" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>43</v>
@@ -2640,26 +2604,26 @@
       <c r="Q17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>42</v>
+      <c r="R17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V17" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>42</v>
+      <c r="W17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y17" s="2" t="s">
         <v>43</v>
@@ -2687,68 +2651,68 @@
       <c r="C18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>43</v>
+      <c r="D18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>43</v>
+      <c r="G18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X18" s="2" t="s">
-        <v>43</v>
+      <c r="R18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y18" s="2" t="s">
         <v>43</v>
@@ -2818,14 +2782,14 @@
       <c r="Q19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>42</v>
+      <c r="R19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>42</v>
@@ -2868,41 +2832,41 @@
       <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>42</v>
+      <c r="E20" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>42</v>
+      <c r="G20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>43</v>
@@ -2916,17 +2880,17 @@
       <c r="T20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>42</v>
+      <c r="U20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>43</v>
@@ -3046,29 +3010,29 @@
       <c r="D22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>43</v>
+      <c r="E22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>43</v>
+      <c r="G22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>43</v>
@@ -3076,11 +3040,11 @@
       <c r="N22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O22" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P22" s="2" t="s">
-        <v>43</v>
+      <c r="O22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>43</v>
@@ -3094,8 +3058,8 @@
       <c r="T22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U22" s="2" t="s">
-        <v>43</v>
+      <c r="U22" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>43</v>
@@ -3159,11 +3123,11 @@
       <c r="L23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>43</v>
+      <c r="M23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>42</v>
@@ -3171,17 +3135,17 @@
       <c r="P23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>43</v>
+      <c r="Q23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T23" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U23" s="1" t="s">
         <v>42</v>
@@ -3248,11 +3212,11 @@
       <c r="L24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>42</v>
+      <c r="M24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>42</v>
@@ -3263,14 +3227,14 @@
       <c r="Q24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>42</v>
+      <c r="R24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U24" s="1" t="s">
         <v>42</v>
@@ -3310,8 +3274,8 @@
       <c r="C25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>42</v>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>42</v>
@@ -3319,23 +3283,23 @@
       <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>42</v>
+      <c r="G25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>43</v>
@@ -3346,11 +3310,11 @@
       <c r="O25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P25" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>42</v>
+      <c r="P25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R25" s="2" t="s">
         <v>43</v>
@@ -3361,8 +3325,8 @@
       <c r="T25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>42</v>
+      <c r="U25" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V25" s="2" t="s">
         <v>43</v>
@@ -3399,11 +3363,11 @@
       <c r="C26" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>42</v>
+      <c r="D26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>42</v>
@@ -3432,8 +3396,8 @@
       <c r="N26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>42</v>
+      <c r="O26" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P26" s="2" t="s">
         <v>43</v>
@@ -3491,8 +3455,8 @@
       <c r="D27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>43</v>
+      <c r="E27" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>42</v>
@@ -3509,8 +3473,8 @@
       <c r="J27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K27" s="2" t="s">
-        <v>43</v>
+      <c r="K27" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>43</v>
@@ -3524,11 +3488,11 @@
       <c r="O27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>43</v>
+      <c r="P27" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>43</v>
@@ -3539,8 +3503,8 @@
       <c r="T27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U27" s="2" t="s">
-        <v>43</v>
+      <c r="U27" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>43</v>
@@ -3604,8 +3568,8 @@
       <c r="L28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>43</v>
+      <c r="M28" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>43</v>
@@ -3616,8 +3580,8 @@
       <c r="P28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q28" s="1" t="s">
-        <v>42</v>
+      <c r="Q28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>43</v>
@@ -3675,14 +3639,14 @@
       <c r="F29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>43</v>
+      <c r="G29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>43</v>
+      <c r="I29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>43</v>
@@ -3693,20 +3657,20 @@
       <c r="L29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>42</v>
+      <c r="M29" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O29" s="2" t="s">
-        <v>43</v>
+      <c r="O29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q29" s="2" t="s">
-        <v>43</v>
+      <c r="Q29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>43</v>
@@ -3758,20 +3722,20 @@
       <c r="D30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>43</v>
+      <c r="E30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>43</v>
+      <c r="I30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>43</v>
@@ -3782,29 +3746,29 @@
       <c r="L30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>42</v>
+      <c r="M30" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>42</v>
+      <c r="O30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U30" s="1" t="s">
         <v>42</v>
@@ -3847,26 +3811,26 @@
       <c r="D31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>42</v>
+      <c r="E31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>42</v>
+      <c r="I31" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>42</v>
+      <c r="K31" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>43</v>
@@ -3877,14 +3841,14 @@
       <c r="N31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>42</v>
+      <c r="O31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>43</v>
@@ -3895,8 +3859,8 @@
       <c r="T31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U31" s="1" t="s">
-        <v>42</v>
+      <c r="U31" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V31" s="2" t="s">
         <v>43</v>
@@ -3933,23 +3897,23 @@
       <c r="C32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>42</v>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>42</v>
+      <c r="I32" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>43</v>
@@ -3957,8 +3921,8 @@
       <c r="K32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L32" s="2" t="s">
-        <v>43</v>
+      <c r="L32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>43</v>
@@ -3966,8 +3930,8 @@
       <c r="N32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>42</v>
+      <c r="O32" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>42</v>
@@ -4022,8 +3986,8 @@
       <c r="C33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>42</v>
+      <c r="D33" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>43</v>
@@ -4043,11 +4007,11 @@
       <c r="J33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>43</v>
+      <c r="K33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>43</v>
@@ -4058,11 +4022,11 @@
       <c r="O33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>43</v>
+      <c r="P33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>43</v>
@@ -4073,8 +4037,8 @@
       <c r="T33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U33" s="2" t="s">
-        <v>43</v>
+      <c r="U33" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>43</v>
@@ -4200,8 +4164,8 @@
       <c r="C35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>43</v>
+      <c r="D35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>43</v>
@@ -4221,11 +4185,11 @@
       <c r="J35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>42</v>
+      <c r="K35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>43</v>
@@ -4236,11 +4200,11 @@
       <c r="O35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>42</v>
+      <c r="P35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>43</v>
@@ -4251,8 +4215,8 @@
       <c r="T35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U35" s="1" t="s">
-        <v>42</v>
+      <c r="U35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>43</v>
@@ -4289,47 +4253,47 @@
       <c r="C36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>43</v>
+      <c r="D36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I36" s="2" t="s">
-        <v>43</v>
+      <c r="I36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N36" s="2" t="s">
-        <v>43</v>
+      <c r="K36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>42</v>
+      <c r="P36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>43</v>
@@ -4340,8 +4304,8 @@
       <c r="T36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U36" s="1" t="s">
-        <v>42</v>
+      <c r="U36" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>43</v>
@@ -4378,8 +4342,8 @@
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>42</v>
+      <c r="D37" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>43</v>
@@ -4441,8 +4405,8 @@
       <c r="X37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y37" s="2" t="s">
-        <v>43</v>
+      <c r="Y37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>43</v>
@@ -4488,8 +4452,8 @@
       <c r="J38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>43</v>
+      <c r="K38" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>43</v>
@@ -4500,26 +4464,26 @@
       <c r="N38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>43</v>
+      <c r="O38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U38" s="2" t="s">
-        <v>43</v>
+      <c r="R38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U38" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>43</v>
@@ -4556,8 +4520,8 @@
       <c r="C39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>43</v>
+      <c r="D39" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>43</v>
@@ -4583,8 +4547,8 @@
       <c r="L39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>43</v>
+      <c r="M39" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>43</v>
@@ -4619,8 +4583,8 @@
       <c r="X39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y39" s="1" t="s">
-        <v>42</v>
+      <c r="Y39" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z39" s="2" t="s">
         <v>43</v>
@@ -4666,8 +4630,8 @@
       <c r="J40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>42</v>
+      <c r="K40" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>43</v>
@@ -4678,8 +4642,8 @@
       <c r="N40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>42</v>
+      <c r="O40" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>42</v>
@@ -4687,17 +4651,17 @@
       <c r="Q40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>42</v>
+      <c r="R40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>43</v>
@@ -4761,8 +4725,8 @@
       <c r="L41" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M41" s="1" t="s">
-        <v>42</v>
+      <c r="M41" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>43</v>
@@ -4826,14 +4790,14 @@
       <c r="D42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>42</v>
+      <c r="E42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>43</v>
@@ -4915,20 +4879,20 @@
       <c r="D43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>43</v>
+      <c r="E43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>43</v>
+      <c r="I43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>43</v>
@@ -4939,11 +4903,11 @@
       <c r="L43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>43</v>
+      <c r="M43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>43</v>
@@ -5004,11 +4968,11 @@
       <c r="D44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>43</v>
+      <c r="E44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>43</v>
@@ -5016,14 +4980,14 @@
       <c r="H44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>42</v>
+      <c r="I44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>43</v>
+      <c r="K44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>43</v>
@@ -5031,14 +4995,14 @@
       <c r="M44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N44" s="1" t="s">
-        <v>42</v>
+      <c r="N44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P44" s="2" t="s">
-        <v>43</v>
+      <c r="P44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>43</v>
@@ -5052,8 +5016,8 @@
       <c r="T44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U44" s="2" t="s">
-        <v>43</v>
+      <c r="U44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>43</v>
@@ -5174,16 +5138,16 @@
         <v>128</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>42</v>
+      <c r="D46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>42</v>
@@ -5200,14 +5164,14 @@
       <c r="J46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>42</v>
+      <c r="K46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M46" s="1" t="s">
-        <v>42</v>
+      <c r="M46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>43</v>
@@ -5215,8 +5179,8 @@
       <c r="O46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P46" s="1" t="s">
-        <v>42</v>
+      <c r="P46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>43</v>
@@ -5230,8 +5194,8 @@
       <c r="T46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U46" s="1" t="s">
-        <v>42</v>
+      <c r="U46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V46" s="2" t="s">
         <v>43</v>
@@ -5260,37 +5224,37 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s">
         <v>130</v>
       </c>
-      <c r="B47" t="s">
-        <v>131</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>42</v>
+      <c r="C47" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>43</v>
+      <c r="E47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>43</v>
+      <c r="I47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>42</v>
+      <c r="K47" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>43</v>
@@ -5298,8 +5262,8 @@
       <c r="M47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N47" s="2" t="s">
-        <v>43</v>
+      <c r="N47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>43</v>
@@ -5310,17 +5274,17 @@
       <c r="Q47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>42</v>
+      <c r="R47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U47" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V47" s="2" t="s">
         <v>43</v>
@@ -5349,25 +5313,25 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
+        <v>131</v>
+      </c>
+      <c r="B48" t="s">
         <v>132</v>
       </c>
-      <c r="B48" t="s">
-        <v>133</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>42</v>
+      <c r="E48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>43</v>
@@ -5438,7 +5402,7 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" t="s">
         <v>134</v>
@@ -5446,14 +5410,14 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>43</v>
+      <c r="D49" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>42</v>
+      <c r="F49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>43</v>
@@ -5461,8 +5425,8 @@
       <c r="H49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I49" s="2" t="s">
-        <v>43</v>
+      <c r="I49" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>43</v>
@@ -5473,11 +5437,11 @@
       <c r="L49" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>43</v>
+      <c r="M49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>43</v>
@@ -5532,26 +5496,26 @@
       <c r="B50" t="s">
         <v>136</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>43</v>
+      <c r="C50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>42</v>
+      <c r="E50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>42</v>
+      <c r="I50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>43</v>
@@ -5562,11 +5526,11 @@
       <c r="L50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N50" s="1" t="s">
-        <v>42</v>
+      <c r="M50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>43</v>
@@ -5627,11 +5591,11 @@
       <c r="D51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>43</v>
+      <c r="E51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>43</v>
@@ -5639,14 +5603,14 @@
       <c r="H51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>42</v>
+      <c r="I51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>43</v>
+      <c r="K51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>43</v>
@@ -5654,14 +5618,14 @@
       <c r="M51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>42</v>
+      <c r="N51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>43</v>
+      <c r="P51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>43</v>
@@ -5675,8 +5639,8 @@
       <c r="T51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U51" s="2" t="s">
-        <v>43</v>
+      <c r="U51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>43</v>
@@ -5716,14 +5680,14 @@
       <c r="D52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>43</v>
+      <c r="E52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>43</v>
@@ -5734,8 +5698,8 @@
       <c r="J52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K52" s="2" t="s">
-        <v>43</v>
+      <c r="K52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>43</v>
@@ -5743,14 +5707,14 @@
       <c r="M52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N52" s="1" t="s">
-        <v>42</v>
+      <c r="N52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>43</v>
+      <c r="P52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>43</v>
@@ -5764,17 +5728,17 @@
       <c r="T52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U52" s="2" t="s">
-        <v>43</v>
+      <c r="U52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X52" s="2" t="s">
-        <v>43</v>
+      <c r="W52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>43</v>
@@ -5805,65 +5769,65 @@
       <c r="D53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X53" s="2" t="s">
-        <v>43</v>
+      <c r="E53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X53" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>43</v>
@@ -5900,38 +5864,38 @@
       <c r="F54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>43</v>
+      <c r="G54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L54" s="2" t="s">
-        <v>43</v>
+      <c r="L54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>43</v>
+      <c r="N54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q54" s="2" t="s">
-        <v>43</v>
+      <c r="Q54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>43</v>
@@ -5945,14 +5909,14 @@
       <c r="U54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X54" s="2" t="s">
-        <v>43</v>
+      <c r="V54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>43</v>
@@ -6072,65 +6036,65 @@
       <c r="D56" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X56" s="1" t="s">
-        <v>42</v>
+      <c r="E56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W56" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X56" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y56" s="2" t="s">
         <v>43</v>
@@ -6268,23 +6232,23 @@
       <c r="J58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K58" s="1" t="s">
-        <v>42</v>
+      <c r="K58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M58" s="1" t="s">
-        <v>42</v>
+      <c r="M58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O58" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P58" s="1" t="s">
-        <v>42</v>
+      <c r="O58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>43</v>
@@ -6298,17 +6262,17 @@
       <c r="T58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U58" s="1" t="s">
-        <v>42</v>
+      <c r="U58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X58" s="1" t="s">
-        <v>42</v>
+      <c r="W58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>43</v>
@@ -6336,8 +6300,8 @@
       <c r="C59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>42</v>
+      <c r="D59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>43</v>
@@ -6357,14 +6321,14 @@
       <c r="J59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K59" s="1" t="s">
-        <v>42</v>
+      <c r="K59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M59" s="1" t="s">
-        <v>42</v>
+      <c r="M59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>43</v>
@@ -6378,26 +6342,26 @@
       <c r="Q59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U59" s="1" t="s">
-        <v>42</v>
+      <c r="R59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V59" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X59" s="1" t="s">
-        <v>42</v>
+      <c r="W59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>43</v>
@@ -6428,20 +6392,20 @@
       <c r="D60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>43</v>
+      <c r="E60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I60" s="2" t="s">
-        <v>43</v>
+      <c r="I60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>43</v>
@@ -6458,8 +6422,8 @@
       <c r="N60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O60" s="2" t="s">
-        <v>43</v>
+      <c r="O60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P60" s="2" t="s">
         <v>43</v>
@@ -6526,35 +6490,35 @@
       <c r="G61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>42</v>
+      <c r="H61" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>42</v>
+      <c r="J61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>42</v>
+      <c r="P61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>43</v>
@@ -6565,17 +6529,17 @@
       <c r="T61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X61" s="1" t="s">
-        <v>42</v>
+      <c r="U61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X61" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>43</v>
@@ -6615,53 +6579,53 @@
       <c r="G62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>43</v>
+      <c r="H62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N62" s="2" t="s">
-        <v>43</v>
+      <c r="J62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P62" s="2" t="s">
-        <v>43</v>
+      <c r="P62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W62" s="2" t="s">
-        <v>43</v>
+      <c r="R62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>43</v>
@@ -6692,23 +6656,23 @@
       <c r="C63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>43</v>
+      <c r="D63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I63" s="2" t="s">
-        <v>43</v>
+      <c r="I63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>43</v>
@@ -6725,8 +6689,8 @@
       <c r="N63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O63" s="2" t="s">
-        <v>43</v>
+      <c r="O63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P63" s="2" t="s">
         <v>43</v>
@@ -6781,23 +6745,23 @@
       <c r="C64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>42</v>
+      <c r="D64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>42</v>
+      <c r="I64" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>43</v>
@@ -6814,8 +6778,8 @@
       <c r="N64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>42</v>
+      <c r="O64" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>43</v>
@@ -6844,8 +6808,8 @@
       <c r="X64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y64" s="2" t="s">
-        <v>43</v>
+      <c r="Y64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>43</v>
@@ -6879,35 +6843,35 @@
       <c r="F65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G65" s="1" t="s">
-        <v>42</v>
+      <c r="G65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>42</v>
+      <c r="I65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K65" s="2" t="s">
-        <v>43</v>
+      <c r="K65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M65" s="2" t="s">
-        <v>43</v>
+      <c r="M65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P65" s="2" t="s">
-        <v>43</v>
+      <c r="O65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>43</v>
@@ -6921,17 +6885,17 @@
       <c r="T65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U65" s="2" t="s">
-        <v>43</v>
+      <c r="U65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X65" s="2" t="s">
-        <v>43</v>
+      <c r="W65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>43</v>
@@ -6959,65 +6923,65 @@
       <c r="C66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>42</v>
+      <c r="D66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W66" s="1" t="s">
-        <v>42</v>
+      <c r="R66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X66" s="2" t="s">
         <v>43</v>
@@ -7051,20 +7015,20 @@
       <c r="D67" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E67" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>42</v>
+      <c r="E67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>42</v>
+      <c r="I67" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>43</v>
@@ -7081,8 +7045,8 @@
       <c r="N67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O67" s="1" t="s">
-        <v>42</v>
+      <c r="O67" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>43</v>
@@ -7137,23 +7101,23 @@
       <c r="C68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>43</v>
+      <c r="D68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I68" s="2" t="s">
-        <v>43</v>
+      <c r="I68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>43</v>
@@ -7170,8 +7134,8 @@
       <c r="N68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O68" s="2" t="s">
-        <v>43</v>
+      <c r="O68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P68" s="2" t="s">
         <v>43</v>
@@ -7200,8 +7164,8 @@
       <c r="X68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y68" s="1" t="s">
-        <v>42</v>
+      <c r="Y68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z68" s="2" t="s">
         <v>43</v>
@@ -7235,32 +7199,32 @@
       <c r="F69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G69" s="2" t="s">
-        <v>43</v>
+      <c r="G69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I69" s="2" t="s">
-        <v>43</v>
+      <c r="I69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>42</v>
+      <c r="K69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M69" s="1" t="s">
-        <v>42</v>
+      <c r="M69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O69" s="2" t="s">
-        <v>43</v>
+      <c r="O69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P69" s="1" t="s">
         <v>42</v>
@@ -7277,17 +7241,17 @@
       <c r="T69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U69" s="1" t="s">
-        <v>42</v>
+      <c r="U69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W69" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>42</v>
+      <c r="W69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y69" s="2" t="s">
         <v>43</v>
@@ -7315,8 +7279,8 @@
       <c r="C70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>43</v>
+      <c r="D70" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>43</v>
@@ -7407,20 +7371,20 @@
       <c r="D71" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>43</v>
+      <c r="E71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I71" s="2" t="s">
-        <v>43</v>
+      <c r="I71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>43</v>
@@ -7437,8 +7401,8 @@
       <c r="N71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O71" s="2" t="s">
-        <v>43</v>
+      <c r="O71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P71" s="2" t="s">
         <v>43</v>
@@ -7467,8 +7431,8 @@
       <c r="X71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y71" s="2" t="s">
-        <v>43</v>
+      <c r="Y71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z71" s="2" t="s">
         <v>43</v>
@@ -7488,7 +7452,7 @@
         <v>179</v>
       </c>
       <c r="B72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>42</v>
@@ -7496,38 +7460,38 @@
       <c r="D72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>43</v>
+      <c r="E72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I72" s="2" t="s">
-        <v>43</v>
+      <c r="I72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>42</v>
+      <c r="K72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M72" s="1" t="s">
-        <v>42</v>
+      <c r="M72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O72" s="2" t="s">
-        <v>43</v>
+      <c r="O72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>43</v>
@@ -7535,26 +7499,26 @@
       <c r="Q72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U72" s="1" t="s">
-        <v>42</v>
+      <c r="R72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X72" s="1" t="s">
-        <v>42</v>
+      <c r="W72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>43</v>
@@ -7574,10 +7538,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="3">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B73" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>42</v>
@@ -7663,10 +7627,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="3">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>42</v>
@@ -7752,16 +7716,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>42</v>
+      <c r="D75" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>43</v>
@@ -7841,10 +7805,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="B76" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>42</v>
@@ -7852,20 +7816,20 @@
       <c r="D76" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G76" s="1" t="s">
-        <v>42</v>
+      <c r="E76" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I76" s="1" t="s">
-        <v>42</v>
+      <c r="I76" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>43</v>
@@ -7882,8 +7846,8 @@
       <c r="N76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O76" s="1" t="s">
-        <v>42</v>
+      <c r="O76" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P76" s="2" t="s">
         <v>43</v>
@@ -7912,8 +7876,8 @@
       <c r="X76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y76" s="1" t="s">
-        <v>42</v>
+      <c r="Y76" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z76" s="2" t="s">
         <v>43</v>
@@ -7930,34 +7894,34 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="3">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B77" t="s">
-        <v>189</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>42</v>
+        <v>185</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H77" s="2" t="s">
-        <v>43</v>
+      <c r="H77" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J77" s="2" t="s">
-        <v>43</v>
+      <c r="J77" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>43</v>
@@ -7971,8 +7935,8 @@
       <c r="N77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O77" s="1" t="s">
-        <v>42</v>
+      <c r="O77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>43</v>
@@ -8019,10 +7983,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="3">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B78" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>42</v>
@@ -8039,29 +8003,29 @@
       <c r="G78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H78" s="2" t="s">
-        <v>43</v>
+      <c r="H78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>43</v>
+      <c r="J78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M78" s="2" t="s">
-        <v>43</v>
+      <c r="M78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O78" s="1" t="s">
-        <v>42</v>
+      <c r="O78" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>43</v>
@@ -8069,17 +8033,17 @@
       <c r="Q78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U78" s="2" t="s">
-        <v>43</v>
+      <c r="R78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V78" s="2" t="s">
         <v>43</v>
@@ -8108,31 +8072,31 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="3">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B79" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D79" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G79" s="1" t="s">
-        <v>42</v>
+      <c r="D79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I79" s="1" t="s">
-        <v>42</v>
+      <c r="I79" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>43</v>
@@ -8149,8 +8113,8 @@
       <c r="N79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O79" s="1" t="s">
-        <v>42</v>
+      <c r="O79" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>43</v>
@@ -8197,10 +8161,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="3">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B80" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>42</v>
@@ -8286,7 +8250,7 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="3">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B81" t="s">
         <v>193</v>
@@ -8294,8 +8258,8 @@
       <c r="C81" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>42</v>
+      <c r="D81" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>43</v>
@@ -8380,29 +8344,29 @@
       <c r="B82" t="s">
         <v>195</v>
       </c>
-      <c r="C82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>42</v>
+      <c r="C82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>43</v>
@@ -8425,26 +8389,26 @@
       <c r="Q82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U82" s="2" t="s">
-        <v>43</v>
+      <c r="R82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U82" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X82" s="2" t="s">
-        <v>43</v>
+      <c r="W82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X82" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y82" s="2" t="s">
         <v>43</v>
@@ -8475,32 +8439,32 @@
       <c r="D83" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>42</v>
+      <c r="E83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K83" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M83" s="1" t="s">
-        <v>42</v>
+      <c r="M83" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>43</v>
@@ -8514,17 +8478,17 @@
       <c r="Q83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U83" s="1" t="s">
-        <v>42</v>
+      <c r="R83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U83" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V83" s="2" t="s">
         <v>43</v>
@@ -8558,17 +8522,17 @@
       <c r="B84" t="s">
         <v>199</v>
       </c>
-      <c r="C84" s="1" t="s">
-        <v>42</v>
+      <c r="C84" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>43</v>
+      <c r="E84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>43</v>
@@ -8650,8 +8614,8 @@
       <c r="C85" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>43</v>
+      <c r="D85" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>43</v>
@@ -8739,14 +8703,14 @@
       <c r="C86" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>43</v>
+      <c r="D86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>43</v>
@@ -8754,20 +8718,20 @@
       <c r="H86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>43</v>
+      <c r="I86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K86" s="2" t="s">
-        <v>43</v>
+      <c r="K86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M86" s="2" t="s">
-        <v>43</v>
+      <c r="M86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>43</v>
@@ -8775,32 +8739,32 @@
       <c r="O86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P86" s="2" t="s">
-        <v>43</v>
+      <c r="P86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U86" s="2" t="s">
-        <v>43</v>
+      <c r="R86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X86" s="2" t="s">
-        <v>43</v>
+      <c r="W86" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X86" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y86" s="2" t="s">
         <v>43</v>
@@ -8843,20 +8807,20 @@
       <c r="H87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>43</v>
+      <c r="I87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K87" s="2" t="s">
-        <v>43</v>
+      <c r="K87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M87" s="2" t="s">
-        <v>43</v>
+      <c r="M87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>43</v>
@@ -8864,20 +8828,20 @@
       <c r="O87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P87" s="2" t="s">
-        <v>43</v>
+      <c r="P87" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T87" s="1" t="s">
-        <v>42</v>
+      <c r="R87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U87" s="1" t="s">
         <v>42</v>
@@ -9003,17 +8967,17 @@
       <c r="B89" t="s">
         <v>209</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>43</v>
+      <c r="C89" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>42</v>
+      <c r="E89" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>43</v>
@@ -9101,8 +9065,8 @@
       <c r="E90" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>43</v>
+      <c r="F90" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>43</v>
@@ -9184,11 +9148,11 @@
       <c r="C91" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>42</v>
+      <c r="D91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>42</v>
@@ -9199,20 +9163,20 @@
       <c r="H91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>42</v>
+      <c r="I91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>42</v>
+      <c r="K91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M91" s="1" t="s">
-        <v>42</v>
+      <c r="M91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N91" s="2" t="s">
         <v>43</v>
@@ -9220,32 +9184,32 @@
       <c r="O91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P91" s="1" t="s">
-        <v>42</v>
+      <c r="P91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U91" s="1" t="s">
-        <v>42</v>
+      <c r="R91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X91" s="1" t="s">
-        <v>42</v>
+      <c r="W91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y91" s="2" t="s">
         <v>43</v>
@@ -9273,14 +9237,14 @@
       <c r="C92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>42</v>
+      <c r="D92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>43</v>
@@ -9288,20 +9252,20 @@
       <c r="H92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>42</v>
+      <c r="I92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>42</v>
+      <c r="K92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M92" s="1" t="s">
-        <v>42</v>
+      <c r="M92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>43</v>
@@ -9309,8 +9273,8 @@
       <c r="O92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P92" s="1" t="s">
-        <v>42</v>
+      <c r="P92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q92" s="2" t="s">
         <v>43</v>
@@ -9324,17 +9288,17 @@
       <c r="T92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U92" s="1" t="s">
-        <v>42</v>
+      <c r="U92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X92" s="1" t="s">
-        <v>42</v>
+      <c r="W92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>43</v>
@@ -9362,8 +9326,8 @@
       <c r="C93" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>42</v>
+      <c r="D93" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>43</v>
@@ -9451,14 +9415,14 @@
       <c r="C94" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>43</v>
+      <c r="D94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>43</v>
@@ -9493,26 +9457,26 @@
       <c r="Q94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U94" s="2" t="s">
-        <v>43</v>
+      <c r="R94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X94" s="2" t="s">
-        <v>43</v>
+      <c r="W94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y94" s="2" t="s">
         <v>43</v>
@@ -9543,8 +9507,8 @@
       <c r="D95" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>43</v>
+      <c r="E95" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>42</v>
@@ -9591,17 +9555,17 @@
       <c r="T95" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U95" s="2" t="s">
-        <v>43</v>
+      <c r="U95" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V95" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W95" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X95" s="2" t="s">
-        <v>43</v>
+      <c r="W95" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X95" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>43</v>
@@ -9635,8 +9599,8 @@
       <c r="E96" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>42</v>
+      <c r="F96" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>43</v>
@@ -9718,8 +9682,8 @@
       <c r="C97" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>43</v>
+      <c r="D97" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>43</v>
@@ -9905,23 +9869,23 @@
       <c r="F99" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>43</v>
+      <c r="G99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I99" s="2" t="s">
-        <v>43</v>
+      <c r="I99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K99" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L99" s="2" t="s">
-        <v>43</v>
+      <c r="K99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>43</v>
@@ -9929,11 +9893,11 @@
       <c r="N99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O99" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P99" s="2" t="s">
-        <v>43</v>
+      <c r="O99" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q99" s="2" t="s">
         <v>43</v>
@@ -10000,8 +9964,8 @@
       <c r="H100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I100" s="2" t="s">
-        <v>43</v>
+      <c r="I100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>43</v>
@@ -10012,11 +9976,11 @@
       <c r="L100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M100" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N100" s="2" t="s">
-        <v>43</v>
+      <c r="M100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>43</v>
@@ -10030,11 +9994,11 @@
       <c r="R100" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="S100" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T100" s="2" t="s">
-        <v>43</v>
+      <c r="S100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U100" s="2" t="s">
         <v>43</v>
@@ -10077,11 +10041,11 @@
       <c r="D101" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>42</v>
+      <c r="E101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>43</v>
@@ -10101,8 +10065,8 @@
       <c r="L101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M101" s="2" t="s">
-        <v>43</v>
+      <c r="M101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>43</v>
@@ -10116,26 +10080,26 @@
       <c r="Q101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>42</v>
+      <c r="R101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X101" s="1" t="s">
-        <v>42</v>
+      <c r="W101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>43</v>
@@ -10163,41 +10127,41 @@
       <c r="C102" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>43</v>
+      <c r="D102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O102" s="2" t="s">
-        <v>43</v>
+      <c r="I102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P102" s="2" t="s">
         <v>43</v>
@@ -10220,8 +10184,8 @@
       <c r="V102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W102" s="2" t="s">
-        <v>43</v>
+      <c r="W102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X102" s="2" t="s">
         <v>43</v>
@@ -10252,8 +10216,8 @@
       <c r="C103" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>42</v>
+      <c r="D103" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>43</v>
@@ -10273,11 +10237,11 @@
       <c r="J103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L103" s="2" t="s">
-        <v>43</v>
+      <c r="K103" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>43</v>
@@ -10288,8 +10252,8 @@
       <c r="O103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P103" s="2" t="s">
-        <v>43</v>
+      <c r="P103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q103" s="2" t="s">
         <v>43</v>
@@ -10303,8 +10267,8 @@
       <c r="T103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U103" s="2" t="s">
-        <v>43</v>
+      <c r="U103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V103" s="2" t="s">
         <v>43</v>
@@ -10362,11 +10326,11 @@
       <c r="J104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K104" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L104" s="2" t="s">
-        <v>43</v>
+      <c r="K104" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L104" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M104" s="2" t="s">
         <v>43</v>
@@ -10392,8 +10356,8 @@
       <c r="T104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U104" s="2" t="s">
-        <v>43</v>
+      <c r="U104" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V104" s="2" t="s">
         <v>43</v>
@@ -10430,23 +10394,23 @@
       <c r="C105" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>42</v>
+      <c r="D105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>42</v>
+      <c r="I105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>43</v>
@@ -10463,23 +10427,23 @@
       <c r="N105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P105" s="1" t="s">
-        <v>42</v>
+      <c r="O105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T105" s="1" t="s">
-        <v>42</v>
+      <c r="R105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U105" s="1" t="s">
         <v>42</v>
@@ -10487,11 +10451,11 @@
       <c r="V105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X105" s="1" t="s">
-        <v>42</v>
+      <c r="W105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y105" s="2" t="s">
         <v>43</v>
@@ -10519,8 +10483,8 @@
       <c r="C106" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>42</v>
+      <c r="D106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>43</v>
@@ -10534,23 +10498,23 @@
       <c r="H106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>42</v>
+      <c r="I106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N106" s="1" t="s">
-        <v>42</v>
+      <c r="K106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>43</v>
@@ -10561,17 +10525,17 @@
       <c r="Q106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U106" s="2" t="s">
-        <v>43</v>
+      <c r="R106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V106" s="2" t="s">
         <v>43</v>
@@ -10608,8 +10572,8 @@
       <c r="C107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>42</v>
+      <c r="D107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>43</v>
@@ -10629,14 +10593,14 @@
       <c r="J107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K107" s="2" t="s">
-        <v>43</v>
+      <c r="K107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M107" s="1" t="s">
-        <v>42</v>
+      <c r="M107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>43</v>
@@ -10650,17 +10614,17 @@
       <c r="Q107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U107" s="2" t="s">
-        <v>43</v>
+      <c r="R107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V107" s="2" t="s">
         <v>43</v>
@@ -10697,26 +10661,26 @@
       <c r="C108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>42</v>
+      <c r="D108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>42</v>
+      <c r="I108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>42</v>
@@ -10724,14 +10688,14 @@
       <c r="L108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>42</v>
+      <c r="M108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P108" s="2" t="s">
         <v>43</v>
@@ -10748,14 +10712,14 @@
       <c r="T108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U108" s="2" t="s">
-        <v>43</v>
+      <c r="U108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W108" s="1" t="s">
-        <v>42</v>
+      <c r="W108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X108" s="2" t="s">
         <v>43</v>
@@ -10822,8 +10786,8 @@
       <c r="O109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P109" s="1" t="s">
-        <v>42</v>
+      <c r="P109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>43</v>
@@ -10899,8 +10863,8 @@
       <c r="K110" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L110" s="1" t="s">
-        <v>42</v>
+      <c r="L110" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M110" s="2" t="s">
         <v>43</v>
@@ -11166,8 +11130,8 @@
       <c r="K113" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L113" s="2" t="s">
-        <v>43</v>
+      <c r="L113" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M113" s="2" t="s">
         <v>43</v>
@@ -11344,8 +11308,8 @@
       <c r="K115" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L115" s="1" t="s">
-        <v>42</v>
+      <c r="L115" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M115" s="2" t="s">
         <v>43</v>
@@ -11409,68 +11373,68 @@
       <c r="C116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>43</v>
+      <c r="D116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J116" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P116" s="2" t="s">
-        <v>43</v>
+      <c r="L116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P116" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q116" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T116" s="2" t="s">
-        <v>43</v>
+      <c r="R116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T116" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X116" s="2" t="s">
-        <v>43</v>
+      <c r="V116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W116" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X116" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y116" s="2" t="s">
         <v>43</v>
@@ -11498,32 +11462,32 @@
       <c r="C117" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D117" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G117" s="2" t="s">
-        <v>43</v>
+      <c r="D117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I117" s="2" t="s">
-        <v>43</v>
+      <c r="I117" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>42</v>
+      <c r="K117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>43</v>
@@ -11552,14 +11516,14 @@
       <c r="U117" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V117" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W117" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X117" s="2" t="s">
-        <v>43</v>
+      <c r="V117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X117" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y117" s="2" t="s">
         <v>43</v>
@@ -11608,11 +11572,11 @@
       <c r="J118" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K118" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L118" s="1" t="s">
-        <v>42</v>
+      <c r="K118" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M118" s="2" t="s">
         <v>43</v>
@@ -11638,8 +11602,8 @@
       <c r="T118" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U118" s="1" t="s">
-        <v>42</v>
+      <c r="U118" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V118" s="2" t="s">
         <v>43</v>
@@ -11697,11 +11661,11 @@
       <c r="J119" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K119" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>42</v>
+      <c r="K119" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L119" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>43</v>
@@ -11727,8 +11691,8 @@
       <c r="T119" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U119" s="1" t="s">
-        <v>42</v>
+      <c r="U119" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V119" s="2" t="s">
         <v>43</v>
@@ -11762,17 +11726,17 @@
       <c r="B120" t="s">
         <v>271</v>
       </c>
-      <c r="C120" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>43</v>
+      <c r="C120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>43</v>
@@ -11780,8 +11744,8 @@
       <c r="H120" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I120" s="2" t="s">
-        <v>43</v>
+      <c r="I120" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>43</v>
@@ -11792,11 +11756,11 @@
       <c r="L120" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N120" s="2" t="s">
-        <v>43</v>
+      <c r="M120" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>43</v>
@@ -11816,8 +11780,8 @@
       <c r="T120" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U120" s="1" t="s">
-        <v>42</v>
+      <c r="U120" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V120" s="2" t="s">
         <v>43</v>
@@ -11854,14 +11818,14 @@
       <c r="C121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>43</v>
+      <c r="D121" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>43</v>
@@ -11875,8 +11839,8 @@
       <c r="J121" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K121" s="1" t="s">
-        <v>42</v>
+      <c r="K121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>43</v>
@@ -11905,8 +11869,8 @@
       <c r="T121" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U121" s="1" t="s">
-        <v>42</v>
+      <c r="U121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V121" s="2" t="s">
         <v>43</v>
@@ -11946,65 +11910,65 @@
       <c r="D122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>42</v>
+      <c r="E122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q122" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X122" s="1" t="s">
-        <v>42</v>
+      <c r="R122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>43</v>
@@ -12044,8 +12008,8 @@
       <c r="G123" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H123" s="2" t="s">
-        <v>43</v>
+      <c r="H123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>42</v>
@@ -12053,14 +12017,14 @@
       <c r="J123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K123" s="2" t="s">
-        <v>43</v>
+      <c r="K123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M123" s="2" t="s">
-        <v>43</v>
+      <c r="M123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>43</v>
@@ -12074,14 +12038,14 @@
       <c r="Q123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T123" s="2" t="s">
-        <v>43</v>
+      <c r="R123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U123" s="1" t="s">
         <v>42</v>
@@ -12121,14 +12085,14 @@
       <c r="C124" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>43</v>
+      <c r="D124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>43</v>
@@ -12142,14 +12106,14 @@
       <c r="J124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K124" s="2" t="s">
-        <v>43</v>
+      <c r="K124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M124" s="2" t="s">
-        <v>43</v>
+      <c r="M124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>43</v>
@@ -12172,17 +12136,17 @@
       <c r="T124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U124" s="2" t="s">
-        <v>43</v>
+      <c r="U124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X124" s="2" t="s">
-        <v>43</v>
+      <c r="W124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y124" s="2" t="s">
         <v>43</v>
@@ -12210,20 +12174,20 @@
       <c r="C125" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>43</v>
+      <c r="D125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H125" s="2" t="s">
-        <v>43</v>
+      <c r="H125" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>43</v>
@@ -12231,14 +12195,14 @@
       <c r="J125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K125" s="2" t="s">
-        <v>43</v>
+      <c r="K125" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M125" s="2" t="s">
-        <v>43</v>
+      <c r="M125" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>43</v>
@@ -12252,26 +12216,26 @@
       <c r="Q125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W125" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X125" s="2" t="s">
-        <v>43</v>
+      <c r="R125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W125" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X125" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y125" s="2" t="s">
         <v>43</v>
@@ -12308,17 +12272,17 @@
       <c r="F126" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>43</v>
+      <c r="G126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J126" s="2" t="s">
-        <v>43</v>
+      <c r="J126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K126" s="1" t="s">
         <v>42</v>
@@ -12332,11 +12296,11 @@
       <c r="N126" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P126" s="2" t="s">
-        <v>43</v>
+      <c r="O126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q126" s="2" t="s">
         <v>43</v>
@@ -12353,26 +12317,26 @@
       <c r="U126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X126" s="2" t="s">
-        <v>43</v>
+      <c r="V126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z126" s="2" t="s">
-        <v>43</v>
+      <c r="Z126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB126" s="2" t="s">
-        <v>43</v>
+      <c r="AB126" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC126" s="2" t="s">
         <v>43</v>
@@ -12385,17 +12349,17 @@
       <c r="B127" t="s">
         <v>285</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>42</v>
+      <c r="C127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>43</v>
@@ -12454,14 +12418,14 @@
       <c r="Y127" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z127" s="2" t="s">
-        <v>43</v>
+      <c r="Z127" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA127" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB127" s="2" t="s">
-        <v>43</v>
+      <c r="AB127" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC127" s="2" t="s">
         <v>43</v>
@@ -12474,47 +12438,47 @@
       <c r="B128" t="s">
         <v>287</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>42</v>
+      <c r="C128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P128" s="2" t="s">
-        <v>43</v>
+      <c r="E128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P128" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q128" s="2" t="s">
         <v>43</v>
@@ -12531,26 +12495,26 @@
       <c r="U128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X128" s="2" t="s">
-        <v>43</v>
+      <c r="V128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X128" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z128" s="2" t="s">
-        <v>43</v>
+      <c r="Z128" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB128" s="2" t="s">
-        <v>43</v>
+      <c r="AB128" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC128" s="2" t="s">
         <v>43</v>
@@ -12563,38 +12527,38 @@
       <c r="B129" t="s">
         <v>289</v>
       </c>
-      <c r="C129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>42</v>
+      <c r="C129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K129" s="1" t="s">
-        <v>42</v>
+      <c r="K129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M129" s="1" t="s">
-        <v>42</v>
+      <c r="M129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>43</v>
@@ -12608,38 +12572,38 @@
       <c r="Q129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X129" s="1" t="s">
-        <v>42</v>
+      <c r="R129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z129" s="2" t="s">
-        <v>43</v>
+      <c r="Z129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB129" s="2" t="s">
-        <v>43</v>
+      <c r="AB129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC129" s="2" t="s">
         <v>43</v>
@@ -12664,14 +12628,14 @@
       <c r="F130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G130" s="2" t="s">
-        <v>43</v>
+      <c r="G130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I130" s="2" t="s">
-        <v>43</v>
+      <c r="I130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>43</v>
@@ -12679,17 +12643,17 @@
       <c r="K130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L130" s="2" t="s">
-        <v>43</v>
+      <c r="L130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O130" s="2" t="s">
-        <v>43</v>
+      <c r="N130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P130" s="2" t="s">
         <v>43</v>
@@ -12706,8 +12670,8 @@
       <c r="T130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U130" s="1" t="s">
-        <v>42</v>
+      <c r="U130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V130" s="2" t="s">
         <v>43</v>
@@ -12715,8 +12679,8 @@
       <c r="W130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X130" s="1" t="s">
-        <v>42</v>
+      <c r="X130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y130" s="2" t="s">
         <v>43</v>
@@ -12744,20 +12708,20 @@
       <c r="C131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>42</v>
+      <c r="D131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H131" s="1" t="s">
-        <v>42</v>
+      <c r="H131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>43</v>
@@ -12765,14 +12729,14 @@
       <c r="J131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K131" s="1" t="s">
-        <v>42</v>
+      <c r="K131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M131" s="1" t="s">
-        <v>42</v>
+      <c r="M131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N131" s="2" t="s">
         <v>43</v>
@@ -12786,26 +12750,26 @@
       <c r="Q131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X131" s="1" t="s">
-        <v>42</v>
+      <c r="R131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y131" s="2" t="s">
         <v>43</v>
@@ -12830,44 +12794,44 @@
       <c r="B132" t="s">
         <v>295</v>
       </c>
-      <c r="C132" s="2" t="s">
-        <v>43</v>
+      <c r="C132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>42</v>
+      <c r="E132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P132" s="2" t="s">
         <v>43</v>
@@ -12887,26 +12851,26 @@
       <c r="U132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X132" s="1" t="s">
-        <v>42</v>
+      <c r="V132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z132" s="1" t="s">
-        <v>42</v>
+      <c r="Z132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB132" s="1" t="s">
-        <v>42</v>
+      <c r="AB132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC132" s="2" t="s">
         <v>43</v>
@@ -12919,8 +12883,8 @@
       <c r="B133" t="s">
         <v>297</v>
       </c>
-      <c r="C133" s="2" t="s">
-        <v>43</v>
+      <c r="C133" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>43</v>
@@ -12988,14 +12952,14 @@
       <c r="Y133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z133" s="1" t="s">
-        <v>42</v>
+      <c r="Z133" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB133" s="1" t="s">
-        <v>42</v>
+      <c r="AB133" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC133" s="2" t="s">
         <v>43</v>
@@ -13008,8 +12972,8 @@
       <c r="B134" t="s">
         <v>299</v>
       </c>
-      <c r="C134" s="2" t="s">
-        <v>43</v>
+      <c r="C134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>42</v>
@@ -13023,14 +12987,14 @@
       <c r="G134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H134" s="1" t="s">
-        <v>42</v>
+      <c r="H134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J134" s="1" t="s">
-        <v>42</v>
+      <c r="J134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K134" s="1" t="s">
         <v>42</v>
@@ -13047,8 +13011,8 @@
       <c r="O134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P134" s="1" t="s">
-        <v>42</v>
+      <c r="P134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q134" s="2" t="s">
         <v>43</v>
@@ -13065,26 +13029,26 @@
       <c r="U134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V134" s="1" t="s">
-        <v>42</v>
+      <c r="V134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="W134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X134" s="1" t="s">
-        <v>42</v>
+      <c r="X134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z134" s="1" t="s">
-        <v>42</v>
+      <c r="Z134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB134" s="1" t="s">
-        <v>42</v>
+      <c r="AB134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC134" s="2" t="s">
         <v>43</v>
@@ -13097,44 +13061,44 @@
       <c r="B135" t="s">
         <v>301</v>
       </c>
-      <c r="C135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>43</v>
+      <c r="C135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>43</v>
+      <c r="I135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O135" s="2" t="s">
-        <v>43</v>
+      <c r="K135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P135" s="2" t="s">
         <v>43</v>
@@ -13157,8 +13121,8 @@
       <c r="V135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W135" s="2" t="s">
-        <v>43</v>
+      <c r="W135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X135" s="2" t="s">
         <v>43</v>
@@ -13166,14 +13130,14 @@
       <c r="Y135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z135" s="1" t="s">
-        <v>42</v>
+      <c r="Z135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB135" s="1" t="s">
-        <v>42</v>
+      <c r="AB135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC135" s="2" t="s">
         <v>43</v>
@@ -13192,38 +13156,38 @@
       <c r="D136" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>42</v>
+      <c r="E136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I136" s="1" t="s">
-        <v>42</v>
+      <c r="I136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O136" s="1" t="s">
-        <v>42</v>
+      <c r="K136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P136" s="2" t="s">
         <v>43</v>
@@ -13246,8 +13210,8 @@
       <c r="V136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W136" s="1" t="s">
-        <v>42</v>
+      <c r="W136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X136" s="2" t="s">
         <v>43</v>
@@ -13370,11 +13334,11 @@
       <c r="D138" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E138" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>43</v>
+      <c r="E138" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>43</v>
@@ -13388,14 +13352,14 @@
       <c r="J138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K138" s="2" t="s">
-        <v>43</v>
+      <c r="K138" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M138" s="2" t="s">
-        <v>43</v>
+      <c r="M138" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>43</v>
@@ -13424,8 +13388,8 @@
       <c r="V138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W138" s="2" t="s">
-        <v>43</v>
+      <c r="W138" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X138" s="2" t="s">
         <v>43</v>
@@ -13453,8 +13417,8 @@
       <c r="B139" t="s">
         <v>309</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>42</v>
+      <c r="C139" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>43</v>
@@ -13531,8 +13495,8 @@
       <c r="AB139" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AC139" s="2" t="s">
-        <v>43</v>
+      <c r="AC139" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="140">
@@ -13587,17 +13551,17 @@
       <c r="Q140" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U140" s="2" t="s">
-        <v>43</v>
+      <c r="R140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T140" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V140" s="2" t="s">
         <v>43</v>
@@ -13605,8 +13569,8 @@
       <c r="W140" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X140" s="2" t="s">
-        <v>43</v>
+      <c r="X140" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y140" s="2" t="s">
         <v>43</v>
@@ -13631,8 +13595,8 @@
       <c r="B141" t="s">
         <v>313</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>42</v>
+      <c r="C141" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>42</v>
@@ -13640,35 +13604,35 @@
       <c r="E141" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F141" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>42</v>
+      <c r="F141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I141" s="1" t="s">
-        <v>42</v>
+      <c r="I141" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K141" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L141" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M141" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N141" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O141" s="1" t="s">
-        <v>42</v>
+      <c r="K141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O141" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P141" s="2" t="s">
         <v>43</v>
@@ -13691,8 +13655,8 @@
       <c r="V141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W141" s="1" t="s">
-        <v>42</v>
+      <c r="W141" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X141" s="2" t="s">
         <v>43</v>
@@ -13720,8 +13684,8 @@
       <c r="B142" t="s">
         <v>315</v>
       </c>
-      <c r="C142" s="1" t="s">
-        <v>42</v>
+      <c r="C142" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>42</v>
@@ -13799,540 +13763,6 @@
         <v>43</v>
       </c>
       <c r="AC142" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s" s="3">
-        <v>316</v>
-      </c>
-      <c r="B143" t="s">
-        <v>317</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC143" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s" s="3">
-        <v>318</v>
-      </c>
-      <c r="B144" t="s">
-        <v>319</v>
-      </c>
-      <c r="C144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC144" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s" s="3">
-        <v>320</v>
-      </c>
-      <c r="B145" t="s">
-        <v>321</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC145" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s" s="3">
-        <v>322</v>
-      </c>
-      <c r="B146" t="s">
-        <v>323</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC146" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s" s="3">
-        <v>324</v>
-      </c>
-      <c r="B147" t="s">
-        <v>325</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC147" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s" s="3">
-        <v>326</v>
-      </c>
-      <c r="B148" t="s">
-        <v>327</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC148" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -14348,12 +13778,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -966,7 +966,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.61.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -966,7 +966,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.61.0-SNAPSHOT</t>
+    <t>1.0.0</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4120" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4468" uniqueCount="330">
   <si>
     <t>User Right</t>
   </si>
@@ -231,6 +231,24 @@
     <t>Merge cases</t>
   </si>
   <si>
+    <t>IMMUNIZATION_MANAGEMENT_ACCESS</t>
+  </si>
+  <si>
+    <t>IMMUNIZATION_VIEW</t>
+  </si>
+  <si>
+    <t>IMMUNIZATION_CREATE</t>
+  </si>
+  <si>
+    <t>IMMUNIZATION_EDIT</t>
+  </si>
+  <si>
+    <t>IMMUNIZATION_DELETE</t>
+  </si>
+  <si>
+    <t>IMMUNIZATION_ARCHIVE</t>
+  </si>
+  <si>
     <t>PERSON_VIEW</t>
   </si>
   <si>
@@ -961,6 +979,24 @@
   </si>
   <si>
     <t>Perform bulk operations in lab messages list</t>
+  </si>
+  <si>
+    <t>TRAVEL_ENTRY_MANAGEMENT_ACCESS</t>
+  </si>
+  <si>
+    <t>TRAVEL_ENTRY_VIEW</t>
+  </si>
+  <si>
+    <t>TRAVEL_ENTRY_CREATE</t>
+  </si>
+  <si>
+    <t>TRAVEL_ENTRY_EDIT</t>
+  </si>
+  <si>
+    <t>TRAVEL_ENTRY_DELETE</t>
+  </si>
+  <si>
+    <t>TRAVEL_ENTRY_ARCHIVE</t>
   </si>
   <si>
     <t>SORMAS Version</t>
@@ -1094,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD142"/>
+  <dimension ref="A1:AD154"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -2646,7 +2682,7 @@
         <v>72</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>42</v>
@@ -2732,10 +2768,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>42</v>
@@ -2782,14 +2818,14 @@
       <c r="Q19" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>43</v>
+      <c r="R19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U19" s="1" t="s">
         <v>42</v>
@@ -2821,10 +2857,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="3">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>42</v>
@@ -2832,41 +2868,41 @@
       <c r="D20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>43</v>
+      <c r="E20" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>43</v>
+      <c r="G20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>43</v>
@@ -2880,17 +2916,17 @@
       <c r="T20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X20" s="2" t="s">
-        <v>43</v>
+      <c r="U20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y20" s="2" t="s">
         <v>43</v>
@@ -2910,10 +2946,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="3">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>42</v>
@@ -2921,41 +2957,41 @@
       <c r="D21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>43</v>
+      <c r="E21" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P21" s="2" t="s">
-        <v>43</v>
+      <c r="G21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q21" s="2" t="s">
         <v>43</v>
@@ -2969,17 +3005,17 @@
       <c r="T21" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X21" s="2" t="s">
-        <v>43</v>
+      <c r="U21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y21" s="2" t="s">
         <v>43</v>
@@ -2999,10 +3035,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="3">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>42</v>
@@ -3010,29 +3046,29 @@
       <c r="D22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>42</v>
+      <c r="E22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>42</v>
+      <c r="G22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>43</v>
@@ -3040,11 +3076,11 @@
       <c r="N22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>42</v>
+      <c r="O22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>43</v>
@@ -3058,8 +3094,8 @@
       <c r="T22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>42</v>
+      <c r="U22" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V22" s="2" t="s">
         <v>43</v>
@@ -3088,67 +3124,67 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="3">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>42</v>
+      <c r="D23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V23" s="2" t="s">
         <v>43</v>
@@ -3177,10 +3213,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="3">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B24" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>42</v>
@@ -3212,11 +3248,11 @@
       <c r="L24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>43</v>
+      <c r="M24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>42</v>
@@ -3224,29 +3260,29 @@
       <c r="P24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q24" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T24" s="2" t="s">
-        <v>43</v>
+      <c r="Q24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U24" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W24" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X24" s="2" t="s">
-        <v>43</v>
+      <c r="V24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y24" s="2" t="s">
         <v>43</v>
@@ -3266,16 +3302,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="3">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>43</v>
+      <c r="D25" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>42</v>
@@ -3283,35 +3319,35 @@
       <c r="F25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>43</v>
+      <c r="G25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>43</v>
+      <c r="P25" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q25" s="2" t="s">
         <v>43</v>
@@ -3325,17 +3361,17 @@
       <c r="T25" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W25" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X25" s="2" t="s">
-        <v>43</v>
+      <c r="U25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y25" s="2" t="s">
         <v>43</v>
@@ -3355,10 +3391,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="3">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>42</v>
@@ -3444,10 +3480,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="3">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>42</v>
@@ -3455,8 +3491,8 @@
       <c r="D27" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>42</v>
+      <c r="E27" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>42</v>
@@ -3473,8 +3509,8 @@
       <c r="J27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>42</v>
+      <c r="K27" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>43</v>
@@ -3488,11 +3524,11 @@
       <c r="O27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>42</v>
+      <c r="P27" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>43</v>
@@ -3503,8 +3539,8 @@
       <c r="T27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>42</v>
+      <c r="U27" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V27" s="2" t="s">
         <v>43</v>
@@ -3533,10 +3569,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="3">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>42</v>
@@ -3550,32 +3586,32 @@
       <c r="F28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>43</v>
+      <c r="G28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>42</v>
+      <c r="L28" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O28" s="2" t="s">
-        <v>43</v>
+      <c r="O28" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P28" s="1" t="s">
         <v>42</v>
@@ -3622,10 +3658,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="3">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>42</v>
@@ -3642,26 +3678,26 @@
       <c r="G29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>43</v>
+      <c r="H29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J29" s="2" t="s">
-        <v>43</v>
+      <c r="J29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N29" s="2" t="s">
-        <v>43</v>
+      <c r="L29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>42</v>
@@ -3672,14 +3708,14 @@
       <c r="Q29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T29" s="2" t="s">
-        <v>43</v>
+      <c r="R29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T29" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U29" s="1" t="s">
         <v>42</v>
@@ -3711,10 +3747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="3">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>42</v>
@@ -3731,20 +3767,20 @@
       <c r="G30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>43</v>
+      <c r="H30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J30" s="2" t="s">
-        <v>43</v>
+      <c r="J30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>43</v>
+      <c r="L30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>43</v>
@@ -3800,22 +3836,22 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>43</v>
+      <c r="D31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>43</v>
@@ -3841,8 +3877,8 @@
       <c r="N31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>43</v>
+      <c r="O31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P31" s="2" t="s">
         <v>43</v>
@@ -3889,22 +3925,22 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="3">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>43</v>
+      <c r="D32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>43</v>
+      <c r="F32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>43</v>
@@ -3918,11 +3954,11 @@
       <c r="J32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>42</v>
+      <c r="K32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>43</v>
@@ -3933,11 +3969,11 @@
       <c r="O32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>42</v>
+      <c r="P32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R32" s="2" t="s">
         <v>43</v>
@@ -3948,8 +3984,8 @@
       <c r="T32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U32" s="1" t="s">
-        <v>42</v>
+      <c r="U32" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V32" s="2" t="s">
         <v>43</v>
@@ -3978,22 +4014,22 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="3">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>43</v>
+      <c r="D33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>43</v>
@@ -4010,8 +4046,8 @@
       <c r="K33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>42</v>
+      <c r="L33" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>43</v>
@@ -4067,22 +4103,22 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="3">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B34" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>43</v>
+      <c r="D34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>43</v>
@@ -4099,11 +4135,11 @@
       <c r="K34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M34" s="2" t="s">
-        <v>43</v>
+      <c r="L34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>43</v>
@@ -4114,8 +4150,8 @@
       <c r="P34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q34" s="1" t="s">
-        <v>42</v>
+      <c r="Q34" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>43</v>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="3">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>42</v>
@@ -4167,26 +4203,26 @@
       <c r="D35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>43</v>
+      <c r="E35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I35" s="2" t="s">
-        <v>43</v>
+      <c r="I35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K35" s="2" t="s">
-        <v>43</v>
+      <c r="K35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>43</v>
@@ -4197,14 +4233,14 @@
       <c r="N35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>43</v>
+      <c r="O35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>43</v>
@@ -4215,8 +4251,8 @@
       <c r="T35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U35" s="2" t="s">
-        <v>43</v>
+      <c r="U35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V35" s="2" t="s">
         <v>43</v>
@@ -4245,10 +4281,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="3">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>42</v>
@@ -4274,26 +4310,26 @@
       <c r="J36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K36" s="2" t="s">
-        <v>43</v>
+      <c r="K36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q36" s="2" t="s">
-        <v>43</v>
+      <c r="M36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R36" s="2" t="s">
         <v>43</v>
@@ -4304,8 +4340,8 @@
       <c r="T36" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U36" s="2" t="s">
-        <v>43</v>
+      <c r="U36" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V36" s="2" t="s">
         <v>43</v>
@@ -4334,16 +4370,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="3">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>43</v>
+      <c r="D37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>43</v>
@@ -4405,8 +4441,8 @@
       <c r="X37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y37" s="1" t="s">
-        <v>42</v>
+      <c r="Y37" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z37" s="2" t="s">
         <v>43</v>
@@ -4423,31 +4459,31 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="3">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>42</v>
+      <c r="D38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>42</v>
+      <c r="I38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>43</v>
@@ -4455,32 +4491,32 @@
       <c r="K38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>42</v>
+      <c r="L38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>42</v>
+      <c r="Q38" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U38" s="1" t="s">
         <v>42</v>
@@ -4512,16 +4548,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="3">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>42</v>
+      <c r="D39" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>43</v>
@@ -4541,14 +4577,14 @@
       <c r="J39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>42</v>
+      <c r="K39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>43</v>
@@ -4556,11 +4592,11 @@
       <c r="O39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P39" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q39" s="2" t="s">
-        <v>43</v>
+      <c r="P39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R39" s="2" t="s">
         <v>43</v>
@@ -4571,8 +4607,8 @@
       <c r="T39" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U39" s="2" t="s">
-        <v>43</v>
+      <c r="U39" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V39" s="2" t="s">
         <v>43</v>
@@ -4601,46 +4637,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="3">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>42</v>
+      <c r="D40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>42</v>
+      <c r="I40" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>42</v>
+      <c r="K40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>43</v>
@@ -4648,8 +4684,8 @@
       <c r="P40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q40" s="2" t="s">
-        <v>43</v>
+      <c r="Q40" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R40" s="2" t="s">
         <v>43</v>
@@ -4660,8 +4696,8 @@
       <c r="T40" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U40" s="2" t="s">
-        <v>43</v>
+      <c r="U40" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V40" s="2" t="s">
         <v>43</v>
@@ -4690,10 +4726,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="3">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>42</v>
@@ -4779,10 +4815,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="3">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>42</v>
@@ -4790,14 +4826,14 @@
       <c r="D42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>43</v>
+      <c r="E42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>43</v>
@@ -4868,31 +4904,31 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="3">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B43" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>42</v>
+      <c r="D43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>42</v>
+      <c r="I43" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>43</v>
@@ -4903,11 +4939,11 @@
       <c r="L43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M43" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>42</v>
+      <c r="M43" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>43</v>
@@ -4939,8 +4975,8 @@
       <c r="X43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y43" s="2" t="s">
-        <v>43</v>
+      <c r="Y43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>43</v>
@@ -4957,10 +4993,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="3">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B44" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>42</v>
@@ -4974,14 +5010,14 @@
       <c r="F44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G44" s="2" t="s">
-        <v>43</v>
+      <c r="G44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I44" s="2" t="s">
-        <v>43</v>
+      <c r="I44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>43</v>
@@ -4995,11 +5031,11 @@
       <c r="M44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>43</v>
+      <c r="N44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P44" s="1" t="s">
         <v>42</v>
@@ -5007,14 +5043,14 @@
       <c r="Q44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T44" s="2" t="s">
-        <v>43</v>
+      <c r="R44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S44" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U44" s="1" t="s">
         <v>42</v>
@@ -5046,10 +5082,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="3">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>42</v>
@@ -5057,20 +5093,20 @@
       <c r="D45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>42</v>
+      <c r="E45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>42</v>
+      <c r="I45" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>43</v>
@@ -5084,8 +5120,8 @@
       <c r="M45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N45" s="1" t="s">
-        <v>42</v>
+      <c r="N45" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>43</v>
@@ -5135,31 +5171,31 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="3">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>43</v>
+      <c r="D46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>43</v>
+      <c r="G46" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I46" s="2" t="s">
-        <v>43</v>
+      <c r="I46" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>43</v>
@@ -5170,17 +5206,17 @@
       <c r="L46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N46" s="2" t="s">
-        <v>43</v>
+      <c r="M46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P46" s="2" t="s">
-        <v>43</v>
+      <c r="P46" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>43</v>
@@ -5224,31 +5260,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>43</v>
+        <v>125</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>42</v>
+      <c r="E47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>42</v>
+      <c r="I47" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>43</v>
@@ -5259,11 +5295,11 @@
       <c r="L47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M47" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>42</v>
+      <c r="M47" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>43</v>
@@ -5313,10 +5349,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>42</v>
@@ -5402,10 +5438,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B49" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>42</v>
@@ -5413,14 +5449,14 @@
       <c r="D49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>43</v>
+      <c r="E49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>43</v>
@@ -5491,10 +5527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B50" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>42</v>
@@ -5502,11 +5538,11 @@
       <c r="D50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>43</v>
+      <c r="E50" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>43</v>
@@ -5520,14 +5556,14 @@
       <c r="J50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="2" t="s">
-        <v>43</v>
+      <c r="K50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M50" s="2" t="s">
-        <v>43</v>
+      <c r="M50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>43</v>
@@ -5535,8 +5571,8 @@
       <c r="O50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P50" s="2" t="s">
-        <v>43</v>
+      <c r="P50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q50" s="2" t="s">
         <v>43</v>
@@ -5550,8 +5586,8 @@
       <c r="T50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U50" s="2" t="s">
-        <v>43</v>
+      <c r="U50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V50" s="2" t="s">
         <v>43</v>
@@ -5580,10 +5616,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B51" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>42</v>
@@ -5597,20 +5633,20 @@
       <c r="F51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G51" s="2" t="s">
-        <v>43</v>
+      <c r="G51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I51" s="2" t="s">
-        <v>43</v>
+      <c r="I51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K51" s="1" t="s">
-        <v>42</v>
+      <c r="K51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>43</v>
@@ -5618,14 +5654,14 @@
       <c r="M51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N51" s="2" t="s">
-        <v>43</v>
+      <c r="N51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P51" s="1" t="s">
-        <v>42</v>
+      <c r="P51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>43</v>
@@ -5639,8 +5675,8 @@
       <c r="T51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U51" s="1" t="s">
-        <v>42</v>
+      <c r="U51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>43</v>
@@ -5669,43 +5705,43 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>42</v>
+      <c r="D52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>42</v>
+      <c r="G52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>42</v>
+      <c r="I52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K52" s="1" t="s">
-        <v>42</v>
+      <c r="K52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M52" s="1" t="s">
-        <v>42</v>
+      <c r="M52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>43</v>
@@ -5713,8 +5749,8 @@
       <c r="O52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P52" s="1" t="s">
-        <v>42</v>
+      <c r="P52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q52" s="2" t="s">
         <v>43</v>
@@ -5728,17 +5764,17 @@
       <c r="T52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U52" s="1" t="s">
-        <v>42</v>
+      <c r="U52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W52" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X52" s="1" t="s">
-        <v>42</v>
+      <c r="W52" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y52" s="2" t="s">
         <v>43</v>
@@ -5758,13 +5794,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="3">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B53" t="s">
-        <v>142</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>42</v>
+        <v>136</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>42</v>
@@ -5778,20 +5814,20 @@
       <c r="G53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H53" s="1" t="s">
-        <v>42</v>
+      <c r="H53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>42</v>
+      <c r="J53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>42</v>
@@ -5799,35 +5835,35 @@
       <c r="N53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X53" s="1" t="s">
-        <v>42</v>
+      <c r="O53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y53" s="2" t="s">
         <v>43</v>
@@ -5847,10 +5883,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>42</v>
@@ -5858,29 +5894,29 @@
       <c r="D54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>42</v>
+      <c r="E54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L54" s="1" t="s">
-        <v>42</v>
+      <c r="J54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M54" s="1" t="s">
         <v>42</v>
@@ -5888,14 +5924,14 @@
       <c r="N54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>42</v>
+      <c r="O54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R54" s="2" t="s">
         <v>43</v>
@@ -5906,17 +5942,17 @@
       <c r="T54" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W54" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X54" s="1" t="s">
-        <v>42</v>
+      <c r="U54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W54" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y54" s="2" t="s">
         <v>43</v>
@@ -5936,10 +5972,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B55" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>42</v>
@@ -5947,14 +5983,14 @@
       <c r="D55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>42</v>
+      <c r="E55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>43</v>
@@ -5965,8 +6001,8 @@
       <c r="J55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K55" s="1" t="s">
-        <v>42</v>
+      <c r="K55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>43</v>
@@ -5974,14 +6010,14 @@
       <c r="M55" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N55" s="2" t="s">
-        <v>43</v>
+      <c r="N55" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P55" s="1" t="s">
-        <v>42</v>
+      <c r="P55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q55" s="2" t="s">
         <v>43</v>
@@ -5995,17 +6031,17 @@
       <c r="T55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U55" s="1" t="s">
-        <v>42</v>
+      <c r="U55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W55" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X55" s="1" t="s">
-        <v>42</v>
+      <c r="W55" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y55" s="2" t="s">
         <v>43</v>
@@ -6025,10 +6061,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>42</v>
@@ -6114,10 +6150,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>42</v>
@@ -6131,38 +6167,38 @@
       <c r="F57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>42</v>
+      <c r="G57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>42</v>
+      <c r="L57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>42</v>
+      <c r="N57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q57" s="1" t="s">
-        <v>42</v>
+      <c r="Q57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R57" s="2" t="s">
         <v>43</v>
@@ -6176,14 +6212,14 @@
       <c r="U57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X57" s="1" t="s">
-        <v>42</v>
+      <c r="V57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y57" s="2" t="s">
         <v>43</v>
@@ -6203,10 +6239,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>42</v>
@@ -6232,23 +6268,23 @@
       <c r="J58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K58" s="2" t="s">
-        <v>43</v>
+      <c r="K58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M58" s="2" t="s">
-        <v>43</v>
+      <c r="M58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>43</v>
+      <c r="O58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q58" s="2" t="s">
         <v>43</v>
@@ -6262,17 +6298,17 @@
       <c r="T58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U58" s="2" t="s">
-        <v>43</v>
+      <c r="U58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W58" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X58" s="2" t="s">
-        <v>43</v>
+      <c r="W58" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X58" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>43</v>
@@ -6292,76 +6328,76 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W59" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X59" s="2" t="s">
-        <v>43</v>
+      <c r="D59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W59" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X59" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y59" s="2" t="s">
         <v>43</v>
@@ -6381,10 +6417,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B60" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>42</v>
@@ -6401,35 +6437,35 @@
       <c r="G60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>43</v>
+      <c r="H60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N60" s="2" t="s">
-        <v>43</v>
+      <c r="J60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>43</v>
+      <c r="P60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R60" s="2" t="s">
         <v>43</v>
@@ -6440,17 +6476,17 @@
       <c r="T60" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X60" s="2" t="s">
-        <v>43</v>
+      <c r="U60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y60" s="2" t="s">
         <v>43</v>
@@ -6470,10 +6506,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B61" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>42</v>
@@ -6499,23 +6535,23 @@
       <c r="J61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K61" s="2" t="s">
-        <v>43</v>
+      <c r="K61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M61" s="2" t="s">
-        <v>43</v>
+      <c r="M61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P61" s="2" t="s">
-        <v>43</v>
+      <c r="O61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q61" s="2" t="s">
         <v>43</v>
@@ -6529,17 +6565,17 @@
       <c r="T61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U61" s="2" t="s">
-        <v>43</v>
+      <c r="U61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X61" s="2" t="s">
-        <v>43</v>
+      <c r="W61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y61" s="2" t="s">
         <v>43</v>
@@ -6559,10 +6595,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="B62" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>42</v>
@@ -6570,62 +6606,62 @@
       <c r="D62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>42</v>
+      <c r="E62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W62" s="1" t="s">
-        <v>42</v>
+      <c r="R62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W62" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X62" s="2" t="s">
         <v>43</v>
@@ -6648,10 +6684,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="B63" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>42</v>
@@ -6668,35 +6704,35 @@
       <c r="G63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H63" s="2" t="s">
-        <v>43</v>
+      <c r="H63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N63" s="2" t="s">
-        <v>43</v>
+      <c r="J63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q63" s="2" t="s">
-        <v>43</v>
+      <c r="P63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>43</v>
@@ -6707,17 +6743,17 @@
       <c r="T63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X63" s="2" t="s">
-        <v>43</v>
+      <c r="U63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W63" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X63" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y63" s="2" t="s">
         <v>43</v>
@@ -6737,31 +6773,31 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="B64" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>43</v>
+      <c r="D64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I64" s="2" t="s">
-        <v>43</v>
+      <c r="I64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>43</v>
@@ -6778,8 +6814,8 @@
       <c r="N64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O64" s="2" t="s">
-        <v>43</v>
+      <c r="O64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>43</v>
@@ -6808,8 +6844,8 @@
       <c r="X64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y64" s="1" t="s">
-        <v>42</v>
+      <c r="Y64" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z64" s="2" t="s">
         <v>43</v>
@@ -6826,22 +6862,22 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="3">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="B65" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>42</v>
+      <c r="D65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>43</v>
@@ -6855,14 +6891,14 @@
       <c r="J65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>42</v>
+      <c r="K65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>42</v>
+      <c r="M65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>43</v>
@@ -6870,8 +6906,8 @@
       <c r="O65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P65" s="1" t="s">
-        <v>42</v>
+      <c r="P65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q65" s="2" t="s">
         <v>43</v>
@@ -6885,17 +6921,17 @@
       <c r="T65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U65" s="1" t="s">
-        <v>42</v>
+      <c r="U65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X65" s="1" t="s">
-        <v>42</v>
+      <c r="W65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y65" s="2" t="s">
         <v>43</v>
@@ -6915,31 +6951,31 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="3">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="B66" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>43</v>
+      <c r="D66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I66" s="2" t="s">
-        <v>43</v>
+      <c r="I66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>43</v>
@@ -6956,8 +6992,8 @@
       <c r="N66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O66" s="2" t="s">
-        <v>43</v>
+      <c r="O66" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>43</v>
@@ -7004,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="3">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B67" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>42</v>
@@ -7015,20 +7051,20 @@
       <c r="D67" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>43</v>
+      <c r="E67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I67" s="2" t="s">
-        <v>43</v>
+      <c r="I67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>43</v>
@@ -7045,8 +7081,8 @@
       <c r="N67" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O67" s="2" t="s">
-        <v>43</v>
+      <c r="O67" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P67" s="2" t="s">
         <v>43</v>
@@ -7093,10 +7129,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="3">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="B68" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>42</v>
@@ -7113,53 +7149,53 @@
       <c r="G68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>43</v>
+      <c r="H68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N68" s="2" t="s">
-        <v>43</v>
+      <c r="J68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P68" s="2" t="s">
-        <v>43</v>
+      <c r="P68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W68" s="2" t="s">
-        <v>43</v>
+      <c r="R68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V68" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W68" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X68" s="2" t="s">
         <v>43</v>
@@ -7182,10 +7218,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="3">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>42</v>
@@ -7226,8 +7262,8 @@
       <c r="O69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P69" s="1" t="s">
-        <v>42</v>
+      <c r="P69" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>43</v>
@@ -7271,16 +7307,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="3">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B70" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>42</v>
+      <c r="D70" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>43</v>
@@ -7342,8 +7378,8 @@
       <c r="X70" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y70" s="2" t="s">
-        <v>43</v>
+      <c r="Y70" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>43</v>
@@ -7360,10 +7396,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="3">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="B71" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>42</v>
@@ -7377,35 +7413,35 @@
       <c r="F71" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G71" s="1" t="s">
-        <v>42</v>
+      <c r="G71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I71" s="1" t="s">
-        <v>42</v>
+      <c r="I71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K71" s="2" t="s">
-        <v>43</v>
+      <c r="K71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M71" s="2" t="s">
-        <v>43</v>
+      <c r="M71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P71" s="2" t="s">
-        <v>43</v>
+      <c r="O71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q71" s="2" t="s">
         <v>43</v>
@@ -7419,20 +7455,20 @@
       <c r="T71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U71" s="2" t="s">
-        <v>43</v>
+      <c r="U71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y71" s="1" t="s">
-        <v>42</v>
+      <c r="W71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X71" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z71" s="2" t="s">
         <v>43</v>
@@ -7449,31 +7485,31 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="3">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D72" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>42</v>
+      <c r="D72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>42</v>
+      <c r="G72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I72" s="1" t="s">
-        <v>42</v>
+      <c r="I72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>43</v>
@@ -7490,8 +7526,8 @@
       <c r="N72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>42</v>
+      <c r="O72" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P72" s="2" t="s">
         <v>43</v>
@@ -7538,10 +7574,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="3">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B73" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>42</v>
@@ -7549,20 +7585,20 @@
       <c r="D73" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>42</v>
+      <c r="E73" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G73" s="1" t="s">
-        <v>42</v>
+      <c r="G73" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I73" s="1" t="s">
-        <v>42</v>
+      <c r="I73" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>43</v>
@@ -7579,8 +7615,8 @@
       <c r="N73" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O73" s="1" t="s">
-        <v>42</v>
+      <c r="O73" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P73" s="2" t="s">
         <v>43</v>
@@ -7627,10 +7663,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="3">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B74" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>42</v>
@@ -7716,31 +7752,31 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B75" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D75" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G75" s="2" t="s">
-        <v>43</v>
+      <c r="D75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I75" s="2" t="s">
-        <v>43</v>
+      <c r="I75" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>43</v>
@@ -7757,11 +7793,11 @@
       <c r="N75" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O75" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P75" s="2" t="s">
-        <v>43</v>
+      <c r="O75" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q75" s="2" t="s">
         <v>43</v>
@@ -7805,10 +7841,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B76" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>42</v>
@@ -7894,34 +7930,34 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="3">
+        <v>183</v>
+      </c>
+      <c r="B77" t="s">
         <v>184</v>
       </c>
-      <c r="B77" t="s">
-        <v>185</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>43</v>
+      <c r="C77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>42</v>
+      <c r="H77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>42</v>
+      <c r="J77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K77" s="2" t="s">
         <v>43</v>
@@ -7935,8 +7971,8 @@
       <c r="N77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O77" s="2" t="s">
-        <v>43</v>
+      <c r="O77" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>43</v>
@@ -7965,8 +8001,8 @@
       <c r="X77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y77" s="2" t="s">
-        <v>43</v>
+      <c r="Y77" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z77" s="2" t="s">
         <v>43</v>
@@ -7983,10 +8019,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="3">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B78" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>42</v>
@@ -8003,29 +8039,29 @@
       <c r="G78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H78" s="1" t="s">
-        <v>42</v>
+      <c r="H78" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I78" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>42</v>
+      <c r="J78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M78" s="1" t="s">
-        <v>42</v>
+      <c r="M78" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O78" s="2" t="s">
-        <v>43</v>
+      <c r="O78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P78" s="2" t="s">
         <v>43</v>
@@ -8033,17 +8069,17 @@
       <c r="Q78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R78" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S78" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T78" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U78" s="1" t="s">
-        <v>42</v>
+      <c r="R78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U78" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V78" s="2" t="s">
         <v>43</v>
@@ -8072,31 +8108,31 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="3">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B79" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>43</v>
+      <c r="D79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>43</v>
+      <c r="I79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>43</v>
@@ -8113,8 +8149,8 @@
       <c r="N79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O79" s="2" t="s">
-        <v>43</v>
+      <c r="O79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P79" s="2" t="s">
         <v>43</v>
@@ -8161,31 +8197,31 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="3">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B80" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G80" s="2" t="s">
-        <v>43</v>
+      <c r="D80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>43</v>
+      <c r="I80" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>43</v>
@@ -8202,8 +8238,8 @@
       <c r="N80" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>43</v>
+      <c r="O80" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P80" s="2" t="s">
         <v>43</v>
@@ -8250,10 +8286,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="3">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>42</v>
@@ -8339,10 +8375,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="3">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B82" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>42</v>
@@ -8350,11 +8386,11 @@
       <c r="D82" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>42</v>
+      <c r="E82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>43</v>
@@ -8389,26 +8425,26 @@
       <c r="Q82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U82" s="1" t="s">
-        <v>42</v>
+      <c r="R82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V82" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W82" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X82" s="1" t="s">
-        <v>42</v>
+      <c r="W82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y82" s="2" t="s">
         <v>43</v>
@@ -8428,16 +8464,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="3">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="B83" t="s">
-        <v>197</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>42</v>
+        <v>191</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>43</v>
@@ -8445,17 +8481,17 @@
       <c r="F83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>43</v>
+      <c r="G83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>43</v>
@@ -8517,16 +8553,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="3">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>199</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>43</v>
+        <v>193</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>42</v>
@@ -8534,26 +8570,26 @@
       <c r="F84" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>43</v>
+      <c r="G84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M84" s="2" t="s">
-        <v>43</v>
+      <c r="M84" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>43</v>
@@ -8567,17 +8603,17 @@
       <c r="Q84" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U84" s="2" t="s">
-        <v>43</v>
+      <c r="R84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U84" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>43</v>
@@ -8606,16 +8642,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="3">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>42</v>
+      <c r="D85" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>43</v>
@@ -8695,22 +8731,22 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="3">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="B86" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>42</v>
+      <c r="D86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>43</v>
@@ -8718,20 +8754,20 @@
       <c r="H86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I86" s="1" t="s">
-        <v>42</v>
+      <c r="I86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>42</v>
+      <c r="K86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M86" s="1" t="s">
-        <v>42</v>
+      <c r="M86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>43</v>
@@ -8739,32 +8775,32 @@
       <c r="O86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P86" s="1" t="s">
-        <v>42</v>
+      <c r="P86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U86" s="1" t="s">
-        <v>42</v>
+      <c r="R86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V86" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W86" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X86" s="1" t="s">
-        <v>42</v>
+      <c r="W86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X86" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y86" s="2" t="s">
         <v>43</v>
@@ -8784,22 +8820,22 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="3">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B87" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>42</v>
+      <c r="D87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>43</v>
@@ -8807,20 +8843,20 @@
       <c r="H87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I87" s="1" t="s">
-        <v>42</v>
+      <c r="I87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>42</v>
+      <c r="K87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>42</v>
+      <c r="M87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>43</v>
@@ -8828,8 +8864,8 @@
       <c r="O87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P87" s="1" t="s">
-        <v>42</v>
+      <c r="P87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q87" s="2" t="s">
         <v>43</v>
@@ -8843,17 +8879,17 @@
       <c r="T87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U87" s="1" t="s">
-        <v>42</v>
+      <c r="U87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V87" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W87" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X87" s="1" t="s">
-        <v>42</v>
+      <c r="W87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X87" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y87" s="2" t="s">
         <v>43</v>
@@ -8873,10 +8909,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="3">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B88" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>42</v>
@@ -8884,11 +8920,11 @@
       <c r="D88" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>43</v>
+      <c r="E88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>43</v>
@@ -8923,26 +8959,26 @@
       <c r="Q88" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U88" s="2" t="s">
-        <v>43</v>
+      <c r="R88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U88" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V88" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X88" s="2" t="s">
-        <v>43</v>
+      <c r="W88" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X88" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y88" s="2" t="s">
         <v>43</v>
@@ -8962,16 +8998,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="3">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="B89" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D89" s="2" t="s">
-        <v>43</v>
+      <c r="D89" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>43</v>
@@ -9051,19 +9087,19 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="3">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B90" t="s">
-        <v>211</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>43</v>
+        <v>205</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>42</v>
@@ -9140,22 +9176,22 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="3">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B91" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>43</v>
+      <c r="D91" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>42</v>
+      <c r="F91" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>43</v>
@@ -9229,22 +9265,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="3">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B92" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>43</v>
+      <c r="D92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>43</v>
@@ -9252,20 +9288,20 @@
       <c r="H92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>43</v>
+      <c r="I92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K92" s="2" t="s">
-        <v>43</v>
+      <c r="K92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M92" s="2" t="s">
-        <v>43</v>
+      <c r="M92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>43</v>
@@ -9273,32 +9309,32 @@
       <c r="O92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P92" s="2" t="s">
-        <v>43</v>
+      <c r="P92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U92" s="2" t="s">
-        <v>43</v>
+      <c r="R92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W92" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X92" s="2" t="s">
-        <v>43</v>
+      <c r="W92" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X92" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>43</v>
@@ -9318,22 +9354,22 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="3">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="B93" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>43</v>
+      <c r="D93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>43</v>
@@ -9341,20 +9377,20 @@
       <c r="H93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I93" s="2" t="s">
-        <v>43</v>
+      <c r="I93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K93" s="2" t="s">
-        <v>43</v>
+      <c r="K93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M93" s="2" t="s">
-        <v>43</v>
+      <c r="M93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>43</v>
@@ -9362,8 +9398,8 @@
       <c r="O93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P93" s="2" t="s">
-        <v>43</v>
+      <c r="P93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q93" s="2" t="s">
         <v>43</v>
@@ -9377,17 +9413,17 @@
       <c r="T93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U93" s="2" t="s">
-        <v>43</v>
+      <c r="U93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X93" s="2" t="s">
-        <v>43</v>
+      <c r="W93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y93" s="2" t="s">
         <v>43</v>
@@ -9407,10 +9443,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="3">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B94" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>42</v>
@@ -9418,11 +9454,11 @@
       <c r="D94" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>42</v>
+      <c r="E94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>43</v>
@@ -9457,26 +9493,26 @@
       <c r="Q94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U94" s="1" t="s">
-        <v>42</v>
+      <c r="R94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U94" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W94" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X94" s="1" t="s">
-        <v>42</v>
+      <c r="W94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X94" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y94" s="2" t="s">
         <v>43</v>
@@ -9496,22 +9532,22 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="3">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B95" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>42</v>
+      <c r="D95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>43</v>
@@ -9555,17 +9591,17 @@
       <c r="T95" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U95" s="1" t="s">
-        <v>42</v>
+      <c r="U95" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V95" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W95" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X95" s="1" t="s">
-        <v>42</v>
+      <c r="W95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y95" s="2" t="s">
         <v>43</v>
@@ -9585,22 +9621,22 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="3">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B96" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>43</v>
+      <c r="D96" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>43</v>
+      <c r="F96" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>43</v>
@@ -9674,22 +9710,22 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="3">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B97" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>42</v>
+      <c r="D97" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>43</v>
+      <c r="F97" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>43</v>
@@ -9763,10 +9799,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="3">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B98" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>42</v>
@@ -9852,40 +9888,40 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="3">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B99" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G99" s="1" t="s">
-        <v>42</v>
+      <c r="D99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I99" s="1" t="s">
-        <v>42</v>
+      <c r="I99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L99" s="1" t="s">
-        <v>42</v>
+      <c r="K99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>43</v>
@@ -9893,35 +9929,35 @@
       <c r="N99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P99" s="1" t="s">
-        <v>42</v>
+      <c r="O99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U99" s="1" t="s">
-        <v>42</v>
+      <c r="R99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W99" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X99" s="1" t="s">
-        <v>42</v>
+      <c r="W99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y99" s="2" t="s">
         <v>43</v>
@@ -9941,10 +9977,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="3">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="B100" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>42</v>
@@ -9952,11 +9988,11 @@
       <c r="D100" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>43</v>
+      <c r="E100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>43</v>
@@ -9964,8 +10000,8 @@
       <c r="H100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I100" s="1" t="s">
-        <v>42</v>
+      <c r="I100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>43</v>
@@ -9976,11 +10012,11 @@
       <c r="L100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>42</v>
+      <c r="M100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O100" s="2" t="s">
         <v>43</v>
@@ -10000,17 +10036,17 @@
       <c r="T100" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U100" s="2" t="s">
-        <v>43</v>
+      <c r="U100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W100" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X100" s="2" t="s">
-        <v>43</v>
+      <c r="W100" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X100" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y100" s="2" t="s">
         <v>43</v>
@@ -10030,10 +10066,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="3">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="B101" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>42</v>
@@ -10041,11 +10077,11 @@
       <c r="D101" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>43</v>
+      <c r="E101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>43</v>
@@ -10065,8 +10101,8 @@
       <c r="L101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M101" s="1" t="s">
-        <v>42</v>
+      <c r="M101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>43</v>
@@ -10080,26 +10116,26 @@
       <c r="Q101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U101" s="2" t="s">
-        <v>43</v>
+      <c r="R101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X101" s="2" t="s">
-        <v>43</v>
+      <c r="W101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>43</v>
@@ -10119,49 +10155,49 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="3">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B102" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>42</v>
+      <c r="D102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N102" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O102" s="1" t="s">
-        <v>42</v>
+      <c r="I102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O102" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P102" s="2" t="s">
         <v>43</v>
@@ -10184,8 +10220,8 @@
       <c r="V102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W102" s="1" t="s">
-        <v>42</v>
+      <c r="W102" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X102" s="2" t="s">
         <v>43</v>
@@ -10208,16 +10244,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="3">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="B103" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>43</v>
+      <c r="D103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>43</v>
@@ -10237,11 +10273,11 @@
       <c r="J103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L103" s="1" t="s">
-        <v>42</v>
+      <c r="K103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L103" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M103" s="2" t="s">
         <v>43</v>
@@ -10252,8 +10288,8 @@
       <c r="O103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P103" s="1" t="s">
-        <v>42</v>
+      <c r="P103" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q103" s="2" t="s">
         <v>43</v>
@@ -10267,8 +10303,8 @@
       <c r="T103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U103" s="1" t="s">
-        <v>42</v>
+      <c r="U103" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V103" s="2" t="s">
         <v>43</v>
@@ -10297,10 +10333,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="3">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B104" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>42</v>
@@ -10326,11 +10362,11 @@
       <c r="J104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K104" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L104" s="1" t="s">
-        <v>42</v>
+      <c r="K104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M104" s="2" t="s">
         <v>43</v>
@@ -10356,8 +10392,8 @@
       <c r="T104" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U104" s="1" t="s">
-        <v>42</v>
+      <c r="U104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V104" s="2" t="s">
         <v>43</v>
@@ -10386,31 +10422,31 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="3">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="B105" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>43</v>
+      <c r="D105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>43</v>
+      <c r="I105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>43</v>
@@ -10427,23 +10463,23 @@
       <c r="N105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P105" s="2" t="s">
-        <v>43</v>
+      <c r="O105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T105" s="2" t="s">
-        <v>43</v>
+      <c r="R105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U105" s="1" t="s">
         <v>42</v>
@@ -10451,11 +10487,11 @@
       <c r="V105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X105" s="2" t="s">
-        <v>43</v>
+      <c r="W105" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y105" s="2" t="s">
         <v>43</v>
@@ -10475,16 +10511,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="3">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B106" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>43</v>
+      <c r="D106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>43</v>
@@ -10498,23 +10534,23 @@
       <c r="H106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I106" s="2" t="s">
-        <v>43</v>
+      <c r="I106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N106" s="2" t="s">
-        <v>43</v>
+      <c r="K106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O106" s="2" t="s">
         <v>43</v>
@@ -10525,17 +10561,17 @@
       <c r="Q106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U106" s="1" t="s">
-        <v>42</v>
+      <c r="R106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V106" s="2" t="s">
         <v>43</v>
@@ -10564,16 +10600,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="3">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B107" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D107" s="2" t="s">
-        <v>43</v>
+      <c r="D107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>43</v>
@@ -10593,14 +10629,14 @@
       <c r="J107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K107" s="1" t="s">
-        <v>42</v>
+      <c r="K107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M107" s="2" t="s">
-        <v>43</v>
+      <c r="M107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>43</v>
@@ -10614,17 +10650,17 @@
       <c r="Q107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U107" s="1" t="s">
-        <v>42</v>
+      <c r="R107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U107" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V107" s="2" t="s">
         <v>43</v>
@@ -10653,34 +10689,34 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="3">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B108" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>43</v>
+      <c r="D108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>43</v>
+      <c r="I108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K108" s="1" t="s">
         <v>42</v>
@@ -10688,14 +10724,14 @@
       <c r="L108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>43</v>
+      <c r="M108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P108" s="2" t="s">
         <v>43</v>
@@ -10712,14 +10748,14 @@
       <c r="T108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U108" s="1" t="s">
-        <v>42</v>
+      <c r="U108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W108" s="2" t="s">
-        <v>43</v>
+      <c r="W108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X108" s="2" t="s">
         <v>43</v>
@@ -10742,10 +10778,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="3">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B109" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>42</v>
@@ -10786,8 +10822,8 @@
       <c r="O109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P109" s="2" t="s">
-        <v>43</v>
+      <c r="P109" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>43</v>
@@ -10831,10 +10867,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="3">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="B110" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>42</v>
@@ -10863,8 +10899,8 @@
       <c r="K110" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L110" s="2" t="s">
-        <v>43</v>
+      <c r="L110" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M110" s="2" t="s">
         <v>43</v>
@@ -10920,10 +10956,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="3">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="B111" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>42</v>
@@ -11009,10 +11045,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="3">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="B112" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>42</v>
@@ -11098,10 +11134,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="3">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B113" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>42</v>
@@ -11130,8 +11166,8 @@
       <c r="K113" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L113" s="1" t="s">
-        <v>42</v>
+      <c r="L113" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M113" s="2" t="s">
         <v>43</v>
@@ -11187,10 +11223,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="3">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="B114" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>42</v>
@@ -11276,10 +11312,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="3">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="B115" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>42</v>
@@ -11308,8 +11344,8 @@
       <c r="K115" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L115" s="2" t="s">
-        <v>43</v>
+      <c r="L115" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M115" s="2" t="s">
         <v>43</v>
@@ -11365,76 +11401,76 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="3">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J116" s="1" t="s">
-        <v>42</v>
+      <c r="D116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P116" s="1" t="s">
-        <v>42</v>
+      <c r="L116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P116" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q116" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T116" s="1" t="s">
-        <v>42</v>
+      <c r="R116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T116" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W116" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X116" s="1" t="s">
-        <v>42</v>
+      <c r="V116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X116" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y116" s="2" t="s">
         <v>43</v>
@@ -11454,40 +11490,40 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="3">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="B117" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>42</v>
+      <c r="D117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I117" s="1" t="s">
-        <v>42</v>
+      <c r="I117" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K117" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L117" s="2" t="s">
-        <v>43</v>
+      <c r="K117" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L117" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>43</v>
@@ -11516,14 +11552,14 @@
       <c r="U117" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W117" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X117" s="1" t="s">
-        <v>42</v>
+      <c r="V117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X117" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y117" s="2" t="s">
         <v>43</v>
@@ -11543,10 +11579,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="3">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B118" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>42</v>
@@ -11572,11 +11608,11 @@
       <c r="J118" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K118" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L118" s="2" t="s">
-        <v>43</v>
+      <c r="K118" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L118" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M118" s="2" t="s">
         <v>43</v>
@@ -11602,8 +11638,8 @@
       <c r="T118" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U118" s="2" t="s">
-        <v>43</v>
+      <c r="U118" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V118" s="2" t="s">
         <v>43</v>
@@ -11632,10 +11668,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="3">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B119" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>42</v>
@@ -11661,11 +11697,11 @@
       <c r="J119" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K119" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L119" s="2" t="s">
-        <v>43</v>
+      <c r="K119" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M119" s="2" t="s">
         <v>43</v>
@@ -11691,8 +11727,8 @@
       <c r="T119" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U119" s="2" t="s">
-        <v>43</v>
+      <c r="U119" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V119" s="2" t="s">
         <v>43</v>
@@ -11721,22 +11757,22 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="3">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B120" t="s">
-        <v>271</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>42</v>
+        <v>265</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>43</v>
@@ -11744,8 +11780,8 @@
       <c r="H120" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I120" s="1" t="s">
-        <v>42</v>
+      <c r="I120" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>43</v>
@@ -11756,11 +11792,11 @@
       <c r="L120" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M120" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N120" s="1" t="s">
-        <v>42</v>
+      <c r="M120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N120" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O120" s="2" t="s">
         <v>43</v>
@@ -11780,8 +11816,8 @@
       <c r="T120" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U120" s="2" t="s">
-        <v>43</v>
+      <c r="U120" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V120" s="2" t="s">
         <v>43</v>
@@ -11810,22 +11846,22 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="3">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B121" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>42</v>
+      <c r="D121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G121" s="2" t="s">
         <v>43</v>
@@ -11839,8 +11875,8 @@
       <c r="J121" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K121" s="2" t="s">
-        <v>43</v>
+      <c r="K121" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L121" s="2" t="s">
         <v>43</v>
@@ -11869,8 +11905,8 @@
       <c r="T121" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U121" s="2" t="s">
-        <v>43</v>
+      <c r="U121" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V121" s="2" t="s">
         <v>43</v>
@@ -11899,10 +11935,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="3">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="B122" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>42</v>
@@ -11910,65 +11946,65 @@
       <c r="D122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P122" s="2" t="s">
-        <v>43</v>
+      <c r="E122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P122" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q122" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X122" s="2" t="s">
-        <v>43</v>
+      <c r="R122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W122" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X122" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>43</v>
@@ -11988,10 +12024,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="3">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>42</v>
@@ -12008,8 +12044,8 @@
       <c r="G123" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H123" s="1" t="s">
-        <v>42</v>
+      <c r="H123" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>42</v>
@@ -12017,14 +12053,14 @@
       <c r="J123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K123" s="1" t="s">
-        <v>42</v>
+      <c r="K123" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M123" s="1" t="s">
-        <v>42</v>
+      <c r="M123" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>43</v>
@@ -12038,14 +12074,14 @@
       <c r="Q123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R123" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S123" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T123" s="1" t="s">
-        <v>42</v>
+      <c r="R123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T123" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U123" s="1" t="s">
         <v>42</v>
@@ -12077,22 +12113,22 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="3">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>42</v>
+      <c r="D124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>43</v>
@@ -12106,14 +12142,14 @@
       <c r="J124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K124" s="1" t="s">
-        <v>42</v>
+      <c r="K124" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M124" s="1" t="s">
-        <v>42</v>
+      <c r="M124" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>43</v>
@@ -12136,17 +12172,17 @@
       <c r="T124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U124" s="1" t="s">
-        <v>42</v>
+      <c r="U124" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W124" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X124" s="1" t="s">
-        <v>42</v>
+      <c r="W124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X124" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y124" s="2" t="s">
         <v>43</v>
@@ -12166,28 +12202,28 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="3">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B125" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>42</v>
+      <c r="D125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>42</v>
+      <c r="H125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I125" s="2" t="s">
         <v>43</v>
@@ -12195,14 +12231,14 @@
       <c r="J125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K125" s="1" t="s">
-        <v>42</v>
+      <c r="K125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M125" s="1" t="s">
-        <v>42</v>
+      <c r="M125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>43</v>
@@ -12216,26 +12252,26 @@
       <c r="Q125" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W125" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X125" s="1" t="s">
-        <v>42</v>
+      <c r="R125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X125" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y125" s="2" t="s">
         <v>43</v>
@@ -12255,10 +12291,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="3">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B126" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>43</v>
@@ -12272,17 +12308,17 @@
       <c r="F126" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>42</v>
+      <c r="G126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J126" s="1" t="s">
-        <v>42</v>
+      <c r="J126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K126" s="1" t="s">
         <v>42</v>
@@ -12296,11 +12332,11 @@
       <c r="N126" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="O126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P126" s="1" t="s">
-        <v>42</v>
+      <c r="O126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q126" s="2" t="s">
         <v>43</v>
@@ -12317,26 +12353,26 @@
       <c r="U126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X126" s="1" t="s">
-        <v>42</v>
+      <c r="V126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z126" s="1" t="s">
-        <v>42</v>
+      <c r="Z126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB126" s="1" t="s">
-        <v>42</v>
+      <c r="AB126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC126" s="2" t="s">
         <v>43</v>
@@ -12344,22 +12380,22 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="3">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="B127" t="s">
-        <v>285</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F127" s="2" t="s">
-        <v>43</v>
+        <v>279</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G127" s="2" t="s">
         <v>43</v>
@@ -12418,14 +12454,14 @@
       <c r="Y127" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z127" s="1" t="s">
-        <v>42</v>
+      <c r="Z127" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA127" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB127" s="1" t="s">
-        <v>42</v>
+      <c r="AB127" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC127" s="2" t="s">
         <v>43</v>
@@ -12433,52 +12469,52 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="3">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B128" t="s">
-        <v>287</v>
-      </c>
-      <c r="C128" s="2" t="s">
-        <v>43</v>
+        <v>281</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P128" s="1" t="s">
-        <v>42</v>
+      <c r="E128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q128" s="2" t="s">
         <v>43</v>
@@ -12495,26 +12531,26 @@
       <c r="U128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W128" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X128" s="1" t="s">
-        <v>42</v>
+      <c r="V128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z128" s="1" t="s">
-        <v>42</v>
+      <c r="Z128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA128" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB128" s="1" t="s">
-        <v>42</v>
+      <c r="AB128" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC128" s="2" t="s">
         <v>43</v>
@@ -12522,43 +12558,43 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="3">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="B129" t="s">
-        <v>289</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>43</v>
+        <v>283</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K129" s="2" t="s">
-        <v>43</v>
+      <c r="K129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M129" s="2" t="s">
-        <v>43</v>
+      <c r="M129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>43</v>
@@ -12572,38 +12608,38 @@
       <c r="Q129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X129" s="2" t="s">
-        <v>43</v>
+      <c r="R129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W129" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X129" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z129" s="1" t="s">
-        <v>42</v>
+      <c r="Z129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB129" s="1" t="s">
-        <v>42</v>
+      <c r="AB129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC129" s="2" t="s">
         <v>43</v>
@@ -12611,10 +12647,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="3">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B130" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>42</v>
@@ -12628,14 +12664,14 @@
       <c r="F130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G130" s="1" t="s">
-        <v>42</v>
+      <c r="G130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I130" s="1" t="s">
-        <v>42</v>
+      <c r="I130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>43</v>
@@ -12643,17 +12679,17 @@
       <c r="K130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L130" s="1" t="s">
-        <v>42</v>
+      <c r="L130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N130" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O130" s="1" t="s">
-        <v>42</v>
+      <c r="N130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O130" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P130" s="2" t="s">
         <v>43</v>
@@ -12670,8 +12706,8 @@
       <c r="T130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U130" s="2" t="s">
-        <v>43</v>
+      <c r="U130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V130" s="2" t="s">
         <v>43</v>
@@ -12679,8 +12715,8 @@
       <c r="W130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X130" s="2" t="s">
-        <v>43</v>
+      <c r="X130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y130" s="2" t="s">
         <v>43</v>
@@ -12700,28 +12736,28 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="3">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="B131" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>43</v>
+      <c r="D131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H131" s="2" t="s">
-        <v>43</v>
+      <c r="H131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>43</v>
@@ -12729,14 +12765,14 @@
       <c r="J131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K131" s="2" t="s">
-        <v>43</v>
+      <c r="K131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M131" s="2" t="s">
-        <v>43</v>
+      <c r="M131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N131" s="2" t="s">
         <v>43</v>
@@ -12750,26 +12786,26 @@
       <c r="Q131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X131" s="2" t="s">
-        <v>43</v>
+      <c r="R131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W131" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X131" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y131" s="2" t="s">
         <v>43</v>
@@ -12789,52 +12825,52 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="3">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B132" t="s">
-        <v>295</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>42</v>
+        <v>289</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P132" s="2" t="s">
-        <v>43</v>
+      <c r="E132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q132" s="2" t="s">
         <v>43</v>
@@ -12851,26 +12887,26 @@
       <c r="U132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X132" s="2" t="s">
-        <v>43</v>
+      <c r="V132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z132" s="2" t="s">
-        <v>43</v>
+      <c r="Z132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB132" s="2" t="s">
-        <v>43</v>
+      <c r="AB132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC132" s="2" t="s">
         <v>43</v>
@@ -12878,13 +12914,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="3">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="B133" t="s">
-        <v>297</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>42</v>
+        <v>291</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>43</v>
@@ -12952,14 +12988,14 @@
       <c r="Y133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z133" s="2" t="s">
-        <v>43</v>
+      <c r="Z133" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB133" s="2" t="s">
-        <v>43</v>
+      <c r="AB133" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC133" s="2" t="s">
         <v>43</v>
@@ -12967,13 +13003,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="3">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B134" t="s">
-        <v>299</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>42</v>
+        <v>293</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>42</v>
@@ -12987,14 +13023,14 @@
       <c r="G134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H134" s="2" t="s">
-        <v>43</v>
+      <c r="H134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J134" s="2" t="s">
-        <v>43</v>
+      <c r="J134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K134" s="1" t="s">
         <v>42</v>
@@ -13011,8 +13047,8 @@
       <c r="O134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P134" s="2" t="s">
-        <v>43</v>
+      <c r="P134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q134" s="2" t="s">
         <v>43</v>
@@ -13029,26 +13065,26 @@
       <c r="U134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V134" s="2" t="s">
-        <v>43</v>
+      <c r="V134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="W134" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X134" s="2" t="s">
-        <v>43</v>
+      <c r="X134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z134" s="2" t="s">
-        <v>43</v>
+      <c r="Z134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB134" s="2" t="s">
-        <v>43</v>
+      <c r="AB134" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC134" s="2" t="s">
         <v>43</v>
@@ -13056,49 +13092,49 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="3">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="B135" t="s">
-        <v>301</v>
-      </c>
-      <c r="C135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G135" s="1" t="s">
-        <v>42</v>
+        <v>295</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I135" s="1" t="s">
-        <v>42</v>
+      <c r="I135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N135" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O135" s="1" t="s">
-        <v>42</v>
+      <c r="K135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P135" s="2" t="s">
         <v>43</v>
@@ -13121,8 +13157,8 @@
       <c r="V135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W135" s="1" t="s">
-        <v>42</v>
+      <c r="W135" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X135" s="2" t="s">
         <v>43</v>
@@ -13130,14 +13166,14 @@
       <c r="Y135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z135" s="2" t="s">
-        <v>43</v>
+      <c r="Z135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB135" s="2" t="s">
-        <v>43</v>
+      <c r="AB135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC135" s="2" t="s">
         <v>43</v>
@@ -13145,10 +13181,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="3">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B136" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>42</v>
@@ -13156,38 +13192,38 @@
       <c r="D136" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>43</v>
+      <c r="E136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I136" s="2" t="s">
-        <v>43</v>
+      <c r="I136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O136" s="2" t="s">
-        <v>43</v>
+      <c r="K136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P136" s="2" t="s">
         <v>43</v>
@@ -13210,8 +13246,8 @@
       <c r="V136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W136" s="2" t="s">
-        <v>43</v>
+      <c r="W136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X136" s="2" t="s">
         <v>43</v>
@@ -13234,10 +13270,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="3">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B137" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>42</v>
@@ -13323,10 +13359,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="3">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="B138" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>42</v>
@@ -13334,11 +13370,11 @@
       <c r="D138" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>42</v>
+      <c r="E138" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>43</v>
@@ -13352,14 +13388,14 @@
       <c r="J138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K138" s="1" t="s">
-        <v>42</v>
+      <c r="K138" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M138" s="1" t="s">
-        <v>42</v>
+      <c r="M138" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N138" s="2" t="s">
         <v>43</v>
@@ -13388,8 +13424,8 @@
       <c r="V138" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W138" s="1" t="s">
-        <v>42</v>
+      <c r="W138" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X138" s="2" t="s">
         <v>43</v>
@@ -13412,13 +13448,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="3">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B139" t="s">
-        <v>309</v>
-      </c>
-      <c r="C139" s="2" t="s">
-        <v>43</v>
+        <v>303</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>43</v>
@@ -13495,16 +13531,16 @@
       <c r="AB139" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AC139" s="1" t="s">
-        <v>42</v>
+      <c r="AC139" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="3">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B140" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>42</v>
@@ -13551,17 +13587,17 @@
       <c r="Q140" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U140" s="1" t="s">
-        <v>42</v>
+      <c r="R140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U140" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V140" s="2" t="s">
         <v>43</v>
@@ -13569,8 +13605,8 @@
       <c r="W140" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X140" s="1" t="s">
-        <v>42</v>
+      <c r="X140" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y140" s="2" t="s">
         <v>43</v>
@@ -13590,13 +13626,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="3">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B141" t="s">
-        <v>313</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>43</v>
+        <v>307</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>42</v>
@@ -13604,35 +13640,35 @@
       <c r="E141" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>43</v>
+      <c r="F141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I141" s="2" t="s">
-        <v>43</v>
+      <c r="I141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O141" s="2" t="s">
-        <v>43</v>
+      <c r="K141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N141" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P141" s="2" t="s">
         <v>43</v>
@@ -13655,8 +13691,8 @@
       <c r="V141" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W141" s="2" t="s">
-        <v>43</v>
+      <c r="W141" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X141" s="2" t="s">
         <v>43</v>
@@ -13679,90 +13715,1158 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="3">
+        <v>308</v>
+      </c>
+      <c r="B142" t="s">
+        <v>309</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC142" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="3">
+        <v>310</v>
+      </c>
+      <c r="B143" t="s">
+        <v>311</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC143" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="3">
+        <v>312</v>
+      </c>
+      <c r="B144" t="s">
+        <v>313</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W144" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC144" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="3">
         <v>314</v>
       </c>
-      <c r="B142" t="s">
+      <c r="B145" t="s">
         <v>315</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="R142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="AC142" s="2" t="s">
+      <c r="C145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC145" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="3">
+        <v>316</v>
+      </c>
+      <c r="B146" t="s">
+        <v>317</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X146" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC146" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="3">
+        <v>318</v>
+      </c>
+      <c r="B147" t="s">
+        <v>319</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC147" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="3">
+        <v>320</v>
+      </c>
+      <c r="B148" t="s">
+        <v>321</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC148" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="3">
+        <v>322</v>
+      </c>
+      <c r="B149" t="s">
+        <v>322</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X149" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC149" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="3">
+        <v>323</v>
+      </c>
+      <c r="B150" t="s">
+        <v>323</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X150" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC150" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="3">
+        <v>324</v>
+      </c>
+      <c r="B151" t="s">
+        <v>324</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC151" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="3">
+        <v>325</v>
+      </c>
+      <c r="B152" t="s">
+        <v>325</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X152" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC152" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="3">
+        <v>326</v>
+      </c>
+      <c r="B153" t="s">
+        <v>326</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC153" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="3">
+        <v>327</v>
+      </c>
+      <c r="B154" t="s">
+        <v>327</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC154" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -13778,12 +14882,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -1002,7 +1002,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.62.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -1002,7 +1002,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.62.0-SNAPSHOT</t>
+    <t>1.0.0</t>
   </si>
 </sst>
 </file>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4468" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4497" uniqueCount="331">
   <si>
     <t>User Right</t>
   </si>
@@ -663,6 +663,9 @@
     <t>Perform bulk operations in lists</t>
   </si>
   <si>
+    <t>PERFORM_BULK_OPERATIONS_EVENT</t>
+  </si>
+  <si>
     <t>MANAGE_PUBLIC_EXPORT_CONFIGURATION</t>
   </si>
   <si>
@@ -1002,7 +1005,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.63.0-SNAPSHOT</t>
   </si>
 </sst>
 </file>
@@ -1130,7 +1133,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD154"/>
+  <dimension ref="A1:AD155"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -7253,8 +7256,8 @@
       <c r="L69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M69" s="2" t="s">
-        <v>43</v>
+      <c r="M69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>43</v>
@@ -7496,8 +7499,8 @@
       <c r="D72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>43</v>
+      <c r="E72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>42</v>
@@ -7520,8 +7523,8 @@
       <c r="L72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M72" s="2" t="s">
-        <v>43</v>
+      <c r="M72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>43</v>
@@ -8054,8 +8057,8 @@
       <c r="L78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M78" s="2" t="s">
-        <v>43</v>
+      <c r="M78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>43</v>
@@ -8232,8 +8235,8 @@
       <c r="L80" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>43</v>
+      <c r="M80" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>43</v>
@@ -9624,19 +9627,19 @@
         <v>216</v>
       </c>
       <c r="B96" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>42</v>
+      <c r="D96" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>43</v>
@@ -9656,8 +9659,8 @@
       <c r="L96" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M96" s="2" t="s">
-        <v>43</v>
+      <c r="M96" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>43</v>
@@ -9710,16 +9713,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="3">
+        <v>217</v>
+      </c>
+      <c r="B97" t="s">
         <v>218</v>
       </c>
-      <c r="B97" t="s">
-        <v>219</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>43</v>
+      <c r="D97" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>43</v>
@@ -9799,11 +9802,11 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="3">
+        <v>219</v>
+      </c>
+      <c r="B98" t="s">
         <v>220</v>
       </c>
-      <c r="B98" t="s">
-        <v>221</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>42</v>
       </c>
@@ -9813,8 +9816,8 @@
       <c r="E98" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F98" s="2" t="s">
-        <v>43</v>
+      <c r="F98" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>43</v>
@@ -9888,10 +9891,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="3">
+        <v>221</v>
+      </c>
+      <c r="B99" t="s">
         <v>222</v>
-      </c>
-      <c r="B99" t="s">
-        <v>223</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>42</v>
@@ -9977,22 +9980,22 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="3">
+        <v>223</v>
+      </c>
+      <c r="B100" t="s">
         <v>224</v>
       </c>
-      <c r="B100" t="s">
-        <v>225</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>42</v>
+      <c r="D100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>43</v>
@@ -10027,26 +10030,26 @@
       <c r="Q100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U100" s="1" t="s">
-        <v>42</v>
+      <c r="R100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W100" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X100" s="1" t="s">
-        <v>42</v>
+      <c r="W100" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X100" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y100" s="2" t="s">
         <v>43</v>
@@ -10066,11 +10069,11 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="3">
+        <v>225</v>
+      </c>
+      <c r="B101" t="s">
         <v>226</v>
       </c>
-      <c r="B101" t="s">
-        <v>227</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>42</v>
       </c>
@@ -10116,14 +10119,14 @@
       <c r="Q101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T101" s="2" t="s">
-        <v>43</v>
+      <c r="R101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T101" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U101" s="1" t="s">
         <v>42</v>
@@ -10155,22 +10158,22 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="3">
+        <v>227</v>
+      </c>
+      <c r="B102" t="s">
         <v>228</v>
       </c>
-      <c r="B102" t="s">
-        <v>229</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>43</v>
+      <c r="D102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>43</v>
@@ -10214,17 +10217,17 @@
       <c r="T102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U102" s="2" t="s">
-        <v>43</v>
+      <c r="U102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X102" s="2" t="s">
-        <v>43</v>
+      <c r="W102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y102" s="2" t="s">
         <v>43</v>
@@ -10244,16 +10247,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="3">
+        <v>229</v>
+      </c>
+      <c r="B103" t="s">
         <v>230</v>
       </c>
-      <c r="B103" t="s">
-        <v>231</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>42</v>
+      <c r="D103" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>43</v>
@@ -10333,16 +10336,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="3">
+        <v>231</v>
+      </c>
+      <c r="B104" t="s">
         <v>232</v>
       </c>
-      <c r="B104" t="s">
-        <v>233</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D104" s="2" t="s">
-        <v>43</v>
+      <c r="D104" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>43</v>
@@ -10422,40 +10425,40 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="3">
+        <v>233</v>
+      </c>
+      <c r="B105" t="s">
         <v>234</v>
       </c>
-      <c r="B105" t="s">
-        <v>235</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G105" s="1" t="s">
-        <v>42</v>
+      <c r="D105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I105" s="1" t="s">
-        <v>42</v>
+      <c r="I105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L105" s="1" t="s">
-        <v>42</v>
+      <c r="K105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M105" s="2" t="s">
         <v>43</v>
@@ -10463,35 +10466,35 @@
       <c r="N105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P105" s="1" t="s">
-        <v>42</v>
+      <c r="O105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U105" s="1" t="s">
-        <v>42</v>
+      <c r="R105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V105" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X105" s="1" t="s">
-        <v>42</v>
+      <c r="W105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X105" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y105" s="2" t="s">
         <v>43</v>
@@ -10511,25 +10514,25 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="3">
+        <v>235</v>
+      </c>
+      <c r="B106" t="s">
         <v>236</v>
       </c>
-      <c r="B106" t="s">
-        <v>237</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>43</v>
+      <c r="E106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>43</v>
@@ -10540,23 +10543,23 @@
       <c r="J106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P106" s="2" t="s">
-        <v>43</v>
+      <c r="K106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q106" s="2" t="s">
         <v>43</v>
@@ -10570,17 +10573,17 @@
       <c r="T106" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U106" s="2" t="s">
-        <v>43</v>
+      <c r="U106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X106" s="2" t="s">
-        <v>43</v>
+      <c r="W106" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X106" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y106" s="2" t="s">
         <v>43</v>
@@ -10600,11 +10603,11 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="3">
+        <v>237</v>
+      </c>
+      <c r="B107" t="s">
         <v>238</v>
       </c>
-      <c r="B107" t="s">
-        <v>239</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>42</v>
       </c>
@@ -10623,8 +10626,8 @@
       <c r="H107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I107" s="2" t="s">
-        <v>43</v>
+      <c r="I107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>43</v>
@@ -10638,8 +10641,8 @@
       <c r="M107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N107" s="2" t="s">
-        <v>43</v>
+      <c r="N107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O107" s="2" t="s">
         <v>43</v>
@@ -10689,49 +10692,49 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="3">
+        <v>239</v>
+      </c>
+      <c r="B108" t="s">
         <v>240</v>
       </c>
-      <c r="B108" t="s">
-        <v>241</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G108" s="1" t="s">
-        <v>42</v>
+      <c r="E108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L108" s="1" t="s">
-        <v>42</v>
+      <c r="I108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N108" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>42</v>
+      <c r="N108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P108" s="2" t="s">
         <v>43</v>
@@ -10739,14 +10742,14 @@
       <c r="Q108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T108" s="2" t="s">
-        <v>43</v>
+      <c r="R108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S108" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U108" s="2" t="s">
         <v>43</v>
@@ -10754,8 +10757,8 @@
       <c r="V108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W108" s="1" t="s">
-        <v>42</v>
+      <c r="W108" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X108" s="2" t="s">
         <v>43</v>
@@ -10778,34 +10781,34 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="3">
+        <v>241</v>
+      </c>
+      <c r="B109" t="s">
         <v>242</v>
       </c>
-      <c r="B109" t="s">
-        <v>243</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>43</v>
+      <c r="D109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>43</v>
+      <c r="I109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K109" s="1" t="s">
         <v>42</v>
@@ -10813,17 +10816,17 @@
       <c r="L109" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P109" s="1" t="s">
-        <v>42</v>
+      <c r="M109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>43</v>
@@ -10837,14 +10840,14 @@
       <c r="T109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U109" s="1" t="s">
-        <v>42</v>
+      <c r="U109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W109" s="2" t="s">
-        <v>43</v>
+      <c r="W109" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X109" s="2" t="s">
         <v>43</v>
@@ -10867,11 +10870,11 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="3">
+        <v>243</v>
+      </c>
+      <c r="B110" t="s">
         <v>244</v>
       </c>
-      <c r="B110" t="s">
-        <v>245</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>42</v>
       </c>
@@ -10911,8 +10914,8 @@
       <c r="O110" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P110" s="2" t="s">
-        <v>43</v>
+      <c r="P110" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q110" s="2" t="s">
         <v>43</v>
@@ -10956,10 +10959,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="3">
+        <v>245</v>
+      </c>
+      <c r="B111" t="s">
         <v>246</v>
-      </c>
-      <c r="B111" t="s">
-        <v>247</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>42</v>
@@ -11045,10 +11048,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="3">
+        <v>247</v>
+      </c>
+      <c r="B112" t="s">
         <v>248</v>
-      </c>
-      <c r="B112" t="s">
-        <v>249</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>42</v>
@@ -11134,11 +11137,11 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="3">
+        <v>249</v>
+      </c>
+      <c r="B113" t="s">
         <v>250</v>
       </c>
-      <c r="B113" t="s">
-        <v>251</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>42</v>
       </c>
@@ -11166,8 +11169,8 @@
       <c r="K113" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L113" s="2" t="s">
-        <v>43</v>
+      <c r="L113" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M113" s="2" t="s">
         <v>43</v>
@@ -11223,11 +11226,11 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="3">
+        <v>251</v>
+      </c>
+      <c r="B114" t="s">
         <v>252</v>
       </c>
-      <c r="B114" t="s">
-        <v>253</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>42</v>
       </c>
@@ -11255,8 +11258,8 @@
       <c r="K114" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L114" s="1" t="s">
-        <v>42</v>
+      <c r="L114" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M114" s="2" t="s">
         <v>43</v>
@@ -11312,10 +11315,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="3">
+        <v>253</v>
+      </c>
+      <c r="B115" t="s">
         <v>254</v>
-      </c>
-      <c r="B115" t="s">
-        <v>255</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>42</v>
@@ -11401,11 +11404,11 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="3">
+        <v>255</v>
+      </c>
+      <c r="B116" t="s">
         <v>256</v>
       </c>
-      <c r="B116" t="s">
-        <v>257</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>42</v>
       </c>
@@ -11433,8 +11436,8 @@
       <c r="K116" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L116" s="2" t="s">
-        <v>43</v>
+      <c r="L116" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M116" s="2" t="s">
         <v>43</v>
@@ -11490,11 +11493,11 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="3">
+        <v>257</v>
+      </c>
+      <c r="B117" t="s">
         <v>258</v>
       </c>
-      <c r="B117" t="s">
-        <v>259</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>42</v>
       </c>
@@ -11522,8 +11525,8 @@
       <c r="K117" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L117" s="1" t="s">
-        <v>42</v>
+      <c r="L117" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M117" s="2" t="s">
         <v>43</v>
@@ -11579,10 +11582,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="3">
+        <v>259</v>
+      </c>
+      <c r="B118" t="s">
         <v>260</v>
-      </c>
-      <c r="B118" t="s">
-        <v>261</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>42</v>
@@ -11668,10 +11671,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="3">
+        <v>261</v>
+      </c>
+      <c r="B119" t="s">
         <v>262</v>
-      </c>
-      <c r="B119" t="s">
-        <v>263</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>42</v>
@@ -11757,10 +11760,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="3">
+        <v>263</v>
+      </c>
+      <c r="B120" t="s">
         <v>264</v>
-      </c>
-      <c r="B120" t="s">
-        <v>265</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>42</v>
@@ -11846,11 +11849,11 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="3">
+        <v>265</v>
+      </c>
+      <c r="B121" t="s">
         <v>266</v>
       </c>
-      <c r="B121" t="s">
-        <v>267</v>
-      </c>
       <c r="C121" s="1" t="s">
         <v>42</v>
       </c>
@@ -11878,8 +11881,8 @@
       <c r="K121" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L121" s="2" t="s">
-        <v>43</v>
+      <c r="L121" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M121" s="2" t="s">
         <v>43</v>
@@ -11935,76 +11938,76 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="3">
+        <v>267</v>
+      </c>
+      <c r="B122" t="s">
         <v>268</v>
       </c>
-      <c r="B122" t="s">
-        <v>269</v>
-      </c>
       <c r="C122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>42</v>
+      <c r="D122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>42</v>
+      <c r="L122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P122" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q122" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>42</v>
+      <c r="R122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T122" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U122" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W122" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X122" s="1" t="s">
-        <v>42</v>
+      <c r="V122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X122" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y122" s="2" t="s">
         <v>43</v>
@@ -12024,11 +12027,11 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="3">
+        <v>269</v>
+      </c>
+      <c r="B123" t="s">
         <v>270</v>
       </c>
-      <c r="B123" t="s">
-        <v>271</v>
-      </c>
       <c r="C123" s="1" t="s">
         <v>42</v>
       </c>
@@ -12044,44 +12047,44 @@
       <c r="G123" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H123" s="2" t="s">
-        <v>43</v>
+      <c r="H123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P123" s="2" t="s">
-        <v>43</v>
+      <c r="J123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q123" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T123" s="2" t="s">
-        <v>43</v>
+      <c r="R123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U123" s="1" t="s">
         <v>42</v>
@@ -12113,31 +12116,31 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="3">
+        <v>271</v>
+      </c>
+      <c r="B124" t="s">
         <v>272</v>
       </c>
-      <c r="B124" t="s">
-        <v>273</v>
-      </c>
       <c r="C124" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>43</v>
+      <c r="D124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I124" s="2" t="s">
-        <v>43</v>
+      <c r="I124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>43</v>
@@ -12172,17 +12175,17 @@
       <c r="T124" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X124" s="2" t="s">
-        <v>43</v>
+      <c r="U124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W124" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X124" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y124" s="2" t="s">
         <v>43</v>
@@ -12202,10 +12205,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="3">
+        <v>273</v>
+      </c>
+      <c r="B125" t="s">
         <v>274</v>
-      </c>
-      <c r="B125" t="s">
-        <v>275</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>42</v>
@@ -12291,22 +12294,22 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="3">
+        <v>275</v>
+      </c>
+      <c r="B126" t="s">
         <v>276</v>
       </c>
-      <c r="B126" t="s">
-        <v>277</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>42</v>
+      <c r="C126" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G126" s="2" t="s">
         <v>43</v>
@@ -12314,23 +12317,23 @@
       <c r="H126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I126" s="1" t="s">
-        <v>42</v>
+      <c r="I126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M126" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N126" s="1" t="s">
-        <v>42</v>
+      <c r="K126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N126" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O126" s="2" t="s">
         <v>43</v>
@@ -12380,13 +12383,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="3">
+        <v>277</v>
+      </c>
+      <c r="B127" t="s">
         <v>278</v>
       </c>
-      <c r="B127" t="s">
-        <v>279</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>42</v>
+      <c r="C127" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>42</v>
@@ -12403,23 +12406,23 @@
       <c r="H127" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I127" s="2" t="s">
-        <v>43</v>
+      <c r="I127" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N127" s="2" t="s">
-        <v>43</v>
+      <c r="K127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M127" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N127" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O127" s="2" t="s">
         <v>43</v>
@@ -12469,22 +12472,22 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="3">
+        <v>279</v>
+      </c>
+      <c r="B128" t="s">
         <v>280</v>
       </c>
-      <c r="B128" t="s">
-        <v>281</v>
-      </c>
       <c r="C128" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F128" s="2" t="s">
-        <v>43</v>
+      <c r="E128" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F128" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G128" s="2" t="s">
         <v>43</v>
@@ -12558,43 +12561,43 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="3">
+        <v>281</v>
+      </c>
+      <c r="B129" t="s">
         <v>282</v>
       </c>
-      <c r="B129" t="s">
-        <v>283</v>
-      </c>
       <c r="C129" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>42</v>
+      <c r="E129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K129" s="1" t="s">
-        <v>42</v>
+      <c r="K129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M129" s="1" t="s">
-        <v>42</v>
+      <c r="M129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>43</v>
@@ -12608,26 +12611,26 @@
       <c r="Q129" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W129" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X129" s="1" t="s">
-        <v>42</v>
+      <c r="R129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X129" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y129" s="2" t="s">
         <v>43</v>
@@ -12647,11 +12650,11 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="3">
+        <v>283</v>
+      </c>
+      <c r="B130" t="s">
         <v>284</v>
       </c>
-      <c r="B130" t="s">
-        <v>285</v>
-      </c>
       <c r="C130" s="1" t="s">
         <v>42</v>
       </c>
@@ -12664,14 +12667,14 @@
       <c r="F130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I130" s="2" t="s">
-        <v>43</v>
+      <c r="G130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>43</v>
@@ -12697,20 +12700,20 @@
       <c r="Q130" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S130" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T130" s="2" t="s">
-        <v>43</v>
+      <c r="R130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S130" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U130" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V130" s="2" t="s">
-        <v>43</v>
+      <c r="V130" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="W130" s="1" t="s">
         <v>42</v>
@@ -12736,11 +12739,11 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="3">
+        <v>285</v>
+      </c>
+      <c r="B131" t="s">
         <v>286</v>
       </c>
-      <c r="B131" t="s">
-        <v>287</v>
-      </c>
       <c r="C131" s="1" t="s">
         <v>42</v>
       </c>
@@ -12756,8 +12759,8 @@
       <c r="G131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H131" s="1" t="s">
-        <v>42</v>
+      <c r="H131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>43</v>
@@ -12786,20 +12789,20 @@
       <c r="Q131" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S131" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T131" s="1" t="s">
-        <v>42</v>
+      <c r="R131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U131" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V131" s="1" t="s">
-        <v>42</v>
+      <c r="V131" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="W131" s="1" t="s">
         <v>42</v>
@@ -12825,13 +12828,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="3">
+        <v>287</v>
+      </c>
+      <c r="B132" t="s">
         <v>288</v>
       </c>
-      <c r="B132" t="s">
-        <v>289</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>43</v>
+      <c r="C132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>42</v>
@@ -12842,50 +12845,50 @@
       <c r="F132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G132" s="1" t="s">
-        <v>42</v>
+      <c r="G132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J132" s="1" t="s">
-        <v>42</v>
+      <c r="I132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L132" s="1" t="s">
-        <v>42</v>
+      <c r="L132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O132" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P132" s="1" t="s">
-        <v>42</v>
+      <c r="N132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U132" s="2" t="s">
-        <v>43</v>
+      <c r="R132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T132" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U132" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V132" s="1" t="s">
         <v>42</v>
@@ -12899,14 +12902,14 @@
       <c r="Y132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z132" s="1" t="s">
-        <v>42</v>
+      <c r="Z132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AA132" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB132" s="1" t="s">
-        <v>42</v>
+      <c r="AB132" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="AC132" s="2" t="s">
         <v>43</v>
@@ -12914,52 +12917,52 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="3">
+        <v>289</v>
+      </c>
+      <c r="B133" t="s">
         <v>290</v>
       </c>
-      <c r="B133" t="s">
-        <v>291</v>
-      </c>
       <c r="C133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P133" s="2" t="s">
-        <v>43</v>
+      <c r="D133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P133" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q133" s="2" t="s">
         <v>43</v>
@@ -12976,14 +12979,14 @@
       <c r="U133" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X133" s="2" t="s">
-        <v>43</v>
+      <c r="V133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W133" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X133" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y133" s="2" t="s">
         <v>43</v>
@@ -13003,52 +13006,52 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="3">
+        <v>291</v>
+      </c>
+      <c r="B134" t="s">
         <v>292</v>
       </c>
-      <c r="B134" t="s">
-        <v>293</v>
-      </c>
       <c r="C134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P134" s="1" t="s">
-        <v>42</v>
+      <c r="D134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q134" s="2" t="s">
         <v>43</v>
@@ -13065,14 +13068,14 @@
       <c r="U134" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W134" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X134" s="1" t="s">
-        <v>42</v>
+      <c r="V134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X134" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y134" s="2" t="s">
         <v>43</v>
@@ -13092,52 +13095,52 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="3">
+        <v>293</v>
+      </c>
+      <c r="B135" t="s">
         <v>294</v>
       </c>
-      <c r="B135" t="s">
-        <v>295</v>
-      </c>
       <c r="C135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P135" s="2" t="s">
-        <v>43</v>
+      <c r="D135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q135" s="2" t="s">
         <v>43</v>
@@ -13154,14 +13157,14 @@
       <c r="U135" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="V135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X135" s="2" t="s">
-        <v>43</v>
+      <c r="V135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W135" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X135" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y135" s="2" t="s">
         <v>43</v>
@@ -13181,49 +13184,49 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="3">
+        <v>295</v>
+      </c>
+      <c r="B136" t="s">
         <v>296</v>
       </c>
-      <c r="B136" t="s">
-        <v>297</v>
-      </c>
-      <c r="C136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G136" s="1" t="s">
-        <v>42</v>
+      <c r="C136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I136" s="1" t="s">
-        <v>42</v>
+      <c r="I136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O136" s="1" t="s">
-        <v>42</v>
+      <c r="K136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P136" s="2" t="s">
         <v>43</v>
@@ -13246,8 +13249,8 @@
       <c r="V136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W136" s="1" t="s">
-        <v>42</v>
+      <c r="W136" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X136" s="2" t="s">
         <v>43</v>
@@ -13255,14 +13258,14 @@
       <c r="Y136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z136" s="2" t="s">
-        <v>43</v>
+      <c r="Z136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AA136" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AB136" s="2" t="s">
-        <v>43</v>
+      <c r="AB136" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="AC136" s="2" t="s">
         <v>43</v>
@@ -13270,49 +13273,49 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="3">
+        <v>297</v>
+      </c>
+      <c r="B137" t="s">
         <v>298</v>
       </c>
-      <c r="B137" t="s">
-        <v>299</v>
-      </c>
       <c r="C137" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>43</v>
+      <c r="D137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I137" s="2" t="s">
-        <v>43</v>
+      <c r="I137" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O137" s="2" t="s">
-        <v>43</v>
+      <c r="K137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N137" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P137" s="2" t="s">
         <v>43</v>
@@ -13335,8 +13338,8 @@
       <c r="V137" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W137" s="2" t="s">
-        <v>43</v>
+      <c r="W137" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X137" s="2" t="s">
         <v>43</v>
@@ -13359,16 +13362,16 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="3">
+        <v>299</v>
+      </c>
+      <c r="B138" t="s">
         <v>300</v>
       </c>
-      <c r="B138" t="s">
-        <v>301</v>
-      </c>
       <c r="C138" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>42</v>
+      <c r="D138" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>43</v>
@@ -13448,16 +13451,16 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="3">
+        <v>301</v>
+      </c>
+      <c r="B139" t="s">
         <v>302</v>
       </c>
-      <c r="B139" t="s">
-        <v>303</v>
-      </c>
       <c r="C139" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D139" s="2" t="s">
-        <v>43</v>
+      <c r="D139" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>43</v>
@@ -13537,49 +13540,49 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="3">
+        <v>303</v>
+      </c>
+      <c r="B140" t="s">
         <v>304</v>
       </c>
-      <c r="B140" t="s">
-        <v>305</v>
-      </c>
       <c r="C140" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>42</v>
+      <c r="D140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I140" s="1" t="s">
-        <v>42</v>
+      <c r="I140" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N140" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O140" s="1" t="s">
-        <v>42</v>
+      <c r="K140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O140" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P140" s="2" t="s">
         <v>43</v>
@@ -13602,8 +13605,8 @@
       <c r="V140" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W140" s="1" t="s">
-        <v>42</v>
+      <c r="W140" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X140" s="2" t="s">
         <v>43</v>
@@ -13626,10 +13629,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="3">
+        <v>305</v>
+      </c>
+      <c r="B141" t="s">
         <v>306</v>
-      </c>
-      <c r="B141" t="s">
-        <v>307</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>42</v>
@@ -13715,49 +13718,49 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="3">
+        <v>307</v>
+      </c>
+      <c r="B142" t="s">
         <v>308</v>
       </c>
-      <c r="B142" t="s">
-        <v>309</v>
-      </c>
       <c r="C142" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>43</v>
+      <c r="E142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I142" s="2" t="s">
-        <v>43</v>
+      <c r="I142" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O142" s="2" t="s">
-        <v>43</v>
+      <c r="K142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N142" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O142" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P142" s="2" t="s">
         <v>43</v>
@@ -13780,8 +13783,8 @@
       <c r="V142" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W142" s="2" t="s">
-        <v>43</v>
+      <c r="W142" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X142" s="2" t="s">
         <v>43</v>
@@ -13804,16 +13807,16 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="3">
+        <v>309</v>
+      </c>
+      <c r="B143" t="s">
         <v>310</v>
       </c>
-      <c r="B143" t="s">
-        <v>311</v>
-      </c>
       <c r="C143" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>43</v>
+      <c r="D143" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>43</v>
@@ -13893,22 +13896,22 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="3">
+        <v>311</v>
+      </c>
+      <c r="B144" t="s">
         <v>312</v>
       </c>
-      <c r="B144" t="s">
-        <v>313</v>
-      </c>
       <c r="C144" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>42</v>
+      <c r="D144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>43</v>
@@ -13922,14 +13925,14 @@
       <c r="J144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K144" s="1" t="s">
-        <v>42</v>
+      <c r="K144" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M144" s="1" t="s">
-        <v>42</v>
+      <c r="M144" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N144" s="2" t="s">
         <v>43</v>
@@ -13958,8 +13961,8 @@
       <c r="V144" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W144" s="1" t="s">
-        <v>42</v>
+      <c r="W144" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X144" s="2" t="s">
         <v>43</v>
@@ -13982,22 +13985,22 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="3">
+        <v>313</v>
+      </c>
+      <c r="B145" t="s">
         <v>314</v>
       </c>
-      <c r="B145" t="s">
-        <v>315</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>43</v>
+      <c r="C145" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G145" s="2" t="s">
         <v>43</v>
@@ -14011,14 +14014,14 @@
       <c r="J145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K145" s="2" t="s">
-        <v>43</v>
+      <c r="K145" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M145" s="2" t="s">
-        <v>43</v>
+      <c r="M145" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N145" s="2" t="s">
         <v>43</v>
@@ -14047,8 +14050,8 @@
       <c r="V145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W145" s="2" t="s">
-        <v>43</v>
+      <c r="W145" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X145" s="2" t="s">
         <v>43</v>
@@ -14065,55 +14068,55 @@
       <c r="AB145" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AC145" s="1" t="s">
-        <v>42</v>
+      <c r="AC145" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="3">
+        <v>315</v>
+      </c>
+      <c r="B146" t="s">
         <v>316</v>
       </c>
-      <c r="B146" t="s">
-        <v>317</v>
-      </c>
-      <c r="C146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>42</v>
+      <c r="C146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I146" s="1" t="s">
-        <v>42</v>
+      <c r="I146" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O146" s="1" t="s">
-        <v>42</v>
+      <c r="K146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O146" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P146" s="2" t="s">
         <v>43</v>
@@ -14121,26 +14124,26 @@
       <c r="Q146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U146" s="1" t="s">
-        <v>42</v>
+      <c r="R146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U146" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W146" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X146" s="1" t="s">
-        <v>42</v>
+      <c r="W146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X146" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y146" s="2" t="s">
         <v>43</v>
@@ -14154,19 +14157,19 @@
       <c r="AB146" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AC146" s="2" t="s">
-        <v>43</v>
+      <c r="AC146" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="3">
+        <v>317</v>
+      </c>
+      <c r="B147" t="s">
         <v>318</v>
       </c>
-      <c r="B147" t="s">
-        <v>319</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>43</v>
+      <c r="C147" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>42</v>
@@ -14174,35 +14177,35 @@
       <c r="E147" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>43</v>
+      <c r="F147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I147" s="2" t="s">
-        <v>43</v>
+      <c r="I147" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O147" s="2" t="s">
-        <v>43</v>
+      <c r="K147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O147" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P147" s="2" t="s">
         <v>43</v>
@@ -14210,26 +14213,26 @@
       <c r="Q147" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U147" s="2" t="s">
-        <v>43</v>
+      <c r="R147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U147" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V147" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X147" s="2" t="s">
-        <v>43</v>
+      <c r="W147" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X147" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y147" s="2" t="s">
         <v>43</v>
@@ -14249,19 +14252,19 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="3">
+        <v>319</v>
+      </c>
+      <c r="B148" t="s">
         <v>320</v>
       </c>
-      <c r="B148" t="s">
-        <v>321</v>
-      </c>
       <c r="C148" s="2" t="s">
         <v>43</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E148" s="2" t="s">
-        <v>43</v>
+      <c r="E148" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>43</v>
@@ -14338,76 +14341,76 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="3">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B149" t="s">
         <v>322</v>
       </c>
-      <c r="C149" s="1" t="s">
-        <v>42</v>
+      <c r="C149" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P149" s="1" t="s">
-        <v>42</v>
+      <c r="E149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P149" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q149" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W149" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X149" s="1" t="s">
-        <v>42</v>
+      <c r="R149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X149" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y149" s="2" t="s">
         <v>43</v>
@@ -14566,14 +14569,14 @@
       <c r="Q151" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R151" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S151" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T151" s="2" t="s">
-        <v>43</v>
+      <c r="R151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S151" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T151" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U151" s="1" t="s">
         <v>42</v>
@@ -14705,41 +14708,41 @@
       <c r="D153" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E153" s="2" t="s">
-        <v>43</v>
+      <c r="E153" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P153" s="2" t="s">
-        <v>43</v>
+      <c r="G153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P153" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q153" s="2" t="s">
         <v>43</v>
@@ -14753,17 +14756,17 @@
       <c r="T153" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X153" s="2" t="s">
-        <v>43</v>
+      <c r="U153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W153" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X153" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y153" s="2" t="s">
         <v>43</v>
@@ -14791,14 +14794,14 @@
       <c r="C154" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D154" s="2" t="s">
-        <v>43</v>
+      <c r="D154" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F154" s="2" t="s">
-        <v>43</v>
+      <c r="F154" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G154" s="2" t="s">
         <v>43</v>
@@ -14867,6 +14870,95 @@
         <v>43</v>
       </c>
       <c r="AC154" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="3">
+        <v>328</v>
+      </c>
+      <c r="B155" t="s">
+        <v>328</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AC155" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -14882,12 +14974,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
   </sheetData>

--- a/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
+++ b/sormas-api/src/main/resources/doc/SORMAS_User_Rights.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4497" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4526" uniqueCount="332">
   <si>
     <t>User Right</t>
   </si>
@@ -273,6 +273,9 @@
     <t>Delete person contact details</t>
   </si>
   <si>
+    <t>PERSON_EXPORT</t>
+  </si>
+  <si>
     <t>SAMPLE_CREATE</t>
   </si>
   <si>
@@ -1005,7 +1008,7 @@
     <t>SORMAS Version</t>
   </si>
   <si>
-    <t>1.63.0-SNAPSHOT</t>
+    <t>1.0.0</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AD155"/>
+  <dimension ref="A1:AD156"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="35.0" customWidth="true"/>
@@ -3575,37 +3578,37 @@
         <v>86</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>42</v>
+        <v>86</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>42</v>
+      <c r="E28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>42</v>
+      <c r="G28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>43</v>
@@ -3613,11 +3616,11 @@
       <c r="N28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O28" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>42</v>
+      <c r="O28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q28" s="2" t="s">
         <v>43</v>
@@ -3631,8 +3634,8 @@
       <c r="T28" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U28" s="1" t="s">
-        <v>42</v>
+      <c r="U28" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V28" s="2" t="s">
         <v>43</v>
@@ -3661,11 +3664,11 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="3">
+        <v>87</v>
+      </c>
+      <c r="B29" t="s">
         <v>88</v>
       </c>
-      <c r="B29" t="s">
-        <v>89</v>
-      </c>
       <c r="C29" s="1" t="s">
         <v>42</v>
       </c>
@@ -3696,11 +3699,11 @@
       <c r="L29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>42</v>
+      <c r="M29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>42</v>
@@ -3708,17 +3711,17 @@
       <c r="P29" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>42</v>
+      <c r="Q29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U29" s="1" t="s">
         <v>42</v>
@@ -3750,11 +3753,11 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="3">
+        <v>89</v>
+      </c>
+      <c r="B30" t="s">
         <v>90</v>
       </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
       <c r="C30" s="1" t="s">
         <v>42</v>
       </c>
@@ -3785,11 +3788,11 @@
       <c r="L30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N30" s="2" t="s">
-        <v>43</v>
+      <c r="M30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>42</v>
@@ -3800,14 +3803,14 @@
       <c r="Q30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>43</v>
+      <c r="R30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T30" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U30" s="1" t="s">
         <v>42</v>
@@ -3839,16 +3842,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="3">
+        <v>91</v>
+      </c>
+      <c r="B31" t="s">
         <v>92</v>
       </c>
-      <c r="B31" t="s">
-        <v>93</v>
-      </c>
       <c r="C31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>43</v>
+      <c r="D31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>42</v>
@@ -3856,23 +3859,23 @@
       <c r="F31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L31" s="2" t="s">
-        <v>43</v>
+      <c r="G31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>43</v>
@@ -3883,11 +3886,11 @@
       <c r="O31" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>43</v>
+      <c r="P31" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>43</v>
@@ -3898,8 +3901,8 @@
       <c r="T31" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U31" s="2" t="s">
-        <v>43</v>
+      <c r="U31" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V31" s="2" t="s">
         <v>43</v>
@@ -3928,19 +3931,19 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="3">
+        <v>93</v>
+      </c>
+      <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
       <c r="C32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>43</v>
+      <c r="D32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>42</v>
@@ -3969,8 +3972,8 @@
       <c r="N32" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O32" s="2" t="s">
-        <v>43</v>
+      <c r="O32" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P32" s="2" t="s">
         <v>43</v>
@@ -4017,19 +4020,19 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="3">
+        <v>95</v>
+      </c>
+      <c r="B33" t="s">
         <v>96</v>
       </c>
-      <c r="B33" t="s">
-        <v>97</v>
-      </c>
       <c r="C33" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E33" s="1" t="s">
-        <v>42</v>
+      <c r="E33" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>42</v>
@@ -4046,8 +4049,8 @@
       <c r="J33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>42</v>
+      <c r="K33" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>43</v>
@@ -4061,11 +4064,11 @@
       <c r="O33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P33" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>42</v>
+      <c r="P33" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R33" s="2" t="s">
         <v>43</v>
@@ -4076,8 +4079,8 @@
       <c r="T33" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U33" s="1" t="s">
-        <v>42</v>
+      <c r="U33" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V33" s="2" t="s">
         <v>43</v>
@@ -4106,11 +4109,11 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="3">
+        <v>97</v>
+      </c>
+      <c r="B34" t="s">
         <v>98</v>
       </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
       <c r="C34" s="1" t="s">
         <v>42</v>
       </c>
@@ -4141,8 +4144,8 @@
       <c r="L34" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>42</v>
+      <c r="M34" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>43</v>
@@ -4153,8 +4156,8 @@
       <c r="P34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q34" s="2" t="s">
-        <v>43</v>
+      <c r="Q34" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R34" s="2" t="s">
         <v>43</v>
@@ -4195,11 +4198,11 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="3">
+        <v>99</v>
+      </c>
+      <c r="B35" t="s">
         <v>100</v>
       </c>
-      <c r="B35" t="s">
-        <v>101</v>
-      </c>
       <c r="C35" s="1" t="s">
         <v>42</v>
       </c>
@@ -4212,14 +4215,14 @@
       <c r="F35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G35" s="1" t="s">
-        <v>42</v>
+      <c r="G35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>42</v>
+      <c r="I35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>43</v>
@@ -4230,20 +4233,20 @@
       <c r="L35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>43</v>
+      <c r="M35" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>42</v>
+      <c r="O35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q35" s="1" t="s">
-        <v>42</v>
+      <c r="Q35" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R35" s="2" t="s">
         <v>43</v>
@@ -4284,10 +4287,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="3">
+        <v>101</v>
+      </c>
+      <c r="B36" t="s">
         <v>102</v>
-      </c>
-      <c r="B36" t="s">
-        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>42</v>
@@ -4373,37 +4376,37 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="3">
+        <v>103</v>
+      </c>
+      <c r="B37" t="s">
         <v>104</v>
       </c>
-      <c r="B37" t="s">
-        <v>105</v>
-      </c>
       <c r="C37" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>43</v>
+      <c r="E37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I37" s="2" t="s">
-        <v>43</v>
+      <c r="I37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K37" s="2" t="s">
-        <v>43</v>
+      <c r="K37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>43</v>
@@ -4414,14 +4417,14 @@
       <c r="N37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P37" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q37" s="2" t="s">
-        <v>43</v>
+      <c r="O37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R37" s="2" t="s">
         <v>43</v>
@@ -4432,8 +4435,8 @@
       <c r="T37" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U37" s="2" t="s">
-        <v>43</v>
+      <c r="U37" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V37" s="2" t="s">
         <v>43</v>
@@ -4462,16 +4465,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="3">
+        <v>105</v>
+      </c>
+      <c r="B38" t="s">
         <v>106</v>
       </c>
-      <c r="B38" t="s">
-        <v>107</v>
-      </c>
       <c r="C38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>43</v>
+      <c r="D38" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>43</v>
@@ -4491,11 +4494,11 @@
       <c r="J38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>42</v>
+      <c r="K38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>43</v>
@@ -4506,11 +4509,11 @@
       <c r="O38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P38" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>42</v>
+      <c r="P38" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>43</v>
@@ -4521,8 +4524,8 @@
       <c r="T38" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U38" s="1" t="s">
-        <v>42</v>
+      <c r="U38" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V38" s="2" t="s">
         <v>43</v>
@@ -4551,10 +4554,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="3">
+        <v>107</v>
+      </c>
+      <c r="B39" t="s">
         <v>108</v>
-      </c>
-      <c r="B39" t="s">
-        <v>109</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>42</v>
@@ -4640,10 +4643,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="3">
+        <v>109</v>
+      </c>
+      <c r="B40" t="s">
         <v>110</v>
-      </c>
-      <c r="B40" t="s">
-        <v>111</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>42</v>
@@ -4729,16 +4732,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="3">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
         <v>112</v>
       </c>
-      <c r="B41" t="s">
-        <v>113</v>
-      </c>
       <c r="C41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>42</v>
+      <c r="D41" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>43</v>
@@ -4758,11 +4761,11 @@
       <c r="J41" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L41" s="2" t="s">
-        <v>43</v>
+      <c r="K41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>43</v>
@@ -4773,11 +4776,11 @@
       <c r="O41" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q41" s="2" t="s">
-        <v>43</v>
+      <c r="P41" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R41" s="2" t="s">
         <v>43</v>
@@ -4788,8 +4791,8 @@
       <c r="T41" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U41" s="2" t="s">
-        <v>43</v>
+      <c r="U41" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V41" s="2" t="s">
         <v>43</v>
@@ -4818,31 +4821,31 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="3">
+        <v>113</v>
+      </c>
+      <c r="B42" t="s">
         <v>114</v>
       </c>
-      <c r="B42" t="s">
-        <v>115</v>
-      </c>
       <c r="C42" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>42</v>
+      <c r="E42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>42</v>
+      <c r="I42" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>43</v>
@@ -4853,11 +4856,11 @@
       <c r="L42" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M42" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>42</v>
+      <c r="M42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O42" s="2" t="s">
         <v>43</v>
@@ -4907,31 +4910,31 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="3">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
         <v>116</v>
       </c>
-      <c r="B43" t="s">
-        <v>117</v>
-      </c>
       <c r="C43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>43</v>
+      <c r="D43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>43</v>
+      <c r="I43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>43</v>
@@ -4942,11 +4945,11 @@
       <c r="L43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N43" s="2" t="s">
-        <v>43</v>
+      <c r="M43" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O43" s="2" t="s">
         <v>43</v>
@@ -4978,8 +4981,8 @@
       <c r="X43" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y43" s="1" t="s">
-        <v>42</v>
+      <c r="Y43" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z43" s="2" t="s">
         <v>43</v>
@@ -4996,67 +4999,67 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="3">
+        <v>117</v>
+      </c>
+      <c r="B44" t="s">
         <v>118</v>
       </c>
-      <c r="B44" t="s">
-        <v>119</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>42</v>
+      <c r="D44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>42</v>
+      <c r="I44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>42</v>
+      <c r="K44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>42</v>
+      <c r="M44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>42</v>
+      <c r="R44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V44" s="2" t="s">
         <v>43</v>
@@ -5067,8 +5070,8 @@
       <c r="X44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y44" s="2" t="s">
-        <v>43</v>
+      <c r="Y44" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z44" s="2" t="s">
         <v>43</v>
@@ -5085,37 +5088,37 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="3">
+        <v>119</v>
+      </c>
+      <c r="B45" t="s">
         <v>120</v>
       </c>
-      <c r="B45" t="s">
-        <v>121</v>
-      </c>
       <c r="C45" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>43</v>
+      <c r="E45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I45" s="2" t="s">
-        <v>43</v>
+      <c r="I45" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>43</v>
+      <c r="K45" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>43</v>
@@ -5123,29 +5126,29 @@
       <c r="M45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P45" s="2" t="s">
-        <v>43</v>
+      <c r="N45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q45" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U45" s="2" t="s">
-        <v>43</v>
+      <c r="R45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V45" s="2" t="s">
         <v>43</v>
@@ -5174,31 +5177,31 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="3">
+        <v>121</v>
+      </c>
+      <c r="B46" t="s">
         <v>122</v>
       </c>
-      <c r="B46" t="s">
-        <v>123</v>
-      </c>
       <c r="C46" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E46" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>42</v>
+      <c r="E46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>42</v>
+      <c r="I46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>43</v>
@@ -5212,14 +5215,14 @@
       <c r="M46" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N46" s="1" t="s">
-        <v>42</v>
+      <c r="N46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P46" s="1" t="s">
-        <v>42</v>
+      <c r="P46" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q46" s="2" t="s">
         <v>43</v>
@@ -5263,31 +5266,31 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="3">
+        <v>123</v>
+      </c>
+      <c r="B47" t="s">
         <v>124</v>
       </c>
-      <c r="B47" t="s">
-        <v>125</v>
-      </c>
       <c r="C47" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>43</v>
+      <c r="E47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I47" s="2" t="s">
-        <v>43</v>
+      <c r="I47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>43</v>
@@ -5298,17 +5301,17 @@
       <c r="L47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>43</v>
+      <c r="M47" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P47" s="2" t="s">
-        <v>43</v>
+      <c r="P47" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q47" s="2" t="s">
         <v>43</v>
@@ -5352,11 +5355,11 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="3">
+        <v>125</v>
+      </c>
+      <c r="B48" t="s">
         <v>126</v>
       </c>
-      <c r="B48" t="s">
-        <v>127</v>
-      </c>
       <c r="C48" s="1" t="s">
         <v>42</v>
       </c>
@@ -5375,8 +5378,8 @@
       <c r="H48" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>42</v>
+      <c r="I48" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>43</v>
@@ -5387,11 +5390,11 @@
       <c r="L48" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M48" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N48" s="1" t="s">
-        <v>42</v>
+      <c r="M48" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>43</v>
@@ -5441,25 +5444,25 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="3">
+        <v>127</v>
+      </c>
+      <c r="B49" t="s">
         <v>128</v>
       </c>
-      <c r="B49" t="s">
-        <v>129</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>42</v>
+      <c r="E49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>43</v>
@@ -5530,11 +5533,11 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="3">
+        <v>129</v>
+      </c>
+      <c r="B50" t="s">
         <v>130</v>
       </c>
-      <c r="B50" t="s">
-        <v>131</v>
-      </c>
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -5547,20 +5550,20 @@
       <c r="F50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G50" s="2" t="s">
-        <v>43</v>
+      <c r="G50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I50" s="2" t="s">
-        <v>43</v>
+      <c r="I50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="1" t="s">
-        <v>42</v>
+      <c r="K50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>43</v>
@@ -5568,14 +5571,14 @@
       <c r="M50" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N50" s="2" t="s">
-        <v>43</v>
+      <c r="N50" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P50" s="1" t="s">
-        <v>42</v>
+      <c r="P50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q50" s="2" t="s">
         <v>43</v>
@@ -5589,8 +5592,8 @@
       <c r="T50" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U50" s="1" t="s">
-        <v>42</v>
+      <c r="U50" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V50" s="2" t="s">
         <v>43</v>
@@ -5619,11 +5622,11 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="3">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
         <v>132</v>
       </c>
-      <c r="B51" t="s">
-        <v>133</v>
-      </c>
       <c r="C51" s="1" t="s">
         <v>42</v>
       </c>
@@ -5636,20 +5639,20 @@
       <c r="F51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G51" s="1" t="s">
-        <v>42</v>
+      <c r="G51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>42</v>
+      <c r="I51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>43</v>
+      <c r="K51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>43</v>
@@ -5657,14 +5660,14 @@
       <c r="M51" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N51" s="1" t="s">
-        <v>42</v>
+      <c r="N51" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P51" s="2" t="s">
-        <v>43</v>
+      <c r="P51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q51" s="2" t="s">
         <v>43</v>
@@ -5678,8 +5681,8 @@
       <c r="T51" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U51" s="2" t="s">
-        <v>43</v>
+      <c r="U51" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V51" s="2" t="s">
         <v>43</v>
@@ -5708,7 +5711,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="3">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
         <v>134</v>
@@ -5716,23 +5719,23 @@
       <c r="C52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>43</v>
+      <c r="D52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G52" s="2" t="s">
-        <v>43</v>
+      <c r="G52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I52" s="2" t="s">
-        <v>43</v>
+      <c r="I52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>43</v>
@@ -5743,11 +5746,11 @@
       <c r="L52" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N52" s="2" t="s">
-        <v>43</v>
+      <c r="M52" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O52" s="2" t="s">
         <v>43</v>
@@ -5800,28 +5803,28 @@
         <v>135</v>
       </c>
       <c r="B53" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>42</v>
+        <v>135</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G53" s="1" t="s">
-        <v>42</v>
+      <c r="G53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>42</v>
+      <c r="I53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>43</v>
@@ -5832,11 +5835,11 @@
       <c r="L53" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>42</v>
+      <c r="M53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>43</v>
@@ -5886,25 +5889,25 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="3">
+        <v>136</v>
+      </c>
+      <c r="B54" t="s">
         <v>137</v>
       </c>
-      <c r="B54" t="s">
-        <v>138</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>42</v>
+      <c r="C54" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>43</v>
+      <c r="E54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>43</v>
@@ -5975,10 +5978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="3">
+        <v>138</v>
+      </c>
+      <c r="B55" t="s">
         <v>139</v>
-      </c>
-      <c r="B55" t="s">
-        <v>140</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>42</v>
@@ -6064,11 +6067,11 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="3">
+        <v>140</v>
+      </c>
+      <c r="B56" t="s">
         <v>141</v>
       </c>
-      <c r="B56" t="s">
-        <v>142</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>42</v>
       </c>
@@ -6087,8 +6090,8 @@
       <c r="H56" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I56" s="2" t="s">
-        <v>43</v>
+      <c r="I56" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>43</v>
@@ -6099,11 +6102,11 @@
       <c r="L56" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M56" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N56" s="2" t="s">
-        <v>43</v>
+      <c r="M56" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>43</v>
@@ -6153,22 +6156,22 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="3">
+        <v>142</v>
+      </c>
+      <c r="B57" t="s">
         <v>143</v>
       </c>
-      <c r="B57" t="s">
-        <v>144</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E57" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>42</v>
+      <c r="E57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>43</v>
@@ -6182,14 +6185,14 @@
       <c r="J57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K57" s="1" t="s">
-        <v>42</v>
+      <c r="K57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M57" s="1" t="s">
-        <v>42</v>
+      <c r="M57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>43</v>
@@ -6197,8 +6200,8 @@
       <c r="O57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P57" s="1" t="s">
-        <v>42</v>
+      <c r="P57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q57" s="2" t="s">
         <v>43</v>
@@ -6212,8 +6215,8 @@
       <c r="T57" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U57" s="1" t="s">
-        <v>42</v>
+      <c r="U57" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V57" s="2" t="s">
         <v>43</v>
@@ -6242,11 +6245,11 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="3">
+        <v>144</v>
+      </c>
+      <c r="B58" t="s">
         <v>145</v>
       </c>
-      <c r="B58" t="s">
-        <v>146</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>42</v>
       </c>
@@ -6259,14 +6262,14 @@
       <c r="F58" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G58" s="1" t="s">
-        <v>42</v>
+      <c r="G58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>42</v>
+      <c r="I58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>43</v>
@@ -6307,11 +6310,11 @@
       <c r="V58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X58" s="1" t="s">
-        <v>42</v>
+      <c r="W58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y58" s="2" t="s">
         <v>43</v>
@@ -6331,11 +6334,11 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="3">
+        <v>146</v>
+      </c>
+      <c r="B59" t="s">
         <v>147</v>
       </c>
-      <c r="B59" t="s">
-        <v>148</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>42</v>
       </c>
@@ -6351,50 +6354,50 @@
       <c r="G59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>42</v>
+      <c r="H59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>42</v>
+      <c r="J59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L59" s="1" t="s">
-        <v>42</v>
+      <c r="L59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>42</v>
+      <c r="N59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>42</v>
+      <c r="Q59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="R59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S59" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="U59" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V59" s="1" t="s">
-        <v>42</v>
+      <c r="V59" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="W59" s="1" t="s">
         <v>42</v>
@@ -6420,11 +6423,11 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="3">
+        <v>148</v>
+      </c>
+      <c r="B60" t="s">
         <v>149</v>
       </c>
-      <c r="B60" t="s">
-        <v>150</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>42</v>
       </c>
@@ -6470,14 +6473,14 @@
       <c r="Q60" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S60" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T60" s="2" t="s">
-        <v>43</v>
+      <c r="R60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U60" s="1" t="s">
         <v>42</v>
@@ -6509,11 +6512,11 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="3">
+        <v>150</v>
+      </c>
+      <c r="B61" t="s">
         <v>151</v>
       </c>
-      <c r="B61" t="s">
-        <v>152</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>42</v>
       </c>
@@ -6529,35 +6532,35 @@
       <c r="G61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="2" t="s">
-        <v>43</v>
+      <c r="H61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J61" s="2" t="s">
-        <v>43</v>
+      <c r="J61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>43</v>
+      <c r="L61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O61" s="2" t="s">
-        <v>43</v>
+      <c r="N61" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q61" s="2" t="s">
-        <v>43</v>
+      <c r="Q61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R61" s="2" t="s">
         <v>43</v>
@@ -6571,8 +6574,8 @@
       <c r="U61" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="V61" s="2" t="s">
-        <v>43</v>
+      <c r="V61" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="W61" s="1" t="s">
         <v>42</v>
@@ -6598,43 +6601,43 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="3">
+        <v>152</v>
+      </c>
+      <c r="B62" t="s">
         <v>153</v>
       </c>
-      <c r="B62" t="s">
-        <v>154</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>43</v>
+      <c r="E62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I62" s="2" t="s">
-        <v>43</v>
+      <c r="I62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K62" s="2" t="s">
-        <v>43</v>
+      <c r="K62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M62" s="2" t="s">
-        <v>43</v>
+      <c r="M62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>43</v>
@@ -6642,8 +6645,8 @@
       <c r="O62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P62" s="2" t="s">
-        <v>43</v>
+      <c r="P62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q62" s="2" t="s">
         <v>43</v>
@@ -6657,17 +6660,17 @@
       <c r="T62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U62" s="2" t="s">
-        <v>43</v>
+      <c r="U62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V62" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X62" s="2" t="s">
-        <v>43</v>
+      <c r="W62" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X62" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y62" s="2" t="s">
         <v>43</v>
@@ -6687,55 +6690,55 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="3">
+        <v>154</v>
+      </c>
+      <c r="B63" t="s">
         <v>155</v>
       </c>
-      <c r="B63" t="s">
-        <v>156</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>42</v>
+      <c r="E63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="R63" s="2" t="s">
         <v>43</v>
@@ -6746,17 +6749,17 @@
       <c r="T63" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W63" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X63" s="1" t="s">
-        <v>42</v>
+      <c r="U63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X63" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y63" s="2" t="s">
         <v>43</v>
@@ -6776,11 +6779,11 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="3">
+        <v>156</v>
+      </c>
+      <c r="B64" t="s">
         <v>157</v>
       </c>
-      <c r="B64" t="s">
-        <v>158</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>42</v>
       </c>
@@ -6796,35 +6799,35 @@
       <c r="G64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H64" s="2" t="s">
-        <v>43</v>
+      <c r="H64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>43</v>
+      <c r="J64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q64" s="2" t="s">
-        <v>43</v>
+      <c r="P64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="R64" s="2" t="s">
         <v>43</v>
@@ -6835,17 +6838,17 @@
       <c r="T64" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X64" s="2" t="s">
-        <v>43</v>
+      <c r="U64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X64" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y64" s="2" t="s">
         <v>43</v>
@@ -6865,31 +6868,31 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="3">
+        <v>158</v>
+      </c>
+      <c r="B65" t="s">
         <v>159</v>
       </c>
-      <c r="B65" t="s">
-        <v>160</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>43</v>
+      <c r="D65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I65" s="2" t="s">
-        <v>43</v>
+      <c r="I65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>43</v>
@@ -6906,8 +6909,8 @@
       <c r="N65" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O65" s="2" t="s">
-        <v>43</v>
+      <c r="O65" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P65" s="2" t="s">
         <v>43</v>
@@ -6954,31 +6957,31 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="3">
+        <v>160</v>
+      </c>
+      <c r="B66" t="s">
         <v>161</v>
       </c>
-      <c r="B66" t="s">
-        <v>162</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>42</v>
+      <c r="D66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>42</v>
+      <c r="I66" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>43</v>
@@ -6995,8 +6998,8 @@
       <c r="N66" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>42</v>
+      <c r="O66" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>43</v>
@@ -7043,10 +7046,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="3">
+        <v>162</v>
+      </c>
+      <c r="B67" t="s">
         <v>163</v>
-      </c>
-      <c r="B67" t="s">
-        <v>164</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>42</v>
@@ -7132,11 +7135,11 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="3">
+        <v>164</v>
+      </c>
+      <c r="B68" t="s">
         <v>165</v>
       </c>
-      <c r="B68" t="s">
-        <v>166</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>42</v>
       </c>
@@ -7152,53 +7155,53 @@
       <c r="G68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H68" s="1" t="s">
-        <v>42</v>
+      <c r="H68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>42</v>
+      <c r="J68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>42</v>
+      <c r="P68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q68" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="V68" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W68" s="1" t="s">
-        <v>42</v>
+      <c r="R68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W68" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X68" s="2" t="s">
         <v>43</v>
@@ -7221,11 +7224,11 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="3">
+        <v>166</v>
+      </c>
+      <c r="B69" t="s">
         <v>167</v>
       </c>
-      <c r="B69" t="s">
-        <v>168</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>42</v>
       </c>
@@ -7241,53 +7244,53 @@
       <c r="G69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H69" s="2" t="s">
-        <v>43</v>
+      <c r="H69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>43</v>
+      <c r="J69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N69" s="2" t="s">
-        <v>43</v>
+      <c r="N69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P69" s="2" t="s">
-        <v>43</v>
+      <c r="P69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q69" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="W69" s="2" t="s">
-        <v>43</v>
+      <c r="R69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="V69" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W69" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X69" s="2" t="s">
         <v>43</v>
@@ -7310,31 +7313,31 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="3">
+        <v>168</v>
+      </c>
+      <c r="B70" t="s">
         <v>169</v>
       </c>
-      <c r="B70" t="s">
-        <v>170</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>43</v>
+      <c r="D70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I70" s="2" t="s">
-        <v>43</v>
+      <c r="I70" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>43</v>
@@ -7345,14 +7348,14 @@
       <c r="L70" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M70" s="2" t="s">
-        <v>43</v>
+      <c r="M70" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O70" s="2" t="s">
-        <v>43</v>
+      <c r="O70" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P70" s="2" t="s">
         <v>43</v>
@@ -7381,8 +7384,8 @@
       <c r="X70" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y70" s="1" t="s">
-        <v>42</v>
+      <c r="Y70" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z70" s="2" t="s">
         <v>43</v>
@@ -7399,22 +7402,22 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="3">
+        <v>170</v>
+      </c>
+      <c r="B71" t="s">
         <v>171</v>
       </c>
-      <c r="B71" t="s">
-        <v>172</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>42</v>
+      <c r="D71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>43</v>
@@ -7428,14 +7431,14 @@
       <c r="J71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>42</v>
+      <c r="K71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M71" s="1" t="s">
-        <v>42</v>
+      <c r="M71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>43</v>
@@ -7443,8 +7446,8 @@
       <c r="O71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P71" s="1" t="s">
-        <v>42</v>
+      <c r="P71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q71" s="2" t="s">
         <v>43</v>
@@ -7458,20 +7461,20 @@
       <c r="T71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U71" s="1" t="s">
-        <v>42</v>
+      <c r="U71" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X71" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y71" s="2" t="s">
-        <v>43</v>
+      <c r="W71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y71" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z71" s="2" t="s">
         <v>43</v>
@@ -7488,16 +7491,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="3">
+        <v>172</v>
+      </c>
+      <c r="B72" t="s">
         <v>173</v>
       </c>
-      <c r="B72" t="s">
-        <v>174</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>43</v>
+      <c r="D72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>42</v>
@@ -7517,8 +7520,8 @@
       <c r="J72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>43</v>
+      <c r="K72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>43</v>
@@ -7532,8 +7535,8 @@
       <c r="O72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P72" s="2" t="s">
-        <v>43</v>
+      <c r="P72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q72" s="2" t="s">
         <v>43</v>
@@ -7547,17 +7550,17 @@
       <c r="T72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U72" s="2" t="s">
-        <v>43</v>
+      <c r="U72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V72" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X72" s="2" t="s">
-        <v>43</v>
+      <c r="W72" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X72" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y72" s="2" t="s">
         <v>43</v>
@@ -7577,19 +7580,19 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="3">
+        <v>174</v>
+      </c>
+      <c r="B73" t="s">
         <v>175</v>
       </c>
-      <c r="B73" t="s">
-        <v>176</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>43</v>
+      <c r="D73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>42</v>
@@ -7612,8 +7615,8 @@
       <c r="L73" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M73" s="2" t="s">
-        <v>43</v>
+      <c r="M73" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>43</v>
@@ -7666,31 +7669,31 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="3">
+        <v>176</v>
+      </c>
+      <c r="B74" t="s">
         <v>177</v>
       </c>
-      <c r="B74" t="s">
-        <v>178</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>42</v>
+      <c r="E74" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>42</v>
+      <c r="G74" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>42</v>
+      <c r="I74" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>43</v>
@@ -7707,8 +7710,8 @@
       <c r="N74" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O74" s="1" t="s">
-        <v>42</v>
+      <c r="O74" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P74" s="2" t="s">
         <v>43</v>
@@ -7755,11 +7758,11 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="3">
+        <v>178</v>
+      </c>
+      <c r="B75" t="s">
         <v>179</v>
       </c>
-      <c r="B75" t="s">
-        <v>180</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>42</v>
       </c>
@@ -7799,8 +7802,8 @@
       <c r="O75" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="P75" s="1" t="s">
-        <v>42</v>
+      <c r="P75" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q75" s="2" t="s">
         <v>43</v>
@@ -7844,31 +7847,31 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="3">
+        <v>180</v>
+      </c>
+      <c r="B76" t="s">
         <v>181</v>
       </c>
-      <c r="B76" t="s">
-        <v>182</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>43</v>
+      <c r="E76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I76" s="2" t="s">
-        <v>43</v>
+      <c r="I76" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>43</v>
@@ -7885,11 +7888,11 @@
       <c r="N76" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P76" s="2" t="s">
-        <v>43</v>
+      <c r="O76" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P76" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q76" s="2" t="s">
         <v>43</v>
@@ -7933,31 +7936,31 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="3">
+        <v>182</v>
+      </c>
+      <c r="B77" t="s">
         <v>183</v>
       </c>
-      <c r="B77" t="s">
-        <v>184</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>42</v>
+      <c r="E77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I77" s="1" t="s">
-        <v>42</v>
+      <c r="I77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>43</v>
@@ -7974,8 +7977,8 @@
       <c r="N77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O77" s="1" t="s">
-        <v>42</v>
+      <c r="O77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P77" s="2" t="s">
         <v>43</v>
@@ -8004,8 +8007,8 @@
       <c r="X77" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y77" s="1" t="s">
-        <v>42</v>
+      <c r="Y77" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Z77" s="2" t="s">
         <v>43</v>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="3">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B78" t="s">
         <v>185</v>
@@ -8057,8 +8060,8 @@
       <c r="L78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M78" s="1" t="s">
-        <v>42</v>
+      <c r="M78" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>43</v>
@@ -8093,8 +8096,8 @@
       <c r="X78" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Y78" s="2" t="s">
-        <v>43</v>
+      <c r="Y78" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Z78" s="2" t="s">
         <v>43</v>
@@ -8146,8 +8149,8 @@
       <c r="L79" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M79" s="2" t="s">
-        <v>43</v>
+      <c r="M79" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>43</v>
@@ -8235,8 +8238,8 @@
       <c r="L80" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>42</v>
+      <c r="M80" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>43</v>
@@ -8297,23 +8300,23 @@
       <c r="C81" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G81" s="2" t="s">
-        <v>43</v>
+      <c r="D81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>43</v>
+      <c r="I81" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>43</v>
@@ -8324,14 +8327,14 @@
       <c r="L81" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M81" s="2" t="s">
-        <v>43</v>
+      <c r="M81" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O81" s="2" t="s">
-        <v>43</v>
+      <c r="O81" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="P81" s="2" t="s">
         <v>43</v>
@@ -8386,8 +8389,8 @@
       <c r="C82" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>42</v>
+      <c r="D82" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>43</v>
@@ -8470,13 +8473,13 @@
         <v>190</v>
       </c>
       <c r="B83" t="s">
-        <v>191</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>43</v>
+        <v>190</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>43</v>
@@ -8484,17 +8487,17 @@
       <c r="F83" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>42</v>
+      <c r="G83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>43</v>
@@ -8556,22 +8559,22 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="3">
+        <v>191</v>
+      </c>
+      <c r="B84" t="s">
         <v>192</v>
       </c>
-      <c r="B84" t="s">
-        <v>193</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>42</v>
+      <c r="C84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>42</v>
@@ -8585,14 +8588,14 @@
       <c r="J84" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K84" s="1" t="s">
-        <v>42</v>
+      <c r="K84" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>42</v>
+      <c r="M84" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>43</v>
@@ -8606,17 +8609,17 @@
       <c r="Q84" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R84" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U84" s="1" t="s">
-        <v>42</v>
+      <c r="R84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V84" s="2" t="s">
         <v>43</v>
@@ -8645,43 +8648,43 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="3">
+        <v>193</v>
+      </c>
+      <c r="B85" t="s">
         <v>194</v>
       </c>
-      <c r="B85" t="s">
-        <v>195</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>43</v>
+      <c r="D85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M85" s="2" t="s">
-        <v>43</v>
+      <c r="M85" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>43</v>
@@ -8695,17 +8698,17 @@
       <c r="Q85" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U85" s="2" t="s">
-        <v>43</v>
+      <c r="R85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T85" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U85" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V85" s="2" t="s">
         <v>43</v>
@@ -8734,10 +8737,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="3">
+        <v>195</v>
+      </c>
+      <c r="B86" t="s">
         <v>196</v>
-      </c>
-      <c r="B86" t="s">
-        <v>197</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>42</v>
@@ -8823,10 +8826,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="3">
+        <v>197</v>
+      </c>
+      <c r="B87" t="s">
         <v>198</v>
-      </c>
-      <c r="B87" t="s">
-        <v>199</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>42</v>
@@ -8912,22 +8915,22 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="3">
+        <v>199</v>
+      </c>
+      <c r="B88" t="s">
         <v>200</v>
       </c>
-      <c r="B88" t="s">
-        <v>201</v>
-      </c>
       <c r="C88" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>42</v>
+      <c r="D88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>43</v>
@@ -8962,26 +8965,26 @@
       <c r="Q88" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U88" s="1" t="s">
-        <v>42</v>
+      <c r="R88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U88" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V88" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W88" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X88" s="1" t="s">
-        <v>42</v>
+      <c r="W88" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y88" s="2" t="s">
         <v>43</v>
@@ -9001,22 +9004,22 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="3">
+        <v>201</v>
+      </c>
+      <c r="B89" t="s">
         <v>202</v>
       </c>
-      <c r="B89" t="s">
-        <v>203</v>
-      </c>
       <c r="C89" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>43</v>
+      <c r="E89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>43</v>
@@ -9051,26 +9054,26 @@
       <c r="Q89" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="U89" s="2" t="s">
-        <v>43</v>
+      <c r="R89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="U89" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V89" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X89" s="2" t="s">
-        <v>43</v>
+      <c r="W89" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X89" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y89" s="2" t="s">
         <v>43</v>
@@ -9090,22 +9093,22 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="3">
+        <v>203</v>
+      </c>
+      <c r="B90" t="s">
         <v>204</v>
       </c>
-      <c r="B90" t="s">
-        <v>205</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>42</v>
+      <c r="C90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>43</v>
@@ -9179,22 +9182,22 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="3">
+        <v>205</v>
+      </c>
+      <c r="B91" t="s">
         <v>206</v>
       </c>
-      <c r="B91" t="s">
-        <v>207</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>43</v>
+      <c r="C91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>43</v>
@@ -9268,22 +9271,22 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="3">
+        <v>207</v>
+      </c>
+      <c r="B92" t="s">
         <v>208</v>
       </c>
-      <c r="B92" t="s">
-        <v>209</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>42</v>
+      <c r="E92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>43</v>
@@ -9291,20 +9294,20 @@
       <c r="H92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I92" s="1" t="s">
-        <v>42</v>
+      <c r="I92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>42</v>
+      <c r="K92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M92" s="1" t="s">
-        <v>42</v>
+      <c r="M92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>43</v>
@@ -9312,32 +9315,32 @@
       <c r="O92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P92" s="1" t="s">
-        <v>42</v>
+      <c r="P92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U92" s="1" t="s">
-        <v>42</v>
+      <c r="R92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V92" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W92" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X92" s="1" t="s">
-        <v>42</v>
+      <c r="W92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X92" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y92" s="2" t="s">
         <v>43</v>
@@ -9357,11 +9360,11 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="3">
+        <v>209</v>
+      </c>
+      <c r="B93" t="s">
         <v>210</v>
       </c>
-      <c r="B93" t="s">
-        <v>211</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>42</v>
       </c>
@@ -9407,14 +9410,14 @@
       <c r="Q93" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T93" s="2" t="s">
-        <v>43</v>
+      <c r="R93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S93" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U93" s="1" t="s">
         <v>42</v>
@@ -9446,22 +9449,22 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="3">
+        <v>211</v>
+      </c>
+      <c r="B94" t="s">
         <v>212</v>
       </c>
-      <c r="B94" t="s">
-        <v>213</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>43</v>
+      <c r="E94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>43</v>
@@ -9469,20 +9472,20 @@
       <c r="H94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I94" s="2" t="s">
-        <v>43</v>
+      <c r="I94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K94" s="2" t="s">
-        <v>43</v>
+      <c r="K94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="L94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M94" s="2" t="s">
-        <v>43</v>
+      <c r="M94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N94" s="2" t="s">
         <v>43</v>
@@ -9490,8 +9493,8 @@
       <c r="O94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P94" s="2" t="s">
-        <v>43</v>
+      <c r="P94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q94" s="2" t="s">
         <v>43</v>
@@ -9505,17 +9508,17 @@
       <c r="T94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U94" s="2" t="s">
-        <v>43</v>
+      <c r="U94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V94" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X94" s="2" t="s">
-        <v>43</v>
+      <c r="W94" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X94" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y94" s="2" t="s">
         <v>43</v>
@@ -9535,16 +9538,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="3">
+        <v>213</v>
+      </c>
+      <c r="B95" t="s">
         <v>214</v>
       </c>
-      <c r="B95" t="s">
-        <v>215</v>
-      </c>
       <c r="C95" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>43</v>
+      <c r="D95" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>43</v>
@@ -9624,7 +9627,7 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="3">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B96" t="s">
         <v>216</v>
@@ -9635,8 +9638,8 @@
       <c r="D96" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>42</v>
+      <c r="E96" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>43</v>
@@ -9659,8 +9662,8 @@
       <c r="L96" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M96" s="1" t="s">
-        <v>42</v>
+      <c r="M96" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>43</v>
@@ -9716,19 +9719,19 @@
         <v>217</v>
       </c>
       <c r="B97" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>42</v>
+      <c r="D97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>43</v>
@@ -9748,8 +9751,8 @@
       <c r="L97" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="M97" s="2" t="s">
-        <v>43</v>
+      <c r="M97" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>43</v>
@@ -9802,16 +9805,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="3">
+        <v>218</v>
+      </c>
+      <c r="B98" t="s">
         <v>219</v>
       </c>
-      <c r="B98" t="s">
-        <v>220</v>
-      </c>
       <c r="C98" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D98" s="2" t="s">
-        <v>43</v>
+      <c r="D98" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>43</v>
@@ -9891,11 +9894,11 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="3">
+        <v>220</v>
+      </c>
+      <c r="B99" t="s">
         <v>221</v>
       </c>
-      <c r="B99" t="s">
-        <v>222</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>42</v>
       </c>
@@ -9905,8 +9908,8 @@
       <c r="E99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F99" s="2" t="s">
-        <v>43</v>
+      <c r="F99" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>43</v>
@@ -9980,10 +9983,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="3">
+        <v>222</v>
+      </c>
+      <c r="B100" t="s">
         <v>223</v>
-      </c>
-      <c r="B100" t="s">
-        <v>224</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>42</v>
@@ -10069,22 +10072,22 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="3">
+        <v>224</v>
+      </c>
+      <c r="B101" t="s">
         <v>225</v>
       </c>
-      <c r="B101" t="s">
-        <v>226</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>42</v>
+      <c r="D101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>43</v>
@@ -10119,26 +10122,26 @@
       <c r="Q101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U101" s="1" t="s">
-        <v>42</v>
+      <c r="R101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V101" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W101" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X101" s="1" t="s">
-        <v>42</v>
+      <c r="W101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X101" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y101" s="2" t="s">
         <v>43</v>
@@ -10158,11 +10161,11 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="3">
+        <v>226</v>
+      </c>
+      <c r="B102" t="s">
         <v>227</v>
       </c>
-      <c r="B102" t="s">
-        <v>228</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>42</v>
       </c>
@@ -10208,14 +10211,14 @@
       <c r="Q102" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T102" s="2" t="s">
-        <v>43</v>
+      <c r="R102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S102" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T102" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U102" s="1" t="s">
         <v>42</v>
@@ -10247,22 +10250,22 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="3">
+        <v>228</v>
+      </c>
+      <c r="B103" t="s">
         <v>229</v>
       </c>
-      <c r="B103" t="s">
-        <v>230</v>
-      </c>
       <c r="C103" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>43</v>
+      <c r="D103" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>43</v>
@@ -10306,17 +10309,17 @@
       <c r="T103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U103" s="2" t="s">
-        <v>43</v>
+      <c r="U103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V103" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X103" s="2" t="s">
-        <v>43</v>
+      <c r="W103" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X103" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y103" s="2" t="s">
         <v>43</v>
@@ -10336,16 +10339,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="3">
+        <v>230</v>
+      </c>
+      <c r="B104" t="s">
         <v>231</v>
       </c>
-      <c r="B104" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>42</v>
+      <c r="D104" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>43</v>
@@ -10425,16 +10428,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="3">
+        <v>232</v>
+      </c>
+      <c r="B105" t="s">
         <v>233</v>
       </c>
-      <c r="B105" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D105" s="2" t="s">
-        <v>43</v>
+      <c r="D105" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>43</v>
@@ -10514,40 +10517,40 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="3">
+        <v>234</v>
+      </c>
+      <c r="B106" t="s">
         <v>235</v>
       </c>
-      <c r="B106" t="s">
-        <v>236</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G106" s="1" t="s">
-        <v>42</v>
+      <c r="D106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I106" s="1" t="s">
-        <v>42</v>
+      <c r="I106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>42</v>
+      <c r="K106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M106" s="2" t="s">
         <v>43</v>
@@ -10555,35 +10558,35 @@
       <c r="N106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="O106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="P106" s="1" t="s">
-        <v>42</v>
+      <c r="O106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="S106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="T106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="U106" s="1" t="s">
-        <v>42</v>
+      <c r="R106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="U106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V106" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W106" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="X106" s="1" t="s">
-        <v>42</v>
+      <c r="W106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="X106" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Y106" s="2" t="s">
         <v>43</v>
@@ -10603,25 +10606,25 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="3">
+        <v>236</v>
+      </c>
+      <c r="B107" t="s">
         <v>237</v>
       </c>
-      <c r="B107" t="s">
-        <v>238</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>43</v>
+      <c r="E107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>43</v>
@@ -10632,23 +10635,23 @@
       <c r="J107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="K107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="N107" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P107" s="2" t="s">
-        <v>43</v>
+      <c r="K107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="L107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q107" s="2" t="s">
         <v>43</v>
@@ -10662,17 +10665,17 @@
       <c r="T107" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="U107" s="2" t="s">
-        <v>43</v>
+      <c r="U107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="V107" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="X107" s="2" t="s">
-        <v>43</v>
+      <c r="W107" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="X107" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y107" s="2" t="s">
         <v>43</v>
@@ -10692,11 +10695,11 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="3">
+        <v>238</v>
+      </c>
+      <c r="B108" t="s">
         <v>239</v>
       </c>
-      <c r="B108" t="s">
-        <v>240</v>
-      </c>
       <c r="C108" s="1" t="s">
         <v>42</v>
       </c>
@@ -10715,8 +10718,8 @@
       <c r="H108" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I108" s="2" t="s">
-        <v>43</v>
+      <c r="I108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>43</v>
@@ -10730,8 +10733,8 @@
       <c r="M108" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N108" s="2" t="s">
-        <v>43</v>
+      <c r="N108" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="O108" s="2" t="s">
         <v>43</v>
@@ -10781,49 +10784,49 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="3">
+        <v>240</v>
+      </c>
+      <c r="B109" t="s">
         <v>241</v>
       </c>
-      <c r="B109" t="s">
-        <v>242</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F109" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G109" s="1" t="s">
-        <v>42</v>
+      <c r="E109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I109" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J109" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="K109" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="L109" s="1" t="s">
-        <v>42</v>
+      <c r="I109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="N109" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>42</v>
+      <c r="N109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="O109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P109" s="2" t="s">
         <v>43</v>
@@ -10831,14 +10834,14 @@
       <c r="Q109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="S109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T109" s="2" t="s">
-        <v>43</v>
+      <c r="R109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="S109" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="T109" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="U109" s="2" t="s">
         <v>43</v>
@@ -10846,8 +10849,8 @@
       <c r="V109" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W109" s="1" t="s">
-        <v>42</v>
+      <c r="W109" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="X109" s="2" t="s">
         <v>43</v>
@@ -10870,34 +10873,34 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="3">
+        <v>242</v>
+      </c>
+      <c r="B110" t="s">
         <v>243</v>
       </c>
-      <c r="B110" t="s">
-        <v>244</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G110" s="2" t="s">
-        <v>43</v>
+      <c r="D110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="I110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>43</v>
+      <c r="I110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="K110" s="1" t="s">
         <v>42</v>
@@ -10905,17 +10908,17 @@
       <c r="L110" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="M110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P110" s="1" t="s">
-        <v>42</v>
+      <c r="M110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="Q110" s="2" t="s">
         <v>43</v>
@@ -10929,14 +10932,14 @@
       <c r="T110" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="U110" s="1" t="s">
-        <v>42</v>
+      <c r="U110" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="V110" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="W110" s="2" t="s">
-        <v>43</v>
+      <c r="W110" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="X110" s="2" t="s">
         <v>43</v>
@@ -10959,11 +10962,11 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="3">
+        <v>244</v>
+      </c>
+      <c r="B111" t="s">
         <v>245</v>
       </c>
-      <c r="B111" t="s">
-        <v>246</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>42</v>
       </c>
@@ -11003,8 +11006,8 @@
       <c r="O111" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="P111" s="2" t="s">
-        <v>43</v>
+      <c r="P111" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Q111" s="2" t="s">
         <v>43</v>
@@ -11048,10 +11051,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="3">
+        <v>246</v>
+      </c>
+      <c r="B112" t="s">
         <v>247</v>
-      </c>
-      <c r="B112" t="s">
-        <v>248</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>42</v>
@@ -11137,10 +11140,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="3">
+        <v>248</v>
+      </c>
+      <c r="B113" t="s">
         <v>249</v>
-      </c>
-      <c r="B113" t="s">
-        <v>250</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>42</v>
@@ -11226,11 +11229,11 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="3">
+        <v>250</v>
+      </c>
+      <c r="B114" t="s">
         <v>251</v>
       </c>
-      <c r="B114" t="s">
-        <v>252</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>42</v>
       </c>
@@ -11258,8 +11261,8 @@
       <c r="K114" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L114" s="2" t="s">
-        <v>43</v>
+      <c r="L114" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="M114" s="2" t="s">
         <v>43</v>
@@ -11315,11 +11318,11 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="3">
+        <v>252</v>
+      </c>
+      <c r="B115" t="s">
         <v>253</v>
       </c>
-      <c r="B115" t="s">
-        <v>254</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>42</v>
       </c>
